--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14410" windowHeight="3410" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14410" windowHeight="2780" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,12 @@
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:D10"/>
+  <oleSize ref="A1:G7"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="1017">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2962,41 +2962,118 @@
     <t>Nexra</t>
   </si>
   <si>
-    <t>Charlie24</t>
-  </si>
-  <si>
-    <t>Milo19</t>
-  </si>
-  <si>
-    <t>Taffy22</t>
-  </si>
-  <si>
-    <t>Cutie14</t>
-  </si>
-  <si>
-    <t>Cinder14</t>
-  </si>
-  <si>
-    <t>pony10</t>
-  </si>
-  <si>
-    <t>fury7</t>
-  </si>
-  <si>
-    <t>Ryder7</t>
-  </si>
-  <si>
-    <t>Rabbit14</t>
-  </si>
-  <si>
-    <t>Sheep13</t>
+    <t>MHYCCP</t>
+  </si>
+  <si>
+    <t>7MAH7R</t>
+  </si>
+  <si>
+    <t>ERYCCD</t>
+  </si>
+  <si>
+    <t>PE6DFR</t>
+  </si>
+  <si>
+    <t>HFKR7H</t>
+  </si>
+  <si>
+    <t>A4RJF7</t>
+  </si>
+  <si>
+    <t>GN6NE4</t>
+  </si>
+  <si>
+    <t>UNYATN</t>
+  </si>
+  <si>
+    <t>EFPAYP</t>
+  </si>
+  <si>
+    <t>PAUHPA</t>
+  </si>
+  <si>
+    <t>MUHDPU</t>
+  </si>
+  <si>
+    <t>TTHFYC</t>
+  </si>
+  <si>
+    <t>JR9TUK</t>
+  </si>
+  <si>
+    <t>PX6PDT</t>
+  </si>
+  <si>
+    <t>VT4KUK</t>
+  </si>
+  <si>
+    <t>VFJEVK</t>
+  </si>
+  <si>
+    <t>MCPKGM</t>
+  </si>
+  <si>
+    <t>KFV7JR</t>
+  </si>
+  <si>
+    <t>9E4R9F</t>
+  </si>
+  <si>
+    <t>UXXEVD</t>
+  </si>
+  <si>
+    <t>DE3VMP</t>
+  </si>
+  <si>
+    <t>YC7CHC</t>
+  </si>
+  <si>
+    <t>HF6RFG</t>
+  </si>
+  <si>
+    <t>NXMMAC</t>
+  </si>
+  <si>
+    <t>G6VTG7</t>
+  </si>
+  <si>
+    <t>JXEFFJ</t>
+  </si>
+  <si>
+    <t>9N77VR</t>
+  </si>
+  <si>
+    <t>FNGKYX</t>
+  </si>
+  <si>
+    <t>UGFMHH</t>
+  </si>
+  <si>
+    <t>VPDVEP</t>
+  </si>
+  <si>
+    <t>REKDKT</t>
+  </si>
+  <si>
+    <t>RARFM9</t>
+  </si>
+  <si>
+    <t>PFMYRN</t>
+  </si>
+  <si>
+    <t>XJUUXF</t>
+  </si>
+  <si>
+    <t>XRMGCJ</t>
+  </si>
+  <si>
+    <t>ER76DX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3052,7 +3129,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3227,18 +3304,99 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3545,21 +3703,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
-    <col min="12" max="16384" style="1" width="8.7265625"/>
+    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -3921,13 +4079,13 @@
       <c r="A21" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="176" t="s">
+      <c r="B21" s="175" t="s">
         <v>119</v>
       </c>
       <c r="C21" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="179" t="s">
+      <c r="D21" s="178" t="s">
         <v>219</v>
       </c>
       <c r="E21" s="24" t="s">
@@ -3938,13 +4096,13 @@
       <c r="A22" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="186" t="s">
         <v>120</v>
       </c>
       <c r="C22" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="D22" s="180" t="s">
+      <c r="D22" s="179" t="s">
         <v>220</v>
       </c>
       <c r="E22" s="25" t="s">
@@ -3955,13 +4113,13 @@
       <c r="A23" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="197" t="s">
         <v>121</v>
       </c>
       <c r="C23" s="77" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="189" t="s">
         <v>221</v>
       </c>
       <c r="E23" s="26" t="s">
@@ -3972,13 +4130,13 @@
       <c r="A24" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="200" t="s">
         <v>122</v>
       </c>
       <c r="C24" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="190" t="s">
         <v>222</v>
       </c>
       <c r="E24" s="27" t="s">
@@ -3989,13 +4147,13 @@
       <c r="A25" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="203" t="s">
         <v>123</v>
       </c>
       <c r="C25" s="100" t="s">
         <v>173</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="209" t="s">
         <v>223</v>
       </c>
       <c r="E25" s="28" t="s">
@@ -4006,13 +4164,13 @@
       <c r="A26" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="206" t="s">
         <v>124</v>
       </c>
       <c r="C26" s="110" t="s">
         <v>174</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="210" t="s">
         <v>224</v>
       </c>
       <c r="E26" s="29" t="s">
@@ -4023,13 +4181,13 @@
       <c r="A27" s="127" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="218" t="s">
         <v>125</v>
       </c>
       <c r="C27" s="130" t="s">
         <v>175</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="220" t="s">
         <v>225</v>
       </c>
       <c r="E27" s="82" t="s">
@@ -4040,13 +4198,13 @@
       <c r="A28" s="129" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="222" t="s">
         <v>126</v>
       </c>
       <c r="C28" s="136" t="s">
         <v>176</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="225" t="s">
         <v>226</v>
       </c>
       <c r="E28" s="83" t="s">
@@ -4057,13 +4215,13 @@
       <c r="A29" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="231" t="s">
         <v>127</v>
       </c>
       <c r="C29" s="142" t="s">
         <v>177</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="226" t="s">
         <v>227</v>
       </c>
       <c r="E29" s="84" t="s">
@@ -4074,13 +4232,13 @@
       <c r="A30" s="135" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="234" t="s">
         <v>128</v>
       </c>
       <c r="C30" s="152" t="s">
         <v>178</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="237" t="s">
         <v>228</v>
       </c>
       <c r="E30" s="85" t="s">
@@ -4091,13 +4249,13 @@
       <c r="A31" s="139" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="244" t="s">
         <v>129</v>
       </c>
       <c r="C31" s="162" t="s">
         <v>179</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="238" t="s">
         <v>229</v>
       </c>
       <c r="E31" s="86" t="s">
@@ -4108,13 +4266,13 @@
       <c r="A32" s="141" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="255" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="178" t="s">
+      <c r="C32" s="177" t="s">
         <v>180</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="247" t="s">
         <v>230</v>
       </c>
       <c r="E32" s="87" t="s">
@@ -4128,10 +4286,10 @@
       <c r="B33" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="188" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="248" t="s">
         <v>231</v>
       </c>
       <c r="E33" s="88" t="s">
@@ -4145,10 +4303,10 @@
       <c r="B34" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="208" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="258" t="s">
         <v>232</v>
       </c>
       <c r="E34" s="89" t="s">
@@ -4162,10 +4320,10 @@
       <c r="B35" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="224" t="s">
         <v>183</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="259" t="s">
         <v>233</v>
       </c>
       <c r="E35" s="90" t="s">
@@ -4179,7 +4337,7 @@
       <c r="B36" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="236" t="s">
         <v>184</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -4196,7 +4354,7 @@
       <c r="B37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="246" t="s">
         <v>185</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -4207,13 +4365,13 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="175" t="s">
+      <c r="A38" s="174" t="s">
         <v>80</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="257" t="s">
         <v>186</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -4224,7 +4382,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="177" t="s">
+      <c r="A39" s="176" t="s">
         <v>81</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -4241,7 +4399,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="185" t="s">
         <v>82</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -4258,7 +4416,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="187" t="s">
         <v>83</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -4275,7 +4433,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="196" t="s">
         <v>84</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -4292,7 +4450,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="198" t="s">
         <v>85</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -4309,7 +4467,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="199" t="s">
         <v>86</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -4326,7 +4484,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="201" t="s">
         <v>87</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -4343,7 +4501,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="202" t="s">
         <v>88</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -4360,7 +4518,7 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="204" t="s">
         <v>89</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -4377,7 +4535,7 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="205" t="s">
         <v>90</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -4391,7 +4549,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="207" t="s">
         <v>91</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -4405,7 +4563,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="216" t="s">
         <v>92</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -4419,7 +4577,7 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="219" t="s">
         <v>93</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -4433,7 +4591,7 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="221" t="s">
         <v>94</v>
       </c>
       <c r="E52" s="121" t="s">
@@ -4441,7 +4599,7 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="223" t="s">
         <v>95</v>
       </c>
       <c r="E53" s="122" t="s">
@@ -4449,7 +4607,7 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="230" t="s">
         <v>96</v>
       </c>
       <c r="E54" s="123" t="s">
@@ -4457,7 +4615,7 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="232" t="s">
         <v>97</v>
       </c>
       <c r="E55" s="145" t="s">
@@ -4465,7 +4623,7 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="233" t="s">
         <v>98</v>
       </c>
       <c r="E56" s="146" t="s">
@@ -4473,7 +4631,7 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="235" t="s">
         <v>99</v>
       </c>
       <c r="E57" s="155" t="s">
@@ -4481,98 +4639,260 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="243" t="s">
+        <v>1007</v>
+      </c>
       <c r="E58" s="156" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="245" t="s">
+        <v>1008</v>
+      </c>
       <c r="E59" s="157" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="254" t="s">
+        <v>1009</v>
+      </c>
       <c r="E60" s="158" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="256" t="s">
+        <v>1010</v>
+      </c>
       <c r="E61" s="165" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="170" t="s">
+        <v>1011</v>
+      </c>
       <c r="E62" s="166" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="170" t="s">
+        <v>1012</v>
+      </c>
       <c r="E63" s="167" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" s="170" t="s">
+        <v>1013</v>
+      </c>
       <c r="E64" s="168" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E65" s="182" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="170" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E65" s="181" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E66" s="183" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="170" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E66" s="182" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E67" s="184" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="170" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E67" s="183" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E68" s="185" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E68" s="184" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E69" s="1" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E69" s="192" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E70" s="1" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E70" s="193" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E71" s="1" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E71" s="194" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E72" s="1" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E72" s="195" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E73" s="1" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E73" s="212" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E74" s="1" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E74" s="213" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E75" s="1" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E75" s="214" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E76" s="1" t="s">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E76" s="215" t="s">
         <v>295</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E77" s="228" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E78" s="229" t="s">
+        <v>983</v>
+      </c>
+      <c r="F78" s="217"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E79" s="240" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E80" s="241" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="81" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E81" s="242" t="s">
+        <v>985</v>
+      </c>
+      <c r="F81" s="217"/>
+    </row>
+    <row r="82" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E82" s="250" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="83" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E83" s="251" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="84" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E84" s="252" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="85" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E85" s="253" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="86" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E86" s="261" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="87" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E87" s="262" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="88" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E88" s="263" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="89" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E89" s="264" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="90" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E90" s="170" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="91" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E91" s="170" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="92" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E92" s="170" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="93" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E93" s="170" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="94" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E94" s="170" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="95" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E95" s="170" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="96" spans="5:6" x14ac:dyDescent="0.35">
+      <c r="E96" s="170" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="97" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E97" s="170" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="98" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E98" s="170" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="99" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E99" s="170" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="100" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E100" s="170" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="101" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E101" s="170" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E102" s="170" t="s">
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
@@ -4586,90 +4906,87 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.453125"/>
-    <col min="3" max="3" customWidth="true" width="35.6328125"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.7265625"/>
-    <col min="6" max="6" customWidth="true" width="32.1796875"/>
-    <col min="7" max="7" customWidth="true" width="33.6328125"/>
-    <col min="8" max="8" customWidth="true" width="31.26953125"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.7265625" customWidth="1"/>
+    <col min="6" max="6" width="32.1796875" customWidth="1"/>
+    <col min="7" max="7" width="33.6328125" customWidth="1"/>
+    <col min="8" max="8" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>29</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>988</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D7" t="s" s="0">
+      <c r="D7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D8" t="s" s="0">
+      <c r="D8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4690,41 +5007,41 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984375"/>
-    <col min="2" max="2" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" width="17.36328125"/>
-    <col min="4" max="5" customWidth="true" width="17.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.36328125"/>
-    <col min="8" max="8" customWidth="true" width="17.1796875"/>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" customWidth="1"/>
+    <col min="4" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="169" t="s">
         <v>296</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>297</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>298</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>299</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>300</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>301</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>302</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4749,7 +5066,7 @@
       <c r="B3" s="170" t="s">
         <v>625</v>
       </c>
-      <c r="C3" s="181" t="s">
+      <c r="C3" s="180" t="s">
         <v>305</v>
       </c>
       <c r="D3" s="173" t="s">
@@ -4763,7 +5080,7 @@
       <c r="B4" s="170" t="s">
         <v>626</v>
       </c>
-      <c r="C4" s="172" t="s">
+      <c r="C4" s="191" t="s">
         <v>306</v>
       </c>
       <c r="D4" s="173" t="s">
@@ -4777,7 +5094,7 @@
       <c r="B5" s="170" t="s">
         <v>627</v>
       </c>
-      <c r="C5" s="172" t="s">
+      <c r="C5" s="211" t="s">
         <v>307</v>
       </c>
       <c r="D5" s="173" t="s">
@@ -4791,7 +5108,7 @@
       <c r="B6" s="170" t="s">
         <v>628</v>
       </c>
-      <c r="C6" s="172" t="s">
+      <c r="C6" s="227" t="s">
         <v>308</v>
       </c>
       <c r="D6" s="173" t="s">
@@ -4805,7 +5122,7 @@
       <c r="B7" s="170" t="s">
         <v>629</v>
       </c>
-      <c r="C7" s="172" t="s">
+      <c r="C7" s="239" t="s">
         <v>309</v>
       </c>
       <c r="D7" s="173" t="s">
@@ -4819,7 +5136,7 @@
       <c r="B8" s="170" t="s">
         <v>630</v>
       </c>
-      <c r="C8" s="172" t="s">
+      <c r="C8" s="249" t="s">
         <v>310</v>
       </c>
       <c r="D8" s="173" t="s">
@@ -4833,7 +5150,7 @@
       <c r="B9" s="170" t="s">
         <v>631</v>
       </c>
-      <c r="C9" s="172" t="s">
+      <c r="C9" s="260" t="s">
         <v>311</v>
       </c>
       <c r="D9" s="173" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14410" windowHeight="2780" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13970" windowHeight="2690" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,12 @@
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:G7"/>
+  <oleSize ref="A1:D7"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="1033">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3068,12 +3068,61 @@
   </si>
   <si>
     <t>ER76DX</t>
+  </si>
+  <si>
+    <t>YFTAXD</t>
+  </si>
+  <si>
+    <t>ECGUPJ</t>
+  </si>
+  <si>
+    <t>JRTJR7</t>
+  </si>
+  <si>
+    <t>KU4K7D</t>
+  </si>
+  <si>
+    <t>G4RJEA</t>
+  </si>
+  <si>
+    <t>NKEGFM</t>
+  </si>
+  <si>
+    <t>JVXX6F</t>
+  </si>
+  <si>
+    <t>39YTKH</t>
+  </si>
+  <si>
+    <t>DFTJEP</t>
+  </si>
+  <si>
+    <t>Charlie48</t>
+  </si>
+  <si>
+    <t>Milo39</t>
+  </si>
+  <si>
+    <t>Taffy37</t>
+  </si>
+  <si>
+    <t>Cutie26</t>
+  </si>
+  <si>
+    <t>Cinder26</t>
+  </si>
+  <si>
+    <t>pony19</t>
+  </si>
+  <si>
+    <t>fury18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3129,7 +3178,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3397,6 +3446,42 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3703,21 +3788,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
+    <col min="12" max="16384" style="1" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -4283,7 +4368,7 @@
       <c r="A33" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="266" t="s">
         <v>131</v>
       </c>
       <c r="C33" s="188" t="s">
@@ -4300,7 +4385,7 @@
       <c r="A34" s="149" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="275" t="s">
         <v>132</v>
       </c>
       <c r="C34" s="208" t="s">
@@ -4317,7 +4402,7 @@
       <c r="A35" s="151" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="284" t="s">
         <v>133</v>
       </c>
       <c r="C35" s="224" t="s">
@@ -4334,13 +4419,13 @@
       <c r="A36" s="159" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="293" t="s">
         <v>134</v>
       </c>
       <c r="C36" s="236" t="s">
         <v>184</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="269" t="s">
         <v>234</v>
       </c>
       <c r="E36" s="91" t="s">
@@ -4357,7 +4442,7 @@
       <c r="C37" s="246" t="s">
         <v>185</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="270" t="s">
         <v>235</v>
       </c>
       <c r="E37" s="92" t="s">
@@ -4374,7 +4459,7 @@
       <c r="C38" s="257" t="s">
         <v>186</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="278" t="s">
         <v>236</v>
       </c>
       <c r="E38" s="93" t="s">
@@ -4388,10 +4473,10 @@
       <c r="B39" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="268" t="s">
         <v>187</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="279" t="s">
         <v>237</v>
       </c>
       <c r="E39" s="94" t="s">
@@ -4405,10 +4490,10 @@
       <c r="B40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="277" t="s">
         <v>188</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="287" t="s">
         <v>238</v>
       </c>
       <c r="E40" s="103" t="s">
@@ -4422,10 +4507,10 @@
       <c r="B41" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="286" t="s">
         <v>189</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="288" t="s">
         <v>239</v>
       </c>
       <c r="E41" s="104" t="s">
@@ -4439,10 +4524,10 @@
       <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="295" t="s">
         <v>190</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="296" t="s">
         <v>240</v>
       </c>
       <c r="E42" s="105" t="s">
@@ -4459,7 +4544,7 @@
       <c r="C43" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="297" t="s">
         <v>241</v>
       </c>
       <c r="E43" s="106" t="s">
@@ -4671,7 +4756,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="170" t="s">
+      <c r="A62" s="265" t="s">
         <v>1011</v>
       </c>
       <c r="E62" s="166" t="s">
@@ -4679,7 +4764,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="170" t="s">
+      <c r="A63" s="267" t="s">
         <v>1012</v>
       </c>
       <c r="E63" s="167" t="s">
@@ -4687,7 +4772,7 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="170" t="s">
+      <c r="A64" s="274" t="s">
         <v>1013</v>
       </c>
       <c r="E64" s="168" t="s">
@@ -4695,7 +4780,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="170" t="s">
+      <c r="A65" s="276" t="s">
         <v>1014</v>
       </c>
       <c r="E65" s="181" t="s">
@@ -4703,7 +4788,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="170" t="s">
+      <c r="A66" s="283" t="s">
         <v>1015</v>
       </c>
       <c r="E66" s="182" t="s">
@@ -4711,7 +4796,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="170" t="s">
+      <c r="A67" s="285" t="s">
         <v>1016</v>
       </c>
       <c r="E67" s="183" t="s">
@@ -4719,46 +4804,73 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="292" t="s">
+        <v>1017</v>
+      </c>
       <c r="E68" s="184" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="294" t="s">
+        <v>1018</v>
+      </c>
       <c r="E69" s="192" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
+        <v>1019</v>
+      </c>
       <c r="E70" s="193" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
+        <v>1020</v>
+      </c>
       <c r="E71" s="194" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
+        <v>1021</v>
+      </c>
       <c r="E72" s="195" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
+        <v>1022</v>
+      </c>
       <c r="E73" s="212" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>1023</v>
+      </c>
       <c r="E74" s="213" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>1024</v>
+      </c>
       <c r="E75" s="214" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
+        <v>1025</v>
+      </c>
       <c r="E76" s="215" t="s">
         <v>295</v>
       </c>
@@ -4831,42 +4943,42 @@
       </c>
     </row>
     <row r="90" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E90" s="170" t="s">
+      <c r="E90" s="272" t="s">
         <v>994</v>
       </c>
     </row>
     <row r="91" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E91" s="170" t="s">
+      <c r="E91" s="273" t="s">
         <v>995</v>
       </c>
     </row>
     <row r="92" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E92" s="170" t="s">
+      <c r="E92" s="281" t="s">
         <v>996</v>
       </c>
     </row>
     <row r="93" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E93" s="170" t="s">
+      <c r="E93" s="282" t="s">
         <v>997</v>
       </c>
     </row>
     <row r="94" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E94" s="170" t="s">
+      <c r="E94" s="290" t="s">
         <v>998</v>
       </c>
     </row>
     <row r="95" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E95" s="170" t="s">
+      <c r="E95" s="291" t="s">
         <v>999</v>
       </c>
     </row>
     <row r="96" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E96" s="170" t="s">
+      <c r="E96" s="299" t="s">
         <v>1000</v>
       </c>
     </row>
     <row r="97" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E97" s="170" t="s">
+      <c r="E97" s="300" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -4906,90 +5018,87 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" customWidth="1"/>
-    <col min="8" max="8" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.453125"/>
+    <col min="3" max="3" customWidth="true" width="35.6328125"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.7265625"/>
+    <col min="6" max="6" customWidth="true" width="32.1796875"/>
+    <col min="7" max="7" customWidth="true" width="33.6328125"/>
+    <col min="8" max="8" customWidth="true" width="31.26953125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B4" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D5" t="s" s="0">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D7" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D6" t="s" s="0">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35"/>
@@ -5002,46 +5111,47 @@
     <row r="18" spans="1:4" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984375"/>
+    <col min="2" max="2" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.36328125"/>
+    <col min="4" max="5" customWidth="true" width="17.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.36328125"/>
+    <col min="8" max="8" customWidth="true" width="17.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="169" t="s">
         <v>296</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>297</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>298</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>299</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>301</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>302</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>303</v>
       </c>
     </row>
@@ -5164,7 +5274,7 @@
       <c r="B10" s="170" t="s">
         <v>632</v>
       </c>
-      <c r="C10" s="172" t="s">
+      <c r="C10" s="271" t="s">
         <v>312</v>
       </c>
       <c r="D10" s="173" t="s">
@@ -5178,7 +5288,7 @@
       <c r="B11" s="170" t="s">
         <v>633</v>
       </c>
-      <c r="C11" s="172" t="s">
+      <c r="C11" s="280" t="s">
         <v>313</v>
       </c>
       <c r="D11" s="173" t="s">
@@ -5192,7 +5302,7 @@
       <c r="B12" s="170" t="s">
         <v>634</v>
       </c>
-      <c r="C12" s="172" t="s">
+      <c r="C12" s="289" t="s">
         <v>314</v>
       </c>
       <c r="D12" s="173" t="s">
@@ -5206,7 +5316,7 @@
       <c r="B13" s="170" t="s">
         <v>635</v>
       </c>
-      <c r="C13" s="172" t="s">
+      <c r="C13" s="298" t="s">
         <v>315</v>
       </c>
       <c r="D13" s="173" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13970" windowHeight="2690" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14020" windowHeight="6080"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,12 @@
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:D7"/>
+  <oleSize ref="A34:G51"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="1045">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3097,32 +3097,67 @@
     <t>DFTJEP</t>
   </si>
   <si>
-    <t>Charlie48</t>
-  </si>
-  <si>
-    <t>Milo39</t>
-  </si>
-  <si>
-    <t>Taffy37</t>
-  </si>
-  <si>
-    <t>Cutie26</t>
-  </si>
-  <si>
-    <t>Cinder26</t>
-  </si>
-  <si>
-    <t>pony19</t>
-  </si>
-  <si>
-    <t>fury18</t>
+    <t>XMNYRP</t>
+  </si>
+  <si>
+    <t>DGRAVD</t>
+  </si>
+  <si>
+    <t>MGPXCA</t>
+  </si>
+  <si>
+    <t>GCHR9P</t>
+  </si>
+  <si>
+    <t>HANTAF</t>
+  </si>
+  <si>
+    <t>UCXJPU</t>
+  </si>
+  <si>
+    <t>3HTVRG</t>
+  </si>
+  <si>
+    <t>EAUVNA</t>
+  </si>
+  <si>
+    <t>XACPDY</t>
+  </si>
+  <si>
+    <t>EXRTGT</t>
+  </si>
+  <si>
+    <t>F9JDEF</t>
+  </si>
+  <si>
+    <t>CADMX6</t>
+  </si>
+  <si>
+    <t>H4NC3U</t>
+  </si>
+  <si>
+    <t>NHM4VX</t>
+  </si>
+  <si>
+    <t>JYCTNK</t>
+  </si>
+  <si>
+    <t>AXKHEA</t>
+  </si>
+  <si>
+    <t>7UYNC7</t>
+  </si>
+  <si>
+    <t>TUCEPN</t>
+  </si>
+  <si>
+    <t>NDCUX3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3178,7 +3213,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="301">
+  <cellXfs count="312">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3473,15 +3508,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3788,21 +3834,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
-    <col min="12" max="16384" style="1" width="8.7265625"/>
+    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -4436,7 +4482,7 @@
       <c r="A37" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="302" t="s">
         <v>135</v>
       </c>
       <c r="C37" s="246" t="s">
@@ -4541,7 +4587,7 @@
       <c r="B43" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="304" t="s">
         <v>191</v>
       </c>
       <c r="D43" s="297" t="s">
@@ -4561,7 +4607,7 @@
       <c r="C44" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="305" t="s">
         <v>242</v>
       </c>
       <c r="E44" s="113" t="s">
@@ -4578,7 +4624,7 @@
       <c r="C45" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="306" t="s">
         <v>243</v>
       </c>
       <c r="E45" s="114" t="s">
@@ -4629,6 +4675,9 @@
       <c r="C48" s="1" t="s">
         <v>196</v>
       </c>
+      <c r="D48" s="170" t="s">
+        <v>1039</v>
+      </c>
       <c r="E48" s="117" t="s">
         <v>267</v>
       </c>
@@ -4643,6 +4692,9 @@
       <c r="C49" s="1" t="s">
         <v>197</v>
       </c>
+      <c r="D49" s="170" t="s">
+        <v>1040</v>
+      </c>
       <c r="E49" s="118" t="s">
         <v>268</v>
       </c>
@@ -4657,6 +4709,9 @@
       <c r="C50" s="1" t="s">
         <v>198</v>
       </c>
+      <c r="D50" s="170" t="s">
+        <v>1041</v>
+      </c>
       <c r="E50" s="119" t="s">
         <v>269</v>
       </c>
@@ -4671,6 +4726,9 @@
       <c r="C51" s="1" t="s">
         <v>199</v>
       </c>
+      <c r="D51" s="170" t="s">
+        <v>1042</v>
+      </c>
       <c r="E51" s="120" t="s">
         <v>270</v>
       </c>
@@ -4679,6 +4737,9 @@
       <c r="A52" s="221" t="s">
         <v>94</v>
       </c>
+      <c r="D52" s="170" t="s">
+        <v>1043</v>
+      </c>
       <c r="E52" s="121" t="s">
         <v>271</v>
       </c>
@@ -4687,6 +4748,9 @@
       <c r="A53" s="223" t="s">
         <v>95</v>
       </c>
+      <c r="D53" s="170" t="s">
+        <v>1044</v>
+      </c>
       <c r="E53" s="122" t="s">
         <v>272</v>
       </c>
@@ -4820,7 +4884,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="301" t="s">
         <v>1019</v>
       </c>
       <c r="E70" s="193" t="s">
@@ -4828,7 +4892,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="303" t="s">
         <v>1020</v>
       </c>
       <c r="E71" s="194" t="s">
@@ -4876,103 +4940,121 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="170" t="s">
+        <v>1026</v>
+      </c>
       <c r="E77" s="228" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="170" t="s">
+        <v>1027</v>
+      </c>
       <c r="E78" s="229" t="s">
         <v>983</v>
       </c>
       <c r="F78" s="217"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="170" t="s">
+        <v>1028</v>
+      </c>
       <c r="E79" s="240" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="170" t="s">
+        <v>1029</v>
+      </c>
       <c r="E80" s="241" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="81" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="170" t="s">
+        <v>1030</v>
+      </c>
       <c r="E81" s="242" t="s">
         <v>985</v>
       </c>
       <c r="F81" s="217"/>
     </row>
-    <row r="82" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="170" t="s">
+        <v>1031</v>
+      </c>
       <c r="E82" s="250" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="83" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E83" s="251" t="s">
         <v>987</v>
       </c>
     </row>
-    <row r="84" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E84" s="252" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="85" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E85" s="253" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="86" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E86" s="261" t="s">
         <v>990</v>
       </c>
     </row>
-    <row r="87" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E87" s="262" t="s">
         <v>991</v>
       </c>
     </row>
-    <row r="88" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E88" s="263" t="s">
         <v>992</v>
       </c>
     </row>
-    <row r="89" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E89" s="264" t="s">
         <v>993</v>
       </c>
     </row>
-    <row r="90" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E90" s="272" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="91" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E91" s="273" t="s">
         <v>995</v>
       </c>
     </row>
-    <row r="92" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E92" s="281" t="s">
         <v>996</v>
       </c>
     </row>
-    <row r="93" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E93" s="282" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="94" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E94" s="290" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="95" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E95" s="291" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="96" spans="5:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E96" s="299" t="s">
         <v>1000</v>
       </c>
@@ -4983,28 +5065,63 @@
       </c>
     </row>
     <row r="98" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E98" s="170" t="s">
+      <c r="E98" s="308" t="s">
         <v>1002</v>
       </c>
     </row>
     <row r="99" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E99" s="170" t="s">
+      <c r="E99" s="309" t="s">
         <v>1003</v>
       </c>
     </row>
     <row r="100" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E100" s="170" t="s">
+      <c r="E100" s="310" t="s">
         <v>1004</v>
       </c>
     </row>
     <row r="101" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E101" s="170" t="s">
+      <c r="E101" s="311" t="s">
         <v>1005</v>
       </c>
     </row>
     <row r="102" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E102" s="170" t="s">
         <v>1006</v>
+      </c>
+    </row>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E103" s="170" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E104" s="170" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="105" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E105" s="170" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="106" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E106" s="170" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="107" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E107" s="170" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="108" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E108" s="170" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="109" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E109" s="170" t="s">
+        <v>1038</v>
       </c>
     </row>
   </sheetData>
@@ -5018,82 +5135,85 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.453125"/>
-    <col min="3" max="3" customWidth="true" width="35.6328125"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.7265625"/>
-    <col min="6" max="6" customWidth="true" width="32.1796875"/>
-    <col min="7" max="7" customWidth="true" width="33.6328125"/>
-    <col min="8" max="8" customWidth="true" width="31.26953125"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.7265625" customWidth="1"/>
+    <col min="6" max="6" width="32.1796875" customWidth="1"/>
+    <col min="7" max="7" width="33.6328125" customWidth="1"/>
+    <col min="8" max="8" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>29</v>
       </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D6" t="s" s="0">
+      <c r="D6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5117,41 +5237,41 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984375"/>
-    <col min="2" max="2" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" width="17.36328125"/>
-    <col min="4" max="5" customWidth="true" width="17.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.36328125"/>
-    <col min="8" max="8" customWidth="true" width="17.1796875"/>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" customWidth="1"/>
+    <col min="4" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="169" t="s">
         <v>296</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>297</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>298</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>299</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>300</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>301</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>302</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>303</v>
       </c>
     </row>
@@ -5330,7 +5450,7 @@
       <c r="B14" s="170" t="s">
         <v>636</v>
       </c>
-      <c r="C14" s="172" t="s">
+      <c r="C14" s="307" t="s">
         <v>316</v>
       </c>
       <c r="D14" s="173" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14020" windowHeight="6080"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14020" windowHeight="4810"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="1045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="1047">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3152,6 +3152,12 @@
   </si>
   <si>
     <t>NDCUX3</t>
+  </si>
+  <si>
+    <t>Charlie54</t>
+  </si>
+  <si>
+    <t>Charlie55</t>
   </si>
 </sst>
 </file>
@@ -3181,7 +3187,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3196,6 +3202,12 @@
     <fill>
       <patternFill patternType="none">
         <fgColor indexed="13"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3213,7 +3225,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="312">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3528,6 +3540,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4900,7 +4913,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="312" t="s">
         <v>1021</v>
       </c>
       <c r="E72" s="195" t="s">
@@ -4908,7 +4921,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="312" t="s">
         <v>1022</v>
       </c>
       <c r="E73" s="212" t="s">
@@ -4916,7 +4929,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="312" t="s">
         <v>1023</v>
       </c>
       <c r="E74" s="213" t="s">
@@ -5173,7 +5186,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>1045</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
@@ -5187,7 +5200,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>1046</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="1047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="1053">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3158,12 +3158,31 @@
   </si>
   <si>
     <t>Charlie55</t>
+  </si>
+  <si>
+    <t>Charlie61</t>
+  </si>
+  <si>
+    <t>Milo44</t>
+  </si>
+  <si>
+    <t>Taffy42</t>
+  </si>
+  <si>
+    <t>Cutie30</t>
+  </si>
+  <si>
+    <t>Cinder30</t>
+  </si>
+  <si>
+    <t>pony23</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3225,7 +3244,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="313">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3541,6 +3560,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3847,21 +3870,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
+    <col min="12" max="16384" style="1" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -4617,7 +4640,7 @@
       <c r="B44" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="315" t="s">
         <v>192</v>
       </c>
       <c r="D44" s="305" t="s">
@@ -4654,7 +4677,7 @@
       <c r="C46" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="316" t="s">
         <v>244</v>
       </c>
       <c r="E46" s="115" t="s">
@@ -4913,7 +4936,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="312" t="s">
+      <c r="A72" s="313" t="s">
         <v>1021</v>
       </c>
       <c r="E72" s="195" t="s">
@@ -4921,7 +4944,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="312" t="s">
+      <c r="A73" s="314" t="s">
         <v>1022</v>
       </c>
       <c r="E73" s="212" t="s">
@@ -5148,85 +5171,91 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" customWidth="1"/>
-    <col min="8" max="8" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.453125"/>
+    <col min="3" max="3" customWidth="true" width="35.6328125"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.7265625"/>
+    <col min="6" max="6" customWidth="true" width="32.1796875"/>
+    <col min="7" max="7" customWidth="true" width="33.6328125"/>
+    <col min="8" max="8" customWidth="true" width="31.26953125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s" s="0">
         <v>29</v>
       </c>
+      <c r="D2" t="s" s="0">
+        <v>29</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s" s="0">
         <v>29</v>
       </c>
+      <c r="D3" t="s" s="0">
+        <v>29</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>1047</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s" s="0">
+        <v>1048</v>
+      </c>
+      <c r="D5" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D6" t="s">
+      <c r="A6" t="s" s="0">
+        <v>1049</v>
+      </c>
+      <c r="D6" t="s" s="0">
         <v>29</v>
       </c>
     </row>
@@ -5250,41 +5279,41 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984375"/>
+    <col min="2" max="2" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.36328125"/>
+    <col min="4" max="5" customWidth="true" width="17.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.36328125"/>
+    <col min="8" max="8" customWidth="true" width="17.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="169" t="s">
         <v>296</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>297</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>298</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>299</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>301</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>302</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>303</v>
       </c>
     </row>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="1059">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3176,6 +3176,24 @@
   </si>
   <si>
     <t>pony23</t>
+  </si>
+  <si>
+    <t>Charlie62</t>
+  </si>
+  <si>
+    <t>Milo45</t>
+  </si>
+  <si>
+    <t>Taffy43</t>
+  </si>
+  <si>
+    <t>Cutie31</t>
+  </si>
+  <si>
+    <t>Cinder31</t>
+  </si>
+  <si>
+    <t>pony24</t>
   </si>
 </sst>
 </file>
@@ -3244,7 +3262,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="317">
+  <cellXfs count="321">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3560,6 +3578,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -4657,7 +4679,7 @@
       <c r="B45" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="319" t="s">
         <v>193</v>
       </c>
       <c r="D45" s="306" t="s">
@@ -4694,7 +4716,7 @@
       <c r="C47" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="320" t="s">
         <v>245</v>
       </c>
       <c r="E47" s="116" t="s">
@@ -4952,7 +4974,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="312" t="s">
+      <c r="A74" s="317" t="s">
         <v>1023</v>
       </c>
       <c r="E74" s="213" t="s">
@@ -4960,7 +4982,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="318" t="s">
         <v>1024</v>
       </c>
       <c r="E75" s="214" t="s">
@@ -5247,6 +5269,9 @@
       <c r="A5" t="s" s="0">
         <v>1048</v>
       </c>
+      <c r="B5" t="s" s="0">
+        <v>1058</v>
+      </c>
       <c r="D5" t="s" s="0">
         <v>29</v>
       </c>
@@ -5259,7 +5284,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s" s="0">
+        <v>1055</v>
+      </c>
+    </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35"/>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="1063">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3194,6 +3194,18 @@
   </si>
   <si>
     <t>pony24</t>
+  </si>
+  <si>
+    <t>Charlie63</t>
+  </si>
+  <si>
+    <t>Cutie32</t>
+  </si>
+  <si>
+    <t>Cinder32</t>
+  </si>
+  <si>
+    <t>pony25</t>
   </si>
 </sst>
 </file>
@@ -3262,7 +3274,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="321">
+  <cellXfs count="323">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3578,6 +3590,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -4696,7 +4710,7 @@
       <c r="B46" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="321" t="s">
         <v>194</v>
       </c>
       <c r="D46" s="316" t="s">
@@ -4733,7 +4747,7 @@
       <c r="C48" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D48" s="170" t="s">
+      <c r="D48" s="322" t="s">
         <v>1039</v>
       </c>
       <c r="E48" s="117" t="s">
@@ -5231,7 +5245,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>29</v>
+        <v>1059</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>29</v>
@@ -5279,6 +5293,9 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s" s="0">
         <v>1049</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>1062</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>29</v>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="1064">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3206,6 +3206,9 @@
   </si>
   <si>
     <t>pony25</t>
+  </si>
+  <si>
+    <t>Charlie64</t>
   </si>
 </sst>
 </file>
@@ -5259,7 +5262,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>29</v>
+        <v>1063</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>29</v>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1068">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3209,6 +3209,18 @@
   </si>
   <si>
     <t>Charlie64</t>
+  </si>
+  <si>
+    <t>Charlie65</t>
+  </si>
+  <si>
+    <t>Cutie33</t>
+  </si>
+  <si>
+    <t>Cinder33</t>
+  </si>
+  <si>
+    <t>pony26</t>
   </si>
 </sst>
 </file>
@@ -3277,7 +3289,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="323">
+  <cellXfs count="325">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3593,6 +3605,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -4730,7 +4744,7 @@
       <c r="B47" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="323" t="s">
         <v>195</v>
       </c>
       <c r="D47" s="320" t="s">
@@ -4767,7 +4781,7 @@
       <c r="C49" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D49" s="170" t="s">
+      <c r="D49" s="324" t="s">
         <v>1040</v>
       </c>
       <c r="E49" s="118" t="s">
@@ -5308,8 +5322,15 @@
       <c r="A7" t="s" s="0">
         <v>1055</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35"/>
+      <c r="B7" t="s" s="0">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s" s="0">
+        <v>1064</v>
+      </c>
+    </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35"/>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="1069">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3221,6 +3221,9 @@
   </si>
   <si>
     <t>pony26</t>
+  </si>
+  <si>
+    <t>Charlie66</t>
   </si>
 </sst>
 </file>
@@ -5331,7 +5334,11 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s" s="0">
+        <v>1068</v>
+      </c>
+    </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35"/>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="1073">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3224,6 +3224,18 @@
   </si>
   <si>
     <t>Charlie66</t>
+  </si>
+  <si>
+    <t>Charlie68</t>
+  </si>
+  <si>
+    <t>Cutie35</t>
+  </si>
+  <si>
+    <t>Cinder35</t>
+  </si>
+  <si>
+    <t>pony28</t>
   </si>
 </sst>
 </file>
@@ -3292,7 +3304,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="325">
+  <cellXfs count="327">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3608,6 +3620,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -4764,7 +4778,7 @@
       <c r="B48" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="325" t="s">
         <v>196</v>
       </c>
       <c r="D48" s="322" t="s">
@@ -4801,7 +4815,7 @@
       <c r="C50" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="170" t="s">
+      <c r="D50" s="326" t="s">
         <v>1041</v>
       </c>
       <c r="E50" s="119" t="s">
@@ -5333,13 +5347,20 @@
       <c r="A8" t="s" s="0">
         <v>1064</v>
       </c>
+      <c r="B8" t="s" s="0">
+        <v>1072</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s" s="0">
         <v>1068</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s" s="0">
+        <v>1069</v>
+      </c>
+    </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35"/>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3246,12 +3246,31 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Charlie70</t>
+  </si>
+  <si>
+    <t>Milo48</t>
+  </si>
+  <si>
+    <t>Taffy46</t>
+  </si>
+  <si>
+    <t>Cutie37</t>
+  </si>
+  <si>
+    <t>Cinder37</t>
+  </si>
+  <si>
+    <t>pony30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -3326,7 +3345,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3340,6 +3359,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3640,20 +3664,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.726563" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
+    <col min="12" max="16384" style="1" width="8.726563"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4494,7 +4519,7 @@
       <c r="B49" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="13" t="s">
         <v>247</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -4531,7 +4556,7 @@
       <c r="C51" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="14" t="s">
         <v>258</v>
       </c>
       <c r="E51" s="2" t="s">
@@ -4548,7 +4573,7 @@
       <c r="C52" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" t="s" s="15">
         <v>263</v>
       </c>
       <c r="E52" s="2" t="s">
@@ -4565,7 +4590,7 @@
       <c r="C53" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" t="s" s="1">
         <v>268</v>
       </c>
       <c r="E53" s="2" t="s">
@@ -4782,7 +4807,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="11" t="s">
         <v>325</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -4790,7 +4815,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="12" t="s">
         <v>327</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -4823,7 +4848,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="1">
         <v>335</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -4832,7 +4857,7 @@
       <c r="F81" s="6"/>
     </row>
     <row r="82">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="1">
         <v>337</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -4971,43 +4996,43 @@
     </row>
     <row r="103">
       <c r="A103" s="1"/>
-      <c r="E103" t="s">
+      <c r="E103" t="s" s="1">
         <v>364</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1"/>
-      <c r="E104" t="s">
+      <c r="E104" t="s" s="1">
         <v>365</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1"/>
-      <c r="E105" t="s">
+      <c r="E105" t="s" s="1">
         <v>366</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1"/>
-      <c r="E106" t="s">
+      <c r="E106" t="s" s="1">
         <v>367</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1"/>
-      <c r="E107" t="s">
+      <c r="E107" t="s" s="1">
         <v>368</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1"/>
-      <c r="E108" t="s">
+      <c r="E108" t="s" s="1">
         <v>369</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1"/>
-      <c r="E109" t="s">
+      <c r="E109" t="s" s="1">
         <v>370</v>
       </c>
     </row>
@@ -5068,99 +5093,108 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.45313" customWidth="1"/>
-    <col min="3" max="3" width="35.63281" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.72656" customWidth="1"/>
-    <col min="6" max="6" width="32.17969" customWidth="1"/>
-    <col min="7" max="7" width="33.63281" customWidth="1"/>
-    <col min="8" max="8" width="31.26953" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.45313"/>
+    <col min="3" max="3" customWidth="true" width="35.63281"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.72656"/>
+    <col min="6" max="6" customWidth="true" width="32.17969"/>
+    <col min="7" max="7" customWidth="true" width="33.63281"/>
+    <col min="8" max="8" customWidth="true" width="31.26953"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>381</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>383</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>385</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>387</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>388</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s" s="0">
         <v>389</v>
       </c>
+      <c r="D2" t="s" s="0">
+        <v>389</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s" s="0">
         <v>389</v>
       </c>
+      <c r="D3" t="s" s="0">
+        <v>389</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4"/>
-      <c r="B4"/>
+      <c r="A4" t="s" s="0">
+        <v>1077</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>389</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="D5" t="s">
+      <c r="A5" s="0"/>
+      <c r="B5" s="0"/>
+      <c r="D5" t="s" s="0">
         <v>389</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="D6" t="s">
+      <c r="A6" s="0"/>
+      <c r="B6" s="0"/>
+      <c r="D6" t="s" s="0">
         <v>389</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7"/>
-      <c r="B7"/>
+      <c r="A7" s="0"/>
+      <c r="B7" s="0"/>
     </row>
     <row r="8">
-      <c r="A8"/>
-      <c r="B8"/>
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
     </row>
     <row r="9">
-      <c r="A9"/>
+      <c r="A9" s="0"/>
     </row>
     <row r="10">
-      <c r="A10"/>
+      <c r="A10" s="0"/>
     </row>
   </sheetData>
   <pageSetup r:id="rId1" orientation="portrait"/>
@@ -5169,48 +5203,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984" customWidth="1"/>
-    <col min="2" max="2" width="17.54297" customWidth="1"/>
-    <col min="3" max="3" width="17.36328" customWidth="1"/>
-    <col min="4" max="5" width="17.26953" customWidth="1"/>
-    <col min="6" max="6" width="17.17969" customWidth="1"/>
-    <col min="7" max="7" width="15.36328" customWidth="1"/>
-    <col min="8" max="8" width="17.17969" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984"/>
+    <col min="2" max="2" customWidth="true" width="17.54297"/>
+    <col min="3" max="3" customWidth="true" width="17.36328"/>
+    <col min="4" max="5" customWidth="true" width="17.26953"/>
+    <col min="6" max="6" customWidth="true" width="17.17969"/>
+    <col min="7" max="7" customWidth="true" width="15.36328"/>
+    <col min="8" max="8" customWidth="true" width="17.17969"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>391</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>393</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>395</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>397</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>399</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -5221,10 +5256,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>403</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -5235,10 +5270,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>406</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>407</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -5249,10 +5284,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>410</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>411</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -5263,10 +5298,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>414</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>415</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -5277,10 +5312,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>418</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>419</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -5291,10 +5326,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>423</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -5305,10 +5340,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>427</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -5319,10 +5354,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>430</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>431</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -5333,10 +5368,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>435</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -5347,10 +5382,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>438</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>439</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -5361,10 +5396,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>443</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -5375,10 +5410,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>447</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -5389,10 +5424,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>450</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>451</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -5403,10 +5438,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>454</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>455</v>
       </c>
       <c r="C16" s="10" t="s">
@@ -5417,10 +5452,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>458</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>459</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -5431,10 +5466,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>463</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -5445,10 +5480,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>466</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>467</v>
       </c>
       <c r="C19" s="10" t="s">
@@ -5459,10 +5494,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>470</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>471</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -5473,10 +5508,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>474</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>475</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -5487,10 +5522,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>478</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>479</v>
       </c>
       <c r="C22" s="10" t="s">
@@ -5501,10 +5536,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>483</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -5515,10 +5550,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>486</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>487</v>
       </c>
       <c r="C24" s="10" t="s">
@@ -5529,10 +5564,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>491</v>
       </c>
       <c r="C25" s="10" t="s">
@@ -5543,10 +5578,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>494</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>495</v>
       </c>
       <c r="C26" s="10" t="s">
@@ -5557,10 +5592,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>498</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>499</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -5571,10 +5606,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>502</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>503</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -5585,10 +5620,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>506</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>507</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -5599,10 +5634,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>510</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>511</v>
       </c>
       <c r="C30" s="10" t="s">
@@ -5613,10 +5648,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>514</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>515</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -5627,10 +5662,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>518</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>519</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -5641,10 +5676,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>522</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>523</v>
       </c>
       <c r="C33" s="10" t="s">
@@ -5655,10 +5690,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>526</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>527</v>
       </c>
       <c r="C34" s="10" t="s">
@@ -5669,10 +5704,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>530</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>531</v>
       </c>
       <c r="C35" s="10" t="s">
@@ -5683,10 +5718,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>534</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>535</v>
       </c>
       <c r="C36" s="10" t="s">
@@ -5697,10 +5732,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>538</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>539</v>
       </c>
       <c r="C37" s="10" t="s">
@@ -5711,10 +5746,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>542</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>543</v>
       </c>
       <c r="C38" s="10" t="s">
@@ -5725,10 +5760,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>546</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>547</v>
       </c>
       <c r="C39" s="10" t="s">
@@ -5739,10 +5774,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>550</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>551</v>
       </c>
       <c r="C40" s="10" t="s">
@@ -5753,10 +5788,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>555</v>
       </c>
       <c r="C41" s="10" t="s">
@@ -5767,10 +5802,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>558</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>559</v>
       </c>
       <c r="C42" s="10" t="s">
@@ -5781,10 +5816,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>562</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>563</v>
       </c>
       <c r="C43" s="10" t="s">
@@ -5795,10 +5830,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>566</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>567</v>
       </c>
       <c r="C44" s="10" t="s">
@@ -5809,10 +5844,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>570</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>571</v>
       </c>
       <c r="C45" s="10" t="s">
@@ -5823,10 +5858,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>574</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>575</v>
       </c>
       <c r="C46" s="10" t="s">
@@ -5837,10 +5872,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>578</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>579</v>
       </c>
       <c r="C47" s="10" t="s">
@@ -5851,10 +5886,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>582</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>583</v>
       </c>
       <c r="C48" s="10" t="s">
@@ -5865,10 +5900,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>586</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>587</v>
       </c>
       <c r="C49" s="10" t="s">
@@ -5879,10 +5914,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>590</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>591</v>
       </c>
       <c r="C50" s="10" t="s">
@@ -5893,10 +5928,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>594</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>595</v>
       </c>
       <c r="C51" s="10" t="s">
@@ -5907,10 +5942,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>598</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>599</v>
       </c>
       <c r="C52" s="10" t="s">
@@ -5921,10 +5956,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>602</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>603</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -5935,10 +5970,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>606</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>607</v>
       </c>
       <c r="C54" s="10" t="s">
@@ -5949,10 +5984,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>610</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>611</v>
       </c>
       <c r="C55" s="10" t="s">
@@ -5963,10 +5998,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>614</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>615</v>
       </c>
       <c r="C56" s="10" t="s">
@@ -5977,10 +6012,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>618</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>619</v>
       </c>
       <c r="C57" s="10" t="s">
@@ -5991,10 +6026,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>622</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>623</v>
       </c>
       <c r="C58" s="10" t="s">
@@ -6005,10 +6040,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>626</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>627</v>
       </c>
       <c r="C59" s="10" t="s">
@@ -6019,10 +6054,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>630</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>631</v>
       </c>
       <c r="C60" s="10" t="s">
@@ -6033,10 +6068,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>634</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>635</v>
       </c>
       <c r="C61" s="10" t="s">
@@ -6047,10 +6082,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>638</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>639</v>
       </c>
       <c r="C62" s="10" t="s">
@@ -6061,10 +6096,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>642</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>643</v>
       </c>
       <c r="C63" s="10" t="s">
@@ -6075,10 +6110,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>646</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>647</v>
       </c>
       <c r="C64" s="10" t="s">
@@ -6089,10 +6124,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>650</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>651</v>
       </c>
       <c r="C65" s="10" t="s">
@@ -6103,10 +6138,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>654</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>655</v>
       </c>
       <c r="C66" s="10" t="s">
@@ -6117,10 +6152,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>658</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>659</v>
       </c>
       <c r="C67" s="10" t="s">
@@ -6131,10 +6166,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>662</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>663</v>
       </c>
       <c r="C68" s="10" t="s">
@@ -6145,10 +6180,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>666</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>667</v>
       </c>
       <c r="C69" s="10" t="s">
@@ -6159,10 +6194,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>670</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>671</v>
       </c>
       <c r="C70" s="10" t="s">
@@ -6173,10 +6208,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>674</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>675</v>
       </c>
       <c r="C71" s="10" t="s">
@@ -6187,10 +6222,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>678</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>679</v>
       </c>
       <c r="C72" s="10" t="s">
@@ -6201,10 +6236,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>682</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>683</v>
       </c>
       <c r="C73" s="10" t="s">
@@ -6215,10 +6250,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>686</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>687</v>
       </c>
       <c r="C74" s="10" t="s">
@@ -6229,10 +6264,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>690</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>691</v>
       </c>
       <c r="C75" s="10" t="s">
@@ -6243,10 +6278,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>694</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>695</v>
       </c>
       <c r="C76" s="10" t="s">
@@ -6257,10 +6292,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>698</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>699</v>
       </c>
       <c r="C77" s="10" t="s">
@@ -6271,10 +6306,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>702</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C78" s="10" t="s">
@@ -6285,10 +6320,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>706</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>707</v>
       </c>
       <c r="C79" s="10" t="s">
@@ -6299,10 +6334,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>710</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>711</v>
       </c>
       <c r="C80" s="10" t="s">
@@ -6313,10 +6348,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>714</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C81" s="10" t="s">
@@ -6327,10 +6362,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>718</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>719</v>
       </c>
       <c r="C82" s="10" t="s">
@@ -6341,10 +6376,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>722</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>723</v>
       </c>
       <c r="C83" s="10" t="s">
@@ -6355,10 +6390,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>726</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>727</v>
       </c>
       <c r="C84" s="10" t="s">
@@ -6369,10 +6404,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>730</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>731</v>
       </c>
       <c r="C85" s="10" t="s">
@@ -6383,10 +6418,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>734</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>735</v>
       </c>
       <c r="C86" s="10" t="s">
@@ -6397,10 +6432,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>738</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>739</v>
       </c>
       <c r="C87" s="10" t="s">
@@ -6411,10 +6446,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>742</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>743</v>
       </c>
       <c r="C88" s="10" t="s">
@@ -6425,10 +6460,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>746</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>747</v>
       </c>
       <c r="C89" s="10" t="s">
@@ -6439,10 +6474,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>750</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>751</v>
       </c>
       <c r="C90" s="10" t="s">
@@ -6453,10 +6488,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>754</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>755</v>
       </c>
       <c r="C91" s="10" t="s">
@@ -6467,10 +6502,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>758</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>759</v>
       </c>
       <c r="C92" s="10" t="s">
@@ -6481,10 +6516,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>762</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>763</v>
       </c>
       <c r="C93" s="10" t="s">
@@ -6495,10 +6530,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>766</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>767</v>
       </c>
       <c r="C94" s="10" t="s">
@@ -6509,10 +6544,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>770</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>771</v>
       </c>
       <c r="C95" s="10" t="s">
@@ -6523,10 +6558,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>774</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>775</v>
       </c>
       <c r="C96" s="10" t="s">
@@ -6537,10 +6572,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>778</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>779</v>
       </c>
       <c r="C97" s="10" t="s">
@@ -6551,10 +6586,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>782</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>783</v>
       </c>
       <c r="C98" s="10" t="s">
@@ -6565,10 +6600,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>786</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>787</v>
       </c>
       <c r="C99" s="10" t="s">
@@ -6579,10 +6614,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>790</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>791</v>
       </c>
       <c r="C100" s="10" t="s">
@@ -6593,10 +6628,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>794</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>795</v>
       </c>
       <c r="C101" s="10" t="s">
@@ -6607,10 +6642,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>798</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>799</v>
       </c>
       <c r="C102" s="10" t="s">
@@ -6621,10 +6656,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>802</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>803</v>
       </c>
       <c r="C103" s="10" t="s">
@@ -6635,10 +6670,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>806</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>807</v>
       </c>
       <c r="C104" s="10" t="s">
@@ -6649,10 +6684,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>810</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>811</v>
       </c>
       <c r="C105" s="10" t="s">
@@ -6663,10 +6698,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>814</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>815</v>
       </c>
       <c r="C106" s="10" t="s">
@@ -6677,10 +6712,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>818</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>819</v>
       </c>
       <c r="C107" s="10" t="s">
@@ -6691,10 +6726,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>822</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>823</v>
       </c>
       <c r="C108" s="10" t="s">
@@ -6705,10 +6740,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>826</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>827</v>
       </c>
       <c r="C109" s="10" t="s">
@@ -6719,10 +6754,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>830</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>831</v>
       </c>
       <c r="C110" s="10" t="s">
@@ -6733,10 +6768,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>834</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>835</v>
       </c>
       <c r="C111" s="10" t="s">
@@ -6747,10 +6782,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>838</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>839</v>
       </c>
       <c r="C112" s="10" t="s">
@@ -6761,10 +6796,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>842</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>843</v>
       </c>
       <c r="C113" s="10" t="s">
@@ -6775,10 +6810,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>846</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>847</v>
       </c>
       <c r="C114" s="10" t="s">
@@ -6789,10 +6824,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>850</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>851</v>
       </c>
       <c r="C115" s="10" t="s">
@@ -6803,10 +6838,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>854</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>855</v>
       </c>
       <c r="C116" s="10" t="s">
@@ -6817,10 +6852,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>858</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>859</v>
       </c>
       <c r="C117" s="10" t="s">
@@ -6831,10 +6866,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>862</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>863</v>
       </c>
       <c r="C118" s="10" t="s">
@@ -6845,10 +6880,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>866</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>867</v>
       </c>
       <c r="C119" s="10" t="s">
@@ -6859,10 +6894,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>870</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>871</v>
       </c>
       <c r="C120" s="10" t="s">
@@ -6873,10 +6908,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>874</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>875</v>
       </c>
       <c r="C121" s="10" t="s">
@@ -6887,10 +6922,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>878</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>879</v>
       </c>
       <c r="C122" s="10" t="s">
@@ -6901,10 +6936,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>882</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>883</v>
       </c>
       <c r="C123" s="10" t="s">
@@ -6915,10 +6950,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>886</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>887</v>
       </c>
       <c r="C124" s="10" t="s">
@@ -6929,10 +6964,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>890</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>891</v>
       </c>
       <c r="C125" s="10" t="s">
@@ -6943,10 +6978,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>894</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>895</v>
       </c>
       <c r="C126" s="10" t="s">
@@ -6957,10 +6992,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>898</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>899</v>
       </c>
       <c r="C127" s="10" t="s">
@@ -6971,10 +7006,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>902</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>903</v>
       </c>
       <c r="C128" s="10" t="s">
@@ -6985,10 +7020,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>906</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>907</v>
       </c>
       <c r="C129" s="10" t="s">
@@ -6999,10 +7034,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>910</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>911</v>
       </c>
       <c r="C130" s="10" t="s">
@@ -7013,10 +7048,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>914</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>915</v>
       </c>
       <c r="C131" s="10" t="s">
@@ -7027,10 +7062,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>918</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>919</v>
       </c>
       <c r="C132" s="10" t="s">
@@ -7041,10 +7076,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>922</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>923</v>
       </c>
       <c r="C133" s="10" t="s">
@@ -7055,10 +7090,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>926</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>927</v>
       </c>
       <c r="C134" s="10" t="s">
@@ -7069,10 +7104,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>930</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>931</v>
       </c>
       <c r="C135" s="10" t="s">
@@ -7083,10 +7118,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>934</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>935</v>
       </c>
       <c r="C136" s="10" t="s">
@@ -7097,10 +7132,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>938</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>939</v>
       </c>
       <c r="C137" s="10" t="s">
@@ -7111,10 +7146,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>942</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>943</v>
       </c>
       <c r="C138" s="10" t="s">
@@ -7125,10 +7160,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>946</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>947</v>
       </c>
       <c r="C139" s="10" t="s">
@@ -7139,10 +7174,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>950</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>951</v>
       </c>
       <c r="C140" s="10" t="s">
@@ -7153,10 +7188,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>954</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>955</v>
       </c>
       <c r="C141" s="10" t="s">
@@ -7167,10 +7202,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>958</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>959</v>
       </c>
       <c r="C142" s="10" t="s">
@@ -7181,10 +7216,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>962</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>963</v>
       </c>
       <c r="C143" s="10" t="s">
@@ -7195,10 +7230,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>966</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>967</v>
       </c>
       <c r="C144" s="10" t="s">
@@ -7209,10 +7244,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>970</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>971</v>
       </c>
       <c r="C145" s="10" t="s">
@@ -7223,10 +7258,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>974</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>975</v>
       </c>
       <c r="C146" s="10" t="s">
@@ -7237,10 +7272,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>978</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>979</v>
       </c>
       <c r="C147" s="10" t="s">
@@ -7251,10 +7286,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>982</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>983</v>
       </c>
       <c r="C148" s="10" t="s">
@@ -7265,10 +7300,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>986</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>987</v>
       </c>
       <c r="C149" s="10" t="s">
@@ -7279,10 +7314,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>990</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>991</v>
       </c>
       <c r="C150" s="10" t="s">
@@ -7293,10 +7328,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>994</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>995</v>
       </c>
       <c r="C151" s="10" t="s">
@@ -7307,10 +7342,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>998</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>999</v>
       </c>
       <c r="C152" s="10" t="s">
@@ -7321,7 +7356,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>1002</v>
       </c>
       <c r="C153" s="10" t="s">
@@ -7332,7 +7367,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>1005</v>
       </c>
       <c r="C154" s="10" t="s">
@@ -7343,7 +7378,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>1008</v>
       </c>
       <c r="C155" s="10" t="s">
@@ -7354,7 +7389,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>1011</v>
       </c>
       <c r="C156" s="10" t="s">
@@ -7365,7 +7400,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>1014</v>
       </c>
       <c r="C157" s="10" t="s">
@@ -7376,7 +7411,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>1017</v>
       </c>
       <c r="C158" s="10" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3246,32 +3246,13 @@
   </si>
   <si>
     <t>Nexra</t>
-  </si>
-  <si>
-    <t>Charlie70</t>
-  </si>
-  <si>
-    <t>Milo48</t>
-  </si>
-  <si>
-    <t>Taffy46</t>
-  </si>
-  <si>
-    <t>Cutie37</t>
-  </si>
-  <si>
-    <t>Cinder37</t>
-  </si>
-  <si>
-    <t>pony30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3288,11 +3269,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -3320,32 +3296,15 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <left>
-        <color indexed="64"/>
-      </left>
-      <right>
-        <color indexed="64"/>
-      </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3359,11 +3318,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3664,21 +3618,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
-    <col min="12" max="16384" style="1" width="8.726563"/>
+    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.726563" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4519,7 +4472,7 @@
       <c r="B49" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="2" t="s">
         <v>247</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -4556,7 +4509,7 @@
       <c r="C51" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="2" t="s">
         <v>258</v>
       </c>
       <c r="E51" s="2" t="s">
@@ -4573,7 +4526,7 @@
       <c r="C52" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D52" t="s" s="15">
+      <c r="D52" s="2" t="s">
         <v>263</v>
       </c>
       <c r="E52" s="2" t="s">
@@ -4590,7 +4543,7 @@
       <c r="C53" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D53" t="s" s="1">
+      <c r="D53" s="1" t="s">
         <v>268</v>
       </c>
       <c r="E53" s="2" t="s">
@@ -4807,7 +4760,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="2" t="s">
         <v>325</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -4815,7 +4768,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="s">
+      <c r="A77" s="2" t="s">
         <v>327</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -4848,7 +4801,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s" s="1">
+      <c r="A81" s="1" t="s">
         <v>335</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -4857,7 +4810,7 @@
       <c r="F81" s="6"/>
     </row>
     <row r="82">
-      <c r="A82" t="s" s="1">
+      <c r="A82" s="1" t="s">
         <v>337</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -4996,43 +4949,43 @@
     </row>
     <row r="103">
       <c r="A103" s="1"/>
-      <c r="E103" t="s" s="1">
+      <c r="E103" s="3" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1"/>
-      <c r="E104" t="s" s="1">
+      <c r="E104" s="1" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1"/>
-      <c r="E105" t="s" s="1">
+      <c r="E105" s="1" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1"/>
-      <c r="E106" t="s" s="1">
+      <c r="E106" s="1" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1"/>
-      <c r="E107" t="s" s="1">
+      <c r="E107" s="1" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1"/>
-      <c r="E108" t="s" s="1">
+      <c r="E108" s="1" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1"/>
-      <c r="E109" t="s" s="1">
+      <c r="E109" s="1" t="s">
         <v>370</v>
       </c>
     </row>
@@ -5093,108 +5046,86 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.45313"/>
-    <col min="3" max="3" customWidth="true" width="35.63281"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.72656"/>
-    <col min="6" max="6" customWidth="true" width="32.17969"/>
-    <col min="7" max="7" customWidth="true" width="33.63281"/>
-    <col min="8" max="8" customWidth="true" width="31.26953"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.45313" customWidth="1"/>
+    <col min="3" max="3" width="35.63281" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.72656" customWidth="1"/>
+    <col min="6" max="6" width="32.17969" customWidth="1"/>
+    <col min="7" max="7" width="33.63281" customWidth="1"/>
+    <col min="8" max="8" width="31.26953" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>381</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>382</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>383</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>384</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>385</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>386</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>387</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>389</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>389</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>389</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>389</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>389</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>389</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>1077</v>
-      </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0"/>
-      <c r="B5" s="0"/>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0"/>
-      <c r="B6" s="0"/>
-      <c r="D6" t="s" s="0">
+      <c r="D6" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0"/>
-      <c r="B7" s="0"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="0"/>
-      <c r="B8" s="0"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="0"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="0"/>
     </row>
   </sheetData>
   <pageSetup r:id="rId1" orientation="portrait"/>
@@ -5203,49 +5134,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984"/>
-    <col min="2" max="2" customWidth="true" width="17.54297"/>
-    <col min="3" max="3" customWidth="true" width="17.36328"/>
-    <col min="4" max="5" customWidth="true" width="17.26953"/>
-    <col min="6" max="6" customWidth="true" width="17.17969"/>
-    <col min="7" max="7" customWidth="true" width="15.36328"/>
-    <col min="8" max="8" customWidth="true" width="17.17969"/>
+    <col min="1" max="1" width="20.08984" customWidth="1"/>
+    <col min="2" max="2" width="17.54297" customWidth="1"/>
+    <col min="3" max="3" width="17.36328" customWidth="1"/>
+    <col min="4" max="5" width="17.26953" customWidth="1"/>
+    <col min="6" max="6" width="17.17969" customWidth="1"/>
+    <col min="7" max="7" width="15.36328" customWidth="1"/>
+    <col min="8" max="8" width="17.17969" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>391</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>392</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>393</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>394</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>395</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>396</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>398</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>399</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -5256,10 +5186,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>402</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>403</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -5270,10 +5200,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>406</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>407</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -5284,10 +5214,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>410</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>411</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -5298,10 +5228,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>414</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>415</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -5312,10 +5242,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="0">
+      <c r="A7" t="s">
         <v>418</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>419</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -5326,10 +5256,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s" s="0">
+      <c r="A8" t="s">
         <v>422</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>423</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -5340,10 +5270,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s" s="0">
+      <c r="A9" t="s">
         <v>426</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>427</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -5354,10 +5284,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="0">
+      <c r="A10" t="s">
         <v>430</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>431</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -5368,10 +5298,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="0">
+      <c r="A11" t="s">
         <v>434</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>435</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -5382,10 +5312,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="0">
+      <c r="A12" t="s">
         <v>438</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>439</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -5396,10 +5326,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="0">
+      <c r="A13" t="s">
         <v>442</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>443</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -5410,10 +5340,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="0">
+      <c r="A14" t="s">
         <v>446</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>447</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -5424,10 +5354,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="0">
+      <c r="A15" t="s">
         <v>450</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>451</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -5438,10 +5368,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s" s="0">
+      <c r="A16" t="s">
         <v>454</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>455</v>
       </c>
       <c r="C16" s="10" t="s">
@@ -5452,10 +5382,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s" s="0">
+      <c r="A17" t="s">
         <v>458</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>459</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -5466,10 +5396,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="0">
+      <c r="A18" t="s">
         <v>462</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>463</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -5480,10 +5410,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s" s="0">
+      <c r="A19" t="s">
         <v>466</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>467</v>
       </c>
       <c r="C19" s="10" t="s">
@@ -5494,10 +5424,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="0">
+      <c r="A20" t="s">
         <v>470</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>471</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -5508,10 +5438,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s" s="0">
+      <c r="A21" t="s">
         <v>474</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B21" t="s">
         <v>475</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -5522,10 +5452,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s" s="0">
+      <c r="A22" t="s">
         <v>478</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="B22" t="s">
         <v>479</v>
       </c>
       <c r="C22" s="10" t="s">
@@ -5536,10 +5466,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s" s="0">
+      <c r="A23" t="s">
         <v>482</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>483</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -5550,10 +5480,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s" s="0">
+      <c r="A24" t="s">
         <v>486</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>487</v>
       </c>
       <c r="C24" s="10" t="s">
@@ -5564,10 +5494,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s" s="0">
+      <c r="A25" t="s">
         <v>490</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B25" t="s">
         <v>491</v>
       </c>
       <c r="C25" s="10" t="s">
@@ -5578,10 +5508,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s" s="0">
+      <c r="A26" t="s">
         <v>494</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>495</v>
       </c>
       <c r="C26" s="10" t="s">
@@ -5592,10 +5522,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s" s="0">
+      <c r="A27" t="s">
         <v>498</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>499</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -5606,10 +5536,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s" s="0">
+      <c r="A28" t="s">
         <v>502</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>503</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -5620,10 +5550,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s" s="0">
+      <c r="A29" t="s">
         <v>506</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="B29" t="s">
         <v>507</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -5634,10 +5564,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s" s="0">
+      <c r="A30" t="s">
         <v>510</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="B30" t="s">
         <v>511</v>
       </c>
       <c r="C30" s="10" t="s">
@@ -5648,10 +5578,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s" s="0">
+      <c r="A31" t="s">
         <v>514</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>515</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -5662,10 +5592,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s" s="0">
+      <c r="A32" t="s">
         <v>518</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>519</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -5676,10 +5606,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s" s="0">
+      <c r="A33" t="s">
         <v>522</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>523</v>
       </c>
       <c r="C33" s="10" t="s">
@@ -5690,10 +5620,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s" s="0">
+      <c r="A34" t="s">
         <v>526</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>527</v>
       </c>
       <c r="C34" s="10" t="s">
@@ -5704,10 +5634,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s" s="0">
+      <c r="A35" t="s">
         <v>530</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B35" t="s">
         <v>531</v>
       </c>
       <c r="C35" s="10" t="s">
@@ -5718,10 +5648,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s" s="0">
+      <c r="A36" t="s">
         <v>534</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="B36" t="s">
         <v>535</v>
       </c>
       <c r="C36" s="10" t="s">
@@ -5732,10 +5662,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s" s="0">
+      <c r="A37" t="s">
         <v>538</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B37" t="s">
         <v>539</v>
       </c>
       <c r="C37" s="10" t="s">
@@ -5746,10 +5676,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s" s="0">
+      <c r="A38" t="s">
         <v>542</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B38" t="s">
         <v>543</v>
       </c>
       <c r="C38" s="10" t="s">
@@ -5760,10 +5690,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s" s="0">
+      <c r="A39" t="s">
         <v>546</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="B39" t="s">
         <v>547</v>
       </c>
       <c r="C39" s="10" t="s">
@@ -5774,10 +5704,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s" s="0">
+      <c r="A40" t="s">
         <v>550</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="B40" t="s">
         <v>551</v>
       </c>
       <c r="C40" s="10" t="s">
@@ -5788,10 +5718,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s" s="0">
+      <c r="A41" t="s">
         <v>554</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="B41" t="s">
         <v>555</v>
       </c>
       <c r="C41" s="10" t="s">
@@ -5802,10 +5732,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s" s="0">
+      <c r="A42" t="s">
         <v>558</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="B42" t="s">
         <v>559</v>
       </c>
       <c r="C42" s="10" t="s">
@@ -5816,10 +5746,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s" s="0">
+      <c r="A43" t="s">
         <v>562</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="B43" t="s">
         <v>563</v>
       </c>
       <c r="C43" s="10" t="s">
@@ -5830,10 +5760,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s" s="0">
+      <c r="A44" t="s">
         <v>566</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B44" t="s">
         <v>567</v>
       </c>
       <c r="C44" s="10" t="s">
@@ -5844,10 +5774,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s" s="0">
+      <c r="A45" t="s">
         <v>570</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="B45" t="s">
         <v>571</v>
       </c>
       <c r="C45" s="10" t="s">
@@ -5858,10 +5788,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s" s="0">
+      <c r="A46" t="s">
         <v>574</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="B46" t="s">
         <v>575</v>
       </c>
       <c r="C46" s="10" t="s">
@@ -5872,10 +5802,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s" s="0">
+      <c r="A47" t="s">
         <v>578</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B47" t="s">
         <v>579</v>
       </c>
       <c r="C47" s="10" t="s">
@@ -5886,10 +5816,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s" s="0">
+      <c r="A48" t="s">
         <v>582</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="B48" t="s">
         <v>583</v>
       </c>
       <c r="C48" s="10" t="s">
@@ -5900,10 +5830,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="0">
+      <c r="A49" t="s">
         <v>586</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="B49" t="s">
         <v>587</v>
       </c>
       <c r="C49" s="10" t="s">
@@ -5914,10 +5844,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s" s="0">
+      <c r="A50" t="s">
         <v>590</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="B50" t="s">
         <v>591</v>
       </c>
       <c r="C50" s="10" t="s">
@@ -5928,10 +5858,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s" s="0">
+      <c r="A51" t="s">
         <v>594</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="B51" t="s">
         <v>595</v>
       </c>
       <c r="C51" s="10" t="s">
@@ -5942,10 +5872,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s" s="0">
+      <c r="A52" t="s">
         <v>598</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="B52" t="s">
         <v>599</v>
       </c>
       <c r="C52" s="10" t="s">
@@ -5956,10 +5886,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s" s="0">
+      <c r="A53" t="s">
         <v>602</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="B53" t="s">
         <v>603</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -5970,10 +5900,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s" s="0">
+      <c r="A54" t="s">
         <v>606</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="B54" t="s">
         <v>607</v>
       </c>
       <c r="C54" s="10" t="s">
@@ -5984,10 +5914,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s" s="0">
+      <c r="A55" t="s">
         <v>610</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s">
         <v>611</v>
       </c>
       <c r="C55" s="10" t="s">
@@ -5998,10 +5928,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s" s="0">
+      <c r="A56" t="s">
         <v>614</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="B56" t="s">
         <v>615</v>
       </c>
       <c r="C56" s="10" t="s">
@@ -6012,10 +5942,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s" s="0">
+      <c r="A57" t="s">
         <v>618</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B57" t="s">
         <v>619</v>
       </c>
       <c r="C57" s="10" t="s">
@@ -6026,10 +5956,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s" s="0">
+      <c r="A58" t="s">
         <v>622</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="B58" t="s">
         <v>623</v>
       </c>
       <c r="C58" s="10" t="s">
@@ -6040,10 +5970,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s" s="0">
+      <c r="A59" t="s">
         <v>626</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="B59" t="s">
         <v>627</v>
       </c>
       <c r="C59" s="10" t="s">
@@ -6054,10 +5984,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s" s="0">
+      <c r="A60" t="s">
         <v>630</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="B60" t="s">
         <v>631</v>
       </c>
       <c r="C60" s="10" t="s">
@@ -6068,10 +5998,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s" s="0">
+      <c r="A61" t="s">
         <v>634</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="B61" t="s">
         <v>635</v>
       </c>
       <c r="C61" s="10" t="s">
@@ -6082,10 +6012,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s" s="0">
+      <c r="A62" t="s">
         <v>638</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="B62" t="s">
         <v>639</v>
       </c>
       <c r="C62" s="10" t="s">
@@ -6096,10 +6026,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s" s="0">
+      <c r="A63" t="s">
         <v>642</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="B63" t="s">
         <v>643</v>
       </c>
       <c r="C63" s="10" t="s">
@@ -6110,10 +6040,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s" s="0">
+      <c r="A64" t="s">
         <v>646</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="B64" t="s">
         <v>647</v>
       </c>
       <c r="C64" s="10" t="s">
@@ -6124,10 +6054,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s" s="0">
+      <c r="A65" t="s">
         <v>650</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="B65" t="s">
         <v>651</v>
       </c>
       <c r="C65" s="10" t="s">
@@ -6138,10 +6068,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s" s="0">
+      <c r="A66" t="s">
         <v>654</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="B66" t="s">
         <v>655</v>
       </c>
       <c r="C66" s="10" t="s">
@@ -6152,10 +6082,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s" s="0">
+      <c r="A67" t="s">
         <v>658</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="B67" t="s">
         <v>659</v>
       </c>
       <c r="C67" s="10" t="s">
@@ -6166,10 +6096,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s" s="0">
+      <c r="A68" t="s">
         <v>662</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B68" t="s">
         <v>663</v>
       </c>
       <c r="C68" s="10" t="s">
@@ -6180,10 +6110,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s" s="0">
+      <c r="A69" t="s">
         <v>666</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B69" t="s">
         <v>667</v>
       </c>
       <c r="C69" s="10" t="s">
@@ -6194,10 +6124,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s" s="0">
+      <c r="A70" t="s">
         <v>670</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="B70" t="s">
         <v>671</v>
       </c>
       <c r="C70" s="10" t="s">
@@ -6208,10 +6138,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="0">
+      <c r="A71" t="s">
         <v>674</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="B71" t="s">
         <v>675</v>
       </c>
       <c r="C71" s="10" t="s">
@@ -6222,10 +6152,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s" s="0">
+      <c r="A72" t="s">
         <v>678</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="B72" t="s">
         <v>679</v>
       </c>
       <c r="C72" s="10" t="s">
@@ -6236,10 +6166,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s" s="0">
+      <c r="A73" t="s">
         <v>682</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="B73" t="s">
         <v>683</v>
       </c>
       <c r="C73" s="10" t="s">
@@ -6250,10 +6180,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s" s="0">
+      <c r="A74" t="s">
         <v>686</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="B74" t="s">
         <v>687</v>
       </c>
       <c r="C74" s="10" t="s">
@@ -6264,10 +6194,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s" s="0">
+      <c r="A75" t="s">
         <v>690</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="B75" t="s">
         <v>691</v>
       </c>
       <c r="C75" s="10" t="s">
@@ -6278,10 +6208,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s" s="0">
+      <c r="A76" t="s">
         <v>694</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B76" t="s">
         <v>695</v>
       </c>
       <c r="C76" s="10" t="s">
@@ -6292,10 +6222,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s" s="0">
+      <c r="A77" t="s">
         <v>698</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="B77" t="s">
         <v>699</v>
       </c>
       <c r="C77" s="10" t="s">
@@ -6306,10 +6236,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s" s="0">
+      <c r="A78" t="s">
         <v>702</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B78" t="s">
         <v>703</v>
       </c>
       <c r="C78" s="10" t="s">
@@ -6320,10 +6250,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s" s="0">
+      <c r="A79" t="s">
         <v>706</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="B79" t="s">
         <v>707</v>
       </c>
       <c r="C79" s="10" t="s">
@@ -6334,10 +6264,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s" s="0">
+      <c r="A80" t="s">
         <v>710</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="B80" t="s">
         <v>711</v>
       </c>
       <c r="C80" s="10" t="s">
@@ -6348,10 +6278,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s" s="0">
+      <c r="A81" t="s">
         <v>714</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B81" t="s">
         <v>715</v>
       </c>
       <c r="C81" s="10" t="s">
@@ -6362,10 +6292,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s" s="0">
+      <c r="A82" t="s">
         <v>718</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="B82" t="s">
         <v>719</v>
       </c>
       <c r="C82" s="10" t="s">
@@ -6376,10 +6306,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s" s="0">
+      <c r="A83" t="s">
         <v>722</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B83" t="s">
         <v>723</v>
       </c>
       <c r="C83" s="10" t="s">
@@ -6390,10 +6320,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s" s="0">
+      <c r="A84" t="s">
         <v>726</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B84" t="s">
         <v>727</v>
       </c>
       <c r="C84" s="10" t="s">
@@ -6404,10 +6334,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s" s="0">
+      <c r="A85" t="s">
         <v>730</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="B85" t="s">
         <v>731</v>
       </c>
       <c r="C85" s="10" t="s">
@@ -6418,10 +6348,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s" s="0">
+      <c r="A86" t="s">
         <v>734</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="B86" t="s">
         <v>735</v>
       </c>
       <c r="C86" s="10" t="s">
@@ -6432,10 +6362,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s" s="0">
+      <c r="A87" t="s">
         <v>738</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="B87" t="s">
         <v>739</v>
       </c>
       <c r="C87" s="10" t="s">
@@ -6446,10 +6376,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s" s="0">
+      <c r="A88" t="s">
         <v>742</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="B88" t="s">
         <v>743</v>
       </c>
       <c r="C88" s="10" t="s">
@@ -6460,10 +6390,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s" s="0">
+      <c r="A89" t="s">
         <v>746</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="B89" t="s">
         <v>747</v>
       </c>
       <c r="C89" s="10" t="s">
@@ -6474,10 +6404,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s" s="0">
+      <c r="A90" t="s">
         <v>750</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="B90" t="s">
         <v>751</v>
       </c>
       <c r="C90" s="10" t="s">
@@ -6488,10 +6418,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s" s="0">
+      <c r="A91" t="s">
         <v>754</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="B91" t="s">
         <v>755</v>
       </c>
       <c r="C91" s="10" t="s">
@@ -6502,10 +6432,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s" s="0">
+      <c r="A92" t="s">
         <v>758</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="B92" t="s">
         <v>759</v>
       </c>
       <c r="C92" s="10" t="s">
@@ -6516,10 +6446,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s" s="0">
+      <c r="A93" t="s">
         <v>762</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B93" t="s">
         <v>763</v>
       </c>
       <c r="C93" s="10" t="s">
@@ -6530,10 +6460,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s" s="0">
+      <c r="A94" t="s">
         <v>766</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="B94" t="s">
         <v>767</v>
       </c>
       <c r="C94" s="10" t="s">
@@ -6544,10 +6474,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s" s="0">
+      <c r="A95" t="s">
         <v>770</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="B95" t="s">
         <v>771</v>
       </c>
       <c r="C95" s="10" t="s">
@@ -6558,10 +6488,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s" s="0">
+      <c r="A96" t="s">
         <v>774</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="B96" t="s">
         <v>775</v>
       </c>
       <c r="C96" s="10" t="s">
@@ -6572,10 +6502,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s" s="0">
+      <c r="A97" t="s">
         <v>778</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="B97" t="s">
         <v>779</v>
       </c>
       <c r="C97" s="10" t="s">
@@ -6586,10 +6516,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s" s="0">
+      <c r="A98" t="s">
         <v>782</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="B98" t="s">
         <v>783</v>
       </c>
       <c r="C98" s="10" t="s">
@@ -6600,10 +6530,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s" s="0">
+      <c r="A99" t="s">
         <v>786</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="B99" t="s">
         <v>787</v>
       </c>
       <c r="C99" s="10" t="s">
@@ -6614,10 +6544,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s" s="0">
+      <c r="A100" t="s">
         <v>790</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="B100" t="s">
         <v>791</v>
       </c>
       <c r="C100" s="10" t="s">
@@ -6628,10 +6558,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s" s="0">
+      <c r="A101" t="s">
         <v>794</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="B101" t="s">
         <v>795</v>
       </c>
       <c r="C101" s="10" t="s">
@@ -6642,10 +6572,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s" s="0">
+      <c r="A102" t="s">
         <v>798</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="B102" t="s">
         <v>799</v>
       </c>
       <c r="C102" s="10" t="s">
@@ -6656,10 +6586,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s" s="0">
+      <c r="A103" t="s">
         <v>802</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="B103" t="s">
         <v>803</v>
       </c>
       <c r="C103" s="10" t="s">
@@ -6670,10 +6600,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s" s="0">
+      <c r="A104" t="s">
         <v>806</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="B104" t="s">
         <v>807</v>
       </c>
       <c r="C104" s="10" t="s">
@@ -6684,10 +6614,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s" s="0">
+      <c r="A105" t="s">
         <v>810</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="B105" t="s">
         <v>811</v>
       </c>
       <c r="C105" s="10" t="s">
@@ -6698,10 +6628,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s" s="0">
+      <c r="A106" t="s">
         <v>814</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="B106" t="s">
         <v>815</v>
       </c>
       <c r="C106" s="10" t="s">
@@ -6712,10 +6642,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s" s="0">
+      <c r="A107" t="s">
         <v>818</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="B107" t="s">
         <v>819</v>
       </c>
       <c r="C107" s="10" t="s">
@@ -6726,10 +6656,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s" s="0">
+      <c r="A108" t="s">
         <v>822</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="B108" t="s">
         <v>823</v>
       </c>
       <c r="C108" s="10" t="s">
@@ -6740,10 +6670,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s" s="0">
+      <c r="A109" t="s">
         <v>826</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="B109" t="s">
         <v>827</v>
       </c>
       <c r="C109" s="10" t="s">
@@ -6754,10 +6684,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s" s="0">
+      <c r="A110" t="s">
         <v>830</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="B110" t="s">
         <v>831</v>
       </c>
       <c r="C110" s="10" t="s">
@@ -6768,10 +6698,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s" s="0">
+      <c r="A111" t="s">
         <v>834</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="B111" t="s">
         <v>835</v>
       </c>
       <c r="C111" s="10" t="s">
@@ -6782,10 +6712,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s" s="0">
+      <c r="A112" t="s">
         <v>838</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="B112" t="s">
         <v>839</v>
       </c>
       <c r="C112" s="10" t="s">
@@ -6796,10 +6726,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s" s="0">
+      <c r="A113" t="s">
         <v>842</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="B113" t="s">
         <v>843</v>
       </c>
       <c r="C113" s="10" t="s">
@@ -6810,10 +6740,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s" s="0">
+      <c r="A114" t="s">
         <v>846</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="B114" t="s">
         <v>847</v>
       </c>
       <c r="C114" s="10" t="s">
@@ -6824,10 +6754,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s" s="0">
+      <c r="A115" t="s">
         <v>850</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="B115" t="s">
         <v>851</v>
       </c>
       <c r="C115" s="10" t="s">
@@ -6838,10 +6768,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s" s="0">
+      <c r="A116" t="s">
         <v>854</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="B116" t="s">
         <v>855</v>
       </c>
       <c r="C116" s="10" t="s">
@@ -6852,10 +6782,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s" s="0">
+      <c r="A117" t="s">
         <v>858</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="B117" t="s">
         <v>859</v>
       </c>
       <c r="C117" s="10" t="s">
@@ -6866,10 +6796,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s" s="0">
+      <c r="A118" t="s">
         <v>862</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="B118" t="s">
         <v>863</v>
       </c>
       <c r="C118" s="10" t="s">
@@ -6880,10 +6810,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s" s="0">
+      <c r="A119" t="s">
         <v>866</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="B119" t="s">
         <v>867</v>
       </c>
       <c r="C119" s="10" t="s">
@@ -6894,10 +6824,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s" s="0">
+      <c r="A120" t="s">
         <v>870</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="B120" t="s">
         <v>871</v>
       </c>
       <c r="C120" s="10" t="s">
@@ -6908,10 +6838,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s" s="0">
+      <c r="A121" t="s">
         <v>874</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="B121" t="s">
         <v>875</v>
       </c>
       <c r="C121" s="10" t="s">
@@ -6922,10 +6852,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s" s="0">
+      <c r="A122" t="s">
         <v>878</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="B122" t="s">
         <v>879</v>
       </c>
       <c r="C122" s="10" t="s">
@@ -6936,10 +6866,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s" s="0">
+      <c r="A123" t="s">
         <v>882</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="B123" t="s">
         <v>883</v>
       </c>
       <c r="C123" s="10" t="s">
@@ -6950,10 +6880,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s" s="0">
+      <c r="A124" t="s">
         <v>886</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="B124" t="s">
         <v>887</v>
       </c>
       <c r="C124" s="10" t="s">
@@ -6964,10 +6894,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s" s="0">
+      <c r="A125" t="s">
         <v>890</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="B125" t="s">
         <v>891</v>
       </c>
       <c r="C125" s="10" t="s">
@@ -6978,10 +6908,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s" s="0">
+      <c r="A126" t="s">
         <v>894</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="B126" t="s">
         <v>895</v>
       </c>
       <c r="C126" s="10" t="s">
@@ -6992,10 +6922,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s" s="0">
+      <c r="A127" t="s">
         <v>898</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="B127" t="s">
         <v>899</v>
       </c>
       <c r="C127" s="10" t="s">
@@ -7006,10 +6936,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s" s="0">
+      <c r="A128" t="s">
         <v>902</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="B128" t="s">
         <v>903</v>
       </c>
       <c r="C128" s="10" t="s">
@@ -7020,10 +6950,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s" s="0">
+      <c r="A129" t="s">
         <v>906</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="B129" t="s">
         <v>907</v>
       </c>
       <c r="C129" s="10" t="s">
@@ -7034,10 +6964,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s" s="0">
+      <c r="A130" t="s">
         <v>910</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="B130" t="s">
         <v>911</v>
       </c>
       <c r="C130" s="10" t="s">
@@ -7048,10 +6978,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s" s="0">
+      <c r="A131" t="s">
         <v>914</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="B131" t="s">
         <v>915</v>
       </c>
       <c r="C131" s="10" t="s">
@@ -7062,10 +6992,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s" s="0">
+      <c r="A132" t="s">
         <v>918</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="B132" t="s">
         <v>919</v>
       </c>
       <c r="C132" s="10" t="s">
@@ -7076,10 +7006,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s" s="0">
+      <c r="A133" t="s">
         <v>922</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="B133" t="s">
         <v>923</v>
       </c>
       <c r="C133" s="10" t="s">
@@ -7090,10 +7020,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s" s="0">
+      <c r="A134" t="s">
         <v>926</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="B134" t="s">
         <v>927</v>
       </c>
       <c r="C134" s="10" t="s">
@@ -7104,10 +7034,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s" s="0">
+      <c r="A135" t="s">
         <v>930</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="B135" t="s">
         <v>931</v>
       </c>
       <c r="C135" s="10" t="s">
@@ -7118,10 +7048,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s" s="0">
+      <c r="A136" t="s">
         <v>934</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="B136" t="s">
         <v>935</v>
       </c>
       <c r="C136" s="10" t="s">
@@ -7132,10 +7062,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s" s="0">
+      <c r="A137" t="s">
         <v>938</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="B137" t="s">
         <v>939</v>
       </c>
       <c r="C137" s="10" t="s">
@@ -7146,10 +7076,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s" s="0">
+      <c r="A138" t="s">
         <v>942</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="B138" t="s">
         <v>943</v>
       </c>
       <c r="C138" s="10" t="s">
@@ -7160,10 +7090,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s" s="0">
+      <c r="A139" t="s">
         <v>946</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="B139" t="s">
         <v>947</v>
       </c>
       <c r="C139" s="10" t="s">
@@ -7174,10 +7104,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s" s="0">
+      <c r="A140" t="s">
         <v>950</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="B140" t="s">
         <v>951</v>
       </c>
       <c r="C140" s="10" t="s">
@@ -7188,10 +7118,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s" s="0">
+      <c r="A141" t="s">
         <v>954</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="B141" t="s">
         <v>955</v>
       </c>
       <c r="C141" s="10" t="s">
@@ -7202,10 +7132,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s" s="0">
+      <c r="A142" t="s">
         <v>958</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="B142" t="s">
         <v>959</v>
       </c>
       <c r="C142" s="10" t="s">
@@ -7216,10 +7146,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s" s="0">
+      <c r="A143" t="s">
         <v>962</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="B143" t="s">
         <v>963</v>
       </c>
       <c r="C143" s="10" t="s">
@@ -7230,10 +7160,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s" s="0">
+      <c r="A144" t="s">
         <v>966</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="B144" t="s">
         <v>967</v>
       </c>
       <c r="C144" s="10" t="s">
@@ -7244,10 +7174,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s" s="0">
+      <c r="A145" t="s">
         <v>970</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="B145" t="s">
         <v>971</v>
       </c>
       <c r="C145" s="10" t="s">
@@ -7258,10 +7188,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s" s="0">
+      <c r="A146" t="s">
         <v>974</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="B146" t="s">
         <v>975</v>
       </c>
       <c r="C146" s="10" t="s">
@@ -7272,10 +7202,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s" s="0">
+      <c r="A147" t="s">
         <v>978</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="B147" t="s">
         <v>979</v>
       </c>
       <c r="C147" s="10" t="s">
@@ -7286,10 +7216,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s" s="0">
+      <c r="A148" t="s">
         <v>982</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="B148" t="s">
         <v>983</v>
       </c>
       <c r="C148" s="10" t="s">
@@ -7300,10 +7230,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s" s="0">
+      <c r="A149" t="s">
         <v>986</v>
       </c>
-      <c r="B149" t="s" s="0">
+      <c r="B149" t="s">
         <v>987</v>
       </c>
       <c r="C149" s="10" t="s">
@@ -7314,10 +7244,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s" s="0">
+      <c r="A150" t="s">
         <v>990</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="B150" t="s">
         <v>991</v>
       </c>
       <c r="C150" s="10" t="s">
@@ -7328,10 +7258,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s" s="0">
+      <c r="A151" t="s">
         <v>994</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="B151" t="s">
         <v>995</v>
       </c>
       <c r="C151" s="10" t="s">
@@ -7342,10 +7272,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s" s="0">
+      <c r="A152" t="s">
         <v>998</v>
       </c>
-      <c r="B152" t="s" s="0">
+      <c r="B152" t="s">
         <v>999</v>
       </c>
       <c r="C152" s="10" t="s">
@@ -7356,7 +7286,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s" s="0">
+      <c r="B153" t="s">
         <v>1002</v>
       </c>
       <c r="C153" s="10" t="s">
@@ -7367,7 +7297,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s" s="0">
+      <c r="B154" t="s">
         <v>1005</v>
       </c>
       <c r="C154" s="10" t="s">
@@ -7378,7 +7308,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s" s="0">
+      <c r="B155" t="s">
         <v>1008</v>
       </c>
       <c r="C155" s="10" t="s">
@@ -7389,7 +7319,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s" s="0">
+      <c r="B156" t="s">
         <v>1011</v>
       </c>
       <c r="C156" s="10" t="s">
@@ -7400,7 +7330,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s" s="0">
+      <c r="B157" t="s">
         <v>1014</v>
       </c>
       <c r="C157" s="10" t="s">
@@ -7411,7 +7341,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s" s="0">
+      <c r="B158" t="s">
         <v>1017</v>
       </c>
       <c r="C158" s="10" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3246,12 +3246,16 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Charlie72</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -3618,20 +3622,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.726563" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
+    <col min="12" max="16384" style="1" width="8.726563"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5046,84 +5051,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.45313" customWidth="1"/>
-    <col min="3" max="3" width="35.63281" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.72656" customWidth="1"/>
-    <col min="6" max="6" width="32.17969" customWidth="1"/>
-    <col min="7" max="7" width="33.63281" customWidth="1"/>
-    <col min="8" max="8" width="31.26953" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.45313"/>
+    <col min="3" max="3" customWidth="true" width="35.63281"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.72656"/>
+    <col min="6" max="6" customWidth="true" width="32.17969"/>
+    <col min="7" max="7" customWidth="true" width="33.63281"/>
+    <col min="8" max="8" customWidth="true" width="31.26953"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>381</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>383</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>385</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>387</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>388</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>1075</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
         <v>389</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
+      <c r="B3" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4">
+      <c r="B4" t="s" s="0">
         <v>389</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="s">
+    <row r="5">
+      <c r="D5" t="s" s="0">
         <v>389</v>
       </c>
     </row>
-    <row r="5">
-      <c r="D5" t="s">
-        <v>389</v>
-      </c>
-    </row>
     <row r="6">
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>389</v>
       </c>
     </row>
@@ -5134,48 +5140,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984" customWidth="1"/>
-    <col min="2" max="2" width="17.54297" customWidth="1"/>
-    <col min="3" max="3" width="17.36328" customWidth="1"/>
-    <col min="4" max="5" width="17.26953" customWidth="1"/>
-    <col min="6" max="6" width="17.17969" customWidth="1"/>
-    <col min="7" max="7" width="15.36328" customWidth="1"/>
-    <col min="8" max="8" width="17.17969" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984"/>
+    <col min="2" max="2" customWidth="true" width="17.54297"/>
+    <col min="3" max="3" customWidth="true" width="17.36328"/>
+    <col min="4" max="5" customWidth="true" width="17.26953"/>
+    <col min="6" max="6" customWidth="true" width="17.17969"/>
+    <col min="7" max="7" customWidth="true" width="15.36328"/>
+    <col min="8" max="8" customWidth="true" width="17.17969"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>391</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>393</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>395</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>397</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>399</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -5186,10 +5193,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>403</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -5200,10 +5207,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>406</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>407</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -5214,10 +5221,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>410</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>411</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -5228,10 +5235,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>414</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>415</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -5242,10 +5249,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>418</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>419</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -5256,10 +5263,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>423</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -5270,10 +5277,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>427</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -5284,10 +5291,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>430</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>431</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -5298,10 +5305,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>435</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -5312,10 +5319,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>438</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>439</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -5326,10 +5333,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>443</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -5340,10 +5347,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>447</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -5354,10 +5361,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>450</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>451</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -5368,10 +5375,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>454</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>455</v>
       </c>
       <c r="C16" s="10" t="s">
@@ -5382,10 +5389,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>458</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>459</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -5396,10 +5403,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>463</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -5410,10 +5417,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>466</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>467</v>
       </c>
       <c r="C19" s="10" t="s">
@@ -5424,10 +5431,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>470</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>471</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -5438,10 +5445,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>474</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>475</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -5452,10 +5459,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>478</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>479</v>
       </c>
       <c r="C22" s="10" t="s">
@@ -5466,10 +5473,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>483</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -5480,10 +5487,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>486</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>487</v>
       </c>
       <c r="C24" s="10" t="s">
@@ -5494,10 +5501,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>491</v>
       </c>
       <c r="C25" s="10" t="s">
@@ -5508,10 +5515,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>494</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>495</v>
       </c>
       <c r="C26" s="10" t="s">
@@ -5522,10 +5529,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>498</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>499</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -5536,10 +5543,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>502</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>503</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -5550,10 +5557,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>506</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>507</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -5564,10 +5571,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>510</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>511</v>
       </c>
       <c r="C30" s="10" t="s">
@@ -5578,10 +5585,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>514</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>515</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -5592,10 +5599,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>518</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>519</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -5606,10 +5613,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>522</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>523</v>
       </c>
       <c r="C33" s="10" t="s">
@@ -5620,10 +5627,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>526</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>527</v>
       </c>
       <c r="C34" s="10" t="s">
@@ -5634,10 +5641,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>530</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>531</v>
       </c>
       <c r="C35" s="10" t="s">
@@ -5648,10 +5655,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>534</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>535</v>
       </c>
       <c r="C36" s="10" t="s">
@@ -5662,10 +5669,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>538</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>539</v>
       </c>
       <c r="C37" s="10" t="s">
@@ -5676,10 +5683,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>542</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>543</v>
       </c>
       <c r="C38" s="10" t="s">
@@ -5690,10 +5697,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>546</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>547</v>
       </c>
       <c r="C39" s="10" t="s">
@@ -5704,10 +5711,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>550</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>551</v>
       </c>
       <c r="C40" s="10" t="s">
@@ -5718,10 +5725,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>555</v>
       </c>
       <c r="C41" s="10" t="s">
@@ -5732,10 +5739,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>558</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>559</v>
       </c>
       <c r="C42" s="10" t="s">
@@ -5746,10 +5753,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>562</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>563</v>
       </c>
       <c r="C43" s="10" t="s">
@@ -5760,10 +5767,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>566</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>567</v>
       </c>
       <c r="C44" s="10" t="s">
@@ -5774,10 +5781,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>570</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>571</v>
       </c>
       <c r="C45" s="10" t="s">
@@ -5788,10 +5795,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>574</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>575</v>
       </c>
       <c r="C46" s="10" t="s">
@@ -5802,10 +5809,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>578</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>579</v>
       </c>
       <c r="C47" s="10" t="s">
@@ -5816,10 +5823,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>582</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>583</v>
       </c>
       <c r="C48" s="10" t="s">
@@ -5830,10 +5837,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>586</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>587</v>
       </c>
       <c r="C49" s="10" t="s">
@@ -5844,10 +5851,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>590</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>591</v>
       </c>
       <c r="C50" s="10" t="s">
@@ -5858,10 +5865,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>594</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>595</v>
       </c>
       <c r="C51" s="10" t="s">
@@ -5872,10 +5879,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>598</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>599</v>
       </c>
       <c r="C52" s="10" t="s">
@@ -5886,10 +5893,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>602</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>603</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -5900,10 +5907,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>606</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>607</v>
       </c>
       <c r="C54" s="10" t="s">
@@ -5914,10 +5921,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>610</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>611</v>
       </c>
       <c r="C55" s="10" t="s">
@@ -5928,10 +5935,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>614</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>615</v>
       </c>
       <c r="C56" s="10" t="s">
@@ -5942,10 +5949,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>618</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>619</v>
       </c>
       <c r="C57" s="10" t="s">
@@ -5956,10 +5963,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>622</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>623</v>
       </c>
       <c r="C58" s="10" t="s">
@@ -5970,10 +5977,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>626</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>627</v>
       </c>
       <c r="C59" s="10" t="s">
@@ -5984,10 +5991,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>630</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>631</v>
       </c>
       <c r="C60" s="10" t="s">
@@ -5998,10 +6005,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>634</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>635</v>
       </c>
       <c r="C61" s="10" t="s">
@@ -6012,10 +6019,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>638</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>639</v>
       </c>
       <c r="C62" s="10" t="s">
@@ -6026,10 +6033,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>642</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>643</v>
       </c>
       <c r="C63" s="10" t="s">
@@ -6040,10 +6047,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>646</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>647</v>
       </c>
       <c r="C64" s="10" t="s">
@@ -6054,10 +6061,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>650</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>651</v>
       </c>
       <c r="C65" s="10" t="s">
@@ -6068,10 +6075,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>654</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>655</v>
       </c>
       <c r="C66" s="10" t="s">
@@ -6082,10 +6089,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>658</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>659</v>
       </c>
       <c r="C67" s="10" t="s">
@@ -6096,10 +6103,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>662</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>663</v>
       </c>
       <c r="C68" s="10" t="s">
@@ -6110,10 +6117,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>666</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>667</v>
       </c>
       <c r="C69" s="10" t="s">
@@ -6124,10 +6131,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>670</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>671</v>
       </c>
       <c r="C70" s="10" t="s">
@@ -6138,10 +6145,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>674</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>675</v>
       </c>
       <c r="C71" s="10" t="s">
@@ -6152,10 +6159,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>678</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>679</v>
       </c>
       <c r="C72" s="10" t="s">
@@ -6166,10 +6173,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>682</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>683</v>
       </c>
       <c r="C73" s="10" t="s">
@@ -6180,10 +6187,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>686</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>687</v>
       </c>
       <c r="C74" s="10" t="s">
@@ -6194,10 +6201,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>690</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>691</v>
       </c>
       <c r="C75" s="10" t="s">
@@ -6208,10 +6215,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>694</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>695</v>
       </c>
       <c r="C76" s="10" t="s">
@@ -6222,10 +6229,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>698</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>699</v>
       </c>
       <c r="C77" s="10" t="s">
@@ -6236,10 +6243,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>702</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C78" s="10" t="s">
@@ -6250,10 +6257,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>706</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>707</v>
       </c>
       <c r="C79" s="10" t="s">
@@ -6264,10 +6271,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>710</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>711</v>
       </c>
       <c r="C80" s="10" t="s">
@@ -6278,10 +6285,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>714</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C81" s="10" t="s">
@@ -6292,10 +6299,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>718</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>719</v>
       </c>
       <c r="C82" s="10" t="s">
@@ -6306,10 +6313,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>722</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>723</v>
       </c>
       <c r="C83" s="10" t="s">
@@ -6320,10 +6327,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>726</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>727</v>
       </c>
       <c r="C84" s="10" t="s">
@@ -6334,10 +6341,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>730</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>731</v>
       </c>
       <c r="C85" s="10" t="s">
@@ -6348,10 +6355,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>734</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>735</v>
       </c>
       <c r="C86" s="10" t="s">
@@ -6362,10 +6369,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>738</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>739</v>
       </c>
       <c r="C87" s="10" t="s">
@@ -6376,10 +6383,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>742</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>743</v>
       </c>
       <c r="C88" s="10" t="s">
@@ -6390,10 +6397,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>746</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>747</v>
       </c>
       <c r="C89" s="10" t="s">
@@ -6404,10 +6411,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>750</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>751</v>
       </c>
       <c r="C90" s="10" t="s">
@@ -6418,10 +6425,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>754</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>755</v>
       </c>
       <c r="C91" s="10" t="s">
@@ -6432,10 +6439,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>758</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>759</v>
       </c>
       <c r="C92" s="10" t="s">
@@ -6446,10 +6453,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>762</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>763</v>
       </c>
       <c r="C93" s="10" t="s">
@@ -6460,10 +6467,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>766</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>767</v>
       </c>
       <c r="C94" s="10" t="s">
@@ -6474,10 +6481,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>770</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>771</v>
       </c>
       <c r="C95" s="10" t="s">
@@ -6488,10 +6495,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>774</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>775</v>
       </c>
       <c r="C96" s="10" t="s">
@@ -6502,10 +6509,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>778</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>779</v>
       </c>
       <c r="C97" s="10" t="s">
@@ -6516,10 +6523,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>782</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>783</v>
       </c>
       <c r="C98" s="10" t="s">
@@ -6530,10 +6537,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>786</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>787</v>
       </c>
       <c r="C99" s="10" t="s">
@@ -6544,10 +6551,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>790</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>791</v>
       </c>
       <c r="C100" s="10" t="s">
@@ -6558,10 +6565,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>794</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>795</v>
       </c>
       <c r="C101" s="10" t="s">
@@ -6572,10 +6579,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>798</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>799</v>
       </c>
       <c r="C102" s="10" t="s">
@@ -6586,10 +6593,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>802</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>803</v>
       </c>
       <c r="C103" s="10" t="s">
@@ -6600,10 +6607,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>806</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>807</v>
       </c>
       <c r="C104" s="10" t="s">
@@ -6614,10 +6621,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>810</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>811</v>
       </c>
       <c r="C105" s="10" t="s">
@@ -6628,10 +6635,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>814</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>815</v>
       </c>
       <c r="C106" s="10" t="s">
@@ -6642,10 +6649,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>818</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>819</v>
       </c>
       <c r="C107" s="10" t="s">
@@ -6656,10 +6663,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>822</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>823</v>
       </c>
       <c r="C108" s="10" t="s">
@@ -6670,10 +6677,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>826</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>827</v>
       </c>
       <c r="C109" s="10" t="s">
@@ -6684,10 +6691,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>830</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>831</v>
       </c>
       <c r="C110" s="10" t="s">
@@ -6698,10 +6705,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>834</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>835</v>
       </c>
       <c r="C111" s="10" t="s">
@@ -6712,10 +6719,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>838</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>839</v>
       </c>
       <c r="C112" s="10" t="s">
@@ -6726,10 +6733,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>842</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>843</v>
       </c>
       <c r="C113" s="10" t="s">
@@ -6740,10 +6747,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>846</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>847</v>
       </c>
       <c r="C114" s="10" t="s">
@@ -6754,10 +6761,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>850</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>851</v>
       </c>
       <c r="C115" s="10" t="s">
@@ -6768,10 +6775,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>854</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>855</v>
       </c>
       <c r="C116" s="10" t="s">
@@ -6782,10 +6789,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>858</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>859</v>
       </c>
       <c r="C117" s="10" t="s">
@@ -6796,10 +6803,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>862</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>863</v>
       </c>
       <c r="C118" s="10" t="s">
@@ -6810,10 +6817,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>866</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>867</v>
       </c>
       <c r="C119" s="10" t="s">
@@ -6824,10 +6831,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>870</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>871</v>
       </c>
       <c r="C120" s="10" t="s">
@@ -6838,10 +6845,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>874</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>875</v>
       </c>
       <c r="C121" s="10" t="s">
@@ -6852,10 +6859,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>878</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>879</v>
       </c>
       <c r="C122" s="10" t="s">
@@ -6866,10 +6873,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>882</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>883</v>
       </c>
       <c r="C123" s="10" t="s">
@@ -6880,10 +6887,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>886</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>887</v>
       </c>
       <c r="C124" s="10" t="s">
@@ -6894,10 +6901,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>890</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>891</v>
       </c>
       <c r="C125" s="10" t="s">
@@ -6908,10 +6915,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>894</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>895</v>
       </c>
       <c r="C126" s="10" t="s">
@@ -6922,10 +6929,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>898</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>899</v>
       </c>
       <c r="C127" s="10" t="s">
@@ -6936,10 +6943,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>902</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>903</v>
       </c>
       <c r="C128" s="10" t="s">
@@ -6950,10 +6957,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>906</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>907</v>
       </c>
       <c r="C129" s="10" t="s">
@@ -6964,10 +6971,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>910</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>911</v>
       </c>
       <c r="C130" s="10" t="s">
@@ -6978,10 +6985,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>914</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>915</v>
       </c>
       <c r="C131" s="10" t="s">
@@ -6992,10 +6999,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>918</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>919</v>
       </c>
       <c r="C132" s="10" t="s">
@@ -7006,10 +7013,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>922</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>923</v>
       </c>
       <c r="C133" s="10" t="s">
@@ -7020,10 +7027,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>926</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>927</v>
       </c>
       <c r="C134" s="10" t="s">
@@ -7034,10 +7041,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>930</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>931</v>
       </c>
       <c r="C135" s="10" t="s">
@@ -7048,10 +7055,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>934</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>935</v>
       </c>
       <c r="C136" s="10" t="s">
@@ -7062,10 +7069,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>938</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>939</v>
       </c>
       <c r="C137" s="10" t="s">
@@ -7076,10 +7083,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>942</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>943</v>
       </c>
       <c r="C138" s="10" t="s">
@@ -7090,10 +7097,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>946</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>947</v>
       </c>
       <c r="C139" s="10" t="s">
@@ -7104,10 +7111,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>950</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>951</v>
       </c>
       <c r="C140" s="10" t="s">
@@ -7118,10 +7125,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>954</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>955</v>
       </c>
       <c r="C141" s="10" t="s">
@@ -7132,10 +7139,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>958</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>959</v>
       </c>
       <c r="C142" s="10" t="s">
@@ -7146,10 +7153,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>962</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>963</v>
       </c>
       <c r="C143" s="10" t="s">
@@ -7160,10 +7167,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>966</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>967</v>
       </c>
       <c r="C144" s="10" t="s">
@@ -7174,10 +7181,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>970</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>971</v>
       </c>
       <c r="C145" s="10" t="s">
@@ -7188,10 +7195,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>974</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>975</v>
       </c>
       <c r="C146" s="10" t="s">
@@ -7202,10 +7209,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>978</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>979</v>
       </c>
       <c r="C147" s="10" t="s">
@@ -7216,10 +7223,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>982</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>983</v>
       </c>
       <c r="C148" s="10" t="s">
@@ -7230,10 +7237,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>986</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>987</v>
       </c>
       <c r="C149" s="10" t="s">
@@ -7244,10 +7251,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>990</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>991</v>
       </c>
       <c r="C150" s="10" t="s">
@@ -7258,10 +7265,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>994</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>995</v>
       </c>
       <c r="C151" s="10" t="s">
@@ -7272,10 +7279,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>998</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>999</v>
       </c>
       <c r="C152" s="10" t="s">
@@ -7286,7 +7293,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>1002</v>
       </c>
       <c r="C153" s="10" t="s">
@@ -7297,7 +7304,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>1005</v>
       </c>
       <c r="C154" s="10" t="s">
@@ -7308,7 +7315,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>1008</v>
       </c>
       <c r="C155" s="10" t="s">
@@ -7319,7 +7326,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>1011</v>
       </c>
       <c r="C156" s="10" t="s">
@@ -7330,7 +7337,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>1014</v>
       </c>
       <c r="C157" s="10" t="s">
@@ -7341,7 +7348,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>1017</v>
       </c>
       <c r="C158" s="10" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -3249,6 +3249,15 @@
   </si>
   <si>
     <t>Charlie72</t>
+  </si>
+  <si>
+    <t>Charlie73</t>
+  </si>
+  <si>
+    <t>Milo50</t>
+  </si>
+  <si>
+    <t>Taffy48</t>
   </si>
 </sst>
 </file>
@@ -3308,7 +3317,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -3322,6 +3331,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4287,7 +4298,7 @@
       <c r="A38" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="12" t="s">
         <v>191</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -4781,7 +4792,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="11" t="s">
         <v>329</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -5092,7 +5103,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>1075</v>
+        <v>389</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>389</v>
@@ -5119,11 +5130,17 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>1077</v>
+      </c>
       <c r="B4" t="s" s="0">
         <v>389</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>1078</v>
+      </c>
       <c r="D5" t="s" s="0">
         <v>389</v>
       </c>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="752">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2264,12 +2264,22 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Charlie74</t>
+  </si>
+  <si>
+    <t>Milo51</t>
+  </si>
+  <si>
+    <t>Taffy49</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2324,7 +2334,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2335,6 +2345,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2641,21 +2654,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
+    <col min="12" max="16384" style="1" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2691,10 +2704,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2708,7 +2721,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2974,82 +2987,85 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" customWidth="1"/>
-    <col min="8" max="8" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.453125"/>
+    <col min="3" max="3" customWidth="true" width="35.6328125"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.7265625"/>
+    <col min="6" max="6" customWidth="true" width="32.1796875"/>
+    <col min="7" max="7" customWidth="true" width="33.6328125"/>
+    <col min="8" max="8" customWidth="true" width="31.26953125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
         <v>63</v>
       </c>
+      <c r="B4" t="s" s="0">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>63</v>
       </c>
     </row>
@@ -3064,46 +3080,46 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984375"/>
+    <col min="2" max="2" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.36328125"/>
+    <col min="4" max="5" customWidth="true" width="17.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.36328125"/>
+    <col min="8" max="8" customWidth="true" width="17.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>72</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>73</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3114,10 +3130,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>77</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3128,10 +3144,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3142,10 +3158,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3156,10 +3172,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3170,10 +3186,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3184,10 +3200,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3198,10 +3214,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3212,10 +3228,10 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>105</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3226,10 +3242,10 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3240,10 +3256,10 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>113</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3254,10 +3270,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>117</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3268,10 +3284,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>121</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3282,10 +3298,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>125</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -3296,10 +3312,10 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>129</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -3310,10 +3326,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>133</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -3324,10 +3340,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>137</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -3338,10 +3354,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>141</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -3352,10 +3368,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>145</v>
       </c>
       <c r="C20" s="7" t="s">
@@ -3366,10 +3382,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>149</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -3380,10 +3396,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>153</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -3394,10 +3410,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>157</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3408,10 +3424,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>161</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -3422,10 +3438,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>165</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -3436,10 +3452,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>169</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -3450,10 +3466,10 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>173</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -3464,10 +3480,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>177</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -3478,10 +3494,10 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>181</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -3492,10 +3508,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>184</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>185</v>
       </c>
       <c r="C30" s="7" t="s">
@@ -3506,10 +3522,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>189</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -3520,10 +3536,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>193</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -3534,10 +3550,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>197</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3548,10 +3564,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>201</v>
       </c>
       <c r="C34" s="7" t="s">
@@ -3562,10 +3578,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>204</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>205</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -3576,10 +3592,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>209</v>
       </c>
       <c r="C36" s="7" t="s">
@@ -3590,10 +3606,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>213</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -3604,10 +3620,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>216</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>217</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -3618,10 +3634,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>221</v>
       </c>
       <c r="C39" s="7" t="s">
@@ -3632,10 +3648,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>225</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -3646,10 +3662,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>228</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>229</v>
       </c>
       <c r="C41" s="7" t="s">
@@ -3660,10 +3676,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>232</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>233</v>
       </c>
       <c r="C42" s="7" t="s">
@@ -3674,10 +3690,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>236</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>237</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -3688,10 +3704,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>240</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>241</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -3702,10 +3718,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>245</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -3716,10 +3732,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>249</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -3730,10 +3746,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>253</v>
       </c>
       <c r="C47" s="7" t="s">
@@ -3744,10 +3760,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>257</v>
       </c>
       <c r="C48" s="7" t="s">
@@ -3758,10 +3774,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C49" s="7" t="s">
@@ -3772,10 +3788,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>265</v>
       </c>
       <c r="C50" s="7" t="s">
@@ -3786,10 +3802,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>269</v>
       </c>
       <c r="C51" s="7" t="s">
@@ -3800,10 +3816,10 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>272</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C52" s="7" t="s">
@@ -3814,10 +3830,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C53" s="7" t="s">
@@ -3828,10 +3844,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>281</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3842,10 +3858,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C55" s="7" t="s">
@@ -3856,10 +3872,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C56" s="7" t="s">
@@ -3870,10 +3886,10 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C57" s="7" t="s">
@@ -3884,10 +3900,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>296</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C58" s="7" t="s">
@@ -3898,10 +3914,10 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>301</v>
       </c>
       <c r="C59" s="7" t="s">
@@ -3912,10 +3928,10 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>305</v>
       </c>
       <c r="C60" s="7" t="s">
@@ -3926,10 +3942,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>308</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>309</v>
       </c>
       <c r="C61" s="7" t="s">
@@ -3940,10 +3956,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>312</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>313</v>
       </c>
       <c r="C62" s="7" t="s">
@@ -3954,10 +3970,10 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>316</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>317</v>
       </c>
       <c r="C63" s="7" t="s">
@@ -3968,10 +3984,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>320</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>321</v>
       </c>
       <c r="C64" s="7" t="s">
@@ -3982,10 +3998,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>325</v>
       </c>
       <c r="C65" s="7" t="s">
@@ -3996,10 +4012,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C66" s="7" t="s">
@@ -4010,10 +4026,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>332</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>333</v>
       </c>
       <c r="C67" s="7" t="s">
@@ -4024,10 +4040,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>336</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>337</v>
       </c>
       <c r="C68" s="7" t="s">
@@ -4038,10 +4054,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>341</v>
       </c>
       <c r="C69" s="7" t="s">
@@ -4052,10 +4068,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>344</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>345</v>
       </c>
       <c r="C70" s="7" t="s">
@@ -4066,10 +4082,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>348</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>349</v>
       </c>
       <c r="C71" s="7" t="s">
@@ -4080,10 +4096,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>353</v>
       </c>
       <c r="C72" s="7" t="s">
@@ -4094,10 +4110,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>356</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>357</v>
       </c>
       <c r="C73" s="7" t="s">
@@ -4108,10 +4124,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>360</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>361</v>
       </c>
       <c r="C74" s="7" t="s">
@@ -4122,10 +4138,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>365</v>
       </c>
       <c r="C75" s="7" t="s">
@@ -4136,10 +4152,10 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>368</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>369</v>
       </c>
       <c r="C76" s="7" t="s">
@@ -4150,10 +4166,10 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>372</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>373</v>
       </c>
       <c r="C77" s="7" t="s">
@@ -4164,10 +4180,10 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>376</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>377</v>
       </c>
       <c r="C78" s="7" t="s">
@@ -4178,10 +4194,10 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>380</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>381</v>
       </c>
       <c r="C79" s="7" t="s">
@@ -4192,10 +4208,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>385</v>
       </c>
       <c r="C80" s="7" t="s">
@@ -4206,10 +4222,10 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>389</v>
       </c>
       <c r="C81" s="7" t="s">
@@ -4220,10 +4236,10 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>393</v>
       </c>
       <c r="C82" s="7" t="s">
@@ -4234,10 +4250,10 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>397</v>
       </c>
       <c r="C83" s="7" t="s">
@@ -4248,10 +4264,10 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>401</v>
       </c>
       <c r="C84" s="7" t="s">
@@ -4262,10 +4278,10 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>405</v>
       </c>
       <c r="C85" s="7" t="s">
@@ -4276,10 +4292,10 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>409</v>
       </c>
       <c r="C86" s="7" t="s">
@@ -4290,10 +4306,10 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>412</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>413</v>
       </c>
       <c r="C87" s="7" t="s">
@@ -4304,10 +4320,10 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>416</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>417</v>
       </c>
       <c r="C88" s="7" t="s">
@@ -4318,10 +4334,10 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>421</v>
       </c>
       <c r="C89" s="7" t="s">
@@ -4332,10 +4348,10 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>425</v>
       </c>
       <c r="C90" s="7" t="s">
@@ -4346,10 +4362,10 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>429</v>
       </c>
       <c r="C91" s="7" t="s">
@@ -4360,10 +4376,10 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>433</v>
       </c>
       <c r="C92" s="7" t="s">
@@ -4374,10 +4390,10 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>436</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>437</v>
       </c>
       <c r="C93" s="7" t="s">
@@ -4388,10 +4404,10 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>440</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>441</v>
       </c>
       <c r="C94" s="7" t="s">
@@ -4402,10 +4418,10 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>445</v>
       </c>
       <c r="C95" s="7" t="s">
@@ -4416,10 +4432,10 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>448</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>449</v>
       </c>
       <c r="C96" s="7" t="s">
@@ -4430,10 +4446,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>453</v>
       </c>
       <c r="C97" s="7" t="s">
@@ -4444,10 +4460,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>457</v>
       </c>
       <c r="C98" s="7" t="s">
@@ -4458,10 +4474,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>460</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>461</v>
       </c>
       <c r="C99" s="7" t="s">
@@ -4472,10 +4488,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>465</v>
       </c>
       <c r="C100" s="7" t="s">
@@ -4486,10 +4502,10 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>468</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>469</v>
       </c>
       <c r="C101" s="7" t="s">
@@ -4500,10 +4516,10 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>472</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>473</v>
       </c>
       <c r="C102" s="7" t="s">
@@ -4514,10 +4530,10 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>476</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>477</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4528,10 +4544,10 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>480</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>481</v>
       </c>
       <c r="C104" s="7" t="s">
@@ -4542,10 +4558,10 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>484</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>485</v>
       </c>
       <c r="C105" s="7" t="s">
@@ -4556,10 +4572,10 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>488</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>489</v>
       </c>
       <c r="C106" s="7" t="s">
@@ -4570,10 +4586,10 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>492</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>493</v>
       </c>
       <c r="C107" s="7" t="s">
@@ -4584,10 +4600,10 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>496</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>497</v>
       </c>
       <c r="C108" s="7" t="s">
@@ -4598,10 +4614,10 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>500</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>501</v>
       </c>
       <c r="C109" s="7" t="s">
@@ -4612,10 +4628,10 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>504</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>505</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4626,10 +4642,10 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>508</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>509</v>
       </c>
       <c r="C111" s="7" t="s">
@@ -4640,10 +4656,10 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>512</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>513</v>
       </c>
       <c r="C112" s="7" t="s">
@@ -4654,10 +4670,10 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>516</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>517</v>
       </c>
       <c r="C113" s="7" t="s">
@@ -4668,10 +4684,10 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>520</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>521</v>
       </c>
       <c r="C114" s="7" t="s">
@@ -4682,10 +4698,10 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>524</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>525</v>
       </c>
       <c r="C115" s="7" t="s">
@@ -4696,10 +4712,10 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>528</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>529</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4710,10 +4726,10 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>532</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>533</v>
       </c>
       <c r="C117" s="7" t="s">
@@ -4724,10 +4740,10 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>536</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>537</v>
       </c>
       <c r="C118" s="7" t="s">
@@ -4738,10 +4754,10 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>540</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>541</v>
       </c>
       <c r="C119" s="7" t="s">
@@ -4752,10 +4768,10 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>544</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>545</v>
       </c>
       <c r="C120" s="7" t="s">
@@ -4766,10 +4782,10 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>548</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>549</v>
       </c>
       <c r="C121" s="7" t="s">
@@ -4780,10 +4796,10 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>552</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>553</v>
       </c>
       <c r="C122" s="7" t="s">
@@ -4794,10 +4810,10 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>557</v>
       </c>
       <c r="C123" s="7" t="s">
@@ -4808,10 +4824,10 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>560</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>561</v>
       </c>
       <c r="C124" s="7" t="s">
@@ -4822,10 +4838,10 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>564</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>565</v>
       </c>
       <c r="C125" s="7" t="s">
@@ -4836,10 +4852,10 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>568</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>569</v>
       </c>
       <c r="C126" s="7" t="s">
@@ -4850,10 +4866,10 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>572</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>573</v>
       </c>
       <c r="C127" s="7" t="s">
@@ -4864,10 +4880,10 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>576</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>577</v>
       </c>
       <c r="C128" s="7" t="s">
@@ -4878,10 +4894,10 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>580</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>581</v>
       </c>
       <c r="C129" s="7" t="s">
@@ -4892,10 +4908,10 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>584</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>585</v>
       </c>
       <c r="C130" s="7" t="s">
@@ -4906,10 +4922,10 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>588</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>589</v>
       </c>
       <c r="C131" s="7" t="s">
@@ -4920,10 +4936,10 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>592</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>593</v>
       </c>
       <c r="C132" s="7" t="s">
@@ -4934,10 +4950,10 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>596</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>597</v>
       </c>
       <c r="C133" s="7" t="s">
@@ -4948,10 +4964,10 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>600</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>601</v>
       </c>
       <c r="C134" s="7" t="s">
@@ -4962,10 +4978,10 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>604</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>605</v>
       </c>
       <c r="C135" s="7" t="s">
@@ -4976,10 +4992,10 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>608</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>609</v>
       </c>
       <c r="C136" s="7" t="s">
@@ -4990,10 +5006,10 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>612</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>613</v>
       </c>
       <c r="C137" s="7" t="s">
@@ -5004,10 +5020,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>616</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>617</v>
       </c>
       <c r="C138" s="7" t="s">
@@ -5018,10 +5034,10 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>620</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>621</v>
       </c>
       <c r="C139" s="7" t="s">
@@ -5032,10 +5048,10 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>624</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>625</v>
       </c>
       <c r="C140" s="7" t="s">
@@ -5046,10 +5062,10 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>628</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>629</v>
       </c>
       <c r="C141" s="7" t="s">
@@ -5060,10 +5076,10 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>632</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>633</v>
       </c>
       <c r="C142" s="7" t="s">
@@ -5074,10 +5090,10 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>636</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>637</v>
       </c>
       <c r="C143" s="7" t="s">
@@ -5088,10 +5104,10 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>640</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>641</v>
       </c>
       <c r="C144" s="7" t="s">
@@ -5102,10 +5118,10 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>644</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>645</v>
       </c>
       <c r="C145" s="7" t="s">
@@ -5116,10 +5132,10 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>648</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>649</v>
       </c>
       <c r="C146" s="7" t="s">
@@ -5130,10 +5146,10 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>652</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>653</v>
       </c>
       <c r="C147" s="7" t="s">
@@ -5144,10 +5160,10 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>656</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>657</v>
       </c>
       <c r="C148" s="7" t="s">
@@ -5158,10 +5174,10 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>660</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>661</v>
       </c>
       <c r="C149" s="7" t="s">
@@ -5172,10 +5188,10 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>664</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>665</v>
       </c>
       <c r="C150" s="7" t="s">
@@ -5186,10 +5202,10 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>668</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>669</v>
       </c>
       <c r="C151" s="7" t="s">
@@ -5200,10 +5216,10 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>672</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>673</v>
       </c>
       <c r="C152" s="7" t="s">
@@ -5214,7 +5230,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>676</v>
       </c>
       <c r="C153" s="7" t="s">
@@ -5225,7 +5241,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>679</v>
       </c>
       <c r="C154" s="7" t="s">
@@ -5236,7 +5252,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>682</v>
       </c>
       <c r="C155" s="7" t="s">
@@ -5247,7 +5263,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>685</v>
       </c>
       <c r="C156" s="7" t="s">
@@ -5258,7 +5274,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>688</v>
       </c>
       <c r="C157" s="7" t="s">
@@ -5269,7 +5285,7 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>691</v>
       </c>
       <c r="C158" s="7" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="758">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2273,6 +2273,24 @@
   </si>
   <si>
     <t>Taffy49</t>
+  </si>
+  <si>
+    <t>Charlie75</t>
+  </si>
+  <si>
+    <t>Milo52</t>
+  </si>
+  <si>
+    <t>Taffy50</t>
+  </si>
+  <si>
+    <t>Cutie39</t>
+  </si>
+  <si>
+    <t>Cinder39</t>
+  </si>
+  <si>
+    <t>pony32</t>
   </si>
 </sst>
 </file>
@@ -2334,7 +2352,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2345,6 +2363,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -2710,10 +2734,10 @@
       <c r="B2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="15" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -2724,13 +2748,13 @@
       <c r="A3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="16" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -2738,7 +2762,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2755,7 +2779,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="764">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2291,6 +2291,24 @@
   </si>
   <si>
     <t>pony32</t>
+  </si>
+  <si>
+    <t>Charlie76</t>
+  </si>
+  <si>
+    <t>Milo53</t>
+  </si>
+  <si>
+    <t>Taffy51</t>
+  </si>
+  <si>
+    <t>Cutie40</t>
+  </si>
+  <si>
+    <t>Cinder40</t>
+  </si>
+  <si>
+    <t>fury25</t>
   </si>
 </sst>
 </file>
@@ -2352,7 +2370,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2363,6 +2381,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -2740,7 +2766,7 @@
       <c r="D2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="22" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2757,7 +2783,7 @@
       <c r="D3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="23" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2765,16 +2791,16 @@
       <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="24" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2796,7 +2822,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2813,7 +2839,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -3066,7 +3092,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>63</v>
+        <v>762</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>63</v>
@@ -3328,7 +3354,7 @@
       <c r="B15" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="21" t="s">
         <v>126</v>
       </c>
       <c r="D15" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13590" windowHeight="4800"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="2810" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,12 @@
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <oleSize ref="A28:G34"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="743">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -49,108 +49,45 @@
     <t>Vet_Fauna</t>
   </si>
   <si>
-    <t>7PVMUV</t>
-  </si>
-  <si>
-    <t>RYCXKM</t>
-  </si>
-  <si>
-    <t>Y6G4FM</t>
-  </si>
-  <si>
     <t>CYGKE6</t>
   </si>
   <si>
     <t>NA6V7C</t>
   </si>
   <si>
-    <t>PATJTJ</t>
-  </si>
-  <si>
     <t>V63CMY</t>
   </si>
   <si>
-    <t>VJYGJP</t>
-  </si>
-  <si>
     <t>MPYAKP</t>
   </si>
   <si>
     <t>XD7DT3</t>
   </si>
   <si>
-    <t>NDCUX3</t>
-  </si>
-  <si>
     <t>394JV9</t>
   </si>
   <si>
     <t>EV6UEC</t>
   </si>
   <si>
-    <t>FK4JHP</t>
-  </si>
-  <si>
     <t>KAR9NK</t>
   </si>
   <si>
     <t>6GAFRG</t>
   </si>
   <si>
-    <t>EECV7H</t>
-  </si>
-  <si>
     <t>FEMHMK</t>
   </si>
   <si>
     <t>X6RDRC</t>
   </si>
   <si>
-    <t>HRFKDJ</t>
-  </si>
-  <si>
-    <t>RRDJNJ</t>
-  </si>
-  <si>
     <t>NNTHRC</t>
   </si>
   <si>
-    <t>HANTAF</t>
-  </si>
-  <si>
-    <t>UCXJPU</t>
-  </si>
-  <si>
-    <t>XEC9NE</t>
-  </si>
-  <si>
-    <t>6MT3TH</t>
-  </si>
-  <si>
-    <t>UKPPVN</t>
-  </si>
-  <si>
-    <t>AUTJHD</t>
-  </si>
-  <si>
     <t>7H6YMR</t>
   </si>
   <si>
-    <t>EAUVNA</t>
-  </si>
-  <si>
-    <t>XACPDY</t>
-  </si>
-  <si>
-    <t>EXRTGT</t>
-  </si>
-  <si>
-    <t>F9JDEF</t>
-  </si>
-  <si>
-    <t>CADMX6</t>
-  </si>
-  <si>
     <t>H4NC3U</t>
   </si>
   <si>
@@ -2266,56 +2203,55 @@
     <t>Nexra</t>
   </si>
   <si>
-    <t>Charlie74</t>
-  </si>
-  <si>
-    <t>Milo51</t>
-  </si>
-  <si>
-    <t>Taffy49</t>
-  </si>
-  <si>
-    <t>Charlie75</t>
-  </si>
-  <si>
-    <t>Milo52</t>
-  </si>
-  <si>
-    <t>Taffy50</t>
-  </si>
-  <si>
-    <t>Cutie39</t>
-  </si>
-  <si>
-    <t>Cinder39</t>
-  </si>
-  <si>
-    <t>pony32</t>
-  </si>
-  <si>
-    <t>Charlie76</t>
-  </si>
-  <si>
-    <t>Milo53</t>
-  </si>
-  <si>
-    <t>Taffy51</t>
-  </si>
-  <si>
-    <t>Cutie40</t>
-  </si>
-  <si>
-    <t>Cinder40</t>
-  </si>
-  <si>
-    <t>fury25</t>
+    <t>GVVFEP</t>
+  </si>
+  <si>
+    <t>FUTHNN</t>
+  </si>
+  <si>
+    <t>XKTDYU</t>
+  </si>
+  <si>
+    <t>J7PTRT</t>
+  </si>
+  <si>
+    <t>FAA9TM</t>
+  </si>
+  <si>
+    <t>HNECET</t>
+  </si>
+  <si>
+    <t>DCHJFC</t>
+  </si>
+  <si>
+    <t>GGYTUT</t>
+  </si>
+  <si>
+    <t>E47DUV</t>
+  </si>
+  <si>
+    <t>E4NC6K</t>
+  </si>
+  <si>
+    <t>PDNXE7</t>
+  </si>
+  <si>
+    <t>VGCJEJ</t>
+  </si>
+  <si>
+    <t>KRRUUJ</t>
+  </si>
+  <si>
+    <t>CKUGMJ</t>
+  </si>
+  <si>
+    <t>FENAMV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2370,7 +2306,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2381,23 +2317,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2704,21 +2624,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
-    <col min="12" max="16384" style="1" width="8.7265625"/>
+    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2754,172 +2674,149 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="9" t="s">
+      <c r="A2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>39</v>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="A3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>737</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" t="s">
+        <v>729</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>41</v>
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>738</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>35</v>
+      <c r="A5" t="s">
+        <v>730</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>739</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>731</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>734</v>
+      </c>
+      <c r="D6" t="s">
+        <v>740</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>732</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>735</v>
+      </c>
+      <c r="D7" t="s">
+        <v>741</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>733</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>736</v>
+      </c>
+      <c r="D8" t="s">
+        <v>742</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1" t="s">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E12" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E13" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E14" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E15" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E16" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E17" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35"/>
@@ -3037,86 +2934,83 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.453125"/>
-    <col min="3" max="3" customWidth="true" width="35.6328125"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.7265625"/>
-    <col min="6" max="6" customWidth="true" width="32.1796875"/>
-    <col min="7" max="7" customWidth="true" width="33.6328125"/>
-    <col min="8" max="8" customWidth="true" width="31.26953125"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.7265625" customWidth="1"/>
+    <col min="6" max="6" width="32.1796875" customWidth="1"/>
+    <col min="7" max="7" width="33.6328125" customWidth="1"/>
+    <col min="8" max="8" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>58</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>59</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>62</v>
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>63</v>
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>762</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>63</v>
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>63</v>
+      <c r="A4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D5" t="s" s="0">
-        <v>63</v>
+      <c r="D5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D6" t="s" s="0">
-        <v>63</v>
+      <c r="D6" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3130,2470 +3024,2470 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984375"/>
-    <col min="2" max="2" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" width="17.36328125"/>
-    <col min="4" max="5" customWidth="true" width="17.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.36328125"/>
-    <col min="8" max="8" customWidth="true" width="17.1796875"/>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" customWidth="1"/>
+    <col min="4" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
         <v>64</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D1" t="s" s="0">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>67</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="B6" t="s">
         <v>68</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="C6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="D6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H1" t="s" s="0">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="B7" t="s">
         <v>72</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="6" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="B8" t="s">
         <v>76</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="6" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
+      <c r="B9" t="s">
         <v>80</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="C9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="6" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
+      <c r="B10" t="s">
         <v>84</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="C10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="6" t="s">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
+      <c r="B11" t="s">
         <v>88</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="C11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D11" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="6" t="s">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
+      <c r="B12" t="s">
         <v>92</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="C12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D12" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="6" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="0">
+      <c r="B13" t="s">
         <v>96</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="C13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D13" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="6" t="s">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s" s="0">
+      <c r="B14" t="s">
         <v>100</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="C14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D14" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="6" t="s">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s" s="0">
+      <c r="B15" t="s">
         <v>104</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="C15" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D15" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="6" t="s">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s" s="0">
+      <c r="B16" t="s">
         <v>108</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="C16" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D16" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="6" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s" s="0">
+      <c r="B17" t="s">
         <v>112</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="C17" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D17" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="6" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s" s="0">
+      <c r="B18" t="s">
         <v>116</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="C18" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D18" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="6" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s" s="0">
+      <c r="B19" t="s">
         <v>120</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="C19" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D19" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="6" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s" s="0">
+      <c r="B20" t="s">
         <v>124</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="C20" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="D20" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="6" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s" s="0">
+      <c r="B21" t="s">
         <v>128</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="C21" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D16" s="6" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s" s="0">
+      <c r="B22" t="s">
         <v>132</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="C22" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="6" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s" s="0">
+      <c r="B23" t="s">
         <v>136</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="C23" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D23" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="6" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s" s="0">
+      <c r="B24" t="s">
         <v>140</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="C24" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="6" t="s">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s" s="0">
+      <c r="B25" t="s">
         <v>144</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="C25" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="6" t="s">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s" s="0">
+      <c r="B26" t="s">
         <v>148</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="C26" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="6" t="s">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s" s="0">
+      <c r="B27" t="s">
         <v>152</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="C27" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="6" t="s">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s" s="0">
+      <c r="B28" t="s">
         <v>156</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="C28" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="6" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s" s="0">
+      <c r="B29" t="s">
         <v>160</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="C29" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="6" t="s">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s" s="0">
+      <c r="B30" t="s">
         <v>164</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="C30" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="D30" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="6" t="s">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s" s="0">
+      <c r="B31" t="s">
         <v>168</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="C31" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D31" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D26" s="6" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s" s="0">
+      <c r="B32" t="s">
         <v>172</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="C32" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="D32" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D27" s="6" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s" s="0">
+      <c r="B33" t="s">
         <v>176</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="C33" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="6" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s" s="0">
+      <c r="B34" t="s">
         <v>180</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="C34" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="6" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s" s="0">
+      <c r="B35" t="s">
         <v>184</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="C35" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D35" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D30" s="6" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s" s="0">
+      <c r="B36" t="s">
         <v>188</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="C36" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D36" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="6" t="s">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s" s="0">
+      <c r="B37" t="s">
         <v>192</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="C37" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D37" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D32" s="6" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s" s="0">
+      <c r="B38" t="s">
         <v>196</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="C38" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D38" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D33" s="6" t="s">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s" s="0">
+      <c r="B39" t="s">
         <v>200</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="C39" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="D39" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D34" s="6" t="s">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s" s="0">
+      <c r="B40" t="s">
         <v>204</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="C40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D40" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D35" s="6" t="s">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s" s="0">
+      <c r="B41" t="s">
         <v>208</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="C41" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="D41" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D36" s="6" t="s">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s" s="0">
+      <c r="B42" t="s">
         <v>212</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="C42" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="D42" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D37" s="6" t="s">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s" s="0">
+      <c r="B43" t="s">
         <v>216</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="C43" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="D43" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D38" s="6" t="s">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s" s="0">
+      <c r="B44" t="s">
         <v>220</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="C44" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="D44" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D39" s="6" t="s">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s" s="0">
+      <c r="B45" t="s">
         <v>224</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="C45" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="D45" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D40" s="6" t="s">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s" s="0">
+      <c r="B46" t="s">
         <v>228</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="C46" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="D46" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D41" s="6" t="s">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s" s="0">
+      <c r="B47" t="s">
         <v>232</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="C47" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="D47" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D42" s="6" t="s">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s" s="0">
+      <c r="B48" t="s">
         <v>236</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="C48" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="D48" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="D43" s="6" t="s">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s" s="0">
+      <c r="B49" t="s">
         <v>240</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="C49" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="D49" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D44" s="6" t="s">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s" s="0">
+      <c r="B50" t="s">
         <v>244</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="C50" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="D50" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D45" s="6" t="s">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s" s="0">
+      <c r="B51" t="s">
         <v>248</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="C51" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="D51" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D46" s="6" t="s">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s" s="0">
+      <c r="B52" t="s">
         <v>252</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="C52" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="D52" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D47" s="6" t="s">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s" s="0">
+      <c r="B53" t="s">
         <v>256</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="C53" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="D53" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D48" s="6" t="s">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s" s="0">
+      <c r="B54" t="s">
         <v>260</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="C54" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="D54" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D49" s="6" t="s">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s" s="0">
+      <c r="B55" t="s">
         <v>264</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="C55" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="D55" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="D50" s="6" t="s">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s" s="0">
+      <c r="B56" t="s">
         <v>268</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="C56" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="D56" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D51" s="6" t="s">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s" s="0">
+      <c r="B57" t="s">
         <v>272</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="C57" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="D57" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D52" s="6" t="s">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s" s="0">
+      <c r="B58" t="s">
         <v>276</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="C58" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="D58" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D53" s="6" t="s">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s" s="0">
+      <c r="B59" t="s">
         <v>280</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="C59" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="D59" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="D54" s="6" t="s">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s" s="0">
+      <c r="B60" t="s">
         <v>284</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="C60" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="D60" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D55" s="6" t="s">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s" s="0">
+      <c r="B61" t="s">
         <v>288</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="C61" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="D61" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="D56" s="6" t="s">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s" s="0">
+      <c r="B62" t="s">
         <v>292</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="C62" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="D62" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="D57" s="6" t="s">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s" s="0">
+      <c r="B63" t="s">
         <v>296</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="C63" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="D63" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="D58" s="6" t="s">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s" s="0">
+      <c r="B64" t="s">
         <v>300</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="C64" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="D64" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="D59" s="6" t="s">
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s" s="0">
+      <c r="B65" t="s">
         <v>304</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="C65" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="D65" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="D60" s="6" t="s">
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s" s="0">
+      <c r="B66" t="s">
         <v>308</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="C66" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="D66" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D61" s="6" t="s">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s" s="0">
+      <c r="B67" t="s">
         <v>312</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="C67" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="D67" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="D62" s="6" t="s">
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s" s="0">
+      <c r="B68" t="s">
         <v>316</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="C68" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="D68" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="D63" s="6" t="s">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s" s="0">
+      <c r="B69" t="s">
         <v>320</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="C69" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="D69" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="D64" s="6" t="s">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s" s="0">
+      <c r="B70" t="s">
         <v>324</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="C70" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="D70" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="D65" s="6" t="s">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s" s="0">
+      <c r="B71" t="s">
         <v>328</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="C71" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="D71" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="D66" s="6" t="s">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s" s="0">
+      <c r="B72" t="s">
         <v>332</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="C72" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="D72" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D67" s="6" t="s">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s" s="0">
+      <c r="B73" t="s">
         <v>336</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="C73" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="D73" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D68" s="6" t="s">
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s" s="0">
+      <c r="B74" t="s">
         <v>340</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="C74" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="D74" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="D69" s="6" t="s">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s" s="0">
+      <c r="B75" t="s">
         <v>344</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="C75" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="D75" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D70" s="6" t="s">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s" s="0">
+      <c r="B76" t="s">
         <v>348</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="C76" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="D76" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="D71" s="6" t="s">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s" s="0">
+      <c r="B77" t="s">
         <v>352</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="C77" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="D77" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="D72" s="6" t="s">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s" s="0">
+      <c r="B78" t="s">
         <v>356</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="C78" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="D78" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="D73" s="6" t="s">
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s" s="0">
+      <c r="B79" t="s">
         <v>360</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="C79" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="D79" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="D74" s="6" t="s">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s" s="0">
+      <c r="B80" t="s">
         <v>364</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="C80" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="D80" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="D75" s="6" t="s">
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s" s="0">
+      <c r="B81" t="s">
         <v>368</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="C81" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="D81" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="D76" s="6" t="s">
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s" s="0">
+      <c r="B82" t="s">
         <v>372</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="C82" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="D82" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="D77" s="6" t="s">
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s" s="0">
+      <c r="B83" t="s">
         <v>376</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="C83" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="D83" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="D78" s="6" t="s">
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s" s="0">
+      <c r="B84" t="s">
         <v>380</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="C84" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="D84" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="D79" s="6" t="s">
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s" s="0">
+      <c r="B85" t="s">
         <v>384</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="C85" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="D85" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="D80" s="6" t="s">
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s" s="0">
+      <c r="B86" t="s">
         <v>388</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="C86" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="D86" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="D81" s="6" t="s">
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s" s="0">
+      <c r="B87" t="s">
         <v>392</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="C87" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="D87" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="D82" s="6" t="s">
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s" s="0">
+      <c r="B88" t="s">
         <v>396</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="C88" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="D88" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="D83" s="6" t="s">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s" s="0">
+      <c r="B89" t="s">
         <v>400</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="C89" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="D89" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="D84" s="6" t="s">
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s" s="0">
+      <c r="B90" t="s">
         <v>404</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="C90" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="D90" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="D85" s="6" t="s">
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s" s="0">
+      <c r="B91" t="s">
         <v>408</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="C91" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="D91" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="D86" s="6" t="s">
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s" s="0">
+      <c r="B92" t="s">
         <v>412</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="C92" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="D92" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="D87" s="6" t="s">
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s" s="0">
+      <c r="B93" t="s">
         <v>416</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="C93" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="D93" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="D88" s="6" t="s">
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s" s="0">
+      <c r="B94" t="s">
         <v>420</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="C94" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="D94" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="D89" s="6" t="s">
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s" s="0">
+      <c r="B95" t="s">
         <v>424</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="C95" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="D95" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="D90" s="6" t="s">
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s" s="0">
+      <c r="B96" t="s">
         <v>428</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="C96" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="D96" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="D91" s="6" t="s">
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s" s="0">
+      <c r="B97" t="s">
         <v>432</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="C97" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="D97" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="D92" s="6" t="s">
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s" s="0">
+      <c r="B98" t="s">
         <v>436</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="C98" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="D98" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="D93" s="6" t="s">
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s" s="0">
+      <c r="B99" t="s">
         <v>440</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="C99" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="D99" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="D94" s="6" t="s">
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s" s="0">
+      <c r="B100" t="s">
         <v>444</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="C100" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="D100" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="D95" s="6" t="s">
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s" s="0">
+      <c r="B101" t="s">
         <v>448</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="C101" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="D101" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="D96" s="6" t="s">
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s" s="0">
+      <c r="B102" t="s">
         <v>452</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="C102" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="D102" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="D97" s="6" t="s">
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s" s="0">
+      <c r="B103" t="s">
         <v>456</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="C103" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="D103" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="D98" s="6" t="s">
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s" s="0">
+      <c r="B104" t="s">
         <v>460</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="C104" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="D104" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="D99" s="6" t="s">
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s" s="0">
+      <c r="B105" t="s">
         <v>464</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="C105" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="D105" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="D100" s="6" t="s">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s" s="0">
+      <c r="B106" t="s">
         <v>468</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="C106" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="D106" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="D101" s="6" t="s">
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s" s="0">
+      <c r="B107" t="s">
         <v>472</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="C107" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="D107" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D102" s="6" t="s">
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s" s="0">
+      <c r="B108" t="s">
         <v>476</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="C108" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="D108" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="D103" s="6" t="s">
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s" s="0">
+      <c r="B109" t="s">
         <v>480</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="C109" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="D109" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="D104" s="6" t="s">
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s" s="0">
+      <c r="B110" t="s">
         <v>484</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="C110" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="C105" s="7" t="s">
+      <c r="D110" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="D105" s="6" t="s">
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s" s="0">
+      <c r="B111" t="s">
         <v>488</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="C111" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="D111" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="D106" s="6" t="s">
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s" s="0">
+      <c r="B112" t="s">
         <v>492</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="C112" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="D112" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="D107" s="6" t="s">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s" s="0">
+      <c r="B113" t="s">
         <v>496</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="C113" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="D113" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="D108" s="6" t="s">
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s" s="0">
+      <c r="B114" t="s">
         <v>500</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="C114" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="C109" s="7" t="s">
+      <c r="D114" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="D109" s="6" t="s">
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s" s="0">
+      <c r="B115" t="s">
         <v>504</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="C115" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="D115" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="D110" s="6" t="s">
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s" s="0">
+      <c r="B116" t="s">
         <v>508</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="C116" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="D116" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="D111" s="6" t="s">
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s" s="0">
+      <c r="B117" t="s">
         <v>512</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="C117" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="D117" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="D112" s="6" t="s">
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s" s="0">
+      <c r="B118" t="s">
         <v>516</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="C118" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="D118" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="D113" s="6" t="s">
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s" s="0">
+      <c r="B119" t="s">
         <v>520</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="C119" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="D119" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="D114" s="6" t="s">
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s" s="0">
+      <c r="B120" t="s">
         <v>524</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="C120" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="D120" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="D115" s="6" t="s">
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s" s="0">
+      <c r="B121" t="s">
         <v>528</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="C121" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="D121" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="D116" s="6" t="s">
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s" s="0">
+      <c r="B122" t="s">
         <v>532</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="C122" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="D122" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="D117" s="6" t="s">
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s" s="0">
+      <c r="B123" t="s">
         <v>536</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="C123" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="D123" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="D118" s="6" t="s">
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s" s="0">
+      <c r="B124" t="s">
         <v>540</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="C124" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="D124" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="D119" s="6" t="s">
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s" s="0">
+      <c r="B125" t="s">
         <v>544</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="C125" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="C120" s="7" t="s">
+      <c r="D125" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="D120" s="6" t="s">
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s" s="0">
+      <c r="B126" t="s">
         <v>548</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="C126" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="C121" s="7" t="s">
+      <c r="D126" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="D121" s="6" t="s">
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s" s="0">
+      <c r="B127" t="s">
         <v>552</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="C127" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="D127" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="D122" s="6" t="s">
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s" s="0">
+      <c r="B128" t="s">
         <v>556</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="C128" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="C123" s="7" t="s">
+      <c r="D128" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="D123" s="6" t="s">
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s" s="0">
+      <c r="B129" t="s">
         <v>560</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="C129" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="D129" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="D124" s="6" t="s">
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s" s="0">
+      <c r="B130" t="s">
         <v>564</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="C130" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="D130" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="D125" s="6" t="s">
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s" s="0">
+      <c r="B131" t="s">
         <v>568</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="C131" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="D131" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="D126" s="6" t="s">
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s" s="0">
+      <c r="B132" t="s">
         <v>572</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="C132" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="D132" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="D127" s="6" t="s">
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s" s="0">
+      <c r="B133" t="s">
         <v>576</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="C133" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="D133" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="D128" s="6" t="s">
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s" s="0">
+      <c r="B134" t="s">
         <v>580</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="C134" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="D134" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="D129" s="6" t="s">
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s" s="0">
+      <c r="B135" t="s">
         <v>584</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="C135" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="D135" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="D130" s="6" t="s">
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s" s="0">
+      <c r="B136" t="s">
         <v>588</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="C136" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="D136" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="D131" s="6" t="s">
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s" s="0">
+      <c r="B137" t="s">
         <v>592</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="C137" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="D137" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="D132" s="6" t="s">
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s" s="0">
+      <c r="B138" t="s">
         <v>596</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="C138" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="D138" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="D133" s="6" t="s">
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s" s="0">
+      <c r="B139" t="s">
         <v>600</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="C139" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="C134" s="7" t="s">
+      <c r="D139" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="D134" s="6" t="s">
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s" s="0">
+      <c r="B140" t="s">
         <v>604</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="C140" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="C135" s="7" t="s">
+      <c r="D140" s="6" t="s">
         <v>606</v>
       </c>
-      <c r="D135" s="6" t="s">
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s" s="0">
+      <c r="B141" t="s">
         <v>608</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="C141" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="C136" s="7" t="s">
+      <c r="D141" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="D136" s="6" t="s">
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s" s="0">
+      <c r="B142" t="s">
         <v>612</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="C142" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="C137" s="7" t="s">
+      <c r="D142" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="D137" s="6" t="s">
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s" s="0">
+      <c r="B143" t="s">
         <v>616</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="C143" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="C138" s="7" t="s">
+      <c r="D143" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="D138" s="6" t="s">
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s" s="0">
+      <c r="B144" t="s">
         <v>620</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="C144" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="C139" s="7" t="s">
+      <c r="D144" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="D139" s="6" t="s">
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s" s="0">
+      <c r="B145" t="s">
         <v>624</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="C145" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="D145" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="D140" s="6" t="s">
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s" s="0">
+      <c r="B146" t="s">
         <v>628</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="C146" s="7" t="s">
         <v>629</v>
       </c>
-      <c r="C141" s="7" t="s">
+      <c r="D146" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="D141" s="6" t="s">
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s" s="0">
+      <c r="B147" t="s">
         <v>632</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="C147" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="D147" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="D142" s="6" t="s">
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s" s="0">
+      <c r="B148" t="s">
         <v>636</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="C148" s="7" t="s">
         <v>637</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="D148" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="D143" s="6" t="s">
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s" s="0">
+      <c r="B149" t="s">
         <v>640</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="C149" s="7" t="s">
         <v>641</v>
       </c>
-      <c r="C144" s="7" t="s">
+      <c r="D149" s="6" t="s">
         <v>642</v>
       </c>
-      <c r="D144" s="6" t="s">
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s" s="0">
+      <c r="B150" t="s">
         <v>644</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="C150" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="D150" s="6" t="s">
         <v>646</v>
       </c>
-      <c r="D145" s="6" t="s">
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s" s="0">
+      <c r="B151" t="s">
         <v>648</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="C151" s="7" t="s">
         <v>649</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="D151" s="6" t="s">
         <v>650</v>
       </c>
-      <c r="D146" s="6" t="s">
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s" s="0">
+      <c r="B152" t="s">
         <v>652</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="C152" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="D152" s="6" t="s">
         <v>654</v>
       </c>
-      <c r="D147" s="6" t="s">
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s" s="0">
+      <c r="C153" s="7" t="s">
         <v>656</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="D153" s="6" t="s">
         <v>657</v>
       </c>
-      <c r="C148" s="7" t="s">
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B154" t="s">
         <v>658</v>
       </c>
-      <c r="D148" s="6" t="s">
+      <c r="C154" s="7" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s" s="0">
+      <c r="D154" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="B149" t="s" s="0">
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
         <v>661</v>
       </c>
-      <c r="C149" s="7" t="s">
+      <c r="C155" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="D149" s="6" t="s">
+      <c r="D155" s="6" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s" s="0">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
         <v>664</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="C156" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="C150" s="7" t="s">
+      <c r="D156" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="D150" s="6" t="s">
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B157" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s" s="0">
+      <c r="C157" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="D157" s="6" t="s">
         <v>669</v>
       </c>
-      <c r="C151" s="7" t="s">
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
         <v>670</v>
       </c>
-      <c r="D151" s="6" t="s">
+      <c r="C158" s="7" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s" s="0">
+      <c r="D158" s="6" t="s">
         <v>672</v>
-      </c>
-      <c r="B152" t="s" s="0">
-        <v>673</v>
-      </c>
-      <c r="C152" s="7" t="s">
-        <v>674</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s" s="0">
-        <v>676</v>
-      </c>
-      <c r="C153" s="7" t="s">
-        <v>677</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s" s="0">
-        <v>679</v>
-      </c>
-      <c r="C154" s="7" t="s">
-        <v>680</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s" s="0">
-        <v>682</v>
-      </c>
-      <c r="C155" s="7" t="s">
-        <v>683</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s" s="0">
-        <v>685</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>686</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s" s="0">
-        <v>688</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>689</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s" s="0">
-        <v>691</v>
-      </c>
-      <c r="C158" s="7" t="s">
-        <v>692</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C159" s="7" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>695</v>
+        <v>674</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C160" s="7" t="s">
-        <v>696</v>
+        <v>675</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
     </row>
     <row r="161" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C161" s="7" t="s">
-        <v>698</v>
+        <v>677</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>699</v>
+        <v>678</v>
       </c>
     </row>
     <row r="162" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C162" s="7" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>701</v>
+        <v>680</v>
       </c>
     </row>
     <row r="163" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C163" s="7" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>703</v>
+        <v>682</v>
       </c>
     </row>
     <row r="164" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C164" s="7" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>705</v>
+        <v>684</v>
       </c>
     </row>
     <row r="165" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C165" s="7" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
     </row>
     <row r="166" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C166" s="7" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
     </row>
     <row r="167" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C167" s="7" t="s">
-        <v>710</v>
+        <v>689</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>711</v>
+        <v>690</v>
       </c>
     </row>
     <row r="168" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C168" s="7" t="s">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
     </row>
     <row r="169" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C169" s="7" t="s">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
     </row>
     <row r="170" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C170" s="7" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
     </row>
     <row r="171" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D171" s="6" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
     </row>
     <row r="172" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D172" s="6" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
     </row>
     <row r="173" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D173" s="6" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
     </row>
     <row r="174" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D174" s="6" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
     </row>
     <row r="175" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D175" s="6" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
     </row>
     <row r="176" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D176" s="6" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
     </row>
     <row r="177" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D177" s="6" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
     </row>
     <row r="178" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D178" s="6" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
     </row>
     <row r="179" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D179" s="6" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
     </row>
     <row r="180" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D180" s="6" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
     </row>
     <row r="181" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D181" s="6" t="s">
-        <v>728</v>
+        <v>707</v>
       </c>
     </row>
     <row r="182" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D182" s="6" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
     </row>
     <row r="183" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D183" s="6" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
     </row>
     <row r="184" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D184" s="6" t="s">
-        <v>731</v>
+        <v>710</v>
       </c>
     </row>
     <row r="185" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D185" s="6" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
     </row>
     <row r="186" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D186" s="6" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
     </row>
     <row r="187" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D187" s="6" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
     </row>
     <row r="188" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D188" s="6" t="s">
-        <v>735</v>
+        <v>714</v>
       </c>
     </row>
     <row r="189" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D189" s="6" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
     </row>
     <row r="190" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D190" s="6" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
     </row>
     <row r="191" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D191" s="6" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
     </row>
     <row r="192" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D192" s="6" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
     </row>
     <row r="193" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D193" s="6" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
     </row>
     <row r="194" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D194" s="6" t="s">
-        <v>741</v>
+        <v>720</v>
       </c>
     </row>
     <row r="195" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D195" s="6" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
     </row>
     <row r="196" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D196" s="6" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
     </row>
     <row r="197" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D197" s="6" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
     </row>
     <row r="198" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D198" s="6" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
     </row>
     <row r="199" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D199" s="6" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
     </row>
     <row r="200" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D200" s="6" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
     </row>
     <row r="201" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D201" s="6" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="751">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2246,12 +2246,37 @@
   </si>
   <si>
     <t>FENAMV</t>
+  </si>
+  <si>
+    <t>Charlie77</t>
+  </si>
+  <si>
+    <t>Milo54</t>
+  </si>
+  <si>
+    <t>Taffy52</t>
+  </si>
+  <si>
+    <t>Cutie42</t>
+  </si>
+  <si>
+    <t>Cinder42</t>
+  </si>
+  <si>
+    <t>pony34</t>
+  </si>
+  <si>
+    <t>fury26</t>
+  </si>
+  <si>
+    <t>Sheep27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2306,7 +2331,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2318,6 +2343,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2624,21 +2659,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
+    <col min="12" max="16384" style="1" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2674,24 +2709,24 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="11">
         <v>728</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2700,15 +2735,15 @@
       <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="14">
         <v>737</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>729</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2717,15 +2752,15 @@
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="1">
         <v>738</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>730</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2734,7 +2769,7 @@
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="1">
         <v>739</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -2742,16 +2777,16 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>731</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="1">
         <v>734</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="1">
         <v>740</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -2759,16 +2794,16 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>732</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="1">
         <v>735</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="1">
         <v>741</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -2776,16 +2811,16 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="1">
         <v>733</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="1">
         <v>736</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="1">
         <v>742</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -2934,82 +2969,85 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" customWidth="1"/>
-    <col min="8" max="8" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.453125"/>
+    <col min="3" max="3" customWidth="true" width="35.6328125"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.7265625"/>
+    <col min="6" max="6" customWidth="true" width="32.1796875"/>
+    <col min="7" max="7" customWidth="true" width="33.6328125"/>
+    <col min="8" max="8" customWidth="true" width="31.26953125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>42</v>
       </c>
+      <c r="B4" t="s" s="0">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>42</v>
       </c>
     </row>
@@ -3024,46 +3062,46 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984375"/>
+    <col min="2" max="2" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.36328125"/>
+    <col min="4" max="5" customWidth="true" width="17.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.36328125"/>
+    <col min="8" max="8" customWidth="true" width="17.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3074,10 +3112,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3088,10 +3126,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3102,10 +3140,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3116,10 +3154,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>68</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3130,10 +3168,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3144,10 +3182,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3158,10 +3196,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>80</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3172,10 +3210,10 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3186,10 +3224,10 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>88</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3200,10 +3238,10 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>92</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3214,10 +3252,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>96</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3228,10 +3266,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>100</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3242,10 +3280,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -3256,13 +3294,13 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="15" t="s">
         <v>109</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -3270,10 +3308,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>112</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -3284,10 +3322,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>115</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>116</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -3298,10 +3336,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>120</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -3312,10 +3350,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>124</v>
       </c>
       <c r="C20" s="7" t="s">
@@ -3326,10 +3364,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>128</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -3340,10 +3378,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>132</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -3354,10 +3392,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>136</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3368,10 +3406,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>139</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>140</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -3382,10 +3420,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>144</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -3396,10 +3434,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>148</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -3410,10 +3448,10 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>151</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>152</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -3424,10 +3462,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>156</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -3438,10 +3476,10 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>159</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>160</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -3452,10 +3490,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>164</v>
       </c>
       <c r="C30" s="7" t="s">
@@ -3466,10 +3504,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>167</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>168</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -3480,10 +3518,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>171</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>172</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -3494,10 +3532,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>176</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3508,10 +3546,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>180</v>
       </c>
       <c r="C34" s="7" t="s">
@@ -3522,10 +3560,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>183</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>184</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -3536,10 +3574,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>187</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>188</v>
       </c>
       <c r="C36" s="7" t="s">
@@ -3550,10 +3588,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>191</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>192</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -3564,10 +3602,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>195</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>196</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -3578,10 +3616,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>199</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>200</v>
       </c>
       <c r="C39" s="7" t="s">
@@ -3592,10 +3630,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>203</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>204</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -3606,10 +3644,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>208</v>
       </c>
       <c r="C41" s="7" t="s">
@@ -3620,10 +3658,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>211</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>212</v>
       </c>
       <c r="C42" s="7" t="s">
@@ -3634,10 +3672,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>215</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>216</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -3648,10 +3686,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>219</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>220</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -3662,10 +3700,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>223</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>224</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -3676,10 +3714,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>227</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>228</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -3690,10 +3728,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>231</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>232</v>
       </c>
       <c r="C47" s="7" t="s">
@@ -3704,10 +3742,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>235</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>236</v>
       </c>
       <c r="C48" s="7" t="s">
@@ -3718,10 +3756,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>239</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>240</v>
       </c>
       <c r="C49" s="7" t="s">
@@ -3732,10 +3770,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>243</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>244</v>
       </c>
       <c r="C50" s="7" t="s">
@@ -3746,10 +3784,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>247</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>248</v>
       </c>
       <c r="C51" s="7" t="s">
@@ -3760,10 +3798,10 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>251</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>252</v>
       </c>
       <c r="C52" s="7" t="s">
@@ -3774,10 +3812,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>255</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>256</v>
       </c>
       <c r="C53" s="7" t="s">
@@ -3788,10 +3826,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>259</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>260</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3802,10 +3840,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>263</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>264</v>
       </c>
       <c r="C55" s="7" t="s">
@@ -3816,10 +3854,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>267</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>268</v>
       </c>
       <c r="C56" s="7" t="s">
@@ -3830,10 +3868,10 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>271</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>272</v>
       </c>
       <c r="C57" s="7" t="s">
@@ -3844,10 +3882,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>275</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>276</v>
       </c>
       <c r="C58" s="7" t="s">
@@ -3858,10 +3896,10 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>279</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>280</v>
       </c>
       <c r="C59" s="7" t="s">
@@ -3872,10 +3910,10 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>283</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>284</v>
       </c>
       <c r="C60" s="7" t="s">
@@ -3886,10 +3924,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>287</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>288</v>
       </c>
       <c r="C61" s="7" t="s">
@@ -3900,10 +3938,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>291</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>292</v>
       </c>
       <c r="C62" s="7" t="s">
@@ -3914,10 +3952,10 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>295</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>296</v>
       </c>
       <c r="C63" s="7" t="s">
@@ -3928,10 +3966,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>299</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>300</v>
       </c>
       <c r="C64" s="7" t="s">
@@ -3942,10 +3980,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>303</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>304</v>
       </c>
       <c r="C65" s="7" t="s">
@@ -3956,10 +3994,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>307</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>308</v>
       </c>
       <c r="C66" s="7" t="s">
@@ -3970,10 +4008,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>311</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>312</v>
       </c>
       <c r="C67" s="7" t="s">
@@ -3984,10 +4022,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>315</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>316</v>
       </c>
       <c r="C68" s="7" t="s">
@@ -3998,10 +4036,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>319</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>320</v>
       </c>
       <c r="C69" s="7" t="s">
@@ -4012,10 +4050,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>323</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>324</v>
       </c>
       <c r="C70" s="7" t="s">
@@ -4026,10 +4064,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>327</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>328</v>
       </c>
       <c r="C71" s="7" t="s">
@@ -4040,10 +4078,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>331</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>332</v>
       </c>
       <c r="C72" s="7" t="s">
@@ -4054,10 +4092,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>335</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>336</v>
       </c>
       <c r="C73" s="7" t="s">
@@ -4068,10 +4106,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>339</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>340</v>
       </c>
       <c r="C74" s="7" t="s">
@@ -4082,10 +4120,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>343</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>344</v>
       </c>
       <c r="C75" s="7" t="s">
@@ -4096,10 +4134,10 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>347</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>348</v>
       </c>
       <c r="C76" s="7" t="s">
@@ -4110,10 +4148,10 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>351</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>352</v>
       </c>
       <c r="C77" s="7" t="s">
@@ -4124,10 +4162,10 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>355</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>356</v>
       </c>
       <c r="C78" s="7" t="s">
@@ -4138,10 +4176,10 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>359</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>360</v>
       </c>
       <c r="C79" s="7" t="s">
@@ -4152,10 +4190,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>363</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>364</v>
       </c>
       <c r="C80" s="7" t="s">
@@ -4166,10 +4204,10 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>367</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>368</v>
       </c>
       <c r="C81" s="7" t="s">
@@ -4180,10 +4218,10 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>371</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>372</v>
       </c>
       <c r="C82" s="7" t="s">
@@ -4194,10 +4232,10 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>375</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>376</v>
       </c>
       <c r="C83" s="7" t="s">
@@ -4208,10 +4246,10 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>379</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>380</v>
       </c>
       <c r="C84" s="7" t="s">
@@ -4222,10 +4260,10 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>383</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>384</v>
       </c>
       <c r="C85" s="7" t="s">
@@ -4236,10 +4274,10 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>387</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>388</v>
       </c>
       <c r="C86" s="7" t="s">
@@ -4250,10 +4288,10 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>391</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>392</v>
       </c>
       <c r="C87" s="7" t="s">
@@ -4264,10 +4302,10 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>395</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>396</v>
       </c>
       <c r="C88" s="7" t="s">
@@ -4278,10 +4316,10 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>399</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>400</v>
       </c>
       <c r="C89" s="7" t="s">
@@ -4292,10 +4330,10 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>404</v>
       </c>
       <c r="C90" s="7" t="s">
@@ -4306,10 +4344,10 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>407</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>408</v>
       </c>
       <c r="C91" s="7" t="s">
@@ -4320,10 +4358,10 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>411</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>412</v>
       </c>
       <c r="C92" s="7" t="s">
@@ -4334,10 +4372,10 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>415</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>416</v>
       </c>
       <c r="C93" s="7" t="s">
@@ -4348,10 +4386,10 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>419</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>420</v>
       </c>
       <c r="C94" s="7" t="s">
@@ -4362,10 +4400,10 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>423</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>424</v>
       </c>
       <c r="C95" s="7" t="s">
@@ -4376,10 +4414,10 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>427</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>428</v>
       </c>
       <c r="C96" s="7" t="s">
@@ -4390,10 +4428,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>431</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>432</v>
       </c>
       <c r="C97" s="7" t="s">
@@ -4404,10 +4442,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>435</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>436</v>
       </c>
       <c r="C98" s="7" t="s">
@@ -4418,10 +4456,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>439</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>440</v>
       </c>
       <c r="C99" s="7" t="s">
@@ -4432,10 +4470,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>443</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>444</v>
       </c>
       <c r="C100" s="7" t="s">
@@ -4446,10 +4484,10 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>447</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>448</v>
       </c>
       <c r="C101" s="7" t="s">
@@ -4460,10 +4498,10 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>451</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>452</v>
       </c>
       <c r="C102" s="7" t="s">
@@ -4474,10 +4512,10 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>455</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>456</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4488,10 +4526,10 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>459</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>460</v>
       </c>
       <c r="C104" s="7" t="s">
@@ -4502,10 +4540,10 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>463</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>464</v>
       </c>
       <c r="C105" s="7" t="s">
@@ -4516,10 +4554,10 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>467</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>468</v>
       </c>
       <c r="C106" s="7" t="s">
@@ -4530,10 +4568,10 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>471</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>472</v>
       </c>
       <c r="C107" s="7" t="s">
@@ -4544,10 +4582,10 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>475</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>476</v>
       </c>
       <c r="C108" s="7" t="s">
@@ -4558,10 +4596,10 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>479</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>480</v>
       </c>
       <c r="C109" s="7" t="s">
@@ -4572,10 +4610,10 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>483</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>484</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4586,10 +4624,10 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>487</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>488</v>
       </c>
       <c r="C111" s="7" t="s">
@@ -4600,10 +4638,10 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>491</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>492</v>
       </c>
       <c r="C112" s="7" t="s">
@@ -4614,10 +4652,10 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>495</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>496</v>
       </c>
       <c r="C113" s="7" t="s">
@@ -4628,10 +4666,10 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>499</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>500</v>
       </c>
       <c r="C114" s="7" t="s">
@@ -4642,10 +4680,10 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>503</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>504</v>
       </c>
       <c r="C115" s="7" t="s">
@@ -4656,10 +4694,10 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>507</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>508</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4670,10 +4708,10 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>511</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>512</v>
       </c>
       <c r="C117" s="7" t="s">
@@ -4684,10 +4722,10 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>515</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>516</v>
       </c>
       <c r="C118" s="7" t="s">
@@ -4698,10 +4736,10 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>519</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>520</v>
       </c>
       <c r="C119" s="7" t="s">
@@ -4712,10 +4750,10 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>523</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>524</v>
       </c>
       <c r="C120" s="7" t="s">
@@ -4726,10 +4764,10 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>527</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>528</v>
       </c>
       <c r="C121" s="7" t="s">
@@ -4740,10 +4778,10 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>531</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>532</v>
       </c>
       <c r="C122" s="7" t="s">
@@ -4754,10 +4792,10 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>535</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>536</v>
       </c>
       <c r="C123" s="7" t="s">
@@ -4768,10 +4806,10 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>539</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>540</v>
       </c>
       <c r="C124" s="7" t="s">
@@ -4782,10 +4820,10 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>543</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>544</v>
       </c>
       <c r="C125" s="7" t="s">
@@ -4796,10 +4834,10 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>547</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>548</v>
       </c>
       <c r="C126" s="7" t="s">
@@ -4810,10 +4848,10 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>551</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>552</v>
       </c>
       <c r="C127" s="7" t="s">
@@ -4824,10 +4862,10 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>555</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>556</v>
       </c>
       <c r="C128" s="7" t="s">
@@ -4838,10 +4876,10 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>559</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>560</v>
       </c>
       <c r="C129" s="7" t="s">
@@ -4852,10 +4890,10 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>563</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>564</v>
       </c>
       <c r="C130" s="7" t="s">
@@ -4866,10 +4904,10 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>567</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>568</v>
       </c>
       <c r="C131" s="7" t="s">
@@ -4880,10 +4918,10 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>571</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>572</v>
       </c>
       <c r="C132" s="7" t="s">
@@ -4894,10 +4932,10 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>575</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>576</v>
       </c>
       <c r="C133" s="7" t="s">
@@ -4908,10 +4946,10 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>579</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>580</v>
       </c>
       <c r="C134" s="7" t="s">
@@ -4922,10 +4960,10 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>583</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>584</v>
       </c>
       <c r="C135" s="7" t="s">
@@ -4936,10 +4974,10 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>587</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>588</v>
       </c>
       <c r="C136" s="7" t="s">
@@ -4950,10 +4988,10 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>591</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>592</v>
       </c>
       <c r="C137" s="7" t="s">
@@ -4964,10 +5002,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>595</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>596</v>
       </c>
       <c r="C138" s="7" t="s">
@@ -4978,10 +5016,10 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>599</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>600</v>
       </c>
       <c r="C139" s="7" t="s">
@@ -4992,10 +5030,10 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>603</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>604</v>
       </c>
       <c r="C140" s="7" t="s">
@@ -5006,10 +5044,10 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>607</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>608</v>
       </c>
       <c r="C141" s="7" t="s">
@@ -5020,10 +5058,10 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>611</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>612</v>
       </c>
       <c r="C142" s="7" t="s">
@@ -5034,10 +5072,10 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>615</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>616</v>
       </c>
       <c r="C143" s="7" t="s">
@@ -5048,10 +5086,10 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>619</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>620</v>
       </c>
       <c r="C144" s="7" t="s">
@@ -5062,10 +5100,10 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>623</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>624</v>
       </c>
       <c r="C145" s="7" t="s">
@@ -5076,10 +5114,10 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>627</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>628</v>
       </c>
       <c r="C146" s="7" t="s">
@@ -5090,10 +5128,10 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>631</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>632</v>
       </c>
       <c r="C147" s="7" t="s">
@@ -5104,10 +5142,10 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>635</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>636</v>
       </c>
       <c r="C148" s="7" t="s">
@@ -5118,10 +5156,10 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>639</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>640</v>
       </c>
       <c r="C149" s="7" t="s">
@@ -5132,10 +5170,10 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>643</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>644</v>
       </c>
       <c r="C150" s="7" t="s">
@@ -5146,10 +5184,10 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>647</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>648</v>
       </c>
       <c r="C151" s="7" t="s">
@@ -5160,10 +5198,10 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>651</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>652</v>
       </c>
       <c r="C152" s="7" t="s">
@@ -5174,7 +5212,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>655</v>
       </c>
       <c r="C153" s="7" t="s">
@@ -5185,7 +5223,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>658</v>
       </c>
       <c r="C154" s="7" t="s">
@@ -5196,7 +5234,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>661</v>
       </c>
       <c r="C155" s="7" t="s">
@@ -5207,7 +5245,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>664</v>
       </c>
       <c r="C156" s="7" t="s">
@@ -5218,7 +5256,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>667</v>
       </c>
       <c r="C157" s="7" t="s">
@@ -5229,7 +5267,7 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>670</v>
       </c>
       <c r="C158" s="7" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="2810" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3150" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,12 @@
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A28:G34"/>
+  <oleSize ref="A1:D9"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="743">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2246,37 +2246,12 @@
   </si>
   <si>
     <t>FENAMV</t>
-  </si>
-  <si>
-    <t>Charlie77</t>
-  </si>
-  <si>
-    <t>Milo54</t>
-  </si>
-  <si>
-    <t>Taffy52</t>
-  </si>
-  <si>
-    <t>Cutie42</t>
-  </si>
-  <si>
-    <t>Cinder42</t>
-  </si>
-  <si>
-    <t>pony34</t>
-  </si>
-  <si>
-    <t>fury26</t>
-  </si>
-  <si>
-    <t>Sheep27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2331,28 +2306,27 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2659,21 +2633,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
-    <col min="12" max="16384" style="1" width="8.7265625"/>
+    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2709,24 +2683,24 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="11">
+      <c r="A3" s="10" t="s">
         <v>728</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2735,15 +2709,15 @@
       <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s" s="14">
+      <c r="D3" s="13" t="s">
         <v>737</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="1">
+      <c r="A4" s="1" t="s">
         <v>729</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2752,15 +2726,15 @@
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="D4" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="1">
+      <c r="A5" s="1" t="s">
         <v>730</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2769,7 +2743,7 @@
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s" s="1">
+      <c r="D5" s="1" t="s">
         <v>739</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -2777,16 +2751,16 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="1">
+      <c r="A6" s="1" t="s">
         <v>731</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s" s="1">
+      <c r="C6" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D6" t="s" s="1">
+      <c r="D6" s="1" t="s">
         <v>740</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -2794,16 +2768,16 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="1">
+      <c r="A7" s="1" t="s">
         <v>732</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s" s="1">
+      <c r="C7" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="D7" t="s" s="1">
+      <c r="D7" s="1" t="s">
         <v>741</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -2811,16 +2785,16 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="1">
+      <c r="A8" s="1" t="s">
         <v>733</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s" s="1">
+      <c r="C8" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="D8" t="s" s="1">
+      <c r="D8" s="1" t="s">
         <v>742</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -2969,88 +2943,80 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.453125"/>
-    <col min="3" max="3" customWidth="true" width="35.6328125"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.7265625"/>
-    <col min="6" max="6" customWidth="true" width="32.1796875"/>
-    <col min="7" max="7" customWidth="true" width="33.6328125"/>
-    <col min="8" max="8" customWidth="true" width="31.26953125"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.7265625" customWidth="1"/>
+    <col min="6" max="6" width="32.1796875" customWidth="1"/>
+    <col min="7" max="7" width="33.6328125" customWidth="1"/>
+    <col min="8" max="8" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s" s="0">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="B3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="D3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" t="s" s="0">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
+      <c r="B4" t="s">
         <v>42</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="D4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D5" t="s" s="0">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D6" t="s" s="0">
-        <v>42</v>
-      </c>
-    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3062,2469 +3028,2469 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984375"/>
-    <col min="2" max="2" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" width="17.36328125"/>
-    <col min="4" max="5" customWidth="true" width="17.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.36328125"/>
-    <col min="8" max="8" customWidth="true" width="17.1796875"/>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" customWidth="1"/>
+    <col min="4" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>47</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>48</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>49</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>51</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>63</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>67</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
+      <c r="A7" t="s">
         <v>71</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="0">
+      <c r="A8" t="s">
         <v>75</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s" s="0">
+      <c r="A9" t="s">
         <v>79</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>80</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s" s="0">
+      <c r="A10" t="s">
         <v>83</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s" s="0">
+      <c r="A11" t="s">
         <v>87</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>88</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s" s="0">
+      <c r="A12" t="s">
         <v>91</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>92</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s" s="0">
+      <c r="A13" t="s">
         <v>95</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>96</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s" s="0">
+      <c r="A14" t="s">
         <v>99</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>100</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s" s="0">
+      <c r="A15" t="s">
         <v>103</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s" s="0">
+      <c r="A16" t="s">
         <v>107</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s" s="0">
+      <c r="A17" t="s">
         <v>111</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s" s="0">
+      <c r="A18" t="s">
         <v>115</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s" s="0">
+      <c r="A19" t="s">
         <v>119</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s" s="0">
+      <c r="A20" t="s">
         <v>123</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s" s="0">
+      <c r="A21" t="s">
         <v>127</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B21" t="s">
         <v>128</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s" s="0">
+      <c r="A22" t="s">
         <v>131</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="B22" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s" s="0">
+      <c r="A23" t="s">
         <v>135</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>136</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s" s="0">
+      <c r="A24" t="s">
         <v>139</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>140</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s" s="0">
+      <c r="A25" t="s">
         <v>143</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B25" t="s">
         <v>144</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s" s="0">
+      <c r="A26" t="s">
         <v>147</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>148</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s" s="0">
+      <c r="A27" t="s">
         <v>151</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>152</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s" s="0">
+      <c r="A28" t="s">
         <v>155</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s" s="0">
+      <c r="A29" t="s">
         <v>159</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="B29" t="s">
         <v>160</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s" s="0">
+      <c r="A30" t="s">
         <v>163</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="B30" t="s">
         <v>164</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s" s="0">
+      <c r="A31" t="s">
         <v>167</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>168</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="5" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s" s="0">
+      <c r="A32" t="s">
         <v>171</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>172</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s" s="0">
+      <c r="A33" t="s">
         <v>175</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s" s="0">
+      <c r="A34" t="s">
         <v>179</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>180</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s" s="0">
+      <c r="A35" t="s">
         <v>183</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B35" t="s">
         <v>184</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s" s="0">
+      <c r="A36" t="s">
         <v>187</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="B36" t="s">
         <v>188</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="5" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s" s="0">
+      <c r="A37" t="s">
         <v>191</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B37" t="s">
         <v>192</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="5" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s" s="0">
+      <c r="A38" t="s">
         <v>195</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B38" t="s">
         <v>196</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s" s="0">
+      <c r="A39" t="s">
         <v>199</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="B39" t="s">
         <v>200</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="5" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s" s="0">
+      <c r="A40" t="s">
         <v>203</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="B40" t="s">
         <v>204</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="5" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s" s="0">
+      <c r="A41" t="s">
         <v>207</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="B41" t="s">
         <v>208</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="5" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s" s="0">
+      <c r="A42" t="s">
         <v>211</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="B42" t="s">
         <v>212</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s" s="0">
+      <c r="A43" t="s">
         <v>215</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="B43" t="s">
         <v>216</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s" s="0">
+      <c r="A44" t="s">
         <v>219</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B44" t="s">
         <v>220</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s" s="0">
+      <c r="A45" t="s">
         <v>223</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="B45" t="s">
         <v>224</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="5" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s" s="0">
+      <c r="A46" t="s">
         <v>227</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="B46" t="s">
         <v>228</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="5" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s" s="0">
+      <c r="A47" t="s">
         <v>231</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B47" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="5" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s" s="0">
+      <c r="A48" t="s">
         <v>235</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="B48" t="s">
         <v>236</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="5" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s" s="0">
+      <c r="A49" t="s">
         <v>239</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="B49" t="s">
         <v>240</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="5" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s" s="0">
+      <c r="A50" t="s">
         <v>243</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="B50" t="s">
         <v>244</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s" s="0">
+      <c r="A51" t="s">
         <v>247</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="B51" t="s">
         <v>248</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s" s="0">
+      <c r="A52" t="s">
         <v>251</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="B52" t="s">
         <v>252</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="5" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s" s="0">
+      <c r="A53" t="s">
         <v>255</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="B53" t="s">
         <v>256</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="5" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s" s="0">
+      <c r="A54" t="s">
         <v>259</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="B54" t="s">
         <v>260</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="5" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s" s="0">
+      <c r="A55" t="s">
         <v>263</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s">
         <v>264</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="5" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s" s="0">
+      <c r="A56" t="s">
         <v>267</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="B56" t="s">
         <v>268</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="5" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s" s="0">
+      <c r="A57" t="s">
         <v>271</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B57" t="s">
         <v>272</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="5" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s" s="0">
+      <c r="A58" t="s">
         <v>275</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="B58" t="s">
         <v>276</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="5" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s" s="0">
+      <c r="A59" t="s">
         <v>279</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="B59" t="s">
         <v>280</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="5" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s" s="0">
+      <c r="A60" t="s">
         <v>283</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="B60" t="s">
         <v>284</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="5" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s" s="0">
+      <c r="A61" t="s">
         <v>287</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="B61" t="s">
         <v>288</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="5" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s" s="0">
+      <c r="A62" t="s">
         <v>291</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="B62" t="s">
         <v>292</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="5" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s" s="0">
+      <c r="A63" t="s">
         <v>295</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="B63" t="s">
         <v>296</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="5" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s" s="0">
+      <c r="A64" t="s">
         <v>299</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="B64" t="s">
         <v>300</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="5" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s" s="0">
+      <c r="A65" t="s">
         <v>303</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="B65" t="s">
         <v>304</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="5" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s" s="0">
+      <c r="A66" t="s">
         <v>307</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="B66" t="s">
         <v>308</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="5" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s" s="0">
+      <c r="A67" t="s">
         <v>311</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="B67" t="s">
         <v>312</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="5" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s" s="0">
+      <c r="A68" t="s">
         <v>315</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B68" t="s">
         <v>316</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="5" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s" s="0">
+      <c r="A69" t="s">
         <v>319</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B69" t="s">
         <v>320</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="5" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s" s="0">
+      <c r="A70" t="s">
         <v>323</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="B70" t="s">
         <v>324</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="5" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s" s="0">
+      <c r="A71" t="s">
         <v>327</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="B71" t="s">
         <v>328</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="5" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s" s="0">
+      <c r="A72" t="s">
         <v>331</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="B72" t="s">
         <v>332</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="5" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s" s="0">
+      <c r="A73" t="s">
         <v>335</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="B73" t="s">
         <v>336</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="5" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s" s="0">
+      <c r="A74" t="s">
         <v>339</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="B74" t="s">
         <v>340</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="5" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s" s="0">
+      <c r="A75" t="s">
         <v>343</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="B75" t="s">
         <v>344</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="5" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s" s="0">
+      <c r="A76" t="s">
         <v>347</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B76" t="s">
         <v>348</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="5" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s" s="0">
+      <c r="A77" t="s">
         <v>351</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="B77" t="s">
         <v>352</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="5" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s" s="0">
+      <c r="A78" t="s">
         <v>355</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B78" t="s">
         <v>356</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="5" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s" s="0">
+      <c r="A79" t="s">
         <v>359</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="B79" t="s">
         <v>360</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="5" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s" s="0">
+      <c r="A80" t="s">
         <v>363</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="B80" t="s">
         <v>364</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="5" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s" s="0">
+      <c r="A81" t="s">
         <v>367</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B81" t="s">
         <v>368</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="5" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s" s="0">
+      <c r="A82" t="s">
         <v>371</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="B82" t="s">
         <v>372</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="5" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s" s="0">
+      <c r="A83" t="s">
         <v>375</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B83" t="s">
         <v>376</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="5" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s" s="0">
+      <c r="A84" t="s">
         <v>379</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B84" t="s">
         <v>380</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="5" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s" s="0">
+      <c r="A85" t="s">
         <v>383</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="B85" t="s">
         <v>384</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="5" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s" s="0">
+      <c r="A86" t="s">
         <v>387</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="B86" t="s">
         <v>388</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="5" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s" s="0">
+      <c r="A87" t="s">
         <v>391</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="B87" t="s">
         <v>392</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="5" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s" s="0">
+      <c r="A88" t="s">
         <v>395</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="B88" t="s">
         <v>396</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="5" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s" s="0">
+      <c r="A89" t="s">
         <v>399</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="B89" t="s">
         <v>400</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="5" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s" s="0">
+      <c r="A90" t="s">
         <v>403</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="B90" t="s">
         <v>404</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D90" s="5" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s" s="0">
+      <c r="A91" t="s">
         <v>407</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="B91" t="s">
         <v>408</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="5" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s" s="0">
+      <c r="A92" t="s">
         <v>411</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="B92" t="s">
         <v>412</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="D92" s="5" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s" s="0">
+      <c r="A93" t="s">
         <v>415</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B93" t="s">
         <v>416</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="5" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s" s="0">
+      <c r="A94" t="s">
         <v>419</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="B94" t="s">
         <v>420</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C94" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="5" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s" s="0">
+      <c r="A95" t="s">
         <v>423</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="B95" t="s">
         <v>424</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="C95" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="5" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s" s="0">
+      <c r="A96" t="s">
         <v>427</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="B96" t="s">
         <v>428</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="C96" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D96" s="5" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s" s="0">
+      <c r="A97" t="s">
         <v>431</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="B97" t="s">
         <v>432</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C97" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="5" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s" s="0">
+      <c r="A98" t="s">
         <v>435</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="B98" t="s">
         <v>436</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C98" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="5" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s" s="0">
+      <c r="A99" t="s">
         <v>439</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="B99" t="s">
         <v>440</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C99" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="5" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s" s="0">
+      <c r="A100" t="s">
         <v>443</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="B100" t="s">
         <v>444</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C100" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="5" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s" s="0">
+      <c r="A101" t="s">
         <v>447</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="B101" t="s">
         <v>448</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C101" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="5" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s" s="0">
+      <c r="A102" t="s">
         <v>451</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="B102" t="s">
         <v>452</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C102" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="5" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s" s="0">
+      <c r="A103" t="s">
         <v>455</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="B103" t="s">
         <v>456</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="C103" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="5" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s" s="0">
+      <c r="A104" t="s">
         <v>459</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="B104" t="s">
         <v>460</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D104" s="5" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s" s="0">
+      <c r="A105" t="s">
         <v>463</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="B105" t="s">
         <v>464</v>
       </c>
-      <c r="C105" s="7" t="s">
+      <c r="C105" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="5" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s" s="0">
+      <c r="A106" t="s">
         <v>467</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="B106" t="s">
         <v>468</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="5" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s" s="0">
+      <c r="A107" t="s">
         <v>471</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="B107" t="s">
         <v>472</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="5" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s" s="0">
+      <c r="A108" t="s">
         <v>475</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="B108" t="s">
         <v>476</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D108" s="5" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s" s="0">
+      <c r="A109" t="s">
         <v>479</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="B109" t="s">
         <v>480</v>
       </c>
-      <c r="C109" s="7" t="s">
+      <c r="C109" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D109" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s" s="0">
+      <c r="A110" t="s">
         <v>483</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="B110" t="s">
         <v>484</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D110" s="5" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s" s="0">
+      <c r="A111" t="s">
         <v>487</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="B111" t="s">
         <v>488</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C111" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="5" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s" s="0">
+      <c r="A112" t="s">
         <v>491</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="B112" t="s">
         <v>492</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="5" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s" s="0">
+      <c r="A113" t="s">
         <v>495</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="B113" t="s">
         <v>496</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C113" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="5" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s" s="0">
+      <c r="A114" t="s">
         <v>499</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="B114" t="s">
         <v>500</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D114" s="5" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s" s="0">
+      <c r="A115" t="s">
         <v>503</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="B115" t="s">
         <v>504</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C115" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="D115" s="5" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s" s="0">
+      <c r="A116" t="s">
         <v>507</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="B116" t="s">
         <v>508</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="5" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s" s="0">
+      <c r="A117" t="s">
         <v>511</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="B117" t="s">
         <v>512</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="C117" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="5" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s" s="0">
+      <c r="A118" t="s">
         <v>515</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="B118" t="s">
         <v>516</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="C118" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="5" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s" s="0">
+      <c r="A119" t="s">
         <v>519</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="B119" t="s">
         <v>520</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="C119" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="5" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s" s="0">
+      <c r="A120" t="s">
         <v>523</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="B120" t="s">
         <v>524</v>
       </c>
-      <c r="C120" s="7" t="s">
+      <c r="C120" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="D120" s="5" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s" s="0">
+      <c r="A121" t="s">
         <v>527</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="B121" t="s">
         <v>528</v>
       </c>
-      <c r="C121" s="7" t="s">
+      <c r="C121" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="D121" s="5" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s" s="0">
+      <c r="A122" t="s">
         <v>531</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="B122" t="s">
         <v>532</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="C122" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="D122" s="5" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s" s="0">
+      <c r="A123" t="s">
         <v>535</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="B123" t="s">
         <v>536</v>
       </c>
-      <c r="C123" s="7" t="s">
+      <c r="C123" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="D123" s="5" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s" s="0">
+      <c r="A124" t="s">
         <v>539</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="B124" t="s">
         <v>540</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="C124" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D124" s="5" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s" s="0">
+      <c r="A125" t="s">
         <v>543</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="B125" t="s">
         <v>544</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="C125" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="D125" s="6" t="s">
+      <c r="D125" s="5" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s" s="0">
+      <c r="A126" t="s">
         <v>547</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="B126" t="s">
         <v>548</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="C126" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="D126" s="5" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s" s="0">
+      <c r="A127" t="s">
         <v>551</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="B127" t="s">
         <v>552</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="C127" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="D127" s="6" t="s">
+      <c r="D127" s="5" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s" s="0">
+      <c r="A128" t="s">
         <v>555</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="B128" t="s">
         <v>556</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C128" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="D128" s="6" t="s">
+      <c r="D128" s="5" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s" s="0">
+      <c r="A129" t="s">
         <v>559</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="B129" t="s">
         <v>560</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="C129" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="D129" s="5" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s" s="0">
+      <c r="A130" t="s">
         <v>563</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="B130" t="s">
         <v>564</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="C130" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="D130" s="6" t="s">
+      <c r="D130" s="5" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s" s="0">
+      <c r="A131" t="s">
         <v>567</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="B131" t="s">
         <v>568</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="C131" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="D131" s="6" t="s">
+      <c r="D131" s="5" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s" s="0">
+      <c r="A132" t="s">
         <v>571</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="B132" t="s">
         <v>572</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="C132" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="D132" s="6" t="s">
+      <c r="D132" s="5" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s" s="0">
+      <c r="A133" t="s">
         <v>575</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="B133" t="s">
         <v>576</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="C133" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="D133" s="6" t="s">
+      <c r="D133" s="5" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s" s="0">
+      <c r="A134" t="s">
         <v>579</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="B134" t="s">
         <v>580</v>
       </c>
-      <c r="C134" s="7" t="s">
+      <c r="C134" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D134" s="5" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s" s="0">
+      <c r="A135" t="s">
         <v>583</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="B135" t="s">
         <v>584</v>
       </c>
-      <c r="C135" s="7" t="s">
+      <c r="C135" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="D135" s="6" t="s">
+      <c r="D135" s="5" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s" s="0">
+      <c r="A136" t="s">
         <v>587</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="B136" t="s">
         <v>588</v>
       </c>
-      <c r="C136" s="7" t="s">
+      <c r="C136" s="6" t="s">
         <v>589</v>
       </c>
-      <c r="D136" s="6" t="s">
+      <c r="D136" s="5" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s" s="0">
+      <c r="A137" t="s">
         <v>591</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="B137" t="s">
         <v>592</v>
       </c>
-      <c r="C137" s="7" t="s">
+      <c r="C137" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="D137" s="6" t="s">
+      <c r="D137" s="5" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s" s="0">
+      <c r="A138" t="s">
         <v>595</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="B138" t="s">
         <v>596</v>
       </c>
-      <c r="C138" s="7" t="s">
+      <c r="C138" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="D138" s="6" t="s">
+      <c r="D138" s="5" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s" s="0">
+      <c r="A139" t="s">
         <v>599</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="B139" t="s">
         <v>600</v>
       </c>
-      <c r="C139" s="7" t="s">
+      <c r="C139" s="6" t="s">
         <v>601</v>
       </c>
-      <c r="D139" s="6" t="s">
+      <c r="D139" s="5" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s" s="0">
+      <c r="A140" t="s">
         <v>603</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="B140" t="s">
         <v>604</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="C140" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="D140" s="5" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s" s="0">
+      <c r="A141" t="s">
         <v>607</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="B141" t="s">
         <v>608</v>
       </c>
-      <c r="C141" s="7" t="s">
+      <c r="C141" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="D141" s="6" t="s">
+      <c r="D141" s="5" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s" s="0">
+      <c r="A142" t="s">
         <v>611</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="B142" t="s">
         <v>612</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="C142" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="D142" s="5" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s" s="0">
+      <c r="A143" t="s">
         <v>615</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="B143" t="s">
         <v>616</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="C143" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="D143" s="5" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s" s="0">
+      <c r="A144" t="s">
         <v>619</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="B144" t="s">
         <v>620</v>
       </c>
-      <c r="C144" s="7" t="s">
+      <c r="C144" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="D144" s="6" t="s">
+      <c r="D144" s="5" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s" s="0">
+      <c r="A145" t="s">
         <v>623</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="B145" t="s">
         <v>624</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="C145" s="6" t="s">
         <v>625</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="D145" s="5" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s" s="0">
+      <c r="A146" t="s">
         <v>627</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="B146" t="s">
         <v>628</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="C146" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="D146" s="5" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s" s="0">
+      <c r="A147" t="s">
         <v>631</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="B147" t="s">
         <v>632</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="C147" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="D147" s="6" t="s">
+      <c r="D147" s="5" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s" s="0">
+      <c r="A148" t="s">
         <v>635</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="B148" t="s">
         <v>636</v>
       </c>
-      <c r="C148" s="7" t="s">
+      <c r="C148" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="D148" s="6" t="s">
+      <c r="D148" s="5" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s" s="0">
+      <c r="A149" t="s">
         <v>639</v>
       </c>
-      <c r="B149" t="s" s="0">
+      <c r="B149" t="s">
         <v>640</v>
       </c>
-      <c r="C149" s="7" t="s">
+      <c r="C149" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="D149" s="6" t="s">
+      <c r="D149" s="5" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s" s="0">
+      <c r="A150" t="s">
         <v>643</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="B150" t="s">
         <v>644</v>
       </c>
-      <c r="C150" s="7" t="s">
+      <c r="C150" s="6" t="s">
         <v>645</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="D150" s="5" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s" s="0">
+      <c r="A151" t="s">
         <v>647</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="B151" t="s">
         <v>648</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="C151" s="6" t="s">
         <v>649</v>
       </c>
-      <c r="D151" s="6" t="s">
+      <c r="D151" s="5" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s" s="0">
+      <c r="A152" t="s">
         <v>651</v>
       </c>
-      <c r="B152" t="s" s="0">
+      <c r="B152" t="s">
         <v>652</v>
       </c>
-      <c r="C152" s="7" t="s">
+      <c r="C152" s="6" t="s">
         <v>653</v>
       </c>
-      <c r="D152" s="6" t="s">
+      <c r="D152" s="5" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s" s="0">
+      <c r="B153" t="s">
         <v>655</v>
       </c>
-      <c r="C153" s="7" t="s">
+      <c r="C153" s="6" t="s">
         <v>656</v>
       </c>
-      <c r="D153" s="6" t="s">
+      <c r="D153" s="5" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s" s="0">
+      <c r="B154" t="s">
         <v>658</v>
       </c>
-      <c r="C154" s="7" t="s">
+      <c r="C154" s="6" t="s">
         <v>659</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="D154" s="5" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s" s="0">
+      <c r="B155" t="s">
         <v>661</v>
       </c>
-      <c r="C155" s="7" t="s">
+      <c r="C155" s="6" t="s">
         <v>662</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D155" s="5" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s" s="0">
+      <c r="B156" t="s">
         <v>664</v>
       </c>
-      <c r="C156" s="7" t="s">
+      <c r="C156" s="6" t="s">
         <v>665</v>
       </c>
-      <c r="D156" s="6" t="s">
+      <c r="D156" s="5" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s" s="0">
+      <c r="B157" t="s">
         <v>667</v>
       </c>
-      <c r="C157" s="7" t="s">
+      <c r="C157" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="D157" s="6" t="s">
+      <c r="D157" s="5" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s" s="0">
+      <c r="B158" t="s">
         <v>670</v>
       </c>
-      <c r="C158" s="7" t="s">
+      <c r="C158" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="D158" s="6" t="s">
+      <c r="D158" s="5" t="s">
         <v>672</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C159" s="7" t="s">
+      <c r="C159" s="6" t="s">
         <v>673</v>
       </c>
-      <c r="D159" s="6" t="s">
+      <c r="D159" s="5" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C160" s="7" t="s">
+      <c r="C160" s="6" t="s">
         <v>675</v>
       </c>
-      <c r="D160" s="6" t="s">
+      <c r="D160" s="5" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="161" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C161" s="7" t="s">
+      <c r="C161" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="D161" s="6" t="s">
+      <c r="D161" s="5" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="162" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C162" s="7" t="s">
+      <c r="C162" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="D162" s="6" t="s">
+      <c r="D162" s="5" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="163" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C163" s="7" t="s">
+      <c r="C163" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="D163" s="6" t="s">
+      <c r="D163" s="5" t="s">
         <v>682</v>
       </c>
     </row>
     <row r="164" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C164" s="7" t="s">
+      <c r="C164" s="6" t="s">
         <v>683</v>
       </c>
-      <c r="D164" s="6" t="s">
+      <c r="D164" s="5" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="165" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C165" s="7" t="s">
+      <c r="C165" s="6" t="s">
         <v>685</v>
       </c>
-      <c r="D165" s="6" t="s">
+      <c r="D165" s="5" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="166" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C166" s="7" t="s">
+      <c r="C166" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="D166" s="6" t="s">
+      <c r="D166" s="5" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="167" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C167" s="7" t="s">
+      <c r="C167" s="6" t="s">
         <v>689</v>
       </c>
-      <c r="D167" s="6" t="s">
+      <c r="D167" s="5" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="168" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C168" s="7" t="s">
+      <c r="C168" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="D168" s="6" t="s">
+      <c r="D168" s="5" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="169" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C169" s="7" t="s">
+      <c r="C169" s="6" t="s">
         <v>693</v>
       </c>
-      <c r="D169" s="6" t="s">
+      <c r="D169" s="5" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="170" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C170" s="7" t="s">
+      <c r="C170" s="6" t="s">
         <v>695</v>
       </c>
-      <c r="D170" s="6" t="s">
+      <c r="D170" s="5" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="171" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="D171" s="6" t="s">
+      <c r="D171" s="5" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="172" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="D172" s="6" t="s">
+      <c r="D172" s="5" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="173" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="D173" s="6" t="s">
+      <c r="D173" s="5" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="174" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="D174" s="6" t="s">
+      <c r="D174" s="5" t="s">
         <v>700</v>
       </c>
     </row>
     <row r="175" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="D175" s="6" t="s">
+      <c r="D175" s="5" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="176" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="D176" s="6" t="s">
+      <c r="D176" s="5" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="177" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D177" s="6" t="s">
+      <c r="D177" s="5" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="178" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D178" s="6" t="s">
+      <c r="D178" s="5" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="179" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D179" s="6" t="s">
+      <c r="D179" s="5" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="180" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D180" s="6" t="s">
+      <c r="D180" s="5" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="181" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D181" s="6" t="s">
+      <c r="D181" s="5" t="s">
         <v>707</v>
       </c>
     </row>
     <row r="182" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D182" s="6" t="s">
+      <c r="D182" s="5" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="183" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D183" s="6" t="s">
+      <c r="D183" s="5" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="184" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D184" s="6" t="s">
+      <c r="D184" s="5" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="185" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D185" s="6" t="s">
+      <c r="D185" s="5" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="186" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D186" s="6" t="s">
+      <c r="D186" s="5" t="s">
         <v>712</v>
       </c>
     </row>
     <row r="187" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D187" s="6" t="s">
+      <c r="D187" s="5" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="188" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D188" s="6" t="s">
+      <c r="D188" s="5" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="189" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D189" s="6" t="s">
+      <c r="D189" s="5" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="190" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D190" s="6" t="s">
+      <c r="D190" s="5" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="191" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D191" s="6" t="s">
+      <c r="D191" s="5" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="192" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D192" s="6" t="s">
+      <c r="D192" s="5" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="193" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D193" s="6" t="s">
+      <c r="D193" s="5" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="194" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D194" s="6" t="s">
+      <c r="D194" s="5" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="195" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D195" s="6" t="s">
+      <c r="D195" s="5" t="s">
         <v>721</v>
       </c>
     </row>
     <row r="196" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D196" s="6" t="s">
+      <c r="D196" s="5" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="197" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D197" s="6" t="s">
+      <c r="D197" s="5" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="198" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D198" s="6" t="s">
+      <c r="D198" s="5" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="199" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D199" s="6" t="s">
+      <c r="D199" s="5" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="200" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D200" s="6" t="s">
+      <c r="D200" s="5" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="201" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D201" s="6" t="s">
+      <c r="D201" s="5" t="s">
         <v>727</v>
       </c>
     </row>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="747">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2246,12 +2246,25 @@
   </si>
   <si>
     <t>FENAMV</t>
+  </si>
+  <si>
+    <t>Charlie78</t>
+  </si>
+  <si>
+    <t>Milo55</t>
+  </si>
+  <si>
+    <t>Taffy53</t>
+  </si>
+  <si>
+    <t>fury27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2306,7 +2319,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2327,6 +2340,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2633,21 +2651,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
+    <col min="12" max="16384" style="1" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2717,7 +2735,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="18" t="s">
         <v>729</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2726,7 +2744,7 @@
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="19" t="s">
         <v>738</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -2746,7 +2764,7 @@
       <c r="D5" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="21" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2763,7 +2781,7 @@
       <c r="D6" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="22" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2943,75 +2961,75 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" customWidth="1"/>
-    <col min="8" max="8" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.453125"/>
+    <col min="3" max="3" customWidth="true" width="35.6328125"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.7265625"/>
+    <col min="6" max="6" customWidth="true" width="32.1796875"/>
+    <col min="7" max="7" customWidth="true" width="33.6328125"/>
+    <col min="8" max="8" customWidth="true" width="31.26953125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>744</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
+        <v>745</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>42</v>
       </c>
     </row>
@@ -3028,46 +3046,46 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984375"/>
+    <col min="2" max="2" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.36328125"/>
+    <col min="4" max="5" customWidth="true" width="17.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.36328125"/>
+    <col min="8" max="8" customWidth="true" width="17.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3078,10 +3096,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3092,10 +3110,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3106,10 +3124,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3120,10 +3138,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>68</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3134,10 +3152,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3148,10 +3166,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3162,10 +3180,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>80</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3176,10 +3194,10 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3190,10 +3208,10 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>88</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3204,10 +3222,10 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>92</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3218,10 +3236,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>96</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3232,10 +3250,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>100</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3246,10 +3264,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -3260,10 +3278,10 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>108</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -3274,13 +3292,13 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="20" t="s">
         <v>113</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -3288,10 +3306,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>115</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>116</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -3302,10 +3320,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>120</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -3316,10 +3334,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>124</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -3330,10 +3348,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>128</v>
       </c>
       <c r="C21" s="6" t="s">
@@ -3344,10 +3362,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>132</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -3358,10 +3376,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>136</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -3372,10 +3390,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>139</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>140</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -3386,10 +3404,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>144</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3400,10 +3418,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>148</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3414,10 +3432,10 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>151</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>152</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3428,10 +3446,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>156</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3442,10 +3460,10 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>159</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>160</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3456,10 +3474,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>164</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3470,10 +3488,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>167</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>168</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3484,10 +3502,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>171</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>172</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3498,10 +3516,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>176</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3512,10 +3530,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>180</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3526,10 +3544,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>183</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>184</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3540,10 +3558,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>187</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>188</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3554,10 +3572,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>191</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>192</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3568,10 +3586,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>195</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>196</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3582,10 +3600,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>199</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>200</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3596,10 +3614,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>203</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>204</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3610,10 +3628,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>208</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3624,10 +3642,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>211</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>212</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3638,10 +3656,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>215</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>216</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3652,10 +3670,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>219</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>220</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3666,10 +3684,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>223</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>224</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3680,10 +3698,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>227</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>228</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3694,10 +3712,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>231</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>232</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3708,10 +3726,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>235</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>236</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3722,10 +3740,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>239</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>240</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3736,10 +3754,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>243</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>244</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3750,10 +3768,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>247</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>248</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3764,10 +3782,10 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>251</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>252</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3778,10 +3796,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>255</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>256</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3792,10 +3810,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>259</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>260</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3806,10 +3824,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>263</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>264</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3820,10 +3838,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>267</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>268</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3834,10 +3852,10 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>271</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>272</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3848,10 +3866,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>275</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>276</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3862,10 +3880,10 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>279</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>280</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3876,10 +3894,10 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>283</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>284</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3890,10 +3908,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>287</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>288</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3904,10 +3922,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>291</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>292</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3918,10 +3936,10 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>295</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>296</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -3932,10 +3950,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>299</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>300</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -3946,10 +3964,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>303</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>304</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -3960,10 +3978,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>307</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>308</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -3974,10 +3992,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>311</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>312</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -3988,10 +4006,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>315</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>316</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4002,10 +4020,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>319</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>320</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4016,10 +4034,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>323</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>324</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4030,10 +4048,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>327</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>328</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4044,10 +4062,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>331</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>332</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4058,10 +4076,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>335</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>336</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4072,10 +4090,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>339</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>340</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4086,10 +4104,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>343</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>344</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4100,10 +4118,10 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>347</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>348</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4114,10 +4132,10 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>351</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>352</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4128,10 +4146,10 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>355</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>356</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4142,10 +4160,10 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>359</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>360</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4156,10 +4174,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>363</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>364</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4170,10 +4188,10 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>367</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>368</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4184,10 +4202,10 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>371</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>372</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4198,10 +4216,10 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>375</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>376</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4212,10 +4230,10 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>379</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>380</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4226,10 +4244,10 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>383</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>384</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4240,10 +4258,10 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>387</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>388</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4254,10 +4272,10 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>391</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>392</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4268,10 +4286,10 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>395</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>396</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4282,10 +4300,10 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>399</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>400</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4296,10 +4314,10 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>404</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4310,10 +4328,10 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>407</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>408</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4324,10 +4342,10 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>411</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>412</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4338,10 +4356,10 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>415</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>416</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4352,10 +4370,10 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>419</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>420</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4366,10 +4384,10 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>423</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>424</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4380,10 +4398,10 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>427</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>428</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4394,10 +4412,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>431</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>432</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4408,10 +4426,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>435</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>436</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4422,10 +4440,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>439</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>440</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4436,10 +4454,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>443</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>444</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4450,10 +4468,10 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>447</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>448</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4464,10 +4482,10 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>451</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>452</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4478,10 +4496,10 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>455</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>456</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4492,10 +4510,10 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>459</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>460</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4506,10 +4524,10 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>463</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>464</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4520,10 +4538,10 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>467</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>468</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4534,10 +4552,10 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>471</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>472</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4548,10 +4566,10 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>475</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>476</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4562,10 +4580,10 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>479</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>480</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4576,10 +4594,10 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>483</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>484</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4590,10 +4608,10 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>487</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>488</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4604,10 +4622,10 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>491</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>492</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4618,10 +4636,10 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>495</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>496</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4632,10 +4650,10 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>499</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>500</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4646,10 +4664,10 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>503</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>504</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4660,10 +4678,10 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>507</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>508</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4674,10 +4692,10 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>511</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>512</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4688,10 +4706,10 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>515</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>516</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4702,10 +4720,10 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>519</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>520</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4716,10 +4734,10 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>523</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>524</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4730,10 +4748,10 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>527</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>528</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4744,10 +4762,10 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>531</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>532</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4758,10 +4776,10 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>535</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>536</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4772,10 +4790,10 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>539</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>540</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4786,10 +4804,10 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>543</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>544</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4800,10 +4818,10 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>547</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>548</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4814,10 +4832,10 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>551</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>552</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4828,10 +4846,10 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>555</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>556</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4842,10 +4860,10 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>559</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>560</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4856,10 +4874,10 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>563</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>564</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4870,10 +4888,10 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>567</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>568</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4884,10 +4902,10 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>571</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>572</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4898,10 +4916,10 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>575</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>576</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4912,10 +4930,10 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>579</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>580</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4926,10 +4944,10 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>583</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>584</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -4940,10 +4958,10 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>587</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>588</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -4954,10 +4972,10 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>591</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>592</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -4968,10 +4986,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>595</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>596</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -4982,10 +5000,10 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>599</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>600</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -4996,10 +5014,10 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>603</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>604</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5010,10 +5028,10 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>607</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>608</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5024,10 +5042,10 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>611</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>612</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5038,10 +5056,10 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>615</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>616</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5052,10 +5070,10 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>619</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>620</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5066,10 +5084,10 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>623</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>624</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5080,10 +5098,10 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>627</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>628</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5094,10 +5112,10 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>631</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>632</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5108,10 +5126,10 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>635</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>636</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5122,10 +5140,10 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>639</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>640</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5136,10 +5154,10 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>643</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>644</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5150,10 +5168,10 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>647</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>648</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5164,10 +5182,10 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>651</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>652</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5178,7 +5196,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>655</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5189,7 +5207,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>658</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5200,7 +5218,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>661</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5211,7 +5229,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>664</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5222,7 +5240,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>667</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5233,7 +5251,7 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>670</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\workspace\testing\animalBiome_Automation\src\test\resources\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3150" activeTab="1"/>
   </bookViews>
@@ -11,13 +16,12 @@
     <sheet name="PET_NAME" sheetId="2" r:id="rId2"/>
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1:D9"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -49,61 +53,106 @@
     <t>Vet_Fauna</t>
   </si>
   <si>
+    <t>7H6YMR</t>
+  </si>
+  <si>
     <t>CYGKE6</t>
   </si>
   <si>
+    <t>XD7DT3</t>
+  </si>
+  <si>
+    <t>NNTHRC</t>
+  </si>
+  <si>
+    <t>H4NC3U</t>
+  </si>
+  <si>
+    <t>GVVFEP</t>
+  </si>
+  <si>
     <t>NA6V7C</t>
   </si>
   <si>
+    <t>EV6UEC</t>
+  </si>
+  <si>
+    <t>E4NC6K</t>
+  </si>
+  <si>
+    <t>D4ARPJ</t>
+  </si>
+  <si>
+    <t>FUTHNN</t>
+  </si>
+  <si>
     <t>V63CMY</t>
   </si>
   <si>
+    <t>6GAFRG</t>
+  </si>
+  <si>
+    <t>PDNXE7</t>
+  </si>
+  <si>
+    <t>FVMMAF</t>
+  </si>
+  <si>
+    <t>XKTDYU</t>
+  </si>
+  <si>
     <t>MPYAKP</t>
   </si>
   <si>
-    <t>XD7DT3</t>
+    <t>X6RDRC</t>
+  </si>
+  <si>
+    <t>VGCJEJ</t>
+  </si>
+  <si>
+    <t>NUPYRG</t>
+  </si>
+  <si>
+    <t>J7PTRT</t>
   </si>
   <si>
     <t>394JV9</t>
   </si>
   <si>
-    <t>EV6UEC</t>
+    <t>DCHJFC</t>
+  </si>
+  <si>
+    <t>KRRUUJ</t>
+  </si>
+  <si>
+    <t>DDV9JY</t>
+  </si>
+  <si>
+    <t>FAA9TM</t>
   </si>
   <si>
     <t>KAR9NK</t>
   </si>
   <si>
-    <t>6GAFRG</t>
+    <t>GGYTUT</t>
+  </si>
+  <si>
+    <t>CKUGMJ</t>
+  </si>
+  <si>
+    <t>9DM4NG</t>
+  </si>
+  <si>
+    <t>HNECET</t>
   </si>
   <si>
     <t>FEMHMK</t>
   </si>
   <si>
-    <t>X6RDRC</t>
-  </si>
-  <si>
-    <t>NNTHRC</t>
-  </si>
-  <si>
-    <t>7H6YMR</t>
-  </si>
-  <si>
-    <t>H4NC3U</t>
-  </si>
-  <si>
-    <t>D4ARPJ</t>
-  </si>
-  <si>
-    <t>FVMMAF</t>
-  </si>
-  <si>
-    <t>NUPYRG</t>
-  </si>
-  <si>
-    <t>DDV9JY</t>
-  </si>
-  <si>
-    <t>9DM4NG</t>
+    <t>E47DUV</t>
+  </si>
+  <si>
+    <t>FENAMV</t>
   </si>
   <si>
     <t>RTNRRD</t>
@@ -2201,71 +2250,13 @@
   </si>
   <si>
     <t>Nexra</t>
-  </si>
-  <si>
-    <t>GVVFEP</t>
-  </si>
-  <si>
-    <t>FUTHNN</t>
-  </si>
-  <si>
-    <t>XKTDYU</t>
-  </si>
-  <si>
-    <t>J7PTRT</t>
-  </si>
-  <si>
-    <t>FAA9TM</t>
-  </si>
-  <si>
-    <t>HNECET</t>
-  </si>
-  <si>
-    <t>DCHJFC</t>
-  </si>
-  <si>
-    <t>GGYTUT</t>
-  </si>
-  <si>
-    <t>E47DUV</t>
-  </si>
-  <si>
-    <t>E4NC6K</t>
-  </si>
-  <si>
-    <t>PDNXE7</t>
-  </si>
-  <si>
-    <t>VGCJEJ</t>
-  </si>
-  <si>
-    <t>KRRUUJ</t>
-  </si>
-  <si>
-    <t>CKUGMJ</t>
-  </si>
-  <si>
-    <t>FENAMV</t>
-  </si>
-  <si>
-    <t>Charlie78</t>
-  </si>
-  <si>
-    <t>Milo55</t>
-  </si>
-  <si>
-    <t>Taffy53</t>
-  </si>
-  <si>
-    <t>fury27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2277,13 +2268,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2306,20 +2290,14 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2327,40 +2305,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1"/>
     <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -2369,10 +2323,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2504,6 +2458,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2527,10 +2482,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2539,13 +2495,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2621,6 +2577,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2640,35 +2597,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J119"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
-    <col min="12" max="16384" style="1" width="8.7265625"/>
+    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.726563" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" ht="15.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2700,2820 +2655,2704 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+    <row r="2" ht="15.5">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="15.5">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="15.5">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
-        <v>728</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>737</v>
-      </c>
-      <c r="E3" s="16" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>729</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>738</v>
-      </c>
-      <c r="E4" s="17" t="s">
+    <row r="5" ht="15.5">
+      <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="15.5">
       <c r="A6" s="1" t="s">
-        <v>731</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>734</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" ht="15.5">
       <c r="A7" s="1" t="s">
-        <v>732</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>735</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>741</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" ht="15.5">
       <c r="A8" s="1" t="s">
-        <v>733</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>736</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>742</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" ht="15.5">
       <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" ht="15.5">
       <c r="E10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" ht="15.5">
       <c r="E11" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" ht="15.5">
       <c r="E12" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="78" ht="15.5">
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" ht="15.5">
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35"/>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35"/>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.453125"/>
-    <col min="3" max="3" customWidth="true" width="35.6328125"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.7265625"/>
-    <col min="6" max="6" customWidth="true" width="32.1796875"/>
-    <col min="7" max="7" customWidth="true" width="33.6328125"/>
-    <col min="8" max="8" customWidth="true" width="31.26953125"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.45313" customWidth="1"/>
+    <col min="3" max="3" width="35.63281" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.72656" customWidth="1"/>
+    <col min="6" max="6" width="32.17969" customWidth="1"/>
+    <col min="7" max="7" width="33.63281" customWidth="1"/>
+    <col min="8" max="8" width="31.26953" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>744</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>745</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984375"/>
-    <col min="2" max="2" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" width="17.36328125"/>
-    <col min="4" max="5" customWidth="true" width="17.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.36328125"/>
-    <col min="8" max="8" customWidth="true" width="17.1796875"/>
+    <col min="1" max="1" width="20.08984" customWidth="1"/>
+    <col min="2" max="2" width="17.54297" customWidth="1"/>
+    <col min="3" max="3" width="17.36328" customWidth="1"/>
+    <col min="4" max="5" width="17.26953" customWidth="1"/>
+    <col min="6" max="6" width="17.17969" customWidth="1"/>
+    <col min="7" max="7" width="15.36328" customWidth="1"/>
+    <col min="8" max="8" width="17.17969" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" ht="14.5">
       <c r="A1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>52</v>
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" ht="14.5">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>56</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>59</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>60</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" ht="14.5">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>64</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
-        <v>67</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>68</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
-        <v>71</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>72</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5">
+      <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="0">
-        <v>75</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>76</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s" s="0">
-        <v>79</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>80</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>84</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>88</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>92</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5">
+      <c r="A12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>96</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5">
+      <c r="A13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" t="s">
+        <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>100</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>115</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>105</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5">
+      <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s" s="0">
-        <v>107</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>109</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" ht="14.5">
+      <c r="A16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s" s="0">
-        <v>111</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>113</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" ht="14.5">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s" s="0">
-        <v>115</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>116</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" ht="14.5">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>131</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s" s="0">
-        <v>119</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>120</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" ht="14.5">
+      <c r="A19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" t="s">
+        <v>135</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s" s="0">
-        <v>123</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>124</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" ht="14.5">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s">
+        <v>139</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s" s="0">
-        <v>127</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>128</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" ht="14.5">
+      <c r="A21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" t="s">
+        <v>143</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>132</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" ht="14.5">
+      <c r="A22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" t="s">
+        <v>147</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>136</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" ht="14.5">
+      <c r="A23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" t="s">
+        <v>151</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s" s="0">
-        <v>139</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>140</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" ht="14.5">
+      <c r="A24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" t="s">
+        <v>155</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s" s="0">
-        <v>143</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>144</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" ht="14.5">
+      <c r="A25" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" t="s">
+        <v>159</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s" s="0">
-        <v>147</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>148</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" ht="14.5">
+      <c r="A26" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" t="s">
+        <v>163</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>152</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" ht="14.5">
+      <c r="A27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" t="s">
+        <v>167</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s" s="0">
-        <v>155</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>156</v>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" ht="14.5">
+      <c r="A28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s" s="0">
-        <v>159</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>160</v>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" ht="14.5">
+      <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" t="s">
+        <v>175</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s" s="0">
-        <v>163</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>164</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" ht="14.5">
+      <c r="A30" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" t="s">
+        <v>179</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s" s="0">
-        <v>167</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>168</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" ht="14.5">
+      <c r="A31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B31" t="s">
+        <v>183</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s" s="0">
-        <v>171</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>172</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" ht="14.5">
+      <c r="A32" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" t="s">
+        <v>187</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s" s="0">
-        <v>175</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>176</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" ht="14.5">
+      <c r="A33" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" t="s">
+        <v>191</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s" s="0">
-        <v>179</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>180</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" ht="14.5">
+      <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
+        <v>195</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s" s="0">
-        <v>183</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>184</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="35" ht="14.5">
+      <c r="A35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B35" t="s">
+        <v>199</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s" s="0">
-        <v>187</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>188</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" ht="14.5">
+      <c r="A36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" t="s">
+        <v>203</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>192</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" ht="14.5">
+      <c r="A37" t="s">
+        <v>206</v>
+      </c>
+      <c r="B37" t="s">
+        <v>207</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s" s="0">
-        <v>195</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>196</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" ht="14.5">
+      <c r="A38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B38" t="s">
+        <v>211</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>200</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="39" ht="14.5">
+      <c r="A39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" t="s">
+        <v>215</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s" s="0">
-        <v>203</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>204</v>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" ht="14.5">
+      <c r="A40" t="s">
+        <v>218</v>
+      </c>
+      <c r="B40" t="s">
+        <v>219</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s" s="0">
-        <v>207</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>208</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" ht="14.5">
+      <c r="A41" t="s">
+        <v>222</v>
+      </c>
+      <c r="B41" t="s">
+        <v>223</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s" s="0">
-        <v>211</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>212</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" ht="14.5">
+      <c r="A42" t="s">
+        <v>226</v>
+      </c>
+      <c r="B42" t="s">
+        <v>227</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s" s="0">
-        <v>215</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>216</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="43" ht="14.5">
+      <c r="A43" t="s">
+        <v>230</v>
+      </c>
+      <c r="B43" t="s">
+        <v>231</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s" s="0">
-        <v>219</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>220</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44" ht="14.5">
+      <c r="A44" t="s">
+        <v>234</v>
+      </c>
+      <c r="B44" t="s">
+        <v>235</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s" s="0">
-        <v>223</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>224</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" ht="14.5">
+      <c r="A45" t="s">
+        <v>238</v>
+      </c>
+      <c r="B45" t="s">
+        <v>239</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s" s="0">
-        <v>227</v>
-      </c>
-      <c r="B46" t="s" s="0">
-        <v>228</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="46" ht="14.5">
+      <c r="A46" t="s">
+        <v>242</v>
+      </c>
+      <c r="B46" t="s">
+        <v>243</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s" s="0">
-        <v>231</v>
-      </c>
-      <c r="B47" t="s" s="0">
-        <v>232</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" ht="14.5">
+      <c r="A47" t="s">
+        <v>246</v>
+      </c>
+      <c r="B47" t="s">
+        <v>247</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s" s="0">
-        <v>235</v>
-      </c>
-      <c r="B48" t="s" s="0">
-        <v>236</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="48" ht="14.5">
+      <c r="A48" t="s">
+        <v>250</v>
+      </c>
+      <c r="B48" t="s">
+        <v>251</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s" s="0">
-        <v>239</v>
-      </c>
-      <c r="B49" t="s" s="0">
-        <v>240</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="49" ht="14.5">
+      <c r="A49" t="s">
+        <v>254</v>
+      </c>
+      <c r="B49" t="s">
+        <v>255</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s" s="0">
-        <v>243</v>
-      </c>
-      <c r="B50" t="s" s="0">
-        <v>244</v>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50" ht="14.5">
+      <c r="A50" t="s">
+        <v>258</v>
+      </c>
+      <c r="B50" t="s">
+        <v>259</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>248</v>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51" ht="14.5">
+      <c r="A51" t="s">
+        <v>262</v>
+      </c>
+      <c r="B51" t="s">
+        <v>263</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s" s="0">
-        <v>251</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>252</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="52" ht="14.5">
+      <c r="A52" t="s">
+        <v>266</v>
+      </c>
+      <c r="B52" t="s">
+        <v>267</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s" s="0">
-        <v>255</v>
-      </c>
-      <c r="B53" t="s" s="0">
-        <v>256</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="53" ht="14.5">
+      <c r="A53" t="s">
+        <v>270</v>
+      </c>
+      <c r="B53" t="s">
+        <v>271</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s" s="0">
-        <v>259</v>
-      </c>
-      <c r="B54" t="s" s="0">
-        <v>260</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" ht="14.5">
+      <c r="A54" t="s">
+        <v>274</v>
+      </c>
+      <c r="B54" t="s">
+        <v>275</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="B55" t="s" s="0">
-        <v>264</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="55" ht="14.5">
+      <c r="A55" t="s">
+        <v>278</v>
+      </c>
+      <c r="B55" t="s">
+        <v>279</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s" s="0">
-        <v>267</v>
-      </c>
-      <c r="B56" t="s" s="0">
-        <v>268</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="56" ht="14.5">
+      <c r="A56" t="s">
+        <v>282</v>
+      </c>
+      <c r="B56" t="s">
+        <v>283</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s" s="0">
-        <v>271</v>
-      </c>
-      <c r="B57" t="s" s="0">
-        <v>272</v>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" ht="14.5">
+      <c r="A57" t="s">
+        <v>286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>287</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s" s="0">
-        <v>275</v>
-      </c>
-      <c r="B58" t="s" s="0">
-        <v>276</v>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="58" ht="14.5">
+      <c r="A58" t="s">
+        <v>290</v>
+      </c>
+      <c r="B58" t="s">
+        <v>291</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s" s="0">
-        <v>279</v>
-      </c>
-      <c r="B59" t="s" s="0">
-        <v>280</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="59" ht="14.5">
+      <c r="A59" t="s">
+        <v>294</v>
+      </c>
+      <c r="B59" t="s">
+        <v>295</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s" s="0">
-        <v>283</v>
-      </c>
-      <c r="B60" t="s" s="0">
-        <v>284</v>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="60" ht="14.5">
+      <c r="A60" t="s">
+        <v>298</v>
+      </c>
+      <c r="B60" t="s">
+        <v>299</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s" s="0">
-        <v>287</v>
-      </c>
-      <c r="B61" t="s" s="0">
-        <v>288</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="61" ht="14.5">
+      <c r="A61" t="s">
+        <v>302</v>
+      </c>
+      <c r="B61" t="s">
+        <v>303</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s" s="0">
-        <v>291</v>
-      </c>
-      <c r="B62" t="s" s="0">
-        <v>292</v>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" ht="14.5">
+      <c r="A62" t="s">
+        <v>306</v>
+      </c>
+      <c r="B62" t="s">
+        <v>307</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s" s="0">
-        <v>295</v>
-      </c>
-      <c r="B63" t="s" s="0">
-        <v>296</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="63" ht="14.5">
+      <c r="A63" t="s">
+        <v>310</v>
+      </c>
+      <c r="B63" t="s">
+        <v>311</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s" s="0">
-        <v>299</v>
-      </c>
-      <c r="B64" t="s" s="0">
-        <v>300</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="64" ht="14.5">
+      <c r="A64" t="s">
+        <v>314</v>
+      </c>
+      <c r="B64" t="s">
+        <v>315</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s" s="0">
-        <v>303</v>
-      </c>
-      <c r="B65" t="s" s="0">
-        <v>304</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="65" ht="14.5">
+      <c r="A65" t="s">
+        <v>318</v>
+      </c>
+      <c r="B65" t="s">
+        <v>319</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s" s="0">
-        <v>307</v>
-      </c>
-      <c r="B66" t="s" s="0">
-        <v>308</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="66" ht="14.5">
+      <c r="A66" t="s">
+        <v>322</v>
+      </c>
+      <c r="B66" t="s">
+        <v>323</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s" s="0">
-        <v>311</v>
-      </c>
-      <c r="B67" t="s" s="0">
-        <v>312</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="67" ht="14.5">
+      <c r="A67" t="s">
+        <v>326</v>
+      </c>
+      <c r="B67" t="s">
+        <v>327</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s" s="0">
-        <v>315</v>
-      </c>
-      <c r="B68" t="s" s="0">
-        <v>316</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="68" ht="14.5">
+      <c r="A68" t="s">
+        <v>330</v>
+      </c>
+      <c r="B68" t="s">
+        <v>331</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s" s="0">
-        <v>319</v>
-      </c>
-      <c r="B69" t="s" s="0">
-        <v>320</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="69" ht="14.5">
+      <c r="A69" t="s">
+        <v>334</v>
+      </c>
+      <c r="B69" t="s">
+        <v>335</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s" s="0">
-        <v>323</v>
-      </c>
-      <c r="B70" t="s" s="0">
-        <v>324</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="70" ht="14.5">
+      <c r="A70" t="s">
+        <v>338</v>
+      </c>
+      <c r="B70" t="s">
+        <v>339</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s" s="0">
-        <v>327</v>
-      </c>
-      <c r="B71" t="s" s="0">
-        <v>328</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="71" ht="14.5">
+      <c r="A71" t="s">
+        <v>342</v>
+      </c>
+      <c r="B71" t="s">
+        <v>343</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s" s="0">
-        <v>331</v>
-      </c>
-      <c r="B72" t="s" s="0">
-        <v>332</v>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="72" ht="14.5">
+      <c r="A72" t="s">
+        <v>346</v>
+      </c>
+      <c r="B72" t="s">
+        <v>347</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s" s="0">
-        <v>335</v>
-      </c>
-      <c r="B73" t="s" s="0">
-        <v>336</v>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="73" ht="14.5">
+      <c r="A73" t="s">
+        <v>350</v>
+      </c>
+      <c r="B73" t="s">
+        <v>351</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s" s="0">
-        <v>339</v>
-      </c>
-      <c r="B74" t="s" s="0">
-        <v>340</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="74" ht="14.5">
+      <c r="A74" t="s">
+        <v>354</v>
+      </c>
+      <c r="B74" t="s">
+        <v>355</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s" s="0">
-        <v>343</v>
-      </c>
-      <c r="B75" t="s" s="0">
-        <v>344</v>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="75" ht="14.5">
+      <c r="A75" t="s">
+        <v>358</v>
+      </c>
+      <c r="B75" t="s">
+        <v>359</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s" s="0">
-        <v>347</v>
-      </c>
-      <c r="B76" t="s" s="0">
-        <v>348</v>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="76" ht="14.5">
+      <c r="A76" t="s">
+        <v>362</v>
+      </c>
+      <c r="B76" t="s">
+        <v>363</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s" s="0">
-        <v>351</v>
-      </c>
-      <c r="B77" t="s" s="0">
-        <v>352</v>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="77" ht="14.5">
+      <c r="A77" t="s">
+        <v>366</v>
+      </c>
+      <c r="B77" t="s">
+        <v>367</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="B78" t="s" s="0">
-        <v>356</v>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="78" ht="14.5">
+      <c r="A78" t="s">
+        <v>370</v>
+      </c>
+      <c r="B78" t="s">
+        <v>371</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s" s="0">
-        <v>359</v>
-      </c>
-      <c r="B79" t="s" s="0">
-        <v>360</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="79" ht="14.5">
+      <c r="A79" t="s">
+        <v>374</v>
+      </c>
+      <c r="B79" t="s">
+        <v>375</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s" s="0">
-        <v>363</v>
-      </c>
-      <c r="B80" t="s" s="0">
-        <v>364</v>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="80" ht="14.5">
+      <c r="A80" t="s">
+        <v>378</v>
+      </c>
+      <c r="B80" t="s">
+        <v>379</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s" s="0">
-        <v>367</v>
-      </c>
-      <c r="B81" t="s" s="0">
-        <v>368</v>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="81" ht="14.5">
+      <c r="A81" t="s">
+        <v>382</v>
+      </c>
+      <c r="B81" t="s">
+        <v>383</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s" s="0">
-        <v>371</v>
-      </c>
-      <c r="B82" t="s" s="0">
-        <v>372</v>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="82" ht="14.5">
+      <c r="A82" t="s">
+        <v>386</v>
+      </c>
+      <c r="B82" t="s">
+        <v>387</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s" s="0">
-        <v>375</v>
-      </c>
-      <c r="B83" t="s" s="0">
-        <v>376</v>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="83" ht="14.5">
+      <c r="A83" t="s">
+        <v>390</v>
+      </c>
+      <c r="B83" t="s">
+        <v>391</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s" s="0">
-        <v>379</v>
-      </c>
-      <c r="B84" t="s" s="0">
-        <v>380</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="84" ht="14.5">
+      <c r="A84" t="s">
+        <v>394</v>
+      </c>
+      <c r="B84" t="s">
+        <v>395</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s" s="0">
-        <v>383</v>
-      </c>
-      <c r="B85" t="s" s="0">
-        <v>384</v>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="85" ht="14.5">
+      <c r="A85" t="s">
+        <v>398</v>
+      </c>
+      <c r="B85" t="s">
+        <v>399</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s" s="0">
-        <v>387</v>
-      </c>
-      <c r="B86" t="s" s="0">
-        <v>388</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="86" ht="14.5">
+      <c r="A86" t="s">
+        <v>402</v>
+      </c>
+      <c r="B86" t="s">
+        <v>403</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s" s="0">
-        <v>391</v>
-      </c>
-      <c r="B87" t="s" s="0">
-        <v>392</v>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="87" ht="14.5">
+      <c r="A87" t="s">
+        <v>406</v>
+      </c>
+      <c r="B87" t="s">
+        <v>407</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s" s="0">
-        <v>395</v>
-      </c>
-      <c r="B88" t="s" s="0">
-        <v>396</v>
+        <v>409</v>
+      </c>
+    </row>
+    <row r="88" ht="14.5">
+      <c r="A88" t="s">
+        <v>410</v>
+      </c>
+      <c r="B88" t="s">
+        <v>411</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s" s="0">
-        <v>399</v>
-      </c>
-      <c r="B89" t="s" s="0">
-        <v>400</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="89" ht="14.5">
+      <c r="A89" t="s">
+        <v>414</v>
+      </c>
+      <c r="B89" t="s">
+        <v>415</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s" s="0">
-        <v>403</v>
-      </c>
-      <c r="B90" t="s" s="0">
-        <v>404</v>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="90" ht="14.5">
+      <c r="A90" t="s">
+        <v>418</v>
+      </c>
+      <c r="B90" t="s">
+        <v>419</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s" s="0">
-        <v>407</v>
-      </c>
-      <c r="B91" t="s" s="0">
-        <v>408</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="91" ht="14.5">
+      <c r="A91" t="s">
+        <v>422</v>
+      </c>
+      <c r="B91" t="s">
+        <v>423</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s" s="0">
-        <v>411</v>
-      </c>
-      <c r="B92" t="s" s="0">
-        <v>412</v>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="92" ht="14.5">
+      <c r="A92" t="s">
+        <v>426</v>
+      </c>
+      <c r="B92" t="s">
+        <v>427</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s" s="0">
-        <v>415</v>
-      </c>
-      <c r="B93" t="s" s="0">
-        <v>416</v>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="93" ht="14.5">
+      <c r="A93" t="s">
+        <v>430</v>
+      </c>
+      <c r="B93" t="s">
+        <v>431</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s" s="0">
-        <v>419</v>
-      </c>
-      <c r="B94" t="s" s="0">
-        <v>420</v>
+        <v>433</v>
+      </c>
+    </row>
+    <row r="94" ht="14.5">
+      <c r="A94" t="s">
+        <v>434</v>
+      </c>
+      <c r="B94" t="s">
+        <v>435</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="B95" t="s" s="0">
-        <v>424</v>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="95" ht="14.5">
+      <c r="A95" t="s">
+        <v>438</v>
+      </c>
+      <c r="B95" t="s">
+        <v>439</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s" s="0">
-        <v>427</v>
-      </c>
-      <c r="B96" t="s" s="0">
-        <v>428</v>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="96" ht="14.5">
+      <c r="A96" t="s">
+        <v>442</v>
+      </c>
+      <c r="B96" t="s">
+        <v>443</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s" s="0">
-        <v>431</v>
-      </c>
-      <c r="B97" t="s" s="0">
-        <v>432</v>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="97" ht="14.5">
+      <c r="A97" t="s">
+        <v>446</v>
+      </c>
+      <c r="B97" t="s">
+        <v>447</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="B98" t="s" s="0">
-        <v>436</v>
+        <v>449</v>
+      </c>
+    </row>
+    <row r="98" ht="14.5">
+      <c r="A98" t="s">
+        <v>450</v>
+      </c>
+      <c r="B98" t="s">
+        <v>451</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s" s="0">
-        <v>439</v>
-      </c>
-      <c r="B99" t="s" s="0">
-        <v>440</v>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="99" ht="14.5">
+      <c r="A99" t="s">
+        <v>454</v>
+      </c>
+      <c r="B99" t="s">
+        <v>455</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s" s="0">
-        <v>443</v>
-      </c>
-      <c r="B100" t="s" s="0">
-        <v>444</v>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="100" ht="14.5">
+      <c r="A100" t="s">
+        <v>458</v>
+      </c>
+      <c r="B100" t="s">
+        <v>459</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s" s="0">
-        <v>447</v>
-      </c>
-      <c r="B101" t="s" s="0">
-        <v>448</v>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="101" ht="14.5">
+      <c r="A101" t="s">
+        <v>462</v>
+      </c>
+      <c r="B101" t="s">
+        <v>463</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s" s="0">
-        <v>451</v>
-      </c>
-      <c r="B102" t="s" s="0">
-        <v>452</v>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="102" ht="14.5">
+      <c r="A102" t="s">
+        <v>466</v>
+      </c>
+      <c r="B102" t="s">
+        <v>467</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s" s="0">
-        <v>455</v>
-      </c>
-      <c r="B103" t="s" s="0">
-        <v>456</v>
+        <v>469</v>
+      </c>
+    </row>
+    <row r="103" ht="14.5">
+      <c r="A103" t="s">
+        <v>470</v>
+      </c>
+      <c r="B103" t="s">
+        <v>471</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s" s="0">
-        <v>459</v>
-      </c>
-      <c r="B104" t="s" s="0">
-        <v>460</v>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="104" ht="14.5">
+      <c r="A104" t="s">
+        <v>474</v>
+      </c>
+      <c r="B104" t="s">
+        <v>475</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s" s="0">
-        <v>463</v>
-      </c>
-      <c r="B105" t="s" s="0">
-        <v>464</v>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="105" ht="14.5">
+      <c r="A105" t="s">
+        <v>478</v>
+      </c>
+      <c r="B105" t="s">
+        <v>479</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s" s="0">
-        <v>467</v>
-      </c>
-      <c r="B106" t="s" s="0">
-        <v>468</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="106" ht="14.5">
+      <c r="A106" t="s">
+        <v>482</v>
+      </c>
+      <c r="B106" t="s">
+        <v>483</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s" s="0">
-        <v>471</v>
-      </c>
-      <c r="B107" t="s" s="0">
-        <v>472</v>
+        <v>485</v>
+      </c>
+    </row>
+    <row r="107" ht="14.5">
+      <c r="A107" t="s">
+        <v>486</v>
+      </c>
+      <c r="B107" t="s">
+        <v>487</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s" s="0">
-        <v>475</v>
-      </c>
-      <c r="B108" t="s" s="0">
-        <v>476</v>
+        <v>489</v>
+      </c>
+    </row>
+    <row r="108" ht="14.5">
+      <c r="A108" t="s">
+        <v>490</v>
+      </c>
+      <c r="B108" t="s">
+        <v>491</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s" s="0">
-        <v>479</v>
-      </c>
-      <c r="B109" t="s" s="0">
-        <v>480</v>
+        <v>493</v>
+      </c>
+    </row>
+    <row r="109" ht="14.5">
+      <c r="A109" t="s">
+        <v>494</v>
+      </c>
+      <c r="B109" t="s">
+        <v>495</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s" s="0">
-        <v>483</v>
-      </c>
-      <c r="B110" t="s" s="0">
-        <v>484</v>
+        <v>497</v>
+      </c>
+    </row>
+    <row r="110" ht="14.5">
+      <c r="A110" t="s">
+        <v>498</v>
+      </c>
+      <c r="B110" t="s">
+        <v>499</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s" s="0">
-        <v>487</v>
-      </c>
-      <c r="B111" t="s" s="0">
-        <v>488</v>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="111" ht="14.5">
+      <c r="A111" t="s">
+        <v>502</v>
+      </c>
+      <c r="B111" t="s">
+        <v>503</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s" s="0">
-        <v>491</v>
-      </c>
-      <c r="B112" t="s" s="0">
-        <v>492</v>
+        <v>505</v>
+      </c>
+    </row>
+    <row r="112" ht="14.5">
+      <c r="A112" t="s">
+        <v>506</v>
+      </c>
+      <c r="B112" t="s">
+        <v>507</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s" s="0">
-        <v>495</v>
-      </c>
-      <c r="B113" t="s" s="0">
-        <v>496</v>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="113" ht="14.5">
+      <c r="A113" t="s">
+        <v>510</v>
+      </c>
+      <c r="B113" t="s">
+        <v>511</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s" s="0">
-        <v>499</v>
-      </c>
-      <c r="B114" t="s" s="0">
-        <v>500</v>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="114" ht="14.5">
+      <c r="A114" t="s">
+        <v>514</v>
+      </c>
+      <c r="B114" t="s">
+        <v>515</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s" s="0">
-        <v>503</v>
-      </c>
-      <c r="B115" t="s" s="0">
-        <v>504</v>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="115" ht="14.5">
+      <c r="A115" t="s">
+        <v>518</v>
+      </c>
+      <c r="B115" t="s">
+        <v>519</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s" s="0">
-        <v>507</v>
-      </c>
-      <c r="B116" t="s" s="0">
-        <v>508</v>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="116" ht="14.5">
+      <c r="A116" t="s">
+        <v>522</v>
+      </c>
+      <c r="B116" t="s">
+        <v>523</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s" s="0">
-        <v>511</v>
-      </c>
-      <c r="B117" t="s" s="0">
-        <v>512</v>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="117" ht="14.5">
+      <c r="A117" t="s">
+        <v>526</v>
+      </c>
+      <c r="B117" t="s">
+        <v>527</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s" s="0">
-        <v>515</v>
-      </c>
-      <c r="B118" t="s" s="0">
-        <v>516</v>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="118" ht="14.5">
+      <c r="A118" t="s">
+        <v>530</v>
+      </c>
+      <c r="B118" t="s">
+        <v>531</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s" s="0">
-        <v>519</v>
-      </c>
-      <c r="B119" t="s" s="0">
-        <v>520</v>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="119" ht="14.5">
+      <c r="A119" t="s">
+        <v>534</v>
+      </c>
+      <c r="B119" t="s">
+        <v>535</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s" s="0">
-        <v>523</v>
-      </c>
-      <c r="B120" t="s" s="0">
-        <v>524</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="120" ht="14.5">
+      <c r="A120" t="s">
+        <v>538</v>
+      </c>
+      <c r="B120" t="s">
+        <v>539</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s" s="0">
-        <v>527</v>
-      </c>
-      <c r="B121" t="s" s="0">
-        <v>528</v>
+        <v>541</v>
+      </c>
+    </row>
+    <row r="121" ht="14.5">
+      <c r="A121" t="s">
+        <v>542</v>
+      </c>
+      <c r="B121" t="s">
+        <v>543</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s" s="0">
-        <v>531</v>
-      </c>
-      <c r="B122" t="s" s="0">
-        <v>532</v>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="122" ht="14.5">
+      <c r="A122" t="s">
+        <v>546</v>
+      </c>
+      <c r="B122" t="s">
+        <v>547</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s" s="0">
-        <v>535</v>
-      </c>
-      <c r="B123" t="s" s="0">
-        <v>536</v>
+        <v>549</v>
+      </c>
+    </row>
+    <row r="123" ht="14.5">
+      <c r="A123" t="s">
+        <v>550</v>
+      </c>
+      <c r="B123" t="s">
+        <v>551</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s" s="0">
-        <v>539</v>
-      </c>
-      <c r="B124" t="s" s="0">
-        <v>540</v>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="124" ht="14.5">
+      <c r="A124" t="s">
+        <v>554</v>
+      </c>
+      <c r="B124" t="s">
+        <v>555</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s" s="0">
-        <v>543</v>
-      </c>
-      <c r="B125" t="s" s="0">
-        <v>544</v>
+        <v>557</v>
+      </c>
+    </row>
+    <row r="125" ht="14.5">
+      <c r="A125" t="s">
+        <v>558</v>
+      </c>
+      <c r="B125" t="s">
+        <v>559</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s" s="0">
-        <v>547</v>
-      </c>
-      <c r="B126" t="s" s="0">
-        <v>548</v>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="126" ht="14.5">
+      <c r="A126" t="s">
+        <v>562</v>
+      </c>
+      <c r="B126" t="s">
+        <v>563</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s" s="0">
-        <v>551</v>
-      </c>
-      <c r="B127" t="s" s="0">
-        <v>552</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="127" ht="14.5">
+      <c r="A127" t="s">
+        <v>566</v>
+      </c>
+      <c r="B127" t="s">
+        <v>567</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s" s="0">
-        <v>555</v>
-      </c>
-      <c r="B128" t="s" s="0">
-        <v>556</v>
+        <v>569</v>
+      </c>
+    </row>
+    <row r="128" ht="14.5">
+      <c r="A128" t="s">
+        <v>570</v>
+      </c>
+      <c r="B128" t="s">
+        <v>571</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s" s="0">
-        <v>559</v>
-      </c>
-      <c r="B129" t="s" s="0">
-        <v>560</v>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="129" ht="14.5">
+      <c r="A129" t="s">
+        <v>574</v>
+      </c>
+      <c r="B129" t="s">
+        <v>575</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s" s="0">
-        <v>563</v>
-      </c>
-      <c r="B130" t="s" s="0">
-        <v>564</v>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="130" ht="14.5">
+      <c r="A130" t="s">
+        <v>578</v>
+      </c>
+      <c r="B130" t="s">
+        <v>579</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s" s="0">
-        <v>567</v>
-      </c>
-      <c r="B131" t="s" s="0">
-        <v>568</v>
+        <v>581</v>
+      </c>
+    </row>
+    <row r="131" ht="14.5">
+      <c r="A131" t="s">
+        <v>582</v>
+      </c>
+      <c r="B131" t="s">
+        <v>583</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s" s="0">
-        <v>571</v>
-      </c>
-      <c r="B132" t="s" s="0">
-        <v>572</v>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="132" ht="14.5">
+      <c r="A132" t="s">
+        <v>586</v>
+      </c>
+      <c r="B132" t="s">
+        <v>587</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s" s="0">
-        <v>575</v>
-      </c>
-      <c r="B133" t="s" s="0">
-        <v>576</v>
+        <v>589</v>
+      </c>
+    </row>
+    <row r="133" ht="14.5">
+      <c r="A133" t="s">
+        <v>590</v>
+      </c>
+      <c r="B133" t="s">
+        <v>591</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s" s="0">
-        <v>579</v>
-      </c>
-      <c r="B134" t="s" s="0">
-        <v>580</v>
+        <v>593</v>
+      </c>
+    </row>
+    <row r="134" ht="14.5">
+      <c r="A134" t="s">
+        <v>594</v>
+      </c>
+      <c r="B134" t="s">
+        <v>595</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s" s="0">
-        <v>583</v>
-      </c>
-      <c r="B135" t="s" s="0">
-        <v>584</v>
+        <v>597</v>
+      </c>
+    </row>
+    <row r="135" ht="14.5">
+      <c r="A135" t="s">
+        <v>598</v>
+      </c>
+      <c r="B135" t="s">
+        <v>599</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s" s="0">
-        <v>587</v>
-      </c>
-      <c r="B136" t="s" s="0">
-        <v>588</v>
+        <v>601</v>
+      </c>
+    </row>
+    <row r="136" ht="14.5">
+      <c r="A136" t="s">
+        <v>602</v>
+      </c>
+      <c r="B136" t="s">
+        <v>603</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s" s="0">
-        <v>591</v>
-      </c>
-      <c r="B137" t="s" s="0">
-        <v>592</v>
+        <v>605</v>
+      </c>
+    </row>
+    <row r="137" ht="14.5">
+      <c r="A137" t="s">
+        <v>606</v>
+      </c>
+      <c r="B137" t="s">
+        <v>607</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s" s="0">
-        <v>595</v>
-      </c>
-      <c r="B138" t="s" s="0">
-        <v>596</v>
+        <v>609</v>
+      </c>
+    </row>
+    <row r="138" ht="14.5">
+      <c r="A138" t="s">
+        <v>610</v>
+      </c>
+      <c r="B138" t="s">
+        <v>611</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s" s="0">
-        <v>599</v>
-      </c>
-      <c r="B139" t="s" s="0">
-        <v>600</v>
+        <v>613</v>
+      </c>
+    </row>
+    <row r="139" ht="14.5">
+      <c r="A139" t="s">
+        <v>614</v>
+      </c>
+      <c r="B139" t="s">
+        <v>615</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s" s="0">
-        <v>603</v>
-      </c>
-      <c r="B140" t="s" s="0">
-        <v>604</v>
+        <v>617</v>
+      </c>
+    </row>
+    <row r="140" ht="14.5">
+      <c r="A140" t="s">
+        <v>618</v>
+      </c>
+      <c r="B140" t="s">
+        <v>619</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s" s="0">
-        <v>607</v>
-      </c>
-      <c r="B141" t="s" s="0">
-        <v>608</v>
+        <v>621</v>
+      </c>
+    </row>
+    <row r="141" ht="14.5">
+      <c r="A141" t="s">
+        <v>622</v>
+      </c>
+      <c r="B141" t="s">
+        <v>623</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s" s="0">
-        <v>611</v>
-      </c>
-      <c r="B142" t="s" s="0">
-        <v>612</v>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="142" ht="14.5">
+      <c r="A142" t="s">
+        <v>626</v>
+      </c>
+      <c r="B142" t="s">
+        <v>627</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s" s="0">
-        <v>615</v>
-      </c>
-      <c r="B143" t="s" s="0">
-        <v>616</v>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="143" ht="14.5">
+      <c r="A143" t="s">
+        <v>630</v>
+      </c>
+      <c r="B143" t="s">
+        <v>631</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>617</v>
+        <v>632</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s" s="0">
-        <v>619</v>
-      </c>
-      <c r="B144" t="s" s="0">
-        <v>620</v>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="144" ht="14.5">
+      <c r="A144" t="s">
+        <v>634</v>
+      </c>
+      <c r="B144" t="s">
+        <v>635</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s" s="0">
-        <v>623</v>
-      </c>
-      <c r="B145" t="s" s="0">
-        <v>624</v>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="145" ht="14.5">
+      <c r="A145" t="s">
+        <v>638</v>
+      </c>
+      <c r="B145" t="s">
+        <v>639</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s" s="0">
-        <v>627</v>
-      </c>
-      <c r="B146" t="s" s="0">
-        <v>628</v>
+        <v>641</v>
+      </c>
+    </row>
+    <row r="146" ht="14.5">
+      <c r="A146" t="s">
+        <v>642</v>
+      </c>
+      <c r="B146" t="s">
+        <v>643</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s" s="0">
-        <v>631</v>
-      </c>
-      <c r="B147" t="s" s="0">
-        <v>632</v>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="147" ht="14.5">
+      <c r="A147" t="s">
+        <v>646</v>
+      </c>
+      <c r="B147" t="s">
+        <v>647</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>633</v>
+        <v>648</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s" s="0">
-        <v>635</v>
-      </c>
-      <c r="B148" t="s" s="0">
-        <v>636</v>
+        <v>649</v>
+      </c>
+    </row>
+    <row r="148" ht="14.5">
+      <c r="A148" t="s">
+        <v>650</v>
+      </c>
+      <c r="B148" t="s">
+        <v>651</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s" s="0">
-        <v>639</v>
-      </c>
-      <c r="B149" t="s" s="0">
-        <v>640</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="149" ht="14.5">
+      <c r="A149" t="s">
+        <v>654</v>
+      </c>
+      <c r="B149" t="s">
+        <v>655</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s" s="0">
-        <v>643</v>
-      </c>
-      <c r="B150" t="s" s="0">
-        <v>644</v>
+        <v>657</v>
+      </c>
+    </row>
+    <row r="150" ht="14.5">
+      <c r="A150" t="s">
+        <v>658</v>
+      </c>
+      <c r="B150" t="s">
+        <v>659</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s" s="0">
-        <v>647</v>
-      </c>
-      <c r="B151" t="s" s="0">
-        <v>648</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="151" ht="14.5">
+      <c r="A151" t="s">
+        <v>662</v>
+      </c>
+      <c r="B151" t="s">
+        <v>663</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s" s="0">
-        <v>651</v>
-      </c>
-      <c r="B152" t="s" s="0">
-        <v>652</v>
+        <v>665</v>
+      </c>
+    </row>
+    <row r="152" ht="14.5">
+      <c r="A152" t="s">
+        <v>666</v>
+      </c>
+      <c r="B152" t="s">
+        <v>667</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s" s="0">
-        <v>655</v>
+        <v>669</v>
+      </c>
+    </row>
+    <row r="153" ht="14.5">
+      <c r="B153" t="s">
+        <v>670</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>656</v>
+        <v>671</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s" s="0">
-        <v>658</v>
+        <v>672</v>
+      </c>
+    </row>
+    <row r="154" ht="14.5">
+      <c r="B154" t="s">
+        <v>673</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s" s="0">
-        <v>661</v>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="155" ht="14.5">
+      <c r="B155" t="s">
+        <v>676</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s" s="0">
-        <v>664</v>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="156" ht="14.5">
+      <c r="B156" t="s">
+        <v>679</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s" s="0">
-        <v>667</v>
+        <v>681</v>
+      </c>
+    </row>
+    <row r="157" ht="14.5">
+      <c r="B157" t="s">
+        <v>682</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>668</v>
+        <v>683</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s" s="0">
-        <v>670</v>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="158" ht="14.5">
+      <c r="B158" t="s">
+        <v>685</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>671</v>
+        <v>686</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="159" ht="14.5">
       <c r="C159" s="6" t="s">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="160" ht="14.5">
       <c r="C160" s="6" t="s">
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="161" ht="14.5">
       <c r="C161" s="6" t="s">
-        <v>677</v>
+        <v>692</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="162" ht="14.5">
       <c r="C162" s="6" t="s">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="163" ht="14.5">
       <c r="C163" s="6" t="s">
-        <v>681</v>
+        <v>696</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="164" ht="14.5">
       <c r="C164" s="6" t="s">
-        <v>683</v>
+        <v>698</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="165" ht="14.5">
       <c r="C165" s="6" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="166" ht="14.5">
       <c r="C166" s="6" t="s">
-        <v>687</v>
+        <v>702</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="167" ht="14.5">
       <c r="C167" s="6" t="s">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="168" ht="14.5">
       <c r="C168" s="6" t="s">
-        <v>691</v>
+        <v>706</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="169" ht="14.5">
       <c r="C169" s="6" t="s">
-        <v>693</v>
+        <v>708</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="170" spans="3:4" x14ac:dyDescent="0.35">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="170" ht="14.5">
       <c r="C170" s="6" t="s">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="171" spans="3:4" x14ac:dyDescent="0.35">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="171" ht="14.5">
       <c r="D171" s="5" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="172" spans="3:4" x14ac:dyDescent="0.35">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="172" ht="14.5">
       <c r="D172" s="5" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="173" spans="3:4" x14ac:dyDescent="0.35">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="173" ht="14.5">
       <c r="D173" s="5" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="174" spans="3:4" x14ac:dyDescent="0.35">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="174" ht="14.5">
       <c r="D174" s="5" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="175" spans="3:4" x14ac:dyDescent="0.35">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="175" ht="14.5">
       <c r="D175" s="5" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="176" spans="3:4" x14ac:dyDescent="0.35">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="176" ht="14.5">
       <c r="D176" s="5" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.35">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="177" ht="14.5">
       <c r="D177" s="5" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.35">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="178" ht="14.5">
       <c r="D178" s="5" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.35">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="179" ht="14.5">
       <c r="D179" s="5" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.35">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="180" ht="14.5">
       <c r="D180" s="5" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.35">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="181" ht="14.5">
       <c r="D181" s="5" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.35">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="182" ht="14.5">
       <c r="D182" s="5" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.35">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="183" ht="14.5">
       <c r="D183" s="5" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.35">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="184" ht="14.5">
       <c r="D184" s="5" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.35">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="185" ht="14.5">
       <c r="D185" s="5" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.35">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="186" ht="14.5">
       <c r="D186" s="5" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.35">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="187" ht="14.5">
       <c r="D187" s="5" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.35">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="188" ht="14.5">
       <c r="D188" s="5" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.35">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="189" ht="14.5">
       <c r="D189" s="5" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="190" ht="14.5">
       <c r="D190" s="5" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.35">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="191" ht="14.5">
       <c r="D191" s="5" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.35">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="192" ht="14.5">
       <c r="D192" s="5" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.35">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="193" ht="14.5">
       <c r="D193" s="5" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.35">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="194" ht="14.5">
       <c r="D194" s="5" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.35">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="195" ht="14.5">
       <c r="D195" s="5" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.35">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="196" ht="14.5">
       <c r="D196" s="5" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.35">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="197" ht="14.5">
       <c r="D197" s="5" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.35">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="198" ht="14.5">
       <c r="D198" s="5" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.35">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="199" ht="14.5">
       <c r="D199" s="5" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.35">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="200" ht="14.5">
       <c r="D200" s="5" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.35">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="201" ht="14.5">
       <c r="D201" s="5" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2250,12 +2250,37 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Charlie79</t>
+  </si>
+  <si>
+    <t>Milo56</t>
+  </si>
+  <si>
+    <t>Taffy54</t>
+  </si>
+  <si>
+    <t>Cutie43</t>
+  </si>
+  <si>
+    <t>Cinder43</t>
+  </si>
+  <si>
+    <t>pony35</t>
+  </si>
+  <si>
+    <t>fury28</t>
+  </si>
+  <si>
+    <t>Sheep28</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2297,7 +2322,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2307,6 +2332,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2607,20 +2641,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.726563" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
+    <col min="12" max="16384" style="1" width="8.726563"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5">
@@ -2676,10 +2711,10 @@
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -2707,7 +2742,7 @@
       </c>
     </row>
     <row r="5" ht="15.5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2716,7 +2751,7 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="11" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -2724,7 +2759,7 @@
       </c>
     </row>
     <row r="6" ht="15.5">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2733,7 +2768,7 @@
       <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -2753,7 +2788,7 @@
       <c r="D7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="14" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2770,7 +2805,7 @@
       <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="15" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2807,73 +2842,81 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.45313" customWidth="1"/>
-    <col min="3" max="3" width="35.63281" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.72656" customWidth="1"/>
-    <col min="6" max="6" width="32.17969" customWidth="1"/>
-    <col min="7" max="7" width="33.63281" customWidth="1"/>
-    <col min="8" max="8" width="31.26953" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.45313"/>
+    <col min="3" max="3" customWidth="true" width="35.63281"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.72656"/>
+    <col min="6" max="6" customWidth="true" width="32.17969"/>
+    <col min="7" max="7" customWidth="true" width="33.63281"/>
+    <col min="8" max="8" customWidth="true" width="31.26953"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>56</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>57</v>
       </c>
+      <c r="D2" t="s" s="0">
+        <v>750</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s" s="0">
         <v>57</v>
       </c>
+      <c r="D3" t="s" s="0">
+        <v>57</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4"/>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s" s="0">
         <v>57</v>
       </c>
     </row>
@@ -2884,48 +2927,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984" customWidth="1"/>
-    <col min="2" max="2" width="17.54297" customWidth="1"/>
-    <col min="3" max="3" width="17.36328" customWidth="1"/>
-    <col min="4" max="5" width="17.26953" customWidth="1"/>
-    <col min="6" max="6" width="17.17969" customWidth="1"/>
-    <col min="7" max="7" width="15.36328" customWidth="1"/>
-    <col min="8" max="8" width="17.17969" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984"/>
+    <col min="2" max="2" customWidth="true" width="17.54297"/>
+    <col min="3" max="3" customWidth="true" width="17.36328"/>
+    <col min="4" max="5" customWidth="true" width="17.26953"/>
+    <col min="6" max="6" customWidth="true" width="17.17969"/>
+    <col min="7" max="7" customWidth="true" width="15.36328"/>
+    <col min="8" max="8" customWidth="true" width="17.17969"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.5">
       <c r="A1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>65</v>
       </c>
     </row>
     <row r="2" ht="14.5">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2936,10 +2980,10 @@
       </c>
     </row>
     <row r="3" ht="14.5">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2950,10 +2994,10 @@
       </c>
     </row>
     <row r="4" ht="14.5">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2964,10 +3008,10 @@
       </c>
     </row>
     <row r="5" ht="14.5">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>78</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2978,10 +3022,10 @@
       </c>
     </row>
     <row r="6" ht="14.5">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2992,10 +3036,10 @@
       </c>
     </row>
     <row r="7" ht="14.5">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3006,10 +3050,10 @@
       </c>
     </row>
     <row r="8" ht="14.5">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>91</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3020,10 +3064,10 @@
       </c>
     </row>
     <row r="9" ht="14.5">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3034,10 +3078,10 @@
       </c>
     </row>
     <row r="10" ht="14.5">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>99</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3048,10 +3092,10 @@
       </c>
     </row>
     <row r="11" ht="14.5">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3062,10 +3106,10 @@
       </c>
     </row>
     <row r="12" ht="14.5">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>107</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3076,10 +3120,10 @@
       </c>
     </row>
     <row r="13" ht="14.5">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3090,10 +3134,10 @@
       </c>
     </row>
     <row r="14" ht="14.5">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>115</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3104,10 +3148,10 @@
       </c>
     </row>
     <row r="15" ht="14.5">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>119</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3118,10 +3162,10 @@
       </c>
     </row>
     <row r="16" ht="14.5">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>123</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3132,10 +3176,10 @@
       </c>
     </row>
     <row r="17" ht="14.5">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>127</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3146,13 +3190,13 @@
       </c>
     </row>
     <row r="18" ht="14.5">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="13" t="s">
         <v>132</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -3160,10 +3204,10 @@
       </c>
     </row>
     <row r="19" ht="14.5">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>135</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -3174,10 +3218,10 @@
       </c>
     </row>
     <row r="20" ht="14.5">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>138</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>139</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -3188,10 +3232,10 @@
       </c>
     </row>
     <row r="21" ht="14.5">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>143</v>
       </c>
       <c r="C21" s="6" t="s">
@@ -3202,10 +3246,10 @@
       </c>
     </row>
     <row r="22" ht="14.5">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>147</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -3216,10 +3260,10 @@
       </c>
     </row>
     <row r="23" ht="14.5">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>151</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -3230,10 +3274,10 @@
       </c>
     </row>
     <row r="24" ht="14.5">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>154</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>155</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -3244,10 +3288,10 @@
       </c>
     </row>
     <row r="25" ht="14.5">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>159</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3258,10 +3302,10 @@
       </c>
     </row>
     <row r="26" ht="14.5">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>163</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3272,10 +3316,10 @@
       </c>
     </row>
     <row r="27" ht="14.5">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>166</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>167</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3286,10 +3330,10 @@
       </c>
     </row>
     <row r="28" ht="14.5">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>171</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3300,10 +3344,10 @@
       </c>
     </row>
     <row r="29" ht="14.5">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>175</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3314,10 +3358,10 @@
       </c>
     </row>
     <row r="30" ht="14.5">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3328,10 +3372,10 @@
       </c>
     </row>
     <row r="31" ht="14.5">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>182</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>183</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3342,10 +3386,10 @@
       </c>
     </row>
     <row r="32" ht="14.5">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>186</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>187</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3356,10 +3400,10 @@
       </c>
     </row>
     <row r="33" ht="14.5">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>190</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>191</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3370,10 +3414,10 @@
       </c>
     </row>
     <row r="34" ht="14.5">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>195</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3384,10 +3428,10 @@
       </c>
     </row>
     <row r="35" ht="14.5">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>198</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>199</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3398,10 +3442,10 @@
       </c>
     </row>
     <row r="36" ht="14.5">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>202</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>203</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3412,10 +3456,10 @@
       </c>
     </row>
     <row r="37" ht="14.5">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>207</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3426,10 +3470,10 @@
       </c>
     </row>
     <row r="38" ht="14.5">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>211</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3440,10 +3484,10 @@
       </c>
     </row>
     <row r="39" ht="14.5">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>215</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3454,10 +3498,10 @@
       </c>
     </row>
     <row r="40" ht="14.5">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>218</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>219</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3468,10 +3512,10 @@
       </c>
     </row>
     <row r="41" ht="14.5">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>222</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>223</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3482,10 +3526,10 @@
       </c>
     </row>
     <row r="42" ht="14.5">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>227</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3496,10 +3540,10 @@
       </c>
     </row>
     <row r="43" ht="14.5">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>230</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>231</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3510,10 +3554,10 @@
       </c>
     </row>
     <row r="44" ht="14.5">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>234</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>235</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3524,10 +3568,10 @@
       </c>
     </row>
     <row r="45" ht="14.5">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>238</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>239</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3538,10 +3582,10 @@
       </c>
     </row>
     <row r="46" ht="14.5">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>242</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>243</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3552,10 +3596,10 @@
       </c>
     </row>
     <row r="47" ht="14.5">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>247</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3566,10 +3610,10 @@
       </c>
     </row>
     <row r="48" ht="14.5">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>250</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>251</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3580,10 +3624,10 @@
       </c>
     </row>
     <row r="49" ht="14.5">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>254</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>255</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3594,10 +3638,10 @@
       </c>
     </row>
     <row r="50" ht="14.5">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>259</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3608,10 +3652,10 @@
       </c>
     </row>
     <row r="51" ht="14.5">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>262</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>263</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3622,10 +3666,10 @@
       </c>
     </row>
     <row r="52" ht="14.5">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>266</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>267</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3636,10 +3680,10 @@
       </c>
     </row>
     <row r="53" ht="14.5">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>270</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3650,10 +3694,10 @@
       </c>
     </row>
     <row r="54" ht="14.5">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>275</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3664,10 +3708,10 @@
       </c>
     </row>
     <row r="55" ht="14.5">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>279</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3678,10 +3722,10 @@
       </c>
     </row>
     <row r="56" ht="14.5">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>282</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>283</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3692,10 +3736,10 @@
       </c>
     </row>
     <row r="57" ht="14.5">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>286</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>287</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3706,10 +3750,10 @@
       </c>
     </row>
     <row r="58" ht="14.5">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>290</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>291</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3720,10 +3764,10 @@
       </c>
     </row>
     <row r="59" ht="14.5">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>294</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>295</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3734,10 +3778,10 @@
       </c>
     </row>
     <row r="60" ht="14.5">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>298</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>299</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3748,10 +3792,10 @@
       </c>
     </row>
     <row r="61" ht="14.5">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>302</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>303</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3762,10 +3806,10 @@
       </c>
     </row>
     <row r="62" ht="14.5">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>306</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>307</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3776,10 +3820,10 @@
       </c>
     </row>
     <row r="63" ht="14.5">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>311</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -3790,10 +3834,10 @@
       </c>
     </row>
     <row r="64" ht="14.5">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>314</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>315</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -3804,10 +3848,10 @@
       </c>
     </row>
     <row r="65" ht="14.5">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>318</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>319</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -3818,10 +3862,10 @@
       </c>
     </row>
     <row r="66" ht="14.5">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>322</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>323</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -3832,10 +3876,10 @@
       </c>
     </row>
     <row r="67" ht="14.5">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>326</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>327</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -3846,10 +3890,10 @@
       </c>
     </row>
     <row r="68" ht="14.5">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>330</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>331</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -3860,10 +3904,10 @@
       </c>
     </row>
     <row r="69" ht="14.5">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>334</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>335</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -3874,10 +3918,10 @@
       </c>
     </row>
     <row r="70" ht="14.5">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>338</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>339</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -3888,10 +3932,10 @@
       </c>
     </row>
     <row r="71" ht="14.5">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>342</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>343</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -3902,10 +3946,10 @@
       </c>
     </row>
     <row r="72" ht="14.5">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>346</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>347</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -3916,10 +3960,10 @@
       </c>
     </row>
     <row r="73" ht="14.5">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>350</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>351</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -3930,10 +3974,10 @@
       </c>
     </row>
     <row r="74" ht="14.5">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>354</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>355</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -3944,10 +3988,10 @@
       </c>
     </row>
     <row r="75" ht="14.5">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>358</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>359</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -3958,10 +4002,10 @@
       </c>
     </row>
     <row r="76" ht="14.5">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>362</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>363</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -3972,10 +4016,10 @@
       </c>
     </row>
     <row r="77" ht="14.5">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>366</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>367</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -3986,10 +4030,10 @@
       </c>
     </row>
     <row r="78" ht="14.5">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>370</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>371</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4000,10 +4044,10 @@
       </c>
     </row>
     <row r="79" ht="14.5">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>374</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>375</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4014,10 +4058,10 @@
       </c>
     </row>
     <row r="80" ht="14.5">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>378</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>379</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4028,10 +4072,10 @@
       </c>
     </row>
     <row r="81" ht="14.5">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>383</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4042,10 +4086,10 @@
       </c>
     </row>
     <row r="82" ht="14.5">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>387</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4056,10 +4100,10 @@
       </c>
     </row>
     <row r="83" ht="14.5">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>390</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>391</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4070,10 +4114,10 @@
       </c>
     </row>
     <row r="84" ht="14.5">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>395</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4084,10 +4128,10 @@
       </c>
     </row>
     <row r="85" ht="14.5">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>399</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4098,10 +4142,10 @@
       </c>
     </row>
     <row r="86" ht="14.5">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>403</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4112,10 +4156,10 @@
       </c>
     </row>
     <row r="87" ht="14.5">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>406</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>407</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4126,10 +4170,10 @@
       </c>
     </row>
     <row r="88" ht="14.5">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>410</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>411</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4140,10 +4184,10 @@
       </c>
     </row>
     <row r="89" ht="14.5">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>414</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>415</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4154,10 +4198,10 @@
       </c>
     </row>
     <row r="90" ht="14.5">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>418</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>419</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4168,10 +4212,10 @@
       </c>
     </row>
     <row r="91" ht="14.5">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>423</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4182,10 +4226,10 @@
       </c>
     </row>
     <row r="92" ht="14.5">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>427</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4196,10 +4240,10 @@
       </c>
     </row>
     <row r="93" ht="14.5">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>430</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>431</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4210,10 +4254,10 @@
       </c>
     </row>
     <row r="94" ht="14.5">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>435</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4224,10 +4268,10 @@
       </c>
     </row>
     <row r="95" ht="14.5">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>438</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>439</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4238,10 +4282,10 @@
       </c>
     </row>
     <row r="96" ht="14.5">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>443</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4252,10 +4296,10 @@
       </c>
     </row>
     <row r="97" ht="14.5">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>447</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4266,10 +4310,10 @@
       </c>
     </row>
     <row r="98" ht="14.5">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>450</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>451</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4280,10 +4324,10 @@
       </c>
     </row>
     <row r="99" ht="14.5">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>454</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>455</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4294,10 +4338,10 @@
       </c>
     </row>
     <row r="100" ht="14.5">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>458</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>459</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4308,10 +4352,10 @@
       </c>
     </row>
     <row r="101" ht="14.5">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>463</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4322,10 +4366,10 @@
       </c>
     </row>
     <row r="102" ht="14.5">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>466</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>467</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4336,10 +4380,10 @@
       </c>
     </row>
     <row r="103" ht="14.5">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>470</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>471</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4350,10 +4394,10 @@
       </c>
     </row>
     <row r="104" ht="14.5">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>474</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>475</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4364,10 +4408,10 @@
       </c>
     </row>
     <row r="105" ht="14.5">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>478</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>479</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4378,10 +4422,10 @@
       </c>
     </row>
     <row r="106" ht="14.5">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>483</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4392,10 +4436,10 @@
       </c>
     </row>
     <row r="107" ht="14.5">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>486</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>487</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4406,10 +4450,10 @@
       </c>
     </row>
     <row r="108" ht="14.5">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>491</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4420,10 +4464,10 @@
       </c>
     </row>
     <row r="109" ht="14.5">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>494</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>495</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4434,10 +4478,10 @@
       </c>
     </row>
     <row r="110" ht="14.5">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>498</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>499</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4448,10 +4492,10 @@
       </c>
     </row>
     <row r="111" ht="14.5">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>502</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>503</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4462,10 +4506,10 @@
       </c>
     </row>
     <row r="112" ht="14.5">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>506</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>507</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4476,10 +4520,10 @@
       </c>
     </row>
     <row r="113" ht="14.5">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>510</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>511</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4490,10 +4534,10 @@
       </c>
     </row>
     <row r="114" ht="14.5">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>514</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>515</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4504,10 +4548,10 @@
       </c>
     </row>
     <row r="115" ht="14.5">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>518</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>519</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4518,10 +4562,10 @@
       </c>
     </row>
     <row r="116" ht="14.5">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>522</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>523</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4532,10 +4576,10 @@
       </c>
     </row>
     <row r="117" ht="14.5">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>526</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>527</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4546,10 +4590,10 @@
       </c>
     </row>
     <row r="118" ht="14.5">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>530</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>531</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4560,10 +4604,10 @@
       </c>
     </row>
     <row r="119" ht="14.5">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>534</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>535</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4574,10 +4618,10 @@
       </c>
     </row>
     <row r="120" ht="14.5">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>538</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>539</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4588,10 +4632,10 @@
       </c>
     </row>
     <row r="121" ht="14.5">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>542</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>543</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4602,10 +4646,10 @@
       </c>
     </row>
     <row r="122" ht="14.5">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>546</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>547</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4616,10 +4660,10 @@
       </c>
     </row>
     <row r="123" ht="14.5">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>550</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>551</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4630,10 +4674,10 @@
       </c>
     </row>
     <row r="124" ht="14.5">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>555</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4644,10 +4688,10 @@
       </c>
     </row>
     <row r="125" ht="14.5">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>558</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>559</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4658,10 +4702,10 @@
       </c>
     </row>
     <row r="126" ht="14.5">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>562</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>563</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4672,10 +4716,10 @@
       </c>
     </row>
     <row r="127" ht="14.5">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>566</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>567</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4686,10 +4730,10 @@
       </c>
     </row>
     <row r="128" ht="14.5">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>570</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>571</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4700,10 +4744,10 @@
       </c>
     </row>
     <row r="129" ht="14.5">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>574</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>575</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4714,10 +4758,10 @@
       </c>
     </row>
     <row r="130" ht="14.5">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>578</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>579</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4728,10 +4772,10 @@
       </c>
     </row>
     <row r="131" ht="14.5">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>582</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>583</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4742,10 +4786,10 @@
       </c>
     </row>
     <row r="132" ht="14.5">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>586</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>587</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4756,10 +4800,10 @@
       </c>
     </row>
     <row r="133" ht="14.5">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>590</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>591</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4770,10 +4814,10 @@
       </c>
     </row>
     <row r="134" ht="14.5">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>594</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>595</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4784,10 +4828,10 @@
       </c>
     </row>
     <row r="135" ht="14.5">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>598</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>599</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -4798,10 +4842,10 @@
       </c>
     </row>
     <row r="136" ht="14.5">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>602</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>603</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -4812,10 +4856,10 @@
       </c>
     </row>
     <row r="137" ht="14.5">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>606</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>607</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -4826,10 +4870,10 @@
       </c>
     </row>
     <row r="138" ht="14.5">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>610</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>611</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -4840,10 +4884,10 @@
       </c>
     </row>
     <row r="139" ht="14.5">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>614</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>615</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -4854,10 +4898,10 @@
       </c>
     </row>
     <row r="140" ht="14.5">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>618</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>619</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -4868,10 +4912,10 @@
       </c>
     </row>
     <row r="141" ht="14.5">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>622</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>623</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -4882,10 +4926,10 @@
       </c>
     </row>
     <row r="142" ht="14.5">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>626</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>627</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -4896,10 +4940,10 @@
       </c>
     </row>
     <row r="143" ht="14.5">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>630</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>631</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -4910,10 +4954,10 @@
       </c>
     </row>
     <row r="144" ht="14.5">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>634</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>635</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -4924,10 +4968,10 @@
       </c>
     </row>
     <row r="145" ht="14.5">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>638</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>639</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -4938,10 +4982,10 @@
       </c>
     </row>
     <row r="146" ht="14.5">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>642</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>643</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -4952,10 +4996,10 @@
       </c>
     </row>
     <row r="147" ht="14.5">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>646</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>647</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -4966,10 +5010,10 @@
       </c>
     </row>
     <row r="148" ht="14.5">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>650</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>651</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -4980,10 +5024,10 @@
       </c>
     </row>
     <row r="149" ht="14.5">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>654</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>655</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -4994,10 +5038,10 @@
       </c>
     </row>
     <row r="150" ht="14.5">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>658</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>659</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5008,10 +5052,10 @@
       </c>
     </row>
     <row r="151" ht="14.5">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>662</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>663</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5022,10 +5066,10 @@
       </c>
     </row>
     <row r="152" ht="14.5">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>666</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>667</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5036,7 +5080,7 @@
       </c>
     </row>
     <row r="153" ht="14.5">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>670</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5047,7 +5091,7 @@
       </c>
     </row>
     <row r="154" ht="14.5">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>673</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5058,7 +5102,7 @@
       </c>
     </row>
     <row r="155" ht="14.5">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>676</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5069,7 +5113,7 @@
       </c>
     </row>
     <row r="156" ht="14.5">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>679</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5080,7 +5124,7 @@
       </c>
     </row>
     <row r="157" ht="14.5">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>682</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5091,7 +5135,7 @@
       </c>
     </row>
     <row r="158" ht="14.5">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>685</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -1,27 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\workspace\testing\animalBiome_Automation\src\test\resources\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3150" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3090" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
     <sheet name="PET_NAME" sheetId="2" r:id="rId2"/>
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A28:G35"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="773">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2252,36 +2248,101 @@
     <t>Nexra</t>
   </si>
   <si>
-    <t>Charlie79</t>
-  </si>
-  <si>
-    <t>Milo56</t>
-  </si>
-  <si>
-    <t>Taffy54</t>
-  </si>
-  <si>
-    <t>Cutie43</t>
-  </si>
-  <si>
-    <t>Cinder43</t>
-  </si>
-  <si>
-    <t>pony35</t>
-  </si>
-  <si>
-    <t>fury28</t>
-  </si>
-  <si>
-    <t>Sheep28</t>
+    <t>JDAGGA</t>
+  </si>
+  <si>
+    <t>AV9GCG</t>
+  </si>
+  <si>
+    <t>NKNGH7</t>
+  </si>
+  <si>
+    <t>J6MGVG</t>
+  </si>
+  <si>
+    <t>4F66HY</t>
+  </si>
+  <si>
+    <t>HHUXJN</t>
+  </si>
+  <si>
+    <t>GUMCDP</t>
+  </si>
+  <si>
+    <t>FVRDEY</t>
+  </si>
+  <si>
+    <t>CM4KEX</t>
+  </si>
+  <si>
+    <t>MVY7E7</t>
+  </si>
+  <si>
+    <t>E4FR3M</t>
+  </si>
+  <si>
+    <t>EMDDGE</t>
+  </si>
+  <si>
+    <t>4PEEDE</t>
+  </si>
+  <si>
+    <t>MT3YXX</t>
+  </si>
+  <si>
+    <t>XHFYNX</t>
+  </si>
+  <si>
+    <t>ENJTEH</t>
+  </si>
+  <si>
+    <t>VJFKAH</t>
+  </si>
+  <si>
+    <t>RVYMTD</t>
+  </si>
+  <si>
+    <t>HTD7FV</t>
+  </si>
+  <si>
+    <t>D7RM3G</t>
+  </si>
+  <si>
+    <t>DPXN44</t>
+  </si>
+  <si>
+    <t>EVAYHN</t>
+  </si>
+  <si>
+    <t>GTGXFA</t>
+  </si>
+  <si>
+    <t>HC7FGA</t>
+  </si>
+  <si>
+    <t>6G4AUX</t>
+  </si>
+  <si>
+    <t>FKCAP9</t>
+  </si>
+  <si>
+    <t>6C9EJE</t>
+  </si>
+  <si>
+    <t>HJ6NJX</t>
+  </si>
+  <si>
+    <t>PA7EFN</t>
+  </si>
+  <si>
+    <t>MJAPC7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2293,6 +2354,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2315,14 +2383,20 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2330,25 +2404,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2"/>
     <cellStyle name="Normal 3" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2357,10 +2442,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2492,7 +2577,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2516,11 +2600,10 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2529,13 +2612,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2611,7 +2694,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2631,34 +2713,35 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K81"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
-    <col min="12" max="16384" style="1" width="8.726563"/>
+    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2690,7 +2773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="15.5">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2707,7 +2790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="15.5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -2724,7 +2807,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="15.5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -2741,7 +2824,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" ht="15.5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
@@ -2758,7 +2841,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="15.5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>30</v>
       </c>
@@ -2775,7 +2858,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" ht="15.5">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
@@ -2792,7 +2875,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" ht="15.5">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -2809,167 +2892,266 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" ht="15.5">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C9" t="s">
+        <v>765</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>749</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" ht="15.5">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C10" t="s">
+        <v>766</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>750</v>
+      </c>
       <c r="E10" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" ht="15.5">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C11" t="s">
+        <v>767</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>751</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="15.5">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="C12" t="s">
+        <v>768</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>752</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="78" ht="15.5">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E13" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="E14" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E15" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E16" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="78" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F78" s="3"/>
     </row>
-    <row r="81" ht="15.5">
+    <row r="81" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F81" s="3"/>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.45313"/>
-    <col min="3" max="3" customWidth="true" width="35.63281"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.72656"/>
-    <col min="6" max="6" customWidth="true" width="32.17969"/>
-    <col min="7" max="7" customWidth="true" width="33.63281"/>
-    <col min="8" max="8" customWidth="true" width="31.26953"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.7265625" customWidth="1"/>
+    <col min="6" max="6" width="32.1796875" customWidth="1"/>
+    <col min="7" max="7" width="33.6328125" customWidth="1"/>
+    <col min="8" max="8" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s" s="0">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>57</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+      <c r="B3" t="s">
         <v>57</v>
       </c>
-      <c r="B3" t="s" s="0">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="B4" t="s">
         <v>57</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984"/>
-    <col min="2" max="2" customWidth="true" width="17.54297"/>
-    <col min="3" max="3" customWidth="true" width="17.36328"/>
-    <col min="4" max="5" customWidth="true" width="17.26953"/>
-    <col min="6" max="6" customWidth="true" width="17.17969"/>
-    <col min="7" max="7" customWidth="true" width="15.36328"/>
-    <col min="8" max="8" customWidth="true" width="17.17969"/>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" customWidth="1"/>
+    <col min="4" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" ht="14.5">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2979,11 +3161,11 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" ht="14.5">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>70</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2993,11 +3175,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" ht="14.5">
-      <c r="A4" t="s" s="0">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>74</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3007,11 +3189,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" ht="14.5">
-      <c r="A5" t="s" s="0">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>78</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3021,11 +3203,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" ht="14.5">
-      <c r="A6" t="s" s="0">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>82</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3035,11 +3217,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" ht="14.5">
-      <c r="A7" t="s" s="0">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>86</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3049,11 +3231,11 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" ht="14.5">
-      <c r="A8" t="s" s="0">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>90</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>91</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3063,11 +3245,11 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" ht="14.5">
-      <c r="A9" t="s" s="0">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>94</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3077,11 +3259,11 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" ht="14.5">
-      <c r="A10" t="s" s="0">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>98</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>99</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3091,11 +3273,11 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" ht="14.5">
-      <c r="A11" t="s" s="0">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>102</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3105,11 +3287,11 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" ht="14.5">
-      <c r="A12" t="s" s="0">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>106</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>107</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3119,11 +3301,11 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" ht="14.5">
-      <c r="A13" t="s" s="0">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>110</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3133,11 +3315,11 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" ht="14.5">
-      <c r="A14" t="s" s="0">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>114</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>115</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3147,11 +3329,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="15" ht="14.5">
-      <c r="A15" t="s" s="0">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>118</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>119</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3161,11 +3343,11 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" ht="14.5">
-      <c r="A16" t="s" s="0">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>122</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>123</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3175,11 +3357,11 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" ht="14.5">
-      <c r="A17" t="s" s="0">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>126</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>127</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3189,11 +3371,11 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" ht="14.5">
-      <c r="A18" t="s" s="0">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>130</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>131</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -3203,53 +3385,53 @@
         <v>133</v>
       </c>
     </row>
-    <row r="19" ht="14.5">
-      <c r="A19" t="s" s="0">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>134</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="16" t="s">
         <v>136</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="20" ht="14.5">
-      <c r="A20" t="s" s="0">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>138</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="17" t="s">
         <v>140</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="21" ht="14.5">
-      <c r="A21" t="s" s="0">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>142</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B21" t="s">
         <v>143</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="18" t="s">
         <v>144</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="22" ht="14.5">
-      <c r="A22" t="s" s="0">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>146</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="B22" t="s">
         <v>147</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -3259,11 +3441,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" ht="14.5">
-      <c r="A23" t="s" s="0">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>150</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>151</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -3273,11 +3455,11 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" ht="14.5">
-      <c r="A24" t="s" s="0">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>154</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>155</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -3287,11 +3469,11 @@
         <v>157</v>
       </c>
     </row>
-    <row r="25" ht="14.5">
-      <c r="A25" t="s" s="0">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>158</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B25" t="s">
         <v>159</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3301,11 +3483,11 @@
         <v>161</v>
       </c>
     </row>
-    <row r="26" ht="14.5">
-      <c r="A26" t="s" s="0">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>162</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>163</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3315,11 +3497,11 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" ht="14.5">
-      <c r="A27" t="s" s="0">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>166</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>167</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3329,11 +3511,11 @@
         <v>169</v>
       </c>
     </row>
-    <row r="28" ht="14.5">
-      <c r="A28" t="s" s="0">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>170</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>171</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3343,11 +3525,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="29" ht="14.5">
-      <c r="A29" t="s" s="0">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>174</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="B29" t="s">
         <v>175</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3357,11 +3539,11 @@
         <v>177</v>
       </c>
     </row>
-    <row r="30" ht="14.5">
-      <c r="A30" t="s" s="0">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>178</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="B30" t="s">
         <v>179</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3371,11 +3553,11 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" ht="14.5">
-      <c r="A31" t="s" s="0">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>182</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>183</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3385,11 +3567,11 @@
         <v>185</v>
       </c>
     </row>
-    <row r="32" ht="14.5">
-      <c r="A32" t="s" s="0">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>186</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>187</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3399,11 +3581,11 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" ht="14.5">
-      <c r="A33" t="s" s="0">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>190</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>191</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3413,11 +3595,11 @@
         <v>193</v>
       </c>
     </row>
-    <row r="34" ht="14.5">
-      <c r="A34" t="s" s="0">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>194</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>195</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3427,11 +3609,11 @@
         <v>197</v>
       </c>
     </row>
-    <row r="35" ht="14.5">
-      <c r="A35" t="s" s="0">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>198</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B35" t="s">
         <v>199</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3441,11 +3623,11 @@
         <v>201</v>
       </c>
     </row>
-    <row r="36" ht="14.5">
-      <c r="A36" t="s" s="0">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>202</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="B36" t="s">
         <v>203</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3455,11 +3637,11 @@
         <v>205</v>
       </c>
     </row>
-    <row r="37" ht="14.5">
-      <c r="A37" t="s" s="0">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>206</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B37" t="s">
         <v>207</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3469,11 +3651,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="38" ht="14.5">
-      <c r="A38" t="s" s="0">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>210</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B38" t="s">
         <v>211</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3483,11 +3665,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="39" ht="14.5">
-      <c r="A39" t="s" s="0">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>214</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="B39" t="s">
         <v>215</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3497,11 +3679,11 @@
         <v>217</v>
       </c>
     </row>
-    <row r="40" ht="14.5">
-      <c r="A40" t="s" s="0">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>218</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="B40" t="s">
         <v>219</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3511,11 +3693,11 @@
         <v>221</v>
       </c>
     </row>
-    <row r="41" ht="14.5">
-      <c r="A41" t="s" s="0">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>222</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="B41" t="s">
         <v>223</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3525,11 +3707,11 @@
         <v>225</v>
       </c>
     </row>
-    <row r="42" ht="14.5">
-      <c r="A42" t="s" s="0">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>226</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="B42" t="s">
         <v>227</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3539,11 +3721,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="43" ht="14.5">
-      <c r="A43" t="s" s="0">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>230</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="B43" t="s">
         <v>231</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3553,11 +3735,11 @@
         <v>233</v>
       </c>
     </row>
-    <row r="44" ht="14.5">
-      <c r="A44" t="s" s="0">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>234</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B44" t="s">
         <v>235</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3567,11 +3749,11 @@
         <v>237</v>
       </c>
     </row>
-    <row r="45" ht="14.5">
-      <c r="A45" t="s" s="0">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>238</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="B45" t="s">
         <v>239</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3581,11 +3763,11 @@
         <v>241</v>
       </c>
     </row>
-    <row r="46" ht="14.5">
-      <c r="A46" t="s" s="0">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>242</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="B46" t="s">
         <v>243</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3595,11 +3777,11 @@
         <v>245</v>
       </c>
     </row>
-    <row r="47" ht="14.5">
-      <c r="A47" t="s" s="0">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>246</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B47" t="s">
         <v>247</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3609,11 +3791,11 @@
         <v>249</v>
       </c>
     </row>
-    <row r="48" ht="14.5">
-      <c r="A48" t="s" s="0">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>250</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="B48" t="s">
         <v>251</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3623,11 +3805,11 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" ht="14.5">
-      <c r="A49" t="s" s="0">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>254</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="B49" t="s">
         <v>255</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3637,11 +3819,11 @@
         <v>257</v>
       </c>
     </row>
-    <row r="50" ht="14.5">
-      <c r="A50" t="s" s="0">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>258</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="B50" t="s">
         <v>259</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3651,11 +3833,11 @@
         <v>261</v>
       </c>
     </row>
-    <row r="51" ht="14.5">
-      <c r="A51" t="s" s="0">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>262</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="B51" t="s">
         <v>263</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3665,11 +3847,11 @@
         <v>265</v>
       </c>
     </row>
-    <row r="52" ht="14.5">
-      <c r="A52" t="s" s="0">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>266</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="B52" t="s">
         <v>267</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3679,11 +3861,11 @@
         <v>269</v>
       </c>
     </row>
-    <row r="53" ht="14.5">
-      <c r="A53" t="s" s="0">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>270</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="B53" t="s">
         <v>271</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3693,11 +3875,11 @@
         <v>273</v>
       </c>
     </row>
-    <row r="54" ht="14.5">
-      <c r="A54" t="s" s="0">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>274</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="B54" t="s">
         <v>275</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3707,11 +3889,11 @@
         <v>277</v>
       </c>
     </row>
-    <row r="55" ht="14.5">
-      <c r="A55" t="s" s="0">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>278</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s">
         <v>279</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3721,11 +3903,11 @@
         <v>281</v>
       </c>
     </row>
-    <row r="56" ht="14.5">
-      <c r="A56" t="s" s="0">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>282</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="B56" t="s">
         <v>283</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3735,11 +3917,11 @@
         <v>285</v>
       </c>
     </row>
-    <row r="57" ht="14.5">
-      <c r="A57" t="s" s="0">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>286</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B57" t="s">
         <v>287</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3749,11 +3931,11 @@
         <v>289</v>
       </c>
     </row>
-    <row r="58" ht="14.5">
-      <c r="A58" t="s" s="0">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>290</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="B58" t="s">
         <v>291</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3763,11 +3945,11 @@
         <v>293</v>
       </c>
     </row>
-    <row r="59" ht="14.5">
-      <c r="A59" t="s" s="0">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>294</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="B59" t="s">
         <v>295</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3777,11 +3959,11 @@
         <v>297</v>
       </c>
     </row>
-    <row r="60" ht="14.5">
-      <c r="A60" t="s" s="0">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>298</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="B60" t="s">
         <v>299</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3791,11 +3973,11 @@
         <v>301</v>
       </c>
     </row>
-    <row r="61" ht="14.5">
-      <c r="A61" t="s" s="0">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>302</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="B61" t="s">
         <v>303</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3805,11 +3987,11 @@
         <v>305</v>
       </c>
     </row>
-    <row r="62" ht="14.5">
-      <c r="A62" t="s" s="0">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>306</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="B62" t="s">
         <v>307</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3819,11 +4001,11 @@
         <v>309</v>
       </c>
     </row>
-    <row r="63" ht="14.5">
-      <c r="A63" t="s" s="0">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>310</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="B63" t="s">
         <v>311</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -3833,11 +4015,11 @@
         <v>313</v>
       </c>
     </row>
-    <row r="64" ht="14.5">
-      <c r="A64" t="s" s="0">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>314</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="B64" t="s">
         <v>315</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -3847,11 +4029,11 @@
         <v>317</v>
       </c>
     </row>
-    <row r="65" ht="14.5">
-      <c r="A65" t="s" s="0">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>318</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="B65" t="s">
         <v>319</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -3861,11 +4043,11 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" ht="14.5">
-      <c r="A66" t="s" s="0">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>322</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="B66" t="s">
         <v>323</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -3875,11 +4057,11 @@
         <v>325</v>
       </c>
     </row>
-    <row r="67" ht="14.5">
-      <c r="A67" t="s" s="0">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>326</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="B67" t="s">
         <v>327</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -3889,11 +4071,11 @@
         <v>329</v>
       </c>
     </row>
-    <row r="68" ht="14.5">
-      <c r="A68" t="s" s="0">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>330</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B68" t="s">
         <v>331</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -3903,11 +4085,11 @@
         <v>333</v>
       </c>
     </row>
-    <row r="69" ht="14.5">
-      <c r="A69" t="s" s="0">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>334</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B69" t="s">
         <v>335</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -3917,11 +4099,11 @@
         <v>337</v>
       </c>
     </row>
-    <row r="70" ht="14.5">
-      <c r="A70" t="s" s="0">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>338</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="B70" t="s">
         <v>339</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -3931,11 +4113,11 @@
         <v>341</v>
       </c>
     </row>
-    <row r="71" ht="14.5">
-      <c r="A71" t="s" s="0">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>342</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="B71" t="s">
         <v>343</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -3945,11 +4127,11 @@
         <v>345</v>
       </c>
     </row>
-    <row r="72" ht="14.5">
-      <c r="A72" t="s" s="0">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>346</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="B72" t="s">
         <v>347</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -3959,11 +4141,11 @@
         <v>349</v>
       </c>
     </row>
-    <row r="73" ht="14.5">
-      <c r="A73" t="s" s="0">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>350</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="B73" t="s">
         <v>351</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -3973,11 +4155,11 @@
         <v>353</v>
       </c>
     </row>
-    <row r="74" ht="14.5">
-      <c r="A74" t="s" s="0">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>354</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="B74" t="s">
         <v>355</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -3987,11 +4169,11 @@
         <v>357</v>
       </c>
     </row>
-    <row r="75" ht="14.5">
-      <c r="A75" t="s" s="0">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>358</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="B75" t="s">
         <v>359</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4001,11 +4183,11 @@
         <v>361</v>
       </c>
     </row>
-    <row r="76" ht="14.5">
-      <c r="A76" t="s" s="0">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>362</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B76" t="s">
         <v>363</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4015,11 +4197,11 @@
         <v>365</v>
       </c>
     </row>
-    <row r="77" ht="14.5">
-      <c r="A77" t="s" s="0">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>366</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="B77" t="s">
         <v>367</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4029,11 +4211,11 @@
         <v>369</v>
       </c>
     </row>
-    <row r="78" ht="14.5">
-      <c r="A78" t="s" s="0">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>370</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B78" t="s">
         <v>371</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4043,11 +4225,11 @@
         <v>373</v>
       </c>
     </row>
-    <row r="79" ht="14.5">
-      <c r="A79" t="s" s="0">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>374</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="B79" t="s">
         <v>375</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4057,11 +4239,11 @@
         <v>377</v>
       </c>
     </row>
-    <row r="80" ht="14.5">
-      <c r="A80" t="s" s="0">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>378</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="B80" t="s">
         <v>379</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4071,11 +4253,11 @@
         <v>381</v>
       </c>
     </row>
-    <row r="81" ht="14.5">
-      <c r="A81" t="s" s="0">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>382</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B81" t="s">
         <v>383</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4085,11 +4267,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="82" ht="14.5">
-      <c r="A82" t="s" s="0">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>386</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="B82" t="s">
         <v>387</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4099,11 +4281,11 @@
         <v>389</v>
       </c>
     </row>
-    <row r="83" ht="14.5">
-      <c r="A83" t="s" s="0">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>390</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B83" t="s">
         <v>391</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4113,11 +4295,11 @@
         <v>393</v>
       </c>
     </row>
-    <row r="84" ht="14.5">
-      <c r="A84" t="s" s="0">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>394</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B84" t="s">
         <v>395</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4127,11 +4309,11 @@
         <v>397</v>
       </c>
     </row>
-    <row r="85" ht="14.5">
-      <c r="A85" t="s" s="0">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>398</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="B85" t="s">
         <v>399</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4141,11 +4323,11 @@
         <v>401</v>
       </c>
     </row>
-    <row r="86" ht="14.5">
-      <c r="A86" t="s" s="0">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>402</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="B86" t="s">
         <v>403</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4155,11 +4337,11 @@
         <v>405</v>
       </c>
     </row>
-    <row r="87" ht="14.5">
-      <c r="A87" t="s" s="0">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>406</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="B87" t="s">
         <v>407</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4169,11 +4351,11 @@
         <v>409</v>
       </c>
     </row>
-    <row r="88" ht="14.5">
-      <c r="A88" t="s" s="0">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>410</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="B88" t="s">
         <v>411</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4183,11 +4365,11 @@
         <v>413</v>
       </c>
     </row>
-    <row r="89" ht="14.5">
-      <c r="A89" t="s" s="0">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>414</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="B89" t="s">
         <v>415</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4197,11 +4379,11 @@
         <v>417</v>
       </c>
     </row>
-    <row r="90" ht="14.5">
-      <c r="A90" t="s" s="0">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>418</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="B90" t="s">
         <v>419</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4211,11 +4393,11 @@
         <v>421</v>
       </c>
     </row>
-    <row r="91" ht="14.5">
-      <c r="A91" t="s" s="0">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>422</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="B91" t="s">
         <v>423</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4225,11 +4407,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="92" ht="14.5">
-      <c r="A92" t="s" s="0">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>426</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="B92" t="s">
         <v>427</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4239,11 +4421,11 @@
         <v>429</v>
       </c>
     </row>
-    <row r="93" ht="14.5">
-      <c r="A93" t="s" s="0">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>430</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B93" t="s">
         <v>431</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4253,11 +4435,11 @@
         <v>433</v>
       </c>
     </row>
-    <row r="94" ht="14.5">
-      <c r="A94" t="s" s="0">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>434</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="B94" t="s">
         <v>435</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4267,11 +4449,11 @@
         <v>437</v>
       </c>
     </row>
-    <row r="95" ht="14.5">
-      <c r="A95" t="s" s="0">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>438</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="B95" t="s">
         <v>439</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4281,11 +4463,11 @@
         <v>441</v>
       </c>
     </row>
-    <row r="96" ht="14.5">
-      <c r="A96" t="s" s="0">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>442</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="B96" t="s">
         <v>443</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4295,11 +4477,11 @@
         <v>445</v>
       </c>
     </row>
-    <row r="97" ht="14.5">
-      <c r="A97" t="s" s="0">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
         <v>446</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="B97" t="s">
         <v>447</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4309,11 +4491,11 @@
         <v>449</v>
       </c>
     </row>
-    <row r="98" ht="14.5">
-      <c r="A98" t="s" s="0">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
         <v>450</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="B98" t="s">
         <v>451</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4323,11 +4505,11 @@
         <v>453</v>
       </c>
     </row>
-    <row r="99" ht="14.5">
-      <c r="A99" t="s" s="0">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>454</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="B99" t="s">
         <v>455</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4337,11 +4519,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="100" ht="14.5">
-      <c r="A100" t="s" s="0">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>458</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="B100" t="s">
         <v>459</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4351,11 +4533,11 @@
         <v>461</v>
       </c>
     </row>
-    <row r="101" ht="14.5">
-      <c r="A101" t="s" s="0">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>462</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="B101" t="s">
         <v>463</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4365,11 +4547,11 @@
         <v>465</v>
       </c>
     </row>
-    <row r="102" ht="14.5">
-      <c r="A102" t="s" s="0">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>466</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="B102" t="s">
         <v>467</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4379,11 +4561,11 @@
         <v>469</v>
       </c>
     </row>
-    <row r="103" ht="14.5">
-      <c r="A103" t="s" s="0">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>470</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="B103" t="s">
         <v>471</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4393,11 +4575,11 @@
         <v>473</v>
       </c>
     </row>
-    <row r="104" ht="14.5">
-      <c r="A104" t="s" s="0">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
         <v>474</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="B104" t="s">
         <v>475</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4407,11 +4589,11 @@
         <v>477</v>
       </c>
     </row>
-    <row r="105" ht="14.5">
-      <c r="A105" t="s" s="0">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>478</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="B105" t="s">
         <v>479</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4421,11 +4603,11 @@
         <v>481</v>
       </c>
     </row>
-    <row r="106" ht="14.5">
-      <c r="A106" t="s" s="0">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
         <v>482</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="B106" t="s">
         <v>483</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4435,11 +4617,11 @@
         <v>485</v>
       </c>
     </row>
-    <row r="107" ht="14.5">
-      <c r="A107" t="s" s="0">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
         <v>486</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="B107" t="s">
         <v>487</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4449,11 +4631,11 @@
         <v>489</v>
       </c>
     </row>
-    <row r="108" ht="14.5">
-      <c r="A108" t="s" s="0">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
         <v>490</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="B108" t="s">
         <v>491</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4463,11 +4645,11 @@
         <v>493</v>
       </c>
     </row>
-    <row r="109" ht="14.5">
-      <c r="A109" t="s" s="0">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>494</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="B109" t="s">
         <v>495</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4477,11 +4659,11 @@
         <v>497</v>
       </c>
     </row>
-    <row r="110" ht="14.5">
-      <c r="A110" t="s" s="0">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>498</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="B110" t="s">
         <v>499</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4491,11 +4673,11 @@
         <v>501</v>
       </c>
     </row>
-    <row r="111" ht="14.5">
-      <c r="A111" t="s" s="0">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>502</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="B111" t="s">
         <v>503</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4505,11 +4687,11 @@
         <v>505</v>
       </c>
     </row>
-    <row r="112" ht="14.5">
-      <c r="A112" t="s" s="0">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>506</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="B112" t="s">
         <v>507</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4519,11 +4701,11 @@
         <v>509</v>
       </c>
     </row>
-    <row r="113" ht="14.5">
-      <c r="A113" t="s" s="0">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
         <v>510</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="B113" t="s">
         <v>511</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4533,11 +4715,11 @@
         <v>513</v>
       </c>
     </row>
-    <row r="114" ht="14.5">
-      <c r="A114" t="s" s="0">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
         <v>514</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="B114" t="s">
         <v>515</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4547,11 +4729,11 @@
         <v>517</v>
       </c>
     </row>
-    <row r="115" ht="14.5">
-      <c r="A115" t="s" s="0">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>518</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="B115" t="s">
         <v>519</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4561,11 +4743,11 @@
         <v>521</v>
       </c>
     </row>
-    <row r="116" ht="14.5">
-      <c r="A116" t="s" s="0">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>522</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="B116" t="s">
         <v>523</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4575,11 +4757,11 @@
         <v>525</v>
       </c>
     </row>
-    <row r="117" ht="14.5">
-      <c r="A117" t="s" s="0">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>526</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="B117" t="s">
         <v>527</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4589,11 +4771,11 @@
         <v>529</v>
       </c>
     </row>
-    <row r="118" ht="14.5">
-      <c r="A118" t="s" s="0">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
         <v>530</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="B118" t="s">
         <v>531</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4603,11 +4785,11 @@
         <v>533</v>
       </c>
     </row>
-    <row r="119" ht="14.5">
-      <c r="A119" t="s" s="0">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>534</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="B119" t="s">
         <v>535</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4617,11 +4799,11 @@
         <v>537</v>
       </c>
     </row>
-    <row r="120" ht="14.5">
-      <c r="A120" t="s" s="0">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
         <v>538</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="B120" t="s">
         <v>539</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4631,11 +4813,11 @@
         <v>541</v>
       </c>
     </row>
-    <row r="121" ht="14.5">
-      <c r="A121" t="s" s="0">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
         <v>542</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="B121" t="s">
         <v>543</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4645,11 +4827,11 @@
         <v>545</v>
       </c>
     </row>
-    <row r="122" ht="14.5">
-      <c r="A122" t="s" s="0">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>546</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="B122" t="s">
         <v>547</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4659,11 +4841,11 @@
         <v>549</v>
       </c>
     </row>
-    <row r="123" ht="14.5">
-      <c r="A123" t="s" s="0">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
         <v>550</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="B123" t="s">
         <v>551</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4673,11 +4855,11 @@
         <v>553</v>
       </c>
     </row>
-    <row r="124" ht="14.5">
-      <c r="A124" t="s" s="0">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
         <v>554</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="B124" t="s">
         <v>555</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4687,11 +4869,11 @@
         <v>557</v>
       </c>
     </row>
-    <row r="125" ht="14.5">
-      <c r="A125" t="s" s="0">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
         <v>558</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="B125" t="s">
         <v>559</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4701,11 +4883,11 @@
         <v>561</v>
       </c>
     </row>
-    <row r="126" ht="14.5">
-      <c r="A126" t="s" s="0">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>562</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="B126" t="s">
         <v>563</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4715,11 +4897,11 @@
         <v>565</v>
       </c>
     </row>
-    <row r="127" ht="14.5">
-      <c r="A127" t="s" s="0">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
         <v>566</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="B127" t="s">
         <v>567</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4729,11 +4911,11 @@
         <v>569</v>
       </c>
     </row>
-    <row r="128" ht="14.5">
-      <c r="A128" t="s" s="0">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>570</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="B128" t="s">
         <v>571</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4743,11 +4925,11 @@
         <v>573</v>
       </c>
     </row>
-    <row r="129" ht="14.5">
-      <c r="A129" t="s" s="0">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>574</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="B129" t="s">
         <v>575</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4757,11 +4939,11 @@
         <v>577</v>
       </c>
     </row>
-    <row r="130" ht="14.5">
-      <c r="A130" t="s" s="0">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>578</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="B130" t="s">
         <v>579</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4771,11 +4953,11 @@
         <v>581</v>
       </c>
     </row>
-    <row r="131" ht="14.5">
-      <c r="A131" t="s" s="0">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
         <v>582</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="B131" t="s">
         <v>583</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4785,11 +4967,11 @@
         <v>585</v>
       </c>
     </row>
-    <row r="132" ht="14.5">
-      <c r="A132" t="s" s="0">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
         <v>586</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="B132" t="s">
         <v>587</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4799,11 +4981,11 @@
         <v>589</v>
       </c>
     </row>
-    <row r="133" ht="14.5">
-      <c r="A133" t="s" s="0">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
         <v>590</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="B133" t="s">
         <v>591</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4813,11 +4995,11 @@
         <v>593</v>
       </c>
     </row>
-    <row r="134" ht="14.5">
-      <c r="A134" t="s" s="0">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
         <v>594</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="B134" t="s">
         <v>595</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4827,11 +5009,11 @@
         <v>597</v>
       </c>
     </row>
-    <row r="135" ht="14.5">
-      <c r="A135" t="s" s="0">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
         <v>598</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="B135" t="s">
         <v>599</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -4841,11 +5023,11 @@
         <v>601</v>
       </c>
     </row>
-    <row r="136" ht="14.5">
-      <c r="A136" t="s" s="0">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
         <v>602</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="B136" t="s">
         <v>603</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -4855,11 +5037,11 @@
         <v>605</v>
       </c>
     </row>
-    <row r="137" ht="14.5">
-      <c r="A137" t="s" s="0">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
         <v>606</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="B137" t="s">
         <v>607</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -4869,11 +5051,11 @@
         <v>609</v>
       </c>
     </row>
-    <row r="138" ht="14.5">
-      <c r="A138" t="s" s="0">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
         <v>610</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="B138" t="s">
         <v>611</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -4883,11 +5065,11 @@
         <v>613</v>
       </c>
     </row>
-    <row r="139" ht="14.5">
-      <c r="A139" t="s" s="0">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
         <v>614</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="B139" t="s">
         <v>615</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -4897,11 +5079,11 @@
         <v>617</v>
       </c>
     </row>
-    <row r="140" ht="14.5">
-      <c r="A140" t="s" s="0">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
         <v>618</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="B140" t="s">
         <v>619</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -4911,11 +5093,11 @@
         <v>621</v>
       </c>
     </row>
-    <row r="141" ht="14.5">
-      <c r="A141" t="s" s="0">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
         <v>622</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="B141" t="s">
         <v>623</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -4925,11 +5107,11 @@
         <v>625</v>
       </c>
     </row>
-    <row r="142" ht="14.5">
-      <c r="A142" t="s" s="0">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
         <v>626</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="B142" t="s">
         <v>627</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -4939,11 +5121,11 @@
         <v>629</v>
       </c>
     </row>
-    <row r="143" ht="14.5">
-      <c r="A143" t="s" s="0">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
         <v>630</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="B143" t="s">
         <v>631</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -4953,11 +5135,11 @@
         <v>633</v>
       </c>
     </row>
-    <row r="144" ht="14.5">
-      <c r="A144" t="s" s="0">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
         <v>634</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="B144" t="s">
         <v>635</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -4967,11 +5149,11 @@
         <v>637</v>
       </c>
     </row>
-    <row r="145" ht="14.5">
-      <c r="A145" t="s" s="0">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
         <v>638</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="B145" t="s">
         <v>639</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -4981,11 +5163,11 @@
         <v>641</v>
       </c>
     </row>
-    <row r="146" ht="14.5">
-      <c r="A146" t="s" s="0">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
         <v>642</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="B146" t="s">
         <v>643</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -4995,11 +5177,11 @@
         <v>645</v>
       </c>
     </row>
-    <row r="147" ht="14.5">
-      <c r="A147" t="s" s="0">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>646</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="B147" t="s">
         <v>647</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5009,11 +5191,11 @@
         <v>649</v>
       </c>
     </row>
-    <row r="148" ht="14.5">
-      <c r="A148" t="s" s="0">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
         <v>650</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="B148" t="s">
         <v>651</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5023,11 +5205,11 @@
         <v>653</v>
       </c>
     </row>
-    <row r="149" ht="14.5">
-      <c r="A149" t="s" s="0">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>654</v>
       </c>
-      <c r="B149" t="s" s="0">
+      <c r="B149" t="s">
         <v>655</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5037,11 +5219,11 @@
         <v>657</v>
       </c>
     </row>
-    <row r="150" ht="14.5">
-      <c r="A150" t="s" s="0">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
         <v>658</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="B150" t="s">
         <v>659</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5051,11 +5233,11 @@
         <v>661</v>
       </c>
     </row>
-    <row r="151" ht="14.5">
-      <c r="A151" t="s" s="0">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
         <v>662</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="B151" t="s">
         <v>663</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5065,11 +5247,11 @@
         <v>665</v>
       </c>
     </row>
-    <row r="152" ht="14.5">
-      <c r="A152" t="s" s="0">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
         <v>666</v>
       </c>
-      <c r="B152" t="s" s="0">
+      <c r="B152" t="s">
         <v>667</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5079,8 +5261,8 @@
         <v>669</v>
       </c>
     </row>
-    <row r="153" ht="14.5">
-      <c r="B153" t="s" s="0">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
         <v>670</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5090,8 +5272,8 @@
         <v>672</v>
       </c>
     </row>
-    <row r="154" ht="14.5">
-      <c r="B154" t="s" s="0">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B154" t="s">
         <v>673</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5101,8 +5283,8 @@
         <v>675</v>
       </c>
     </row>
-    <row r="155" ht="14.5">
-      <c r="B155" t="s" s="0">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
         <v>676</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5112,8 +5294,8 @@
         <v>678</v>
       </c>
     </row>
-    <row r="156" ht="14.5">
-      <c r="B156" t="s" s="0">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
         <v>679</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5123,8 +5305,8 @@
         <v>681</v>
       </c>
     </row>
-    <row r="157" ht="14.5">
-      <c r="B157" t="s" s="0">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B157" t="s">
         <v>682</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5134,8 +5316,8 @@
         <v>684</v>
       </c>
     </row>
-    <row r="158" ht="14.5">
-      <c r="B158" t="s" s="0">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
         <v>685</v>
       </c>
       <c r="C158" s="6" t="s">
@@ -5145,7 +5327,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="159" ht="14.5">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C159" s="6" t="s">
         <v>688</v>
       </c>
@@ -5153,7 +5335,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="160" ht="14.5">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C160" s="6" t="s">
         <v>690</v>
       </c>
@@ -5161,7 +5343,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="161" ht="14.5">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C161" s="6" t="s">
         <v>692</v>
       </c>
@@ -5169,7 +5351,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="162" ht="14.5">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C162" s="6" t="s">
         <v>694</v>
       </c>
@@ -5177,7 +5359,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="163" ht="14.5">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C163" s="6" t="s">
         <v>696</v>
       </c>
@@ -5185,7 +5367,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="164" ht="14.5">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C164" s="6" t="s">
         <v>698</v>
       </c>
@@ -5193,7 +5375,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="165" ht="14.5">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C165" s="6" t="s">
         <v>700</v>
       </c>
@@ -5201,7 +5383,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="166" ht="14.5">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C166" s="6" t="s">
         <v>702</v>
       </c>
@@ -5209,7 +5391,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="167" ht="14.5">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C167" s="6" t="s">
         <v>704</v>
       </c>
@@ -5217,7 +5399,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="168" ht="14.5">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C168" s="6" t="s">
         <v>706</v>
       </c>
@@ -5225,7 +5407,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="169" ht="14.5">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C169" s="6" t="s">
         <v>708</v>
       </c>
@@ -5233,7 +5415,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="170" ht="14.5">
+    <row r="170" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C170" s="6" t="s">
         <v>710</v>
       </c>
@@ -5241,162 +5423,163 @@
         <v>711</v>
       </c>
     </row>
-    <row r="171" ht="14.5">
+    <row r="171" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D171" s="5" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="172" ht="14.5">
+    <row r="172" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D172" s="5" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="173" ht="14.5">
+    <row r="173" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D173" s="5" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="174" ht="14.5">
+    <row r="174" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D174" s="5" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="175" ht="14.5">
+    <row r="175" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D175" s="5" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="176" ht="14.5">
+    <row r="176" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D176" s="5" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="177" ht="14.5">
+    <row r="177" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D177" s="5" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="178" ht="14.5">
+    <row r="178" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D178" s="5" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="179" ht="14.5">
+    <row r="179" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D179" s="5" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="180" ht="14.5">
+    <row r="180" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D180" s="5" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="181" ht="14.5">
+    <row r="181" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D181" s="5" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="182" ht="14.5">
+    <row r="182" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D182" s="5" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="183" ht="14.5">
+    <row r="183" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D183" s="5" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="184" ht="14.5">
+    <row r="184" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D184" s="5" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="185" ht="14.5">
+    <row r="185" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D185" s="5" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="186" ht="14.5">
+    <row r="186" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D186" s="5" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="187" ht="14.5">
+    <row r="187" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D187" s="5" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="188" ht="14.5">
+    <row r="188" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D188" s="5" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="189" ht="14.5">
+    <row r="189" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D189" s="5" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="190" ht="14.5">
+    <row r="190" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D190" s="5" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="191" ht="14.5">
+    <row r="191" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D191" s="5" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="192" ht="14.5">
+    <row r="192" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D192" s="5" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="193" ht="14.5">
+    <row r="193" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D193" s="5" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="194" ht="14.5">
+    <row r="194" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D194" s="5" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="195" ht="14.5">
+    <row r="195" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D195" s="5" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="196" ht="14.5">
+    <row r="196" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D196" s="5" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="197" ht="14.5">
+    <row r="197" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D197" s="5" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="198" ht="14.5">
+    <row r="198" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D198" s="5" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="199" ht="14.5">
+    <row r="199" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D199" s="5" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="200" ht="14.5">
+    <row r="200" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D200" s="5" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="201" ht="14.5">
+    <row r="201" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D201" s="5" t="s">
         <v>742</v>
       </c>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="774">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2336,12 +2336,16 @@
   </si>
   <si>
     <t>MJAPC7</t>
+  </si>
+  <si>
+    <t>Charlie80</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2724,21 +2728,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
+    <col min="12" max="16384" style="1" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2899,7 +2903,7 @@
       <c r="B9" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="1">
         <v>765</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2916,7 +2920,7 @@
       <c r="B10" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="1">
         <v>766</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2933,7 +2937,7 @@
       <c r="B11" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="1">
         <v>767</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2950,7 +2954,7 @@
       <c r="B12" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="1">
         <v>768</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2967,7 +2971,7 @@
       <c r="D13" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="1">
         <v>755</v>
       </c>
     </row>
@@ -2978,47 +2982,47 @@
       <c r="D14" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="1">
         <v>756</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E15" t="s">
+      <c r="E15" t="s" s="1">
         <v>757</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="1">
         <v>758</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="1">
         <v>759</v>
       </c>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E18" t="s">
+      <c r="E18" t="s" s="1">
         <v>760</v>
       </c>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E19" t="s">
+      <c r="E19" t="s" s="1">
         <v>761</v>
       </c>
     </row>
     <row r="20" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="1">
         <v>762</v>
       </c>
     </row>
     <row r="21" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="1">
         <v>763</v>
       </c>
     </row>
     <row r="22" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E22" t="s">
+      <c r="E22" t="s" s="1">
         <v>764</v>
       </c>
     </row>
@@ -3039,63 +3043,63 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" customWidth="1"/>
-    <col min="8" max="8" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.453125"/>
+    <col min="3" max="3" customWidth="true" width="35.6328125"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.7265625"/>
+    <col min="6" max="6" customWidth="true" width="32.1796875"/>
+    <col min="7" max="7" customWidth="true" width="33.6328125"/>
+    <col min="8" max="8" customWidth="true" width="31.26953125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>773</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s" s="0">
         <v>57</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>57</v>
       </c>
     </row>
@@ -3112,46 +3116,46 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984375"/>
+    <col min="2" max="2" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.36328125"/>
+    <col min="4" max="5" customWidth="true" width="17.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.36328125"/>
+    <col min="8" max="8" customWidth="true" width="17.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3162,10 +3166,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3176,10 +3180,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3190,10 +3194,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>78</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>79</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3204,10 +3208,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3218,10 +3222,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3232,10 +3236,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>91</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3246,10 +3250,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3260,10 +3264,10 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>99</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3274,10 +3278,10 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3288,10 +3292,10 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>107</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3302,10 +3306,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3316,10 +3320,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>115</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3330,10 +3334,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>119</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3344,10 +3348,10 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>123</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3358,10 +3362,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>127</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3372,10 +3376,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>131</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -3386,10 +3390,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>135</v>
       </c>
       <c r="C19" s="16" t="s">
@@ -3400,10 +3404,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>138</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>139</v>
       </c>
       <c r="C20" s="17" t="s">
@@ -3414,10 +3418,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>143</v>
       </c>
       <c r="C21" s="18" t="s">
@@ -3428,10 +3432,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>147</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -3442,10 +3446,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>151</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -3456,10 +3460,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>154</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>155</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -3470,10 +3474,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>159</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3484,10 +3488,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>163</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3498,10 +3502,10 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>166</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>167</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3512,10 +3516,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>171</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3526,10 +3530,10 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>175</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3540,10 +3544,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3554,10 +3558,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>182</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>183</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3568,10 +3572,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>186</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>187</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3582,10 +3586,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>190</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>191</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3596,10 +3600,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>195</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3610,10 +3614,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>198</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>199</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3624,10 +3628,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>202</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>203</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3638,10 +3642,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>207</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3652,10 +3656,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>211</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3666,10 +3670,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>215</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3680,10 +3684,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>218</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>219</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3694,10 +3698,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>222</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>223</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3708,10 +3712,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>227</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3722,10 +3726,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>230</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>231</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3736,10 +3740,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>234</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>235</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3750,10 +3754,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>238</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>239</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3764,10 +3768,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>242</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>243</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3778,10 +3782,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>247</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3792,10 +3796,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>250</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>251</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3806,10 +3810,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>254</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>255</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3820,10 +3824,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>259</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3834,10 +3838,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>262</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>263</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3848,10 +3852,10 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>266</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>267</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3862,10 +3866,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>270</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3876,10 +3880,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>275</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3890,10 +3894,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>279</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3904,10 +3908,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>282</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>283</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3918,10 +3922,10 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>286</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>287</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3932,10 +3936,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>290</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>291</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3946,10 +3950,10 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>294</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>295</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3960,10 +3964,10 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>298</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>299</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3974,10 +3978,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>302</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>303</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3988,10 +3992,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>306</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>307</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -4002,10 +4006,10 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>311</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4016,10 +4020,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>314</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>315</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4030,10 +4034,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>318</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>319</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4044,10 +4048,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>322</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>323</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4058,10 +4062,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>326</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>327</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4072,10 +4076,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>330</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>331</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4086,10 +4090,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>334</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>335</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4100,10 +4104,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>338</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>339</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4114,10 +4118,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>342</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>343</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4128,10 +4132,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>346</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>347</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4142,10 +4146,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>350</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>351</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4156,10 +4160,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>354</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>355</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4170,10 +4174,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>358</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>359</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4184,10 +4188,10 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>362</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>363</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4198,10 +4202,10 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>366</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>367</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4212,10 +4216,10 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>370</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>371</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4226,10 +4230,10 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>374</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>375</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4240,10 +4244,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>378</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>379</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4254,10 +4258,10 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>383</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4268,10 +4272,10 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>387</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4282,10 +4286,10 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>390</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>391</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4296,10 +4300,10 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>395</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4310,10 +4314,10 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>399</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4324,10 +4328,10 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>403</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4338,10 +4342,10 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>406</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>407</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4352,10 +4356,10 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>410</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>411</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4366,10 +4370,10 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>414</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>415</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4380,10 +4384,10 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>418</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>419</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4394,10 +4398,10 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>423</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4408,10 +4412,10 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>427</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4422,10 +4426,10 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>430</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>431</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4436,10 +4440,10 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>435</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4450,10 +4454,10 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>438</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>439</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4464,10 +4468,10 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>443</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4478,10 +4482,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>447</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4492,10 +4496,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>450</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>451</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4506,10 +4510,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>454</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>455</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4520,10 +4524,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>458</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>459</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4534,10 +4538,10 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>463</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4548,10 +4552,10 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>466</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>467</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4562,10 +4566,10 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>470</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>471</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4576,10 +4580,10 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>474</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>475</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4590,10 +4594,10 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>478</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>479</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4604,10 +4608,10 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>483</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4618,10 +4622,10 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>486</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>487</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4632,10 +4636,10 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>491</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4646,10 +4650,10 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>494</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>495</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4660,10 +4664,10 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>498</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>499</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4674,10 +4678,10 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>502</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>503</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4688,10 +4692,10 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>506</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>507</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4702,10 +4706,10 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>510</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>511</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4716,10 +4720,10 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>514</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>515</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4730,10 +4734,10 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>518</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>519</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4744,10 +4748,10 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>522</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>523</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4758,10 +4762,10 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>526</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>527</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4772,10 +4776,10 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>530</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>531</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4786,10 +4790,10 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>534</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>535</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4800,10 +4804,10 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>538</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>539</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4814,10 +4818,10 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>542</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>543</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4828,10 +4832,10 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>546</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>547</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4842,10 +4846,10 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>550</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>551</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4856,10 +4860,10 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>555</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4870,10 +4874,10 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>558</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>559</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4884,10 +4888,10 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>562</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>563</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4898,10 +4902,10 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>566</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>567</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4912,10 +4916,10 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>570</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>571</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4926,10 +4930,10 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>574</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>575</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4940,10 +4944,10 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>578</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>579</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4954,10 +4958,10 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>582</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>583</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4968,10 +4972,10 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>586</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>587</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4982,10 +4986,10 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>590</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>591</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4996,10 +5000,10 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>594</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>595</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -5010,10 +5014,10 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>598</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>599</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5024,10 +5028,10 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>602</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>603</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5038,10 +5042,10 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>606</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>607</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5052,10 +5056,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>610</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>611</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5066,10 +5070,10 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>614</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>615</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5080,10 +5084,10 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>618</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>619</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5094,10 +5098,10 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>622</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>623</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5108,10 +5112,10 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>626</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>627</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5122,10 +5126,10 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>630</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>631</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5136,10 +5140,10 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>634</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>635</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5150,10 +5154,10 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>638</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>639</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5164,10 +5168,10 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>642</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>643</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5178,10 +5182,10 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>646</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>647</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5192,10 +5196,10 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>650</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>651</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5206,10 +5210,10 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>654</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>655</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5220,10 +5224,10 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>658</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>659</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5234,10 +5238,10 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>662</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>663</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5248,10 +5252,10 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>666</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>667</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5262,7 +5266,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>670</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5273,7 +5277,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>673</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5284,7 +5288,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>676</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5295,7 +5299,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>679</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5306,7 +5310,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>682</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5317,7 +5321,7 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>685</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\workspace\testing\animalBiome_Automation\src\test\resources\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3090" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3090" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
     <sheet name="PET_NAME" sheetId="2" r:id="rId2"/>
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A28:G35"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -154,18 +158,108 @@
     <t>RTNRRD</t>
   </si>
   <si>
+    <t>JDAGGA</t>
+  </si>
+  <si>
+    <t>6C9EJE</t>
+  </si>
+  <si>
+    <t>GTGXFA</t>
+  </si>
+  <si>
+    <t>GUMCDP</t>
+  </si>
+  <si>
     <t>3DG9GJ</t>
   </si>
   <si>
+    <t>AV9GCG</t>
+  </si>
+  <si>
+    <t>HJ6NJX</t>
+  </si>
+  <si>
+    <t>HC7FGA</t>
+  </si>
+  <si>
+    <t>FVRDEY</t>
+  </si>
+  <si>
     <t>TTKRNN</t>
   </si>
   <si>
+    <t>NKNGH7</t>
+  </si>
+  <si>
+    <t>PA7EFN</t>
+  </si>
+  <si>
+    <t>6G4AUX</t>
+  </si>
+  <si>
+    <t>CM4KEX</t>
+  </si>
+  <si>
     <t>P3K7MR</t>
   </si>
   <si>
+    <t>J6MGVG</t>
+  </si>
+  <si>
+    <t>MJAPC7</t>
+  </si>
+  <si>
+    <t>FKCAP9</t>
+  </si>
+  <si>
+    <t>MVY7E7</t>
+  </si>
+  <si>
     <t>NG9RY6</t>
   </si>
   <si>
+    <t>4F66HY</t>
+  </si>
+  <si>
+    <t>E4FR3M</t>
+  </si>
+  <si>
+    <t>4PEEDE</t>
+  </si>
+  <si>
+    <t>HHUXJN</t>
+  </si>
+  <si>
+    <t>EMDDGE</t>
+  </si>
+  <si>
+    <t>MT3YXX</t>
+  </si>
+  <si>
+    <t>XHFYNX</t>
+  </si>
+  <si>
+    <t>ENJTEH</t>
+  </si>
+  <si>
+    <t>VJFKAH</t>
+  </si>
+  <si>
+    <t>RVYMTD</t>
+  </si>
+  <si>
+    <t>HTD7FV</t>
+  </si>
+  <si>
+    <t>D7RM3G</t>
+  </si>
+  <si>
+    <t>DPXN44</t>
+  </si>
+  <si>
+    <t>EVAYHN</t>
+  </si>
+  <si>
     <t>User_Dog</t>
   </si>
   <si>
@@ -2246,107 +2340,13 @@
   </si>
   <si>
     <t>Nexra</t>
-  </si>
-  <si>
-    <t>JDAGGA</t>
-  </si>
-  <si>
-    <t>AV9GCG</t>
-  </si>
-  <si>
-    <t>NKNGH7</t>
-  </si>
-  <si>
-    <t>J6MGVG</t>
-  </si>
-  <si>
-    <t>4F66HY</t>
-  </si>
-  <si>
-    <t>HHUXJN</t>
-  </si>
-  <si>
-    <t>GUMCDP</t>
-  </si>
-  <si>
-    <t>FVRDEY</t>
-  </si>
-  <si>
-    <t>CM4KEX</t>
-  </si>
-  <si>
-    <t>MVY7E7</t>
-  </si>
-  <si>
-    <t>E4FR3M</t>
-  </si>
-  <si>
-    <t>EMDDGE</t>
-  </si>
-  <si>
-    <t>4PEEDE</t>
-  </si>
-  <si>
-    <t>MT3YXX</t>
-  </si>
-  <si>
-    <t>XHFYNX</t>
-  </si>
-  <si>
-    <t>ENJTEH</t>
-  </si>
-  <si>
-    <t>VJFKAH</t>
-  </si>
-  <si>
-    <t>RVYMTD</t>
-  </si>
-  <si>
-    <t>HTD7FV</t>
-  </si>
-  <si>
-    <t>D7RM3G</t>
-  </si>
-  <si>
-    <t>DPXN44</t>
-  </si>
-  <si>
-    <t>EVAYHN</t>
-  </si>
-  <si>
-    <t>GTGXFA</t>
-  </si>
-  <si>
-    <t>HC7FGA</t>
-  </si>
-  <si>
-    <t>6G4AUX</t>
-  </si>
-  <si>
-    <t>FKCAP9</t>
-  </si>
-  <si>
-    <t>6C9EJE</t>
-  </si>
-  <si>
-    <t>HJ6NJX</t>
-  </si>
-  <si>
-    <t>PA7EFN</t>
-  </si>
-  <si>
-    <t>MJAPC7</t>
-  </si>
-  <si>
-    <t>Charlie80</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2358,13 +2358,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2387,20 +2380,14 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2408,36 +2395,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1"/>
     <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -2446,10 +2413,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2581,6 +2548,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2604,10 +2572,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2616,13 +2585,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2698,6 +2667,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2717,35 +2687,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
-    <col min="12" max="16384" style="1" width="8.7265625"/>
+    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.726563" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2777,7 +2745,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2794,14 +2762,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -2811,7 +2779,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -2828,8 +2796,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2838,15 +2806,15 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2855,14 +2823,14 @@
       <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
@@ -2875,11 +2843,11 @@
       <c r="D7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -2892,2698 +2860,2687 @@
       <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="1" t="s">
-        <v>743</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="C9" t="s" s="1">
-        <v>765</v>
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>749</v>
+        <v>48</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>744</v>
+        <v>50</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="C10" t="s" s="1">
-        <v>766</v>
+        <v>51</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>750</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1" t="s">
-        <v>745</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="C11" t="s" s="1">
-        <v>767</v>
+        <v>56</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>751</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="1" t="s">
-        <v>746</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="C12" t="s" s="1">
-        <v>768</v>
+        <v>61</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>752</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="1" t="s">
-        <v>747</v>
+        <v>65</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E13" t="s" s="1">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="1" t="s">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="E14" t="s" s="1">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E15" t="s" s="1">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E16" t="s" s="1">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E17" t="s" s="1">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E18" t="s" s="1">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E19" t="s" s="1">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E20" t="s" s="1">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E21" t="s" s="1">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E22" t="s" s="1">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78">
       <c r="F78" s="3"/>
     </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="F81" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.453125"/>
-    <col min="3" max="3" customWidth="true" width="35.6328125"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.7265625"/>
-    <col min="6" max="6" customWidth="true" width="32.1796875"/>
-    <col min="7" max="7" customWidth="true" width="33.6328125"/>
-    <col min="8" max="8" customWidth="true" width="31.26953125"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.45313" customWidth="1"/>
+    <col min="3" max="3" width="35.63281" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.72656" customWidth="1"/>
+    <col min="6" max="6" width="32.17969" customWidth="1"/>
+    <col min="7" max="7" width="33.63281" customWidth="1"/>
+    <col min="8" max="8" width="31.26953" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>773</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35"/>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984375"/>
-    <col min="2" max="2" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" width="17.36328125"/>
-    <col min="4" max="5" customWidth="true" width="17.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.36328125"/>
-    <col min="8" max="8" customWidth="true" width="17.1796875"/>
+    <col min="1" max="1" width="20.08984" customWidth="1"/>
+    <col min="2" max="2" width="17.54297" customWidth="1"/>
+    <col min="3" max="3" width="17.36328" customWidth="1"/>
+    <col min="4" max="5" width="17.26953" customWidth="1"/>
+    <col min="6" max="6" width="17.17969" customWidth="1"/>
+    <col min="7" max="7" width="15.36328" customWidth="1"/>
+    <col min="8" max="8" width="17.17969" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>59</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>67</v>
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s">
+        <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>71</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>75</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>79</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>83</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" t="s">
+        <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>87</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s">
+        <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>91</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>95</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" t="s">
+        <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>99</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s" s="0">
-        <v>102</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>103</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>107</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" t="s">
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>111</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" t="s">
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s" s="0">
-        <v>114</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>115</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" t="s">
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>119</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" t="s">
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>123</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" t="s">
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>127</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" t="s">
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s" s="0">
-        <v>130</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>132</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s" s="0">
-        <v>134</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>136</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s" s="0">
-        <v>138</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>139</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>140</v>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>143</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>144</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>147</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" t="s">
+        <v>177</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s" s="0">
-        <v>150</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>151</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" t="s">
+        <v>181</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>155</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" t="s">
+        <v>185</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s" s="0">
-        <v>158</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>159</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" t="s">
+        <v>189</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s" s="0">
-        <v>162</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>163</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B26" t="s">
+        <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>167</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" t="s">
+        <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s" s="0">
-        <v>170</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>171</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B28" t="s">
+        <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s" s="0">
-        <v>174</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>175</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>204</v>
+      </c>
+      <c r="B29" t="s">
+        <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s" s="0">
-        <v>178</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>179</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30" t="s">
+        <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s" s="0">
-        <v>182</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>183</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" t="s">
+        <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s" s="0">
-        <v>186</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>187</v>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" t="s">
+        <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s" s="0">
-        <v>190</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>191</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>220</v>
+      </c>
+      <c r="B33" t="s">
+        <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s" s="0">
-        <v>194</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>195</v>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>224</v>
+      </c>
+      <c r="B34" t="s">
+        <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>199</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" t="s">
+        <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s" s="0">
-        <v>202</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>203</v>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>232</v>
+      </c>
+      <c r="B36" t="s">
+        <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s" s="0">
-        <v>206</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>207</v>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>236</v>
+      </c>
+      <c r="B37" t="s">
+        <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s" s="0">
-        <v>210</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>211</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>240</v>
+      </c>
+      <c r="B38" t="s">
+        <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s" s="0">
-        <v>214</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>215</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>244</v>
+      </c>
+      <c r="B39" t="s">
+        <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s" s="0">
-        <v>218</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>219</v>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>248</v>
+      </c>
+      <c r="B40" t="s">
+        <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s" s="0">
-        <v>222</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>223</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>252</v>
+      </c>
+      <c r="B41" t="s">
+        <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s" s="0">
-        <v>226</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>227</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>256</v>
+      </c>
+      <c r="B42" t="s">
+        <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s" s="0">
-        <v>230</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>231</v>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" t="s">
+        <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s" s="0">
-        <v>234</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>235</v>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>264</v>
+      </c>
+      <c r="B44" t="s">
+        <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s" s="0">
-        <v>238</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>239</v>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>268</v>
+      </c>
+      <c r="B45" t="s">
+        <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s" s="0">
-        <v>242</v>
-      </c>
-      <c r="B46" t="s" s="0">
-        <v>243</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>272</v>
+      </c>
+      <c r="B46" t="s">
+        <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s" s="0">
-        <v>246</v>
-      </c>
-      <c r="B47" t="s" s="0">
-        <v>247</v>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>276</v>
+      </c>
+      <c r="B47" t="s">
+        <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s" s="0">
-        <v>250</v>
-      </c>
-      <c r="B48" t="s" s="0">
-        <v>251</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>280</v>
+      </c>
+      <c r="B48" t="s">
+        <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="B49" t="s" s="0">
-        <v>255</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>284</v>
+      </c>
+      <c r="B49" t="s">
+        <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s" s="0">
-        <v>258</v>
-      </c>
-      <c r="B50" t="s" s="0">
-        <v>259</v>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>288</v>
+      </c>
+      <c r="B50" t="s">
+        <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s" s="0">
-        <v>262</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>263</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>292</v>
+      </c>
+      <c r="B51" t="s">
+        <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>267</v>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>296</v>
+      </c>
+      <c r="B52" t="s">
+        <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s" s="0">
-        <v>270</v>
-      </c>
-      <c r="B53" t="s" s="0">
-        <v>271</v>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>300</v>
+      </c>
+      <c r="B53" t="s">
+        <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s" s="0">
-        <v>274</v>
-      </c>
-      <c r="B54" t="s" s="0">
-        <v>275</v>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>304</v>
+      </c>
+      <c r="B54" t="s">
+        <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s" s="0">
-        <v>278</v>
-      </c>
-      <c r="B55" t="s" s="0">
-        <v>279</v>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>308</v>
+      </c>
+      <c r="B55" t="s">
+        <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s" s="0">
-        <v>282</v>
-      </c>
-      <c r="B56" t="s" s="0">
-        <v>283</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>312</v>
+      </c>
+      <c r="B56" t="s">
+        <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s" s="0">
-        <v>286</v>
-      </c>
-      <c r="B57" t="s" s="0">
-        <v>287</v>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>316</v>
+      </c>
+      <c r="B57" t="s">
+        <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s" s="0">
-        <v>290</v>
-      </c>
-      <c r="B58" t="s" s="0">
-        <v>291</v>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>320</v>
+      </c>
+      <c r="B58" t="s">
+        <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s" s="0">
-        <v>294</v>
-      </c>
-      <c r="B59" t="s" s="0">
-        <v>295</v>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>324</v>
+      </c>
+      <c r="B59" t="s">
+        <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s" s="0">
-        <v>298</v>
-      </c>
-      <c r="B60" t="s" s="0">
-        <v>299</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>328</v>
+      </c>
+      <c r="B60" t="s">
+        <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s" s="0">
-        <v>302</v>
-      </c>
-      <c r="B61" t="s" s="0">
-        <v>303</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>332</v>
+      </c>
+      <c r="B61" t="s">
+        <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s" s="0">
-        <v>306</v>
-      </c>
-      <c r="B62" t="s" s="0">
-        <v>307</v>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>336</v>
+      </c>
+      <c r="B62" t="s">
+        <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="B63" t="s" s="0">
-        <v>311</v>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>340</v>
+      </c>
+      <c r="B63" t="s">
+        <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s" s="0">
-        <v>314</v>
-      </c>
-      <c r="B64" t="s" s="0">
-        <v>315</v>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>344</v>
+      </c>
+      <c r="B64" t="s">
+        <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s" s="0">
-        <v>318</v>
-      </c>
-      <c r="B65" t="s" s="0">
-        <v>319</v>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>348</v>
+      </c>
+      <c r="B65" t="s">
+        <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s" s="0">
-        <v>322</v>
-      </c>
-      <c r="B66" t="s" s="0">
-        <v>323</v>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>352</v>
+      </c>
+      <c r="B66" t="s">
+        <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s" s="0">
-        <v>326</v>
-      </c>
-      <c r="B67" t="s" s="0">
-        <v>327</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>356</v>
+      </c>
+      <c r="B67" t="s">
+        <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="B68" t="s" s="0">
-        <v>331</v>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>360</v>
+      </c>
+      <c r="B68" t="s">
+        <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s" s="0">
-        <v>334</v>
-      </c>
-      <c r="B69" t="s" s="0">
-        <v>335</v>
+        <v>363</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>364</v>
+      </c>
+      <c r="B69" t="s">
+        <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s" s="0">
-        <v>338</v>
-      </c>
-      <c r="B70" t="s" s="0">
-        <v>339</v>
+        <v>367</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>368</v>
+      </c>
+      <c r="B70" t="s">
+        <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s" s="0">
-        <v>342</v>
-      </c>
-      <c r="B71" t="s" s="0">
-        <v>343</v>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>372</v>
+      </c>
+      <c r="B71" t="s">
+        <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s" s="0">
-        <v>346</v>
-      </c>
-      <c r="B72" t="s" s="0">
-        <v>347</v>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>376</v>
+      </c>
+      <c r="B72" t="s">
+        <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s" s="0">
-        <v>350</v>
-      </c>
-      <c r="B73" t="s" s="0">
-        <v>351</v>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>380</v>
+      </c>
+      <c r="B73" t="s">
+        <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s" s="0">
-        <v>354</v>
-      </c>
-      <c r="B74" t="s" s="0">
-        <v>355</v>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>384</v>
+      </c>
+      <c r="B74" t="s">
+        <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s" s="0">
-        <v>358</v>
-      </c>
-      <c r="B75" t="s" s="0">
-        <v>359</v>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>388</v>
+      </c>
+      <c r="B75" t="s">
+        <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s" s="0">
-        <v>362</v>
-      </c>
-      <c r="B76" t="s" s="0">
-        <v>363</v>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>392</v>
+      </c>
+      <c r="B76" t="s">
+        <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="B77" t="s" s="0">
-        <v>367</v>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>396</v>
+      </c>
+      <c r="B77" t="s">
+        <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="B78" t="s" s="0">
-        <v>371</v>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>400</v>
+      </c>
+      <c r="B78" t="s">
+        <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s" s="0">
-        <v>374</v>
-      </c>
-      <c r="B79" t="s" s="0">
-        <v>375</v>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>404</v>
+      </c>
+      <c r="B79" t="s">
+        <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s" s="0">
-        <v>378</v>
-      </c>
-      <c r="B80" t="s" s="0">
-        <v>379</v>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>408</v>
+      </c>
+      <c r="B80" t="s">
+        <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s" s="0">
-        <v>382</v>
-      </c>
-      <c r="B81" t="s" s="0">
-        <v>383</v>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>412</v>
+      </c>
+      <c r="B81" t="s">
+        <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s" s="0">
-        <v>386</v>
-      </c>
-      <c r="B82" t="s" s="0">
-        <v>387</v>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>416</v>
+      </c>
+      <c r="B82" t="s">
+        <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="B83" t="s" s="0">
-        <v>391</v>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>420</v>
+      </c>
+      <c r="B83" t="s">
+        <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s" s="0">
-        <v>394</v>
-      </c>
-      <c r="B84" t="s" s="0">
-        <v>395</v>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>424</v>
+      </c>
+      <c r="B84" t="s">
+        <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s" s="0">
-        <v>398</v>
-      </c>
-      <c r="B85" t="s" s="0">
-        <v>399</v>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>428</v>
+      </c>
+      <c r="B85" t="s">
+        <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s" s="0">
-        <v>402</v>
-      </c>
-      <c r="B86" t="s" s="0">
-        <v>403</v>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>432</v>
+      </c>
+      <c r="B86" t="s">
+        <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s" s="0">
-        <v>406</v>
-      </c>
-      <c r="B87" t="s" s="0">
-        <v>407</v>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>436</v>
+      </c>
+      <c r="B87" t="s">
+        <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s" s="0">
-        <v>410</v>
-      </c>
-      <c r="B88" t="s" s="0">
-        <v>411</v>
+        <v>439</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>440</v>
+      </c>
+      <c r="B88" t="s">
+        <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s" s="0">
-        <v>414</v>
-      </c>
-      <c r="B89" t="s" s="0">
-        <v>415</v>
+        <v>443</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>444</v>
+      </c>
+      <c r="B89" t="s">
+        <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s" s="0">
-        <v>418</v>
-      </c>
-      <c r="B90" t="s" s="0">
-        <v>419</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>448</v>
+      </c>
+      <c r="B90" t="s">
+        <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s" s="0">
-        <v>422</v>
-      </c>
-      <c r="B91" t="s" s="0">
-        <v>423</v>
+        <v>451</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>452</v>
+      </c>
+      <c r="B91" t="s">
+        <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s" s="0">
-        <v>426</v>
-      </c>
-      <c r="B92" t="s" s="0">
-        <v>427</v>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>456</v>
+      </c>
+      <c r="B92" t="s">
+        <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s" s="0">
-        <v>430</v>
-      </c>
-      <c r="B93" t="s" s="0">
-        <v>431</v>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>460</v>
+      </c>
+      <c r="B93" t="s">
+        <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s" s="0">
-        <v>434</v>
-      </c>
-      <c r="B94" t="s" s="0">
-        <v>435</v>
+        <v>463</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>464</v>
+      </c>
+      <c r="B94" t="s">
+        <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s" s="0">
-        <v>438</v>
-      </c>
-      <c r="B95" t="s" s="0">
-        <v>439</v>
+        <v>467</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>468</v>
+      </c>
+      <c r="B95" t="s">
+        <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s" s="0">
-        <v>442</v>
-      </c>
-      <c r="B96" t="s" s="0">
-        <v>443</v>
+        <v>471</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>472</v>
+      </c>
+      <c r="B96" t="s">
+        <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s" s="0">
-        <v>446</v>
-      </c>
-      <c r="B97" t="s" s="0">
-        <v>447</v>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>476</v>
+      </c>
+      <c r="B97" t="s">
+        <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s" s="0">
-        <v>450</v>
-      </c>
-      <c r="B98" t="s" s="0">
-        <v>451</v>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>480</v>
+      </c>
+      <c r="B98" t="s">
+        <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s" s="0">
-        <v>454</v>
-      </c>
-      <c r="B99" t="s" s="0">
-        <v>455</v>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>484</v>
+      </c>
+      <c r="B99" t="s">
+        <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s" s="0">
-        <v>458</v>
-      </c>
-      <c r="B100" t="s" s="0">
-        <v>459</v>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>488</v>
+      </c>
+      <c r="B100" t="s">
+        <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s" s="0">
-        <v>462</v>
-      </c>
-      <c r="B101" t="s" s="0">
-        <v>463</v>
+        <v>491</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>492</v>
+      </c>
+      <c r="B101" t="s">
+        <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s" s="0">
-        <v>466</v>
-      </c>
-      <c r="B102" t="s" s="0">
-        <v>467</v>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>496</v>
+      </c>
+      <c r="B102" t="s">
+        <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s" s="0">
-        <v>470</v>
-      </c>
-      <c r="B103" t="s" s="0">
-        <v>471</v>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>500</v>
+      </c>
+      <c r="B103" t="s">
+        <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s" s="0">
-        <v>474</v>
-      </c>
-      <c r="B104" t="s" s="0">
-        <v>475</v>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>504</v>
+      </c>
+      <c r="B104" t="s">
+        <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s" s="0">
-        <v>478</v>
-      </c>
-      <c r="B105" t="s" s="0">
-        <v>479</v>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>508</v>
+      </c>
+      <c r="B105" t="s">
+        <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s" s="0">
-        <v>482</v>
-      </c>
-      <c r="B106" t="s" s="0">
-        <v>483</v>
+        <v>511</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>512</v>
+      </c>
+      <c r="B106" t="s">
+        <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s" s="0">
-        <v>486</v>
-      </c>
-      <c r="B107" t="s" s="0">
-        <v>487</v>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>516</v>
+      </c>
+      <c r="B107" t="s">
+        <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s" s="0">
-        <v>490</v>
-      </c>
-      <c r="B108" t="s" s="0">
-        <v>491</v>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>520</v>
+      </c>
+      <c r="B108" t="s">
+        <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s" s="0">
-        <v>494</v>
-      </c>
-      <c r="B109" t="s" s="0">
-        <v>495</v>
+        <v>523</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>524</v>
+      </c>
+      <c r="B109" t="s">
+        <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s" s="0">
-        <v>498</v>
-      </c>
-      <c r="B110" t="s" s="0">
-        <v>499</v>
+        <v>527</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>528</v>
+      </c>
+      <c r="B110" t="s">
+        <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s" s="0">
-        <v>502</v>
-      </c>
-      <c r="B111" t="s" s="0">
-        <v>503</v>
+        <v>531</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>532</v>
+      </c>
+      <c r="B111" t="s">
+        <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s" s="0">
-        <v>506</v>
-      </c>
-      <c r="B112" t="s" s="0">
-        <v>507</v>
+        <v>535</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>536</v>
+      </c>
+      <c r="B112" t="s">
+        <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s" s="0">
-        <v>510</v>
-      </c>
-      <c r="B113" t="s" s="0">
-        <v>511</v>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>540</v>
+      </c>
+      <c r="B113" t="s">
+        <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s" s="0">
-        <v>514</v>
-      </c>
-      <c r="B114" t="s" s="0">
-        <v>515</v>
+        <v>543</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>544</v>
+      </c>
+      <c r="B114" t="s">
+        <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s" s="0">
-        <v>518</v>
-      </c>
-      <c r="B115" t="s" s="0">
-        <v>519</v>
+        <v>547</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>548</v>
+      </c>
+      <c r="B115" t="s">
+        <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s" s="0">
-        <v>522</v>
-      </c>
-      <c r="B116" t="s" s="0">
-        <v>523</v>
+        <v>551</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>552</v>
+      </c>
+      <c r="B116" t="s">
+        <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s" s="0">
-        <v>526</v>
-      </c>
-      <c r="B117" t="s" s="0">
-        <v>527</v>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>556</v>
+      </c>
+      <c r="B117" t="s">
+        <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s" s="0">
-        <v>530</v>
-      </c>
-      <c r="B118" t="s" s="0">
-        <v>531</v>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>560</v>
+      </c>
+      <c r="B118" t="s">
+        <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s" s="0">
-        <v>534</v>
-      </c>
-      <c r="B119" t="s" s="0">
-        <v>535</v>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>564</v>
+      </c>
+      <c r="B119" t="s">
+        <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s" s="0">
-        <v>538</v>
-      </c>
-      <c r="B120" t="s" s="0">
-        <v>539</v>
+        <v>567</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>568</v>
+      </c>
+      <c r="B120" t="s">
+        <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s" s="0">
-        <v>542</v>
-      </c>
-      <c r="B121" t="s" s="0">
-        <v>543</v>
+        <v>571</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>572</v>
+      </c>
+      <c r="B121" t="s">
+        <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s" s="0">
-        <v>546</v>
-      </c>
-      <c r="B122" t="s" s="0">
-        <v>547</v>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>576</v>
+      </c>
+      <c r="B122" t="s">
+        <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s" s="0">
-        <v>550</v>
-      </c>
-      <c r="B123" t="s" s="0">
-        <v>551</v>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>580</v>
+      </c>
+      <c r="B123" t="s">
+        <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s" s="0">
-        <v>554</v>
-      </c>
-      <c r="B124" t="s" s="0">
-        <v>555</v>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>584</v>
+      </c>
+      <c r="B124" t="s">
+        <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s" s="0">
-        <v>558</v>
-      </c>
-      <c r="B125" t="s" s="0">
-        <v>559</v>
+        <v>587</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>588</v>
+      </c>
+      <c r="B125" t="s">
+        <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="B126" t="s" s="0">
-        <v>563</v>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>592</v>
+      </c>
+      <c r="B126" t="s">
+        <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s" s="0">
-        <v>566</v>
-      </c>
-      <c r="B127" t="s" s="0">
-        <v>567</v>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>596</v>
+      </c>
+      <c r="B127" t="s">
+        <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s" s="0">
-        <v>570</v>
-      </c>
-      <c r="B128" t="s" s="0">
-        <v>571</v>
+        <v>599</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>600</v>
+      </c>
+      <c r="B128" t="s">
+        <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s" s="0">
-        <v>574</v>
-      </c>
-      <c r="B129" t="s" s="0">
-        <v>575</v>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>604</v>
+      </c>
+      <c r="B129" t="s">
+        <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s" s="0">
-        <v>578</v>
-      </c>
-      <c r="B130" t="s" s="0">
-        <v>579</v>
+        <v>607</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>608</v>
+      </c>
+      <c r="B130" t="s">
+        <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s" s="0">
-        <v>582</v>
-      </c>
-      <c r="B131" t="s" s="0">
-        <v>583</v>
+        <v>611</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>612</v>
+      </c>
+      <c r="B131" t="s">
+        <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s" s="0">
-        <v>586</v>
-      </c>
-      <c r="B132" t="s" s="0">
-        <v>587</v>
+        <v>615</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>616</v>
+      </c>
+      <c r="B132" t="s">
+        <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>588</v>
+        <v>618</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s" s="0">
-        <v>590</v>
-      </c>
-      <c r="B133" t="s" s="0">
-        <v>591</v>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>620</v>
+      </c>
+      <c r="B133" t="s">
+        <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s" s="0">
-        <v>594</v>
-      </c>
-      <c r="B134" t="s" s="0">
-        <v>595</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>624</v>
+      </c>
+      <c r="B134" t="s">
+        <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>596</v>
+        <v>626</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s" s="0">
-        <v>598</v>
-      </c>
-      <c r="B135" t="s" s="0">
-        <v>599</v>
+        <v>627</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>628</v>
+      </c>
+      <c r="B135" t="s">
+        <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s" s="0">
-        <v>602</v>
-      </c>
-      <c r="B136" t="s" s="0">
-        <v>603</v>
+        <v>631</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>632</v>
+      </c>
+      <c r="B136" t="s">
+        <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>604</v>
+        <v>634</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s" s="0">
-        <v>606</v>
-      </c>
-      <c r="B137" t="s" s="0">
-        <v>607</v>
+        <v>635</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>636</v>
+      </c>
+      <c r="B137" t="s">
+        <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>608</v>
+        <v>638</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s" s="0">
-        <v>610</v>
-      </c>
-      <c r="B138" t="s" s="0">
-        <v>611</v>
+        <v>639</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>640</v>
+      </c>
+      <c r="B138" t="s">
+        <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>612</v>
+        <v>642</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s" s="0">
-        <v>614</v>
-      </c>
-      <c r="B139" t="s" s="0">
-        <v>615</v>
+        <v>643</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>644</v>
+      </c>
+      <c r="B139" t="s">
+        <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>616</v>
+        <v>646</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s" s="0">
-        <v>618</v>
-      </c>
-      <c r="B140" t="s" s="0">
-        <v>619</v>
+        <v>647</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>648</v>
+      </c>
+      <c r="B140" t="s">
+        <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s" s="0">
-        <v>622</v>
-      </c>
-      <c r="B141" t="s" s="0">
-        <v>623</v>
+        <v>651</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>652</v>
+      </c>
+      <c r="B141" t="s">
+        <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>624</v>
+        <v>654</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s" s="0">
-        <v>626</v>
-      </c>
-      <c r="B142" t="s" s="0">
-        <v>627</v>
+        <v>655</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>656</v>
+      </c>
+      <c r="B142" t="s">
+        <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>628</v>
+        <v>658</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s" s="0">
-        <v>630</v>
-      </c>
-      <c r="B143" t="s" s="0">
-        <v>631</v>
+        <v>659</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>660</v>
+      </c>
+      <c r="B143" t="s">
+        <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>632</v>
+        <v>662</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s" s="0">
-        <v>634</v>
-      </c>
-      <c r="B144" t="s" s="0">
-        <v>635</v>
+        <v>663</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>664</v>
+      </c>
+      <c r="B144" t="s">
+        <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>636</v>
+        <v>666</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s" s="0">
-        <v>638</v>
-      </c>
-      <c r="B145" t="s" s="0">
-        <v>639</v>
+        <v>667</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>668</v>
+      </c>
+      <c r="B145" t="s">
+        <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s" s="0">
-        <v>642</v>
-      </c>
-      <c r="B146" t="s" s="0">
-        <v>643</v>
+        <v>671</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>672</v>
+      </c>
+      <c r="B146" t="s">
+        <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>644</v>
+        <v>674</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s" s="0">
-        <v>646</v>
-      </c>
-      <c r="B147" t="s" s="0">
-        <v>647</v>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>676</v>
+      </c>
+      <c r="B147" t="s">
+        <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>648</v>
+        <v>678</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s" s="0">
-        <v>650</v>
-      </c>
-      <c r="B148" t="s" s="0">
-        <v>651</v>
+        <v>679</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>680</v>
+      </c>
+      <c r="B148" t="s">
+        <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>652</v>
+        <v>682</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s" s="0">
-        <v>654</v>
-      </c>
-      <c r="B149" t="s" s="0">
-        <v>655</v>
+        <v>683</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>684</v>
+      </c>
+      <c r="B149" t="s">
+        <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>656</v>
+        <v>686</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s" s="0">
-        <v>658</v>
-      </c>
-      <c r="B150" t="s" s="0">
-        <v>659</v>
+        <v>687</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>688</v>
+      </c>
+      <c r="B150" t="s">
+        <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s" s="0">
-        <v>662</v>
-      </c>
-      <c r="B151" t="s" s="0">
-        <v>663</v>
+        <v>691</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>692</v>
+      </c>
+      <c r="B151" t="s">
+        <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>664</v>
+        <v>694</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s" s="0">
-        <v>666</v>
-      </c>
-      <c r="B152" t="s" s="0">
-        <v>667</v>
+        <v>695</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>696</v>
+      </c>
+      <c r="B152" t="s">
+        <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>668</v>
+        <v>698</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s" s="0">
-        <v>670</v>
+        <v>699</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="s">
+        <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>671</v>
+        <v>701</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s" s="0">
-        <v>673</v>
+        <v>702</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="s">
+        <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>674</v>
+        <v>704</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s" s="0">
-        <v>676</v>
+        <v>705</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="s">
+        <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>677</v>
+        <v>707</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s" s="0">
-        <v>679</v>
+        <v>708</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="s">
+        <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s" s="0">
-        <v>682</v>
+        <v>711</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="s">
+        <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s" s="0">
-        <v>685</v>
+        <v>714</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="s">
+        <v>715</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>686</v>
+        <v>716</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="159">
       <c r="C159" s="6" t="s">
-        <v>688</v>
+        <v>718</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="160">
       <c r="C160" s="6" t="s">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="161">
       <c r="C161" s="6" t="s">
-        <v>692</v>
+        <v>722</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="162">
       <c r="C162" s="6" t="s">
-        <v>694</v>
+        <v>724</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="163">
       <c r="C163" s="6" t="s">
-        <v>696</v>
+        <v>726</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="164">
       <c r="C164" s="6" t="s">
-        <v>698</v>
+        <v>728</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="165">
       <c r="C165" s="6" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="166">
       <c r="C166" s="6" t="s">
-        <v>702</v>
+        <v>732</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="167">
       <c r="C167" s="6" t="s">
-        <v>704</v>
+        <v>734</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="168">
       <c r="C168" s="6" t="s">
-        <v>706</v>
+        <v>736</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="169">
       <c r="C169" s="6" t="s">
-        <v>708</v>
+        <v>738</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="170" spans="3:4" x14ac:dyDescent="0.35">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="170">
       <c r="C170" s="6" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="171" spans="3:4" x14ac:dyDescent="0.35">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="171">
       <c r="D171" s="5" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="172" spans="3:4" x14ac:dyDescent="0.35">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="172">
       <c r="D172" s="5" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="173" spans="3:4" x14ac:dyDescent="0.35">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="173">
       <c r="D173" s="5" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="174" spans="3:4" x14ac:dyDescent="0.35">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="174">
       <c r="D174" s="5" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="175" spans="3:4" x14ac:dyDescent="0.35">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="175">
       <c r="D175" s="5" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="176" spans="3:4" x14ac:dyDescent="0.35">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="176">
       <c r="D176" s="5" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.35">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="177">
       <c r="D177" s="5" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.35">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="178">
       <c r="D178" s="5" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.35">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="179">
       <c r="D179" s="5" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.35">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="180">
       <c r="D180" s="5" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.35">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="181">
       <c r="D181" s="5" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.35">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="182">
       <c r="D182" s="5" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.35">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="183">
       <c r="D183" s="5" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.35">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="184">
       <c r="D184" s="5" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.35">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="185">
       <c r="D185" s="5" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.35">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="186">
       <c r="D186" s="5" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.35">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="187">
       <c r="D187" s="5" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.35">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="188">
       <c r="D188" s="5" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="189">
       <c r="D189" s="5" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.35">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="190">
       <c r="D190" s="5" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.35">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="191">
       <c r="D191" s="5" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.35">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="192">
       <c r="D192" s="5" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="193">
       <c r="D193" s="5" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.35">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="194">
       <c r="D194" s="5" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.35">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="195">
       <c r="D195" s="5" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.35">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="196">
       <c r="D196" s="5" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="197">
       <c r="D197" s="5" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.35">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="198">
       <c r="D198" s="5" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.35">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="199">
       <c r="D199" s="5" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.35">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="200">
       <c r="D200" s="5" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.35">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="201">
       <c r="D201" s="5" t="s">
-        <v>742</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2340,12 +2340,16 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Charlie83</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2697,20 +2701,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.726563" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
+    <col min="12" max="16384" style="1" width="8.726563"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3007,61 +3012,64 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.45313" customWidth="1"/>
-    <col min="3" max="3" width="35.63281" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.72656" customWidth="1"/>
-    <col min="6" max="6" width="32.17969" customWidth="1"/>
-    <col min="7" max="7" width="33.63281" customWidth="1"/>
-    <col min="8" max="8" width="31.26953" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.45313"/>
+    <col min="3" max="3" customWidth="true" width="35.63281"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.72656"/>
+    <col min="6" max="6" customWidth="true" width="32.17969"/>
+    <col min="7" max="7" customWidth="true" width="33.63281"/>
+    <col min="8" max="8" customWidth="true" width="31.26953"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>86</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>773</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>87</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" t="s">
+      <c r="A3" s="0"/>
+      <c r="B3" t="s" s="0">
         <v>87</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>87</v>
       </c>
     </row>
@@ -3072,48 +3080,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984" customWidth="1"/>
-    <col min="2" max="2" width="17.54297" customWidth="1"/>
-    <col min="3" max="3" width="17.36328" customWidth="1"/>
-    <col min="4" max="5" width="17.26953" customWidth="1"/>
-    <col min="6" max="6" width="17.17969" customWidth="1"/>
-    <col min="7" max="7" width="15.36328" customWidth="1"/>
-    <col min="8" max="8" width="17.17969" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984"/>
+    <col min="2" max="2" customWidth="true" width="17.54297"/>
+    <col min="3" max="3" customWidth="true" width="17.36328"/>
+    <col min="4" max="5" customWidth="true" width="17.26953"/>
+    <col min="6" max="6" customWidth="true" width="17.17969"/>
+    <col min="7" max="7" customWidth="true" width="15.36328"/>
+    <col min="8" max="8" customWidth="true" width="17.17969"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3124,10 +3133,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3138,10 +3147,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3152,10 +3161,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3166,10 +3175,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3180,10 +3189,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3194,10 +3203,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3208,10 +3217,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3222,10 +3231,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3236,10 +3245,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3250,10 +3259,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3264,10 +3273,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3278,10 +3287,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3292,10 +3301,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3306,10 +3315,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3320,10 +3329,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3334,10 +3343,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3348,10 +3357,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3362,10 +3371,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3376,10 +3385,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3390,10 +3399,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>177</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -3404,10 +3413,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>181</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -3418,10 +3427,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>184</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>185</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -3432,10 +3441,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>189</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3446,10 +3455,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3460,10 +3469,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3474,10 +3483,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3488,10 +3497,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>204</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3502,10 +3511,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3516,10 +3525,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3530,10 +3539,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>216</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3544,10 +3553,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3558,10 +3567,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3572,10 +3581,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>228</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3586,10 +3595,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>232</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3600,10 +3609,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>236</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3614,10 +3623,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>240</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3628,10 +3637,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3642,10 +3651,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3656,10 +3665,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3670,10 +3679,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3684,10 +3693,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3698,10 +3707,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3712,10 +3721,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3726,10 +3735,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>272</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3740,10 +3749,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3754,10 +3763,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3768,10 +3777,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3782,10 +3791,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3796,10 +3805,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3810,10 +3819,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>296</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3824,10 +3833,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3838,10 +3847,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3852,10 +3861,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>308</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3866,10 +3875,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>312</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3880,10 +3889,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>316</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3894,10 +3903,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>320</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3908,10 +3917,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3922,10 +3931,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3936,10 +3945,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>332</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3950,10 +3959,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>336</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3964,10 +3973,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -3978,10 +3987,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>344</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -3992,10 +4001,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>348</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4006,10 +4015,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4020,10 +4029,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>356</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4034,10 +4043,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>360</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4048,10 +4057,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4062,10 +4071,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>368</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4076,10 +4085,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>372</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4090,10 +4099,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>376</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4104,10 +4113,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>380</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4118,10 +4127,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4132,10 +4141,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4146,10 +4155,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4160,10 +4169,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4174,10 +4183,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4188,10 +4197,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4202,10 +4211,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4216,10 +4225,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>412</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4230,10 +4239,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>416</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4244,10 +4253,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4258,10 +4267,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4272,10 +4281,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4286,10 +4295,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4300,10 +4309,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>436</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4314,10 +4323,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>440</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4328,10 +4337,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4342,10 +4351,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>448</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4356,10 +4365,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4370,10 +4379,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4384,10 +4393,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>460</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4398,10 +4407,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4412,10 +4421,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>468</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4426,10 +4435,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>472</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4440,10 +4449,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>476</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4454,10 +4463,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>480</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4468,10 +4477,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>484</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4482,10 +4491,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>488</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4496,10 +4505,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>492</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4510,10 +4519,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>496</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4524,10 +4533,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>500</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4538,10 +4547,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>504</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4552,10 +4561,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>508</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4566,10 +4575,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>512</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4580,10 +4589,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>516</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4594,10 +4603,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>520</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4608,10 +4617,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>524</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4622,10 +4631,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>528</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4636,10 +4645,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>532</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4650,10 +4659,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>536</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4664,10 +4673,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>540</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4678,10 +4687,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>544</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4692,10 +4701,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>548</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4706,10 +4715,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>552</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4720,10 +4729,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4734,10 +4743,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>560</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4748,10 +4757,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>564</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4762,10 +4771,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>568</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4776,10 +4785,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>572</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4790,10 +4799,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>576</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4804,10 +4813,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>580</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4818,10 +4827,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>584</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4832,10 +4841,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>588</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4846,10 +4855,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>592</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4860,10 +4869,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>596</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4874,10 +4883,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>600</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4888,10 +4897,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>604</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4902,10 +4911,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>608</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4916,10 +4925,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>612</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4930,10 +4939,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>616</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4944,10 +4953,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>620</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4958,10 +4967,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>624</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4972,10 +4981,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>628</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -4986,10 +4995,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>632</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5000,10 +5009,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>636</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5014,10 +5023,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>640</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5028,10 +5037,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>644</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5042,10 +5051,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>648</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5056,10 +5065,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>652</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5070,10 +5079,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>656</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5084,10 +5093,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>660</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5098,10 +5107,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>664</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5112,10 +5121,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>668</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5126,10 +5135,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>672</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5140,10 +5149,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>676</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5154,10 +5163,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>680</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5168,10 +5177,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>684</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5182,10 +5191,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>688</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5196,10 +5205,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>692</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5210,10 +5219,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>696</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5224,7 +5233,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5235,7 +5244,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5246,7 +5255,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5257,7 +5266,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5268,7 +5277,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5279,7 +5288,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2343,6 +2343,15 @@
   </si>
   <si>
     <t>Charlie83</t>
+  </si>
+  <si>
+    <t>Charlie85</t>
+  </si>
+  <si>
+    <t>Milo59</t>
+  </si>
+  <si>
+    <t>Taffy57</t>
   </si>
 </sst>
 </file>
@@ -3012,7 +3021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="26.90625"/>
@@ -3060,17 +3069,24 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0"/>
+      <c r="A3" t="s" s="0">
+        <v>774</v>
+      </c>
       <c r="B3" t="s" s="0">
         <v>87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>87</v>
+        <v>775</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>87</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>776</v>
       </c>
     </row>
   </sheetData>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2340,25 +2340,12 @@
   </si>
   <si>
     <t>Nexra</t>
-  </si>
-  <si>
-    <t>Charlie83</t>
-  </si>
-  <si>
-    <t>Charlie85</t>
-  </si>
-  <si>
-    <t>Milo59</t>
-  </si>
-  <si>
-    <t>Taffy57</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2710,21 +2697,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
-    <col min="12" max="16384" style="1" width="8.726563"/>
+    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.726563" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2854,7 +2840,7 @@
       <c r="C7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -2891,7 +2877,7 @@
       <c r="D9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2908,7 +2894,7 @@
       <c r="D10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3021,73 +3007,73 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.45313"/>
-    <col min="3" max="3" customWidth="true" width="35.63281"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.72656"/>
-    <col min="6" max="6" customWidth="true" width="32.17969"/>
-    <col min="7" max="7" customWidth="true" width="33.63281"/>
-    <col min="8" max="8" customWidth="true" width="31.26953"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.45313" customWidth="1"/>
+    <col min="3" max="3" width="35.63281" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.72656" customWidth="1"/>
+    <col min="6" max="6" width="32.17969" customWidth="1"/>
+    <col min="7" max="7" width="33.63281" customWidth="1"/>
+    <col min="8" max="8" width="31.26953" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>79</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>80</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>81</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>82</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>84</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>85</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>773</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2"/>
+      <c r="B2" t="s">
         <v>87</v>
       </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>774</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="A3"/>
+      <c r="B3" t="s">
         <v>87</v>
       </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>775</v>
-      </c>
-      <c r="B4" t="s" s="0">
+      <c r="A4"/>
+      <c r="B4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>776</v>
-      </c>
+      <c r="A5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
     </row>
   </sheetData>
   <pageSetup r:id="rId1" orientation="portrait"/>
@@ -3096,49 +3082,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984"/>
-    <col min="2" max="2" customWidth="true" width="17.54297"/>
-    <col min="3" max="3" customWidth="true" width="17.36328"/>
-    <col min="4" max="5" customWidth="true" width="17.26953"/>
-    <col min="6" max="6" customWidth="true" width="17.17969"/>
-    <col min="7" max="7" customWidth="true" width="15.36328"/>
-    <col min="8" max="8" customWidth="true" width="17.17969"/>
+    <col min="1" max="1" width="20.08984" customWidth="1"/>
+    <col min="2" max="2" width="17.54297" customWidth="1"/>
+    <col min="3" max="3" width="17.36328" customWidth="1"/>
+    <col min="4" max="5" width="17.26953" customWidth="1"/>
+    <col min="6" max="6" width="17.17969" customWidth="1"/>
+    <col min="7" max="7" width="15.36328" customWidth="1"/>
+    <col min="8" max="8" width="17.17969" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>90</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>92</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>93</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>94</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>96</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3149,10 +3134,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>100</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3163,10 +3148,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3177,10 +3162,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>108</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3191,10 +3176,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>112</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3205,10 +3190,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="0">
+      <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3219,10 +3204,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s" s="0">
+      <c r="A8" t="s">
         <v>120</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3233,10 +3218,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s" s="0">
+      <c r="A9" t="s">
         <v>124</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3247,10 +3232,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="0">
+      <c r="A10" t="s">
         <v>128</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3261,10 +3246,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="0">
+      <c r="A11" t="s">
         <v>132</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3275,10 +3260,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="0">
+      <c r="A12" t="s">
         <v>136</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3289,10 +3274,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="0">
+      <c r="A13" t="s">
         <v>140</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3303,10 +3288,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="0">
+      <c r="A14" t="s">
         <v>144</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3317,10 +3302,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="0">
+      <c r="A15" t="s">
         <v>148</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3331,10 +3316,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s" s="0">
+      <c r="A16" t="s">
         <v>152</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3345,10 +3330,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s" s="0">
+      <c r="A17" t="s">
         <v>156</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3359,10 +3344,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="0">
+      <c r="A18" t="s">
         <v>160</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3373,10 +3358,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s" s="0">
+      <c r="A19" t="s">
         <v>164</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3387,10 +3372,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="0">
+      <c r="A20" t="s">
         <v>168</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3401,10 +3386,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s" s="0">
+      <c r="A21" t="s">
         <v>172</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B21" t="s">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3415,13 +3400,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s" s="0">
+      <c r="A22" t="s">
         <v>176</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="B22" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -3429,10 +3414,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s" s="0">
+      <c r="A23" t="s">
         <v>180</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>181</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -3443,10 +3428,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s" s="0">
+      <c r="A24" t="s">
         <v>184</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -3457,10 +3442,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s" s="0">
+      <c r="A25" t="s">
         <v>188</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B25" t="s">
         <v>189</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3471,10 +3456,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s" s="0">
+      <c r="A26" t="s">
         <v>192</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3485,10 +3470,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s" s="0">
+      <c r="A27" t="s">
         <v>196</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3499,10 +3484,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s" s="0">
+      <c r="A28" t="s">
         <v>200</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3513,10 +3498,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s" s="0">
+      <c r="A29" t="s">
         <v>204</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="B29" t="s">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3527,10 +3512,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s" s="0">
+      <c r="A30" t="s">
         <v>208</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="B30" t="s">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3541,10 +3526,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s" s="0">
+      <c r="A31" t="s">
         <v>212</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3555,10 +3540,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s" s="0">
+      <c r="A32" t="s">
         <v>216</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3569,10 +3554,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s" s="0">
+      <c r="A33" t="s">
         <v>220</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3583,10 +3568,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s" s="0">
+      <c r="A34" t="s">
         <v>224</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3597,10 +3582,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s" s="0">
+      <c r="A35" t="s">
         <v>228</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B35" t="s">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3611,10 +3596,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s" s="0">
+      <c r="A36" t="s">
         <v>232</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="B36" t="s">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3625,10 +3610,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s" s="0">
+      <c r="A37" t="s">
         <v>236</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B37" t="s">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3639,10 +3624,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s" s="0">
+      <c r="A38" t="s">
         <v>240</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B38" t="s">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3653,10 +3638,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s" s="0">
+      <c r="A39" t="s">
         <v>244</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="B39" t="s">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3667,10 +3652,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s" s="0">
+      <c r="A40" t="s">
         <v>248</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="B40" t="s">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3681,10 +3666,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s" s="0">
+      <c r="A41" t="s">
         <v>252</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="B41" t="s">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3695,10 +3680,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s" s="0">
+      <c r="A42" t="s">
         <v>256</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="B42" t="s">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3709,10 +3694,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s" s="0">
+      <c r="A43" t="s">
         <v>260</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="B43" t="s">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3723,10 +3708,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s" s="0">
+      <c r="A44" t="s">
         <v>264</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B44" t="s">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3737,10 +3722,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s" s="0">
+      <c r="A45" t="s">
         <v>268</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="B45" t="s">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3751,10 +3736,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s" s="0">
+      <c r="A46" t="s">
         <v>272</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="B46" t="s">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3765,10 +3750,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s" s="0">
+      <c r="A47" t="s">
         <v>276</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B47" t="s">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3779,10 +3764,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s" s="0">
+      <c r="A48" t="s">
         <v>280</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="B48" t="s">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3793,10 +3778,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="0">
+      <c r="A49" t="s">
         <v>284</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="B49" t="s">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3807,10 +3792,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s" s="0">
+      <c r="A50" t="s">
         <v>288</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="B50" t="s">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3821,10 +3806,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s" s="0">
+      <c r="A51" t="s">
         <v>292</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="B51" t="s">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3835,10 +3820,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s" s="0">
+      <c r="A52" t="s">
         <v>296</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="B52" t="s">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3849,10 +3834,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s" s="0">
+      <c r="A53" t="s">
         <v>300</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="B53" t="s">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3863,10 +3848,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s" s="0">
+      <c r="A54" t="s">
         <v>304</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="B54" t="s">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3877,10 +3862,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s" s="0">
+      <c r="A55" t="s">
         <v>308</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3891,10 +3876,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s" s="0">
+      <c r="A56" t="s">
         <v>312</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="B56" t="s">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3905,10 +3890,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s" s="0">
+      <c r="A57" t="s">
         <v>316</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B57" t="s">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3919,10 +3904,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s" s="0">
+      <c r="A58" t="s">
         <v>320</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="B58" t="s">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3933,10 +3918,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s" s="0">
+      <c r="A59" t="s">
         <v>324</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="B59" t="s">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3947,10 +3932,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s" s="0">
+      <c r="A60" t="s">
         <v>328</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="B60" t="s">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3961,10 +3946,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s" s="0">
+      <c r="A61" t="s">
         <v>332</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="B61" t="s">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3975,10 +3960,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s" s="0">
+      <c r="A62" t="s">
         <v>336</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="B62" t="s">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3989,10 +3974,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s" s="0">
+      <c r="A63" t="s">
         <v>340</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="B63" t="s">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4003,10 +3988,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s" s="0">
+      <c r="A64" t="s">
         <v>344</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="B64" t="s">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4017,10 +4002,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s" s="0">
+      <c r="A65" t="s">
         <v>348</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="B65" t="s">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4031,10 +4016,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s" s="0">
+      <c r="A66" t="s">
         <v>352</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="B66" t="s">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4045,10 +4030,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s" s="0">
+      <c r="A67" t="s">
         <v>356</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="B67" t="s">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4059,10 +4044,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s" s="0">
+      <c r="A68" t="s">
         <v>360</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B68" t="s">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4073,10 +4058,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s" s="0">
+      <c r="A69" t="s">
         <v>364</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B69" t="s">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4087,10 +4072,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s" s="0">
+      <c r="A70" t="s">
         <v>368</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="B70" t="s">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4101,10 +4086,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="0">
+      <c r="A71" t="s">
         <v>372</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="B71" t="s">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4115,10 +4100,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s" s="0">
+      <c r="A72" t="s">
         <v>376</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="B72" t="s">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4129,10 +4114,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s" s="0">
+      <c r="A73" t="s">
         <v>380</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="B73" t="s">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4143,10 +4128,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s" s="0">
+      <c r="A74" t="s">
         <v>384</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="B74" t="s">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4157,10 +4142,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s" s="0">
+      <c r="A75" t="s">
         <v>388</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="B75" t="s">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4171,10 +4156,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s" s="0">
+      <c r="A76" t="s">
         <v>392</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B76" t="s">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4185,10 +4170,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s" s="0">
+      <c r="A77" t="s">
         <v>396</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="B77" t="s">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4199,10 +4184,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s" s="0">
+      <c r="A78" t="s">
         <v>400</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B78" t="s">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4213,10 +4198,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s" s="0">
+      <c r="A79" t="s">
         <v>404</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="B79" t="s">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4227,10 +4212,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s" s="0">
+      <c r="A80" t="s">
         <v>408</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="B80" t="s">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4241,10 +4226,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s" s="0">
+      <c r="A81" t="s">
         <v>412</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B81" t="s">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4255,10 +4240,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s" s="0">
+      <c r="A82" t="s">
         <v>416</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="B82" t="s">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4269,10 +4254,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s" s="0">
+      <c r="A83" t="s">
         <v>420</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B83" t="s">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4283,10 +4268,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s" s="0">
+      <c r="A84" t="s">
         <v>424</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B84" t="s">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4297,10 +4282,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s" s="0">
+      <c r="A85" t="s">
         <v>428</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="B85" t="s">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4311,10 +4296,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s" s="0">
+      <c r="A86" t="s">
         <v>432</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="B86" t="s">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4325,10 +4310,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s" s="0">
+      <c r="A87" t="s">
         <v>436</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="B87" t="s">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4339,10 +4324,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s" s="0">
+      <c r="A88" t="s">
         <v>440</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="B88" t="s">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4353,10 +4338,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s" s="0">
+      <c r="A89" t="s">
         <v>444</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="B89" t="s">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4367,10 +4352,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s" s="0">
+      <c r="A90" t="s">
         <v>448</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="B90" t="s">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4381,10 +4366,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s" s="0">
+      <c r="A91" t="s">
         <v>452</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="B91" t="s">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4395,10 +4380,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s" s="0">
+      <c r="A92" t="s">
         <v>456</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="B92" t="s">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4409,10 +4394,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s" s="0">
+      <c r="A93" t="s">
         <v>460</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B93" t="s">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4423,10 +4408,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s" s="0">
+      <c r="A94" t="s">
         <v>464</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="B94" t="s">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4437,10 +4422,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s" s="0">
+      <c r="A95" t="s">
         <v>468</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="B95" t="s">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4451,10 +4436,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s" s="0">
+      <c r="A96" t="s">
         <v>472</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="B96" t="s">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4465,10 +4450,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s" s="0">
+      <c r="A97" t="s">
         <v>476</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="B97" t="s">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4479,10 +4464,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s" s="0">
+      <c r="A98" t="s">
         <v>480</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="B98" t="s">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4493,10 +4478,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s" s="0">
+      <c r="A99" t="s">
         <v>484</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="B99" t="s">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4507,10 +4492,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s" s="0">
+      <c r="A100" t="s">
         <v>488</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="B100" t="s">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4521,10 +4506,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s" s="0">
+      <c r="A101" t="s">
         <v>492</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="B101" t="s">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4535,10 +4520,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s" s="0">
+      <c r="A102" t="s">
         <v>496</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="B102" t="s">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4549,10 +4534,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s" s="0">
+      <c r="A103" t="s">
         <v>500</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="B103" t="s">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4563,10 +4548,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s" s="0">
+      <c r="A104" t="s">
         <v>504</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="B104" t="s">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4577,10 +4562,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s" s="0">
+      <c r="A105" t="s">
         <v>508</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="B105" t="s">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4591,10 +4576,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s" s="0">
+      <c r="A106" t="s">
         <v>512</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="B106" t="s">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4605,10 +4590,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s" s="0">
+      <c r="A107" t="s">
         <v>516</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="B107" t="s">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4619,10 +4604,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s" s="0">
+      <c r="A108" t="s">
         <v>520</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="B108" t="s">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4633,10 +4618,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s" s="0">
+      <c r="A109" t="s">
         <v>524</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="B109" t="s">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4647,10 +4632,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s" s="0">
+      <c r="A110" t="s">
         <v>528</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="B110" t="s">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4661,10 +4646,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s" s="0">
+      <c r="A111" t="s">
         <v>532</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="B111" t="s">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4675,10 +4660,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s" s="0">
+      <c r="A112" t="s">
         <v>536</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="B112" t="s">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4689,10 +4674,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s" s="0">
+      <c r="A113" t="s">
         <v>540</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="B113" t="s">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4703,10 +4688,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s" s="0">
+      <c r="A114" t="s">
         <v>544</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="B114" t="s">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4717,10 +4702,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s" s="0">
+      <c r="A115" t="s">
         <v>548</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="B115" t="s">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4731,10 +4716,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s" s="0">
+      <c r="A116" t="s">
         <v>552</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="B116" t="s">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4745,10 +4730,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s" s="0">
+      <c r="A117" t="s">
         <v>556</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="B117" t="s">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4759,10 +4744,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s" s="0">
+      <c r="A118" t="s">
         <v>560</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="B118" t="s">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4773,10 +4758,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s" s="0">
+      <c r="A119" t="s">
         <v>564</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="B119" t="s">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4787,10 +4772,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s" s="0">
+      <c r="A120" t="s">
         <v>568</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="B120" t="s">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4801,10 +4786,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s" s="0">
+      <c r="A121" t="s">
         <v>572</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="B121" t="s">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4815,10 +4800,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s" s="0">
+      <c r="A122" t="s">
         <v>576</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="B122" t="s">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4829,10 +4814,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s" s="0">
+      <c r="A123" t="s">
         <v>580</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="B123" t="s">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4843,10 +4828,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s" s="0">
+      <c r="A124" t="s">
         <v>584</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="B124" t="s">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4857,10 +4842,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s" s="0">
+      <c r="A125" t="s">
         <v>588</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="B125" t="s">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4871,10 +4856,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s" s="0">
+      <c r="A126" t="s">
         <v>592</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="B126" t="s">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4885,10 +4870,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s" s="0">
+      <c r="A127" t="s">
         <v>596</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="B127" t="s">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4899,10 +4884,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s" s="0">
+      <c r="A128" t="s">
         <v>600</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="B128" t="s">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4913,10 +4898,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s" s="0">
+      <c r="A129" t="s">
         <v>604</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="B129" t="s">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4927,10 +4912,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s" s="0">
+      <c r="A130" t="s">
         <v>608</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="B130" t="s">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4941,10 +4926,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s" s="0">
+      <c r="A131" t="s">
         <v>612</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="B131" t="s">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4955,10 +4940,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s" s="0">
+      <c r="A132" t="s">
         <v>616</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="B132" t="s">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4969,10 +4954,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s" s="0">
+      <c r="A133" t="s">
         <v>620</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="B133" t="s">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4983,10 +4968,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s" s="0">
+      <c r="A134" t="s">
         <v>624</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="B134" t="s">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4997,10 +4982,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s" s="0">
+      <c r="A135" t="s">
         <v>628</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="B135" t="s">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5011,10 +4996,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s" s="0">
+      <c r="A136" t="s">
         <v>632</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="B136" t="s">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5025,10 +5010,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s" s="0">
+      <c r="A137" t="s">
         <v>636</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="B137" t="s">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5039,10 +5024,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s" s="0">
+      <c r="A138" t="s">
         <v>640</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="B138" t="s">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5053,10 +5038,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s" s="0">
+      <c r="A139" t="s">
         <v>644</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="B139" t="s">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5067,10 +5052,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s" s="0">
+      <c r="A140" t="s">
         <v>648</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="B140" t="s">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5081,10 +5066,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s" s="0">
+      <c r="A141" t="s">
         <v>652</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="B141" t="s">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5095,10 +5080,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s" s="0">
+      <c r="A142" t="s">
         <v>656</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="B142" t="s">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5109,10 +5094,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s" s="0">
+      <c r="A143" t="s">
         <v>660</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="B143" t="s">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5123,10 +5108,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s" s="0">
+      <c r="A144" t="s">
         <v>664</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="B144" t="s">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5137,10 +5122,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s" s="0">
+      <c r="A145" t="s">
         <v>668</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="B145" t="s">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5151,10 +5136,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s" s="0">
+      <c r="A146" t="s">
         <v>672</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="B146" t="s">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5165,10 +5150,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s" s="0">
+      <c r="A147" t="s">
         <v>676</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="B147" t="s">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5179,10 +5164,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s" s="0">
+      <c r="A148" t="s">
         <v>680</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="B148" t="s">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5193,10 +5178,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s" s="0">
+      <c r="A149" t="s">
         <v>684</v>
       </c>
-      <c r="B149" t="s" s="0">
+      <c r="B149" t="s">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5207,10 +5192,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s" s="0">
+      <c r="A150" t="s">
         <v>688</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="B150" t="s">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5221,10 +5206,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s" s="0">
+      <c r="A151" t="s">
         <v>692</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="B151" t="s">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5235,10 +5220,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s" s="0">
+      <c r="A152" t="s">
         <v>696</v>
       </c>
-      <c r="B152" t="s" s="0">
+      <c r="B152" t="s">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5249,7 +5234,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s" s="0">
+      <c r="B153" t="s">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5260,7 +5245,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s" s="0">
+      <c r="B154" t="s">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5271,7 +5256,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s" s="0">
+      <c r="B155" t="s">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5282,7 +5267,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s" s="0">
+      <c r="B156" t="s">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5293,7 +5278,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s" s="0">
+      <c r="B157" t="s">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5304,7 +5289,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s" s="0">
+      <c r="B158" t="s">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2340,12 +2340,16 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Charlie87</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2697,20 +2701,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.726563" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
+    <col min="12" max="16384" style="1" width="8.726563"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3007,73 +3012,76 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.45313" customWidth="1"/>
-    <col min="3" max="3" width="35.63281" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.72656" customWidth="1"/>
-    <col min="6" max="6" width="32.17969" customWidth="1"/>
-    <col min="7" max="7" width="33.63281" customWidth="1"/>
-    <col min="8" max="8" width="31.26953" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.45313"/>
+    <col min="3" max="3" customWidth="true" width="35.63281"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.72656"/>
+    <col min="6" max="6" customWidth="true" width="32.17969"/>
+    <col min="7" max="7" customWidth="true" width="33.63281"/>
+    <col min="8" max="8" customWidth="true" width="31.26953"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>86</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>773</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>87</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" t="s">
+      <c r="A3" s="0"/>
+      <c r="B3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>87</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4"/>
-      <c r="B4" t="s">
+      <c r="A4" s="0"/>
+      <c r="B4" t="s" s="0">
         <v>87</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5"/>
+      <c r="A5" s="0"/>
     </row>
     <row r="6">
-      <c r="A6"/>
+      <c r="A6" s="0"/>
     </row>
   </sheetData>
   <pageSetup r:id="rId1" orientation="portrait"/>
@@ -3082,48 +3090,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984" customWidth="1"/>
-    <col min="2" max="2" width="17.54297" customWidth="1"/>
-    <col min="3" max="3" width="17.36328" customWidth="1"/>
-    <col min="4" max="5" width="17.26953" customWidth="1"/>
-    <col min="6" max="6" width="17.17969" customWidth="1"/>
-    <col min="7" max="7" width="15.36328" customWidth="1"/>
-    <col min="8" max="8" width="17.17969" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984"/>
+    <col min="2" max="2" customWidth="true" width="17.54297"/>
+    <col min="3" max="3" customWidth="true" width="17.36328"/>
+    <col min="4" max="5" customWidth="true" width="17.26953"/>
+    <col min="6" max="6" customWidth="true" width="17.17969"/>
+    <col min="7" max="7" customWidth="true" width="15.36328"/>
+    <col min="8" max="8" customWidth="true" width="17.17969"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3134,10 +3143,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3148,10 +3157,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3162,10 +3171,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3176,10 +3185,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3190,10 +3199,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3204,10 +3213,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3218,10 +3227,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3232,10 +3241,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3246,10 +3255,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3260,10 +3269,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3274,10 +3283,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3288,10 +3297,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3302,10 +3311,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3316,10 +3325,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3330,10 +3339,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3344,10 +3353,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3358,10 +3367,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3372,10 +3381,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3386,10 +3395,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3400,10 +3409,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3414,10 +3423,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>181</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -3428,10 +3437,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>184</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>185</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -3442,10 +3451,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>189</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3456,10 +3465,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3470,10 +3479,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3484,10 +3493,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3498,10 +3507,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>204</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3512,10 +3521,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3526,10 +3535,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3540,10 +3549,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>216</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3554,10 +3563,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3568,10 +3577,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3582,10 +3591,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>228</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3596,10 +3605,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>232</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3610,10 +3619,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>236</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3624,10 +3633,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>240</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3638,10 +3647,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3652,10 +3661,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3666,10 +3675,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3680,10 +3689,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3694,10 +3703,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3708,10 +3717,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3722,10 +3731,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3736,10 +3745,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>272</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3750,10 +3759,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3764,10 +3773,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3778,10 +3787,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3792,10 +3801,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3806,10 +3815,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3820,10 +3829,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>296</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3834,10 +3843,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3848,10 +3857,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3862,10 +3871,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>308</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3876,10 +3885,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>312</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3890,10 +3899,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>316</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3904,10 +3913,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>320</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3918,10 +3927,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3932,10 +3941,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3946,10 +3955,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>332</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3960,10 +3969,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>336</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3974,10 +3983,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -3988,10 +3997,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>344</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4002,10 +4011,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>348</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4016,10 +4025,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4030,10 +4039,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>356</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4044,10 +4053,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>360</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4058,10 +4067,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4072,10 +4081,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>368</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4086,10 +4095,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>372</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4100,10 +4109,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>376</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4114,10 +4123,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>380</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4128,10 +4137,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4142,10 +4151,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4156,10 +4165,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4170,10 +4179,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4184,10 +4193,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4198,10 +4207,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4212,10 +4221,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4226,10 +4235,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>412</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4240,10 +4249,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>416</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4254,10 +4263,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4268,10 +4277,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4282,10 +4291,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4296,10 +4305,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4310,10 +4319,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>436</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4324,10 +4333,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>440</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4338,10 +4347,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4352,10 +4361,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>448</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4366,10 +4375,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4380,10 +4389,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4394,10 +4403,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>460</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4408,10 +4417,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4422,10 +4431,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>468</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4436,10 +4445,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>472</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4450,10 +4459,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>476</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4464,10 +4473,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>480</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4478,10 +4487,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>484</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4492,10 +4501,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>488</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4506,10 +4515,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>492</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4520,10 +4529,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>496</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4534,10 +4543,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>500</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4548,10 +4557,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>504</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4562,10 +4571,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>508</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4576,10 +4585,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>512</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4590,10 +4599,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>516</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4604,10 +4613,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>520</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4618,10 +4627,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>524</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4632,10 +4641,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>528</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4646,10 +4655,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>532</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4660,10 +4669,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>536</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4674,10 +4683,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>540</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4688,10 +4697,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>544</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4702,10 +4711,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>548</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4716,10 +4725,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>552</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4730,10 +4739,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4744,10 +4753,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>560</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4758,10 +4767,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>564</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4772,10 +4781,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>568</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4786,10 +4795,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>572</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4800,10 +4809,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>576</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4814,10 +4823,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>580</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4828,10 +4837,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>584</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4842,10 +4851,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>588</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4856,10 +4865,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>592</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4870,10 +4879,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>596</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4884,10 +4893,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>600</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4898,10 +4907,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>604</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4912,10 +4921,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>608</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4926,10 +4935,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>612</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4940,10 +4949,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>616</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4954,10 +4963,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>620</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4968,10 +4977,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>624</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4982,10 +4991,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>628</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -4996,10 +5005,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>632</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5010,10 +5019,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>636</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5024,10 +5033,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>640</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5038,10 +5047,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>644</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5052,10 +5061,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>648</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5066,10 +5075,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>652</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5080,10 +5089,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>656</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5094,10 +5103,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>660</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5108,10 +5117,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>664</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5122,10 +5131,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>668</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5136,10 +5145,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>672</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5150,10 +5159,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>676</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5164,10 +5173,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>680</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5178,10 +5187,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>684</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5192,10 +5201,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>688</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5206,10 +5215,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>692</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5220,10 +5229,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>696</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5234,7 +5243,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5245,7 +5254,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5256,7 +5265,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5267,7 +5276,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5278,7 +5287,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5289,7 +5298,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2343,6 +2343,12 @@
   </si>
   <si>
     <t>Charlie87</t>
+  </si>
+  <si>
+    <t>Charlie88</t>
+  </si>
+  <si>
+    <t>fury34</t>
   </si>
 </sst>
 </file>
@@ -2391,7 +2397,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2401,6 +2407,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2862,7 +2872,7 @@
       <c r="C8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="7" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -2916,7 +2926,7 @@
       <c r="D11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="9" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2933,7 +2943,7 @@
       <c r="D12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="10" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3063,7 +3073,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0"/>
+      <c r="A3" t="s" s="0">
+        <v>774</v>
+      </c>
       <c r="B3" t="s" s="0">
         <v>87</v>
       </c>
@@ -3429,7 +3441,7 @@
       <c r="B23" t="s" s="0">
         <v>181</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D23" s="5" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2349,6 +2349,9 @@
   </si>
   <si>
     <t>fury34</t>
+  </si>
+  <si>
+    <t>Charlie89</t>
   </si>
 </sst>
 </file>
@@ -3084,7 +3087,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0"/>
+      <c r="A4" t="s" s="0">
+        <v>776</v>
+      </c>
       <c r="B4" t="s" s="0">
         <v>87</v>
       </c>

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2340,25 +2340,12 @@
   </si>
   <si>
     <t>Nexra</t>
-  </si>
-  <si>
-    <t>Charlie87</t>
-  </si>
-  <si>
-    <t>Charlie88</t>
-  </si>
-  <si>
-    <t>fury34</t>
-  </si>
-  <si>
-    <t>Charlie89</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2400,7 +2387,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2410,10 +2397,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2714,21 +2697,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
-    <col min="12" max="16384" style="1" width="8.726563"/>
+    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.726563" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2875,7 +2857,7 @@
       <c r="C8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -2929,7 +2911,7 @@
       <c r="D11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="2" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2946,7 +2928,7 @@
       <c r="D12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="2" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3025,80 +3007,76 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.45313"/>
-    <col min="3" max="3" customWidth="true" width="35.63281"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.72656"/>
-    <col min="6" max="6" customWidth="true" width="32.17969"/>
-    <col min="7" max="7" customWidth="true" width="33.63281"/>
-    <col min="8" max="8" customWidth="true" width="31.26953"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.45313" customWidth="1"/>
+    <col min="3" max="3" width="35.63281" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.72656" customWidth="1"/>
+    <col min="6" max="6" width="32.17969" customWidth="1"/>
+    <col min="7" max="7" width="33.63281" customWidth="1"/>
+    <col min="8" max="8" width="31.26953" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>79</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>80</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>81</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>82</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>84</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>85</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>773</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2"/>
+      <c r="B2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>774</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="A3"/>
+      <c r="B3" t="s">
         <v>87</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>776</v>
-      </c>
-      <c r="B4" t="s" s="0">
+      <c r="A4"/>
+      <c r="B4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0"/>
+      <c r="A5"/>
     </row>
     <row r="6">
-      <c r="A6" s="0"/>
+      <c r="A6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
     </row>
   </sheetData>
   <pageSetup r:id="rId1" orientation="portrait"/>
@@ -3107,49 +3085,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984"/>
-    <col min="2" max="2" customWidth="true" width="17.54297"/>
-    <col min="3" max="3" customWidth="true" width="17.36328"/>
-    <col min="4" max="5" customWidth="true" width="17.26953"/>
-    <col min="6" max="6" customWidth="true" width="17.17969"/>
-    <col min="7" max="7" customWidth="true" width="15.36328"/>
-    <col min="8" max="8" customWidth="true" width="17.17969"/>
+    <col min="1" max="1" width="20.08984" customWidth="1"/>
+    <col min="2" max="2" width="17.54297" customWidth="1"/>
+    <col min="3" max="3" width="17.36328" customWidth="1"/>
+    <col min="4" max="5" width="17.26953" customWidth="1"/>
+    <col min="6" max="6" width="17.17969" customWidth="1"/>
+    <col min="7" max="7" width="15.36328" customWidth="1"/>
+    <col min="8" max="8" width="17.17969" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>90</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>92</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>93</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>94</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>96</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3160,10 +3137,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>100</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3174,10 +3151,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3188,10 +3165,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>108</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3202,10 +3179,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>112</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3216,10 +3193,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="0">
+      <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3230,10 +3207,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s" s="0">
+      <c r="A8" t="s">
         <v>120</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3244,10 +3221,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s" s="0">
+      <c r="A9" t="s">
         <v>124</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3258,10 +3235,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="0">
+      <c r="A10" t="s">
         <v>128</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3272,10 +3249,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="0">
+      <c r="A11" t="s">
         <v>132</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3286,10 +3263,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="0">
+      <c r="A12" t="s">
         <v>136</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3300,10 +3277,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="0">
+      <c r="A13" t="s">
         <v>140</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3314,10 +3291,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="0">
+      <c r="A14" t="s">
         <v>144</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3328,10 +3305,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="0">
+      <c r="A15" t="s">
         <v>148</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3342,10 +3319,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s" s="0">
+      <c r="A16" t="s">
         <v>152</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3356,10 +3333,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s" s="0">
+      <c r="A17" t="s">
         <v>156</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3370,10 +3347,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="0">
+      <c r="A18" t="s">
         <v>160</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3384,10 +3361,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s" s="0">
+      <c r="A19" t="s">
         <v>164</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3398,10 +3375,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="0">
+      <c r="A20" t="s">
         <v>168</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3412,10 +3389,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s" s="0">
+      <c r="A21" t="s">
         <v>172</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B21" t="s">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3426,10 +3403,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s" s="0">
+      <c r="A22" t="s">
         <v>176</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="B22" t="s">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3440,13 +3417,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s" s="0">
+      <c r="A23" t="s">
         <v>180</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>181</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="2" t="s">
         <v>182</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -3454,10 +3431,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s" s="0">
+      <c r="A24" t="s">
         <v>184</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -3468,10 +3445,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s" s="0">
+      <c r="A25" t="s">
         <v>188</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B25" t="s">
         <v>189</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3482,10 +3459,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s" s="0">
+      <c r="A26" t="s">
         <v>192</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3496,10 +3473,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s" s="0">
+      <c r="A27" t="s">
         <v>196</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3510,10 +3487,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s" s="0">
+      <c r="A28" t="s">
         <v>200</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3524,10 +3501,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s" s="0">
+      <c r="A29" t="s">
         <v>204</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="B29" t="s">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3538,10 +3515,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s" s="0">
+      <c r="A30" t="s">
         <v>208</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="B30" t="s">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3552,10 +3529,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s" s="0">
+      <c r="A31" t="s">
         <v>212</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3566,10 +3543,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s" s="0">
+      <c r="A32" t="s">
         <v>216</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3580,10 +3557,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s" s="0">
+      <c r="A33" t="s">
         <v>220</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3594,10 +3571,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s" s="0">
+      <c r="A34" t="s">
         <v>224</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3608,10 +3585,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s" s="0">
+      <c r="A35" t="s">
         <v>228</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B35" t="s">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3622,10 +3599,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s" s="0">
+      <c r="A36" t="s">
         <v>232</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="B36" t="s">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3636,10 +3613,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s" s="0">
+      <c r="A37" t="s">
         <v>236</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B37" t="s">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3650,10 +3627,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s" s="0">
+      <c r="A38" t="s">
         <v>240</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B38" t="s">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3664,10 +3641,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s" s="0">
+      <c r="A39" t="s">
         <v>244</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="B39" t="s">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3678,10 +3655,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s" s="0">
+      <c r="A40" t="s">
         <v>248</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="B40" t="s">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3692,10 +3669,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s" s="0">
+      <c r="A41" t="s">
         <v>252</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="B41" t="s">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3706,10 +3683,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s" s="0">
+      <c r="A42" t="s">
         <v>256</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="B42" t="s">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3720,10 +3697,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s" s="0">
+      <c r="A43" t="s">
         <v>260</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="B43" t="s">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3734,10 +3711,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s" s="0">
+      <c r="A44" t="s">
         <v>264</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B44" t="s">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3748,10 +3725,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s" s="0">
+      <c r="A45" t="s">
         <v>268</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="B45" t="s">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3762,10 +3739,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s" s="0">
+      <c r="A46" t="s">
         <v>272</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="B46" t="s">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3776,10 +3753,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s" s="0">
+      <c r="A47" t="s">
         <v>276</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B47" t="s">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3790,10 +3767,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s" s="0">
+      <c r="A48" t="s">
         <v>280</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="B48" t="s">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3804,10 +3781,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="0">
+      <c r="A49" t="s">
         <v>284</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="B49" t="s">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3818,10 +3795,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s" s="0">
+      <c r="A50" t="s">
         <v>288</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="B50" t="s">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3832,10 +3809,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s" s="0">
+      <c r="A51" t="s">
         <v>292</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="B51" t="s">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3846,10 +3823,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s" s="0">
+      <c r="A52" t="s">
         <v>296</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="B52" t="s">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3860,10 +3837,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s" s="0">
+      <c r="A53" t="s">
         <v>300</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="B53" t="s">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3874,10 +3851,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s" s="0">
+      <c r="A54" t="s">
         <v>304</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="B54" t="s">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3888,10 +3865,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s" s="0">
+      <c r="A55" t="s">
         <v>308</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3902,10 +3879,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s" s="0">
+      <c r="A56" t="s">
         <v>312</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="B56" t="s">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3916,10 +3893,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s" s="0">
+      <c r="A57" t="s">
         <v>316</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B57" t="s">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3930,10 +3907,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s" s="0">
+      <c r="A58" t="s">
         <v>320</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="B58" t="s">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3944,10 +3921,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s" s="0">
+      <c r="A59" t="s">
         <v>324</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="B59" t="s">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3958,10 +3935,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s" s="0">
+      <c r="A60" t="s">
         <v>328</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="B60" t="s">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3972,10 +3949,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s" s="0">
+      <c r="A61" t="s">
         <v>332</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="B61" t="s">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3986,10 +3963,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s" s="0">
+      <c r="A62" t="s">
         <v>336</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="B62" t="s">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -4000,10 +3977,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s" s="0">
+      <c r="A63" t="s">
         <v>340</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="B63" t="s">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4014,10 +3991,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s" s="0">
+      <c r="A64" t="s">
         <v>344</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="B64" t="s">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4028,10 +4005,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s" s="0">
+      <c r="A65" t="s">
         <v>348</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="B65" t="s">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4042,10 +4019,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s" s="0">
+      <c r="A66" t="s">
         <v>352</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="B66" t="s">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4056,10 +4033,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s" s="0">
+      <c r="A67" t="s">
         <v>356</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="B67" t="s">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4070,10 +4047,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s" s="0">
+      <c r="A68" t="s">
         <v>360</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B68" t="s">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4084,10 +4061,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s" s="0">
+      <c r="A69" t="s">
         <v>364</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B69" t="s">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4098,10 +4075,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s" s="0">
+      <c r="A70" t="s">
         <v>368</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="B70" t="s">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4112,10 +4089,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="0">
+      <c r="A71" t="s">
         <v>372</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="B71" t="s">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4126,10 +4103,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s" s="0">
+      <c r="A72" t="s">
         <v>376</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="B72" t="s">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4140,10 +4117,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s" s="0">
+      <c r="A73" t="s">
         <v>380</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="B73" t="s">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4154,10 +4131,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s" s="0">
+      <c r="A74" t="s">
         <v>384</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="B74" t="s">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4168,10 +4145,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s" s="0">
+      <c r="A75" t="s">
         <v>388</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="B75" t="s">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4182,10 +4159,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s" s="0">
+      <c r="A76" t="s">
         <v>392</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B76" t="s">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4196,10 +4173,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s" s="0">
+      <c r="A77" t="s">
         <v>396</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="B77" t="s">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4210,10 +4187,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s" s="0">
+      <c r="A78" t="s">
         <v>400</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B78" t="s">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4224,10 +4201,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s" s="0">
+      <c r="A79" t="s">
         <v>404</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="B79" t="s">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4238,10 +4215,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s" s="0">
+      <c r="A80" t="s">
         <v>408</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="B80" t="s">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4252,10 +4229,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s" s="0">
+      <c r="A81" t="s">
         <v>412</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B81" t="s">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4266,10 +4243,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s" s="0">
+      <c r="A82" t="s">
         <v>416</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="B82" t="s">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4280,10 +4257,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s" s="0">
+      <c r="A83" t="s">
         <v>420</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B83" t="s">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4294,10 +4271,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s" s="0">
+      <c r="A84" t="s">
         <v>424</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B84" t="s">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4308,10 +4285,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s" s="0">
+      <c r="A85" t="s">
         <v>428</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="B85" t="s">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4322,10 +4299,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s" s="0">
+      <c r="A86" t="s">
         <v>432</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="B86" t="s">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4336,10 +4313,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s" s="0">
+      <c r="A87" t="s">
         <v>436</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="B87" t="s">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4350,10 +4327,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s" s="0">
+      <c r="A88" t="s">
         <v>440</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="B88" t="s">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4364,10 +4341,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s" s="0">
+      <c r="A89" t="s">
         <v>444</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="B89" t="s">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4378,10 +4355,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s" s="0">
+      <c r="A90" t="s">
         <v>448</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="B90" t="s">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4392,10 +4369,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s" s="0">
+      <c r="A91" t="s">
         <v>452</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="B91" t="s">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4406,10 +4383,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s" s="0">
+      <c r="A92" t="s">
         <v>456</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="B92" t="s">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4420,10 +4397,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s" s="0">
+      <c r="A93" t="s">
         <v>460</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B93" t="s">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4434,10 +4411,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s" s="0">
+      <c r="A94" t="s">
         <v>464</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="B94" t="s">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4448,10 +4425,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s" s="0">
+      <c r="A95" t="s">
         <v>468</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="B95" t="s">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4462,10 +4439,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s" s="0">
+      <c r="A96" t="s">
         <v>472</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="B96" t="s">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4476,10 +4453,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s" s="0">
+      <c r="A97" t="s">
         <v>476</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="B97" t="s">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4490,10 +4467,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s" s="0">
+      <c r="A98" t="s">
         <v>480</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="B98" t="s">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4504,10 +4481,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s" s="0">
+      <c r="A99" t="s">
         <v>484</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="B99" t="s">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4518,10 +4495,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s" s="0">
+      <c r="A100" t="s">
         <v>488</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="B100" t="s">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4532,10 +4509,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s" s="0">
+      <c r="A101" t="s">
         <v>492</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="B101" t="s">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4546,10 +4523,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s" s="0">
+      <c r="A102" t="s">
         <v>496</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="B102" t="s">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4560,10 +4537,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s" s="0">
+      <c r="A103" t="s">
         <v>500</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="B103" t="s">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4574,10 +4551,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s" s="0">
+      <c r="A104" t="s">
         <v>504</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="B104" t="s">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4588,10 +4565,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s" s="0">
+      <c r="A105" t="s">
         <v>508</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="B105" t="s">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4602,10 +4579,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s" s="0">
+      <c r="A106" t="s">
         <v>512</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="B106" t="s">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4616,10 +4593,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s" s="0">
+      <c r="A107" t="s">
         <v>516</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="B107" t="s">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4630,10 +4607,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s" s="0">
+      <c r="A108" t="s">
         <v>520</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="B108" t="s">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4644,10 +4621,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s" s="0">
+      <c r="A109" t="s">
         <v>524</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="B109" t="s">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4658,10 +4635,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s" s="0">
+      <c r="A110" t="s">
         <v>528</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="B110" t="s">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4672,10 +4649,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s" s="0">
+      <c r="A111" t="s">
         <v>532</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="B111" t="s">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4686,10 +4663,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s" s="0">
+      <c r="A112" t="s">
         <v>536</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="B112" t="s">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4700,10 +4677,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s" s="0">
+      <c r="A113" t="s">
         <v>540</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="B113" t="s">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4714,10 +4691,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s" s="0">
+      <c r="A114" t="s">
         <v>544</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="B114" t="s">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4728,10 +4705,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s" s="0">
+      <c r="A115" t="s">
         <v>548</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="B115" t="s">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4742,10 +4719,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s" s="0">
+      <c r="A116" t="s">
         <v>552</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="B116" t="s">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4756,10 +4733,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s" s="0">
+      <c r="A117" t="s">
         <v>556</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="B117" t="s">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4770,10 +4747,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s" s="0">
+      <c r="A118" t="s">
         <v>560</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="B118" t="s">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4784,10 +4761,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s" s="0">
+      <c r="A119" t="s">
         <v>564</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="B119" t="s">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4798,10 +4775,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s" s="0">
+      <c r="A120" t="s">
         <v>568</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="B120" t="s">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4812,10 +4789,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s" s="0">
+      <c r="A121" t="s">
         <v>572</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="B121" t="s">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4826,10 +4803,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s" s="0">
+      <c r="A122" t="s">
         <v>576</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="B122" t="s">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4840,10 +4817,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s" s="0">
+      <c r="A123" t="s">
         <v>580</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="B123" t="s">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4854,10 +4831,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s" s="0">
+      <c r="A124" t="s">
         <v>584</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="B124" t="s">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4868,10 +4845,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s" s="0">
+      <c r="A125" t="s">
         <v>588</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="B125" t="s">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4882,10 +4859,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s" s="0">
+      <c r="A126" t="s">
         <v>592</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="B126" t="s">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4896,10 +4873,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s" s="0">
+      <c r="A127" t="s">
         <v>596</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="B127" t="s">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4910,10 +4887,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s" s="0">
+      <c r="A128" t="s">
         <v>600</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="B128" t="s">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4924,10 +4901,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s" s="0">
+      <c r="A129" t="s">
         <v>604</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="B129" t="s">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4938,10 +4915,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s" s="0">
+      <c r="A130" t="s">
         <v>608</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="B130" t="s">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4952,10 +4929,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s" s="0">
+      <c r="A131" t="s">
         <v>612</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="B131" t="s">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4966,10 +4943,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s" s="0">
+      <c r="A132" t="s">
         <v>616</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="B132" t="s">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4980,10 +4957,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s" s="0">
+      <c r="A133" t="s">
         <v>620</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="B133" t="s">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4994,10 +4971,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s" s="0">
+      <c r="A134" t="s">
         <v>624</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="B134" t="s">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -5008,10 +4985,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s" s="0">
+      <c r="A135" t="s">
         <v>628</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="B135" t="s">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5022,10 +4999,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s" s="0">
+      <c r="A136" t="s">
         <v>632</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="B136" t="s">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5036,10 +5013,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s" s="0">
+      <c r="A137" t="s">
         <v>636</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="B137" t="s">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5050,10 +5027,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s" s="0">
+      <c r="A138" t="s">
         <v>640</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="B138" t="s">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5064,10 +5041,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s" s="0">
+      <c r="A139" t="s">
         <v>644</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="B139" t="s">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5078,10 +5055,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s" s="0">
+      <c r="A140" t="s">
         <v>648</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="B140" t="s">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5092,10 +5069,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s" s="0">
+      <c r="A141" t="s">
         <v>652</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="B141" t="s">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5106,10 +5083,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s" s="0">
+      <c r="A142" t="s">
         <v>656</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="B142" t="s">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5120,10 +5097,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s" s="0">
+      <c r="A143" t="s">
         <v>660</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="B143" t="s">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5134,10 +5111,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s" s="0">
+      <c r="A144" t="s">
         <v>664</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="B144" t="s">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5148,10 +5125,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s" s="0">
+      <c r="A145" t="s">
         <v>668</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="B145" t="s">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5162,10 +5139,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s" s="0">
+      <c r="A146" t="s">
         <v>672</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="B146" t="s">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5176,10 +5153,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s" s="0">
+      <c r="A147" t="s">
         <v>676</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="B147" t="s">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5190,10 +5167,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s" s="0">
+      <c r="A148" t="s">
         <v>680</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="B148" t="s">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5204,10 +5181,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s" s="0">
+      <c r="A149" t="s">
         <v>684</v>
       </c>
-      <c r="B149" t="s" s="0">
+      <c r="B149" t="s">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5218,10 +5195,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s" s="0">
+      <c r="A150" t="s">
         <v>688</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="B150" t="s">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5232,10 +5209,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s" s="0">
+      <c r="A151" t="s">
         <v>692</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="B151" t="s">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5246,10 +5223,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s" s="0">
+      <c r="A152" t="s">
         <v>696</v>
       </c>
-      <c r="B152" t="s" s="0">
+      <c r="B152" t="s">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5260,7 +5237,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s" s="0">
+      <c r="B153" t="s">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5271,7 +5248,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s" s="0">
+      <c r="B154" t="s">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5282,7 +5259,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s" s="0">
+      <c r="B155" t="s">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5293,7 +5270,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s" s="0">
+      <c r="B156" t="s">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5304,7 +5281,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s" s="0">
+      <c r="B157" t="s">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5315,7 +5292,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s" s="0">
+      <c r="B158" t="s">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2340,12 +2340,37 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Charlie91</t>
+  </si>
+  <si>
+    <t>Milo61</t>
+  </si>
+  <si>
+    <t>Taffy59</t>
+  </si>
+  <si>
+    <t>Cutie46</t>
+  </si>
+  <si>
+    <t>Cinder46</t>
+  </si>
+  <si>
+    <t>pony38</t>
+  </si>
+  <si>
+    <t>fury35</t>
+  </si>
+  <si>
+    <t>Sheep31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2387,7 +2412,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2397,6 +2422,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2697,20 +2732,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.726563" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
+    <col min="12" max="16384" style="1" width="8.726563"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2783,10 +2819,10 @@
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -2831,7 +2867,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -2848,7 +2884,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2874,7 +2910,7 @@
       <c r="C9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="11" t="s">
         <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -2891,7 +2927,7 @@
       <c r="C10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="12" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -2939,7 +2975,7 @@
       <c r="D13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="14" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2950,12 +2986,12 @@
       <c r="D14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="15" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="16" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3007,76 +3043,86 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.45313" customWidth="1"/>
-    <col min="3" max="3" width="35.63281" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.72656" customWidth="1"/>
-    <col min="6" max="6" width="32.17969" customWidth="1"/>
-    <col min="7" max="7" width="33.63281" customWidth="1"/>
-    <col min="8" max="8" width="31.26953" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.45313"/>
+    <col min="3" max="3" customWidth="true" width="35.63281"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.72656"/>
+    <col min="6" max="6" customWidth="true" width="32.17969"/>
+    <col min="7" max="7" customWidth="true" width="33.63281"/>
+    <col min="8" max="8" customWidth="true" width="31.26953"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>86</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
         <v>87</v>
       </c>
+      <c r="C2" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>87</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
         <v>87</v>
       </c>
+      <c r="C3" t="s" s="0">
+        <v>87</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4"/>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
         <v>87</v>
       </c>
+      <c r="B4" t="s" s="0">
+        <v>87</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5"/>
+      <c r="A5" s="0"/>
     </row>
     <row r="6">
-      <c r="A6"/>
+      <c r="A6" s="0"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" s="0"/>
     </row>
   </sheetData>
   <pageSetup r:id="rId1" orientation="portrait"/>
@@ -3085,48 +3131,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984" customWidth="1"/>
-    <col min="2" max="2" width="17.54297" customWidth="1"/>
-    <col min="3" max="3" width="17.36328" customWidth="1"/>
-    <col min="4" max="5" width="17.26953" customWidth="1"/>
-    <col min="6" max="6" width="17.17969" customWidth="1"/>
-    <col min="7" max="7" width="15.36328" customWidth="1"/>
-    <col min="8" max="8" width="17.17969" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984"/>
+    <col min="2" max="2" customWidth="true" width="17.54297"/>
+    <col min="3" max="3" customWidth="true" width="17.36328"/>
+    <col min="4" max="5" customWidth="true" width="17.26953"/>
+    <col min="6" max="6" customWidth="true" width="17.17969"/>
+    <col min="7" max="7" customWidth="true" width="15.36328"/>
+    <col min="8" max="8" customWidth="true" width="17.17969"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3137,10 +3184,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3151,10 +3198,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3165,10 +3212,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3179,10 +3226,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3193,10 +3240,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3207,10 +3254,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3221,10 +3268,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3235,10 +3282,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3249,10 +3296,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3263,10 +3310,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3277,10 +3324,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3291,10 +3338,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3305,10 +3352,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3319,10 +3366,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3333,10 +3380,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3347,10 +3394,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3361,10 +3408,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3375,10 +3422,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3389,10 +3436,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3403,10 +3450,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3417,10 +3464,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3431,13 +3478,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>184</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>185</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="13" t="s">
         <v>186</v>
       </c>
       <c r="D24" s="5" t="s">
@@ -3445,10 +3492,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>189</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -3459,10 +3506,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3473,10 +3520,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3487,10 +3534,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3501,10 +3548,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>204</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3515,10 +3562,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3529,10 +3576,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3543,10 +3590,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>216</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3557,10 +3604,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3571,10 +3618,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3585,10 +3632,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>228</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3599,10 +3646,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>232</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3613,10 +3660,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>236</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3627,10 +3674,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>240</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3641,10 +3688,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3655,10 +3702,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3669,10 +3716,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3683,10 +3730,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3697,10 +3744,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3711,10 +3758,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3725,10 +3772,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3739,10 +3786,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>272</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3753,10 +3800,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3767,10 +3814,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3781,10 +3828,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3795,10 +3842,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3809,10 +3856,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3823,10 +3870,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>296</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3837,10 +3884,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3851,10 +3898,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3865,10 +3912,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>308</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3879,10 +3926,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>312</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3893,10 +3940,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>316</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3907,10 +3954,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>320</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3921,10 +3968,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3935,10 +3982,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3949,10 +3996,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>332</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3963,10 +4010,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>336</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3977,10 +4024,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -3991,10 +4038,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>344</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4005,10 +4052,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>348</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4019,10 +4066,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4033,10 +4080,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>356</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4047,10 +4094,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>360</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4061,10 +4108,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4075,10 +4122,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>368</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4089,10 +4136,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>372</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4103,10 +4150,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>376</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4117,10 +4164,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>380</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4131,10 +4178,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4145,10 +4192,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4159,10 +4206,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4173,10 +4220,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4187,10 +4234,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4201,10 +4248,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4215,10 +4262,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4229,10 +4276,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>412</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4243,10 +4290,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>416</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4257,10 +4304,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4271,10 +4318,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4285,10 +4332,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4299,10 +4346,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4313,10 +4360,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>436</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4327,10 +4374,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>440</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4341,10 +4388,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4355,10 +4402,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>448</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4369,10 +4416,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4383,10 +4430,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4397,10 +4444,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>460</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4411,10 +4458,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4425,10 +4472,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>468</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4439,10 +4486,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>472</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4453,10 +4500,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>476</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4467,10 +4514,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>480</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4481,10 +4528,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>484</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4495,10 +4542,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>488</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4509,10 +4556,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>492</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4523,10 +4570,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>496</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4537,10 +4584,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>500</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4551,10 +4598,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>504</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4565,10 +4612,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>508</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4579,10 +4626,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>512</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4593,10 +4640,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>516</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4607,10 +4654,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>520</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4621,10 +4668,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>524</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4635,10 +4682,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>528</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4649,10 +4696,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>532</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4663,10 +4710,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>536</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4677,10 +4724,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>540</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4691,10 +4738,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>544</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4705,10 +4752,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>548</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4719,10 +4766,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>552</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4733,10 +4780,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4747,10 +4794,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>560</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4761,10 +4808,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>564</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4775,10 +4822,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>568</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4789,10 +4836,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>572</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4803,10 +4850,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>576</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4817,10 +4864,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>580</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4831,10 +4878,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>584</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4845,10 +4892,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>588</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4859,10 +4906,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>592</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4873,10 +4920,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>596</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4887,10 +4934,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>600</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4901,10 +4948,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>604</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4915,10 +4962,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>608</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4929,10 +4976,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>612</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4943,10 +4990,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>616</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4957,10 +5004,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>620</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4971,10 +5018,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>624</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4985,10 +5032,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>628</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -4999,10 +5046,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>632</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5013,10 +5060,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>636</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5027,10 +5074,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>640</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5041,10 +5088,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>644</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5055,10 +5102,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>648</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5069,10 +5116,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>652</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5083,10 +5130,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>656</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5097,10 +5144,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>660</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5111,10 +5158,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>664</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5125,10 +5172,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>668</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5139,10 +5186,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>672</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5153,10 +5200,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>676</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5167,10 +5214,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>680</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5181,10 +5228,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>684</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5195,10 +5242,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>688</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5209,10 +5256,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>692</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5223,10 +5270,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>696</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5237,7 +5284,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5248,7 +5295,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5259,7 +5306,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5270,7 +5317,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5281,7 +5328,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5292,7 +5339,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2340,37 +2340,12 @@
   </si>
   <si>
     <t>Nexra</t>
-  </si>
-  <si>
-    <t>Charlie91</t>
-  </si>
-  <si>
-    <t>Milo61</t>
-  </si>
-  <si>
-    <t>Taffy59</t>
-  </si>
-  <si>
-    <t>Cutie46</t>
-  </si>
-  <si>
-    <t>Cinder46</t>
-  </si>
-  <si>
-    <t>pony38</t>
-  </si>
-  <si>
-    <t>fury35</t>
-  </si>
-  <si>
-    <t>Sheep31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2412,7 +2387,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2422,16 +2397,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2732,21 +2697,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
-    <col min="12" max="16384" style="1" width="8.726563"/>
+    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.726563" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2819,10 +2783,10 @@
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -2836,10 +2800,10 @@
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -2867,7 +2831,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -2884,7 +2848,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2901,7 +2865,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -2910,7 +2874,7 @@
       <c r="C9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -2918,7 +2882,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -2927,7 +2891,7 @@
       <c r="C10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -2944,7 +2908,7 @@
       <c r="C11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -2961,7 +2925,7 @@
       <c r="C12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -2975,7 +2939,7 @@
       <c r="D13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="2" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2986,22 +2950,22 @@
       <c r="D14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3043,86 +3007,74 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.45313"/>
-    <col min="3" max="3" customWidth="true" width="35.63281"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.72656"/>
-    <col min="6" max="6" customWidth="true" width="32.17969"/>
-    <col min="7" max="7" customWidth="true" width="33.63281"/>
-    <col min="8" max="8" customWidth="true" width="31.26953"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.45313" customWidth="1"/>
+    <col min="3" max="3" width="35.63281" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.72656" customWidth="1"/>
+    <col min="6" max="6" width="32.17969" customWidth="1"/>
+    <col min="7" max="7" width="33.63281" customWidth="1"/>
+    <col min="8" max="8" width="31.26953" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>79</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>80</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>81</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>82</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>84</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>85</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>87</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>87</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+      <c r="B3" t="s">
         <v>87</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C3" t="s">
         <v>87</v>
       </c>
-      <c r="C3" t="s" s="0">
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+      <c r="B4" t="s">
         <v>87</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="0"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="0"/>
     </row>
   </sheetData>
   <pageSetup r:id="rId1" orientation="portrait"/>
@@ -3131,49 +3083,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984"/>
-    <col min="2" max="2" customWidth="true" width="17.54297"/>
-    <col min="3" max="3" customWidth="true" width="17.36328"/>
-    <col min="4" max="5" customWidth="true" width="17.26953"/>
-    <col min="6" max="6" customWidth="true" width="17.17969"/>
-    <col min="7" max="7" customWidth="true" width="15.36328"/>
-    <col min="8" max="8" customWidth="true" width="17.17969"/>
+    <col min="1" max="1" width="20.08984" customWidth="1"/>
+    <col min="2" max="2" width="17.54297" customWidth="1"/>
+    <col min="3" max="3" width="17.36328" customWidth="1"/>
+    <col min="4" max="5" width="17.26953" customWidth="1"/>
+    <col min="6" max="6" width="17.17969" customWidth="1"/>
+    <col min="7" max="7" width="15.36328" customWidth="1"/>
+    <col min="8" max="8" width="17.17969" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>90</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>92</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>93</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>94</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>96</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3184,10 +3135,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>100</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3198,10 +3149,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3212,10 +3163,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>108</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3226,10 +3177,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>112</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3240,10 +3191,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="0">
+      <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3254,10 +3205,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s" s="0">
+      <c r="A8" t="s">
         <v>120</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3268,10 +3219,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s" s="0">
+      <c r="A9" t="s">
         <v>124</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3282,10 +3233,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="0">
+      <c r="A10" t="s">
         <v>128</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3296,10 +3247,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="0">
+      <c r="A11" t="s">
         <v>132</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3310,10 +3261,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="0">
+      <c r="A12" t="s">
         <v>136</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3324,10 +3275,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="0">
+      <c r="A13" t="s">
         <v>140</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3338,10 +3289,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="0">
+      <c r="A14" t="s">
         <v>144</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3352,10 +3303,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="0">
+      <c r="A15" t="s">
         <v>148</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3366,10 +3317,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s" s="0">
+      <c r="A16" t="s">
         <v>152</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3380,10 +3331,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s" s="0">
+      <c r="A17" t="s">
         <v>156</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3394,10 +3345,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="0">
+      <c r="A18" t="s">
         <v>160</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3408,10 +3359,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s" s="0">
+      <c r="A19" t="s">
         <v>164</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3422,10 +3373,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="0">
+      <c r="A20" t="s">
         <v>168</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3436,10 +3387,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s" s="0">
+      <c r="A21" t="s">
         <v>172</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B21" t="s">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3450,10 +3401,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s" s="0">
+      <c r="A22" t="s">
         <v>176</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="B22" t="s">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3464,10 +3415,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s" s="0">
+      <c r="A23" t="s">
         <v>180</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3478,13 +3429,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s" s="0">
+      <c r="A24" t="s">
         <v>184</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>185</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="2" t="s">
         <v>186</v>
       </c>
       <c r="D24" s="5" t="s">
@@ -3492,13 +3443,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s" s="0">
+      <c r="A25" t="s">
         <v>188</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B25" t="s">
         <v>189</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="D25" s="5" t="s">
@@ -3506,10 +3457,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s" s="0">
+      <c r="A26" t="s">
         <v>192</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3520,10 +3471,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s" s="0">
+      <c r="A27" t="s">
         <v>196</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3534,10 +3485,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s" s="0">
+      <c r="A28" t="s">
         <v>200</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3548,10 +3499,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s" s="0">
+      <c r="A29" t="s">
         <v>204</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="B29" t="s">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3562,10 +3513,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s" s="0">
+      <c r="A30" t="s">
         <v>208</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="B30" t="s">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3576,10 +3527,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s" s="0">
+      <c r="A31" t="s">
         <v>212</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3590,10 +3541,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s" s="0">
+      <c r="A32" t="s">
         <v>216</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3604,10 +3555,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s" s="0">
+      <c r="A33" t="s">
         <v>220</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3618,10 +3569,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s" s="0">
+      <c r="A34" t="s">
         <v>224</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3632,10 +3583,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s" s="0">
+      <c r="A35" t="s">
         <v>228</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B35" t="s">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3646,10 +3597,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s" s="0">
+      <c r="A36" t="s">
         <v>232</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="B36" t="s">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3660,10 +3611,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s" s="0">
+      <c r="A37" t="s">
         <v>236</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B37" t="s">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3674,10 +3625,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s" s="0">
+      <c r="A38" t="s">
         <v>240</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B38" t="s">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3688,10 +3639,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s" s="0">
+      <c r="A39" t="s">
         <v>244</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="B39" t="s">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3702,10 +3653,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s" s="0">
+      <c r="A40" t="s">
         <v>248</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="B40" t="s">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3716,10 +3667,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s" s="0">
+      <c r="A41" t="s">
         <v>252</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="B41" t="s">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3730,10 +3681,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s" s="0">
+      <c r="A42" t="s">
         <v>256</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="B42" t="s">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3744,10 +3695,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s" s="0">
+      <c r="A43" t="s">
         <v>260</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="B43" t="s">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3758,10 +3709,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s" s="0">
+      <c r="A44" t="s">
         <v>264</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B44" t="s">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3772,10 +3723,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s" s="0">
+      <c r="A45" t="s">
         <v>268</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="B45" t="s">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3786,10 +3737,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s" s="0">
+      <c r="A46" t="s">
         <v>272</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="B46" t="s">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3800,10 +3751,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s" s="0">
+      <c r="A47" t="s">
         <v>276</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B47" t="s">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3814,10 +3765,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s" s="0">
+      <c r="A48" t="s">
         <v>280</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="B48" t="s">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3828,10 +3779,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="0">
+      <c r="A49" t="s">
         <v>284</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="B49" t="s">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3842,10 +3793,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s" s="0">
+      <c r="A50" t="s">
         <v>288</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="B50" t="s">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3856,10 +3807,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s" s="0">
+      <c r="A51" t="s">
         <v>292</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="B51" t="s">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3870,10 +3821,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s" s="0">
+      <c r="A52" t="s">
         <v>296</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="B52" t="s">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3884,10 +3835,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s" s="0">
+      <c r="A53" t="s">
         <v>300</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="B53" t="s">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3898,10 +3849,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s" s="0">
+      <c r="A54" t="s">
         <v>304</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="B54" t="s">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3912,10 +3863,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s" s="0">
+      <c r="A55" t="s">
         <v>308</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3926,10 +3877,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s" s="0">
+      <c r="A56" t="s">
         <v>312</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="B56" t="s">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3940,10 +3891,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s" s="0">
+      <c r="A57" t="s">
         <v>316</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B57" t="s">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3954,10 +3905,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s" s="0">
+      <c r="A58" t="s">
         <v>320</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="B58" t="s">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3968,10 +3919,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s" s="0">
+      <c r="A59" t="s">
         <v>324</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="B59" t="s">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3982,10 +3933,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s" s="0">
+      <c r="A60" t="s">
         <v>328</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="B60" t="s">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3996,10 +3947,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s" s="0">
+      <c r="A61" t="s">
         <v>332</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="B61" t="s">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -4010,10 +3961,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s" s="0">
+      <c r="A62" t="s">
         <v>336</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="B62" t="s">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -4024,10 +3975,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s" s="0">
+      <c r="A63" t="s">
         <v>340</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="B63" t="s">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4038,10 +3989,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s" s="0">
+      <c r="A64" t="s">
         <v>344</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="B64" t="s">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4052,10 +4003,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s" s="0">
+      <c r="A65" t="s">
         <v>348</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="B65" t="s">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4066,10 +4017,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s" s="0">
+      <c r="A66" t="s">
         <v>352</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="B66" t="s">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4080,10 +4031,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s" s="0">
+      <c r="A67" t="s">
         <v>356</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="B67" t="s">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4094,10 +4045,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s" s="0">
+      <c r="A68" t="s">
         <v>360</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B68" t="s">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4108,10 +4059,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s" s="0">
+      <c r="A69" t="s">
         <v>364</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B69" t="s">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4122,10 +4073,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s" s="0">
+      <c r="A70" t="s">
         <v>368</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="B70" t="s">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4136,10 +4087,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="0">
+      <c r="A71" t="s">
         <v>372</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="B71" t="s">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4150,10 +4101,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s" s="0">
+      <c r="A72" t="s">
         <v>376</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="B72" t="s">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4164,10 +4115,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s" s="0">
+      <c r="A73" t="s">
         <v>380</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="B73" t="s">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4178,10 +4129,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s" s="0">
+      <c r="A74" t="s">
         <v>384</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="B74" t="s">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4192,10 +4143,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s" s="0">
+      <c r="A75" t="s">
         <v>388</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="B75" t="s">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4206,10 +4157,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s" s="0">
+      <c r="A76" t="s">
         <v>392</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B76" t="s">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4220,10 +4171,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s" s="0">
+      <c r="A77" t="s">
         <v>396</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="B77" t="s">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4234,10 +4185,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s" s="0">
+      <c r="A78" t="s">
         <v>400</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B78" t="s">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4248,10 +4199,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s" s="0">
+      <c r="A79" t="s">
         <v>404</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="B79" t="s">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4262,10 +4213,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s" s="0">
+      <c r="A80" t="s">
         <v>408</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="B80" t="s">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4276,10 +4227,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s" s="0">
+      <c r="A81" t="s">
         <v>412</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B81" t="s">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4290,10 +4241,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s" s="0">
+      <c r="A82" t="s">
         <v>416</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="B82" t="s">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4304,10 +4255,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s" s="0">
+      <c r="A83" t="s">
         <v>420</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B83" t="s">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4318,10 +4269,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s" s="0">
+      <c r="A84" t="s">
         <v>424</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B84" t="s">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4332,10 +4283,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s" s="0">
+      <c r="A85" t="s">
         <v>428</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="B85" t="s">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4346,10 +4297,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s" s="0">
+      <c r="A86" t="s">
         <v>432</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="B86" t="s">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4360,10 +4311,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s" s="0">
+      <c r="A87" t="s">
         <v>436</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="B87" t="s">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4374,10 +4325,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s" s="0">
+      <c r="A88" t="s">
         <v>440</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="B88" t="s">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4388,10 +4339,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s" s="0">
+      <c r="A89" t="s">
         <v>444</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="B89" t="s">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4402,10 +4353,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s" s="0">
+      <c r="A90" t="s">
         <v>448</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="B90" t="s">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4416,10 +4367,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s" s="0">
+      <c r="A91" t="s">
         <v>452</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="B91" t="s">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4430,10 +4381,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s" s="0">
+      <c r="A92" t="s">
         <v>456</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="B92" t="s">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4444,10 +4395,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s" s="0">
+      <c r="A93" t="s">
         <v>460</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B93" t="s">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4458,10 +4409,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s" s="0">
+      <c r="A94" t="s">
         <v>464</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="B94" t="s">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4472,10 +4423,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s" s="0">
+      <c r="A95" t="s">
         <v>468</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="B95" t="s">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4486,10 +4437,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s" s="0">
+      <c r="A96" t="s">
         <v>472</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="B96" t="s">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4500,10 +4451,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s" s="0">
+      <c r="A97" t="s">
         <v>476</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="B97" t="s">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4514,10 +4465,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s" s="0">
+      <c r="A98" t="s">
         <v>480</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="B98" t="s">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4528,10 +4479,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s" s="0">
+      <c r="A99" t="s">
         <v>484</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="B99" t="s">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4542,10 +4493,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s" s="0">
+      <c r="A100" t="s">
         <v>488</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="B100" t="s">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4556,10 +4507,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s" s="0">
+      <c r="A101" t="s">
         <v>492</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="B101" t="s">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4570,10 +4521,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s" s="0">
+      <c r="A102" t="s">
         <v>496</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="B102" t="s">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4584,10 +4535,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s" s="0">
+      <c r="A103" t="s">
         <v>500</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="B103" t="s">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4598,10 +4549,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s" s="0">
+      <c r="A104" t="s">
         <v>504</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="B104" t="s">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4612,10 +4563,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s" s="0">
+      <c r="A105" t="s">
         <v>508</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="B105" t="s">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4626,10 +4577,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s" s="0">
+      <c r="A106" t="s">
         <v>512</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="B106" t="s">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4640,10 +4591,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s" s="0">
+      <c r="A107" t="s">
         <v>516</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="B107" t="s">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4654,10 +4605,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s" s="0">
+      <c r="A108" t="s">
         <v>520</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="B108" t="s">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4668,10 +4619,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s" s="0">
+      <c r="A109" t="s">
         <v>524</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="B109" t="s">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4682,10 +4633,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s" s="0">
+      <c r="A110" t="s">
         <v>528</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="B110" t="s">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4696,10 +4647,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s" s="0">
+      <c r="A111" t="s">
         <v>532</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="B111" t="s">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4710,10 +4661,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s" s="0">
+      <c r="A112" t="s">
         <v>536</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="B112" t="s">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4724,10 +4675,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s" s="0">
+      <c r="A113" t="s">
         <v>540</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="B113" t="s">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4738,10 +4689,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s" s="0">
+      <c r="A114" t="s">
         <v>544</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="B114" t="s">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4752,10 +4703,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s" s="0">
+      <c r="A115" t="s">
         <v>548</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="B115" t="s">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4766,10 +4717,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s" s="0">
+      <c r="A116" t="s">
         <v>552</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="B116" t="s">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4780,10 +4731,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s" s="0">
+      <c r="A117" t="s">
         <v>556</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="B117" t="s">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4794,10 +4745,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s" s="0">
+      <c r="A118" t="s">
         <v>560</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="B118" t="s">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4808,10 +4759,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s" s="0">
+      <c r="A119" t="s">
         <v>564</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="B119" t="s">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4822,10 +4773,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s" s="0">
+      <c r="A120" t="s">
         <v>568</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="B120" t="s">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4836,10 +4787,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s" s="0">
+      <c r="A121" t="s">
         <v>572</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="B121" t="s">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4850,10 +4801,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s" s="0">
+      <c r="A122" t="s">
         <v>576</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="B122" t="s">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4864,10 +4815,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s" s="0">
+      <c r="A123" t="s">
         <v>580</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="B123" t="s">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4878,10 +4829,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s" s="0">
+      <c r="A124" t="s">
         <v>584</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="B124" t="s">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4892,10 +4843,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s" s="0">
+      <c r="A125" t="s">
         <v>588</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="B125" t="s">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4906,10 +4857,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s" s="0">
+      <c r="A126" t="s">
         <v>592</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="B126" t="s">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4920,10 +4871,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s" s="0">
+      <c r="A127" t="s">
         <v>596</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="B127" t="s">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4934,10 +4885,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s" s="0">
+      <c r="A128" t="s">
         <v>600</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="B128" t="s">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4948,10 +4899,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s" s="0">
+      <c r="A129" t="s">
         <v>604</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="B129" t="s">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4962,10 +4913,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s" s="0">
+      <c r="A130" t="s">
         <v>608</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="B130" t="s">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4976,10 +4927,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s" s="0">
+      <c r="A131" t="s">
         <v>612</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="B131" t="s">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4990,10 +4941,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s" s="0">
+      <c r="A132" t="s">
         <v>616</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="B132" t="s">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -5004,10 +4955,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s" s="0">
+      <c r="A133" t="s">
         <v>620</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="B133" t="s">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -5018,10 +4969,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s" s="0">
+      <c r="A134" t="s">
         <v>624</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="B134" t="s">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -5032,10 +4983,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s" s="0">
+      <c r="A135" t="s">
         <v>628</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="B135" t="s">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5046,10 +4997,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s" s="0">
+      <c r="A136" t="s">
         <v>632</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="B136" t="s">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5060,10 +5011,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s" s="0">
+      <c r="A137" t="s">
         <v>636</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="B137" t="s">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5074,10 +5025,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s" s="0">
+      <c r="A138" t="s">
         <v>640</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="B138" t="s">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5088,10 +5039,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s" s="0">
+      <c r="A139" t="s">
         <v>644</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="B139" t="s">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5102,10 +5053,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s" s="0">
+      <c r="A140" t="s">
         <v>648</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="B140" t="s">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5116,10 +5067,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s" s="0">
+      <c r="A141" t="s">
         <v>652</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="B141" t="s">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5130,10 +5081,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s" s="0">
+      <c r="A142" t="s">
         <v>656</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="B142" t="s">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5144,10 +5095,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s" s="0">
+      <c r="A143" t="s">
         <v>660</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="B143" t="s">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5158,10 +5109,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s" s="0">
+      <c r="A144" t="s">
         <v>664</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="B144" t="s">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5172,10 +5123,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s" s="0">
+      <c r="A145" t="s">
         <v>668</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="B145" t="s">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5186,10 +5137,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s" s="0">
+      <c r="A146" t="s">
         <v>672</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="B146" t="s">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5200,10 +5151,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s" s="0">
+      <c r="A147" t="s">
         <v>676</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="B147" t="s">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5214,10 +5165,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s" s="0">
+      <c r="A148" t="s">
         <v>680</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="B148" t="s">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5228,10 +5179,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s" s="0">
+      <c r="A149" t="s">
         <v>684</v>
       </c>
-      <c r="B149" t="s" s="0">
+      <c r="B149" t="s">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5242,10 +5193,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s" s="0">
+      <c r="A150" t="s">
         <v>688</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="B150" t="s">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5256,10 +5207,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s" s="0">
+      <c r="A151" t="s">
         <v>692</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="B151" t="s">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5270,10 +5221,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s" s="0">
+      <c r="A152" t="s">
         <v>696</v>
       </c>
-      <c r="B152" t="s" s="0">
+      <c r="B152" t="s">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5284,7 +5235,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s" s="0">
+      <c r="B153" t="s">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5295,7 +5246,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s" s="0">
+      <c r="B154" t="s">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5306,7 +5257,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s" s="0">
+      <c r="B155" t="s">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5317,7 +5268,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s" s="0">
+      <c r="B156" t="s">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5328,7 +5279,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s" s="0">
+      <c r="B157" t="s">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5339,7 +5290,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s" s="0">
+      <c r="B158" t="s">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2340,12 +2340,19 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Rabbit36</t>
+  </si>
+  <si>
+    <t>Sheep32</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2387,7 +2394,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2397,6 +2404,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2697,20 +2706,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.726563" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
+    <col min="12" max="16384" style="1" width="8.726563"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2970,12 +2980,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="19">
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3007,72 +3017,78 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.45313" customWidth="1"/>
-    <col min="3" max="3" width="35.63281" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.72656" customWidth="1"/>
-    <col min="6" max="6" width="32.17969" customWidth="1"/>
-    <col min="7" max="7" width="33.63281" customWidth="1"/>
-    <col min="8" max="8" width="31.26953" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.45313"/>
+    <col min="3" max="3" customWidth="true" width="35.63281"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.72656"/>
+    <col min="6" max="6" customWidth="true" width="32.17969"/>
+    <col min="7" max="7" customWidth="true" width="33.63281"/>
+    <col min="8" max="8" customWidth="true" width="31.26953"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>86</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" t="s" s="0">
+        <v>87</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>87</v>
       </c>
+      <c r="D3" t="s" s="0">
+        <v>87</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>87</v>
       </c>
     </row>
@@ -3083,48 +3099,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984" customWidth="1"/>
-    <col min="2" max="2" width="17.54297" customWidth="1"/>
-    <col min="3" max="3" width="17.36328" customWidth="1"/>
-    <col min="4" max="5" width="17.26953" customWidth="1"/>
-    <col min="6" max="6" width="17.17969" customWidth="1"/>
-    <col min="7" max="7" width="15.36328" customWidth="1"/>
-    <col min="8" max="8" width="17.17969" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984"/>
+    <col min="2" max="2" customWidth="true" width="17.54297"/>
+    <col min="3" max="3" customWidth="true" width="17.36328"/>
+    <col min="4" max="5" customWidth="true" width="17.26953"/>
+    <col min="6" max="6" customWidth="true" width="17.17969"/>
+    <col min="7" max="7" customWidth="true" width="15.36328"/>
+    <col min="8" max="8" customWidth="true" width="17.17969"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3135,10 +3152,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3149,10 +3166,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3163,10 +3180,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3177,10 +3194,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3191,10 +3208,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3205,10 +3222,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3219,10 +3236,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3233,10 +3250,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3247,10 +3264,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3261,10 +3278,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3275,10 +3292,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3289,10 +3306,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3303,10 +3320,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3317,10 +3334,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3331,10 +3348,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3345,10 +3362,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3359,10 +3376,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3373,10 +3390,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3387,10 +3404,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3401,10 +3418,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3415,10 +3432,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3429,10 +3446,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>184</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3443,10 +3460,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3457,10 +3474,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3471,10 +3488,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3485,10 +3502,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3499,10 +3516,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>204</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3513,10 +3530,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3527,10 +3544,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3541,10 +3558,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>216</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3555,10 +3572,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3569,10 +3586,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3583,10 +3600,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>228</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3597,10 +3614,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>232</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3611,10 +3628,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>236</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3625,10 +3642,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>240</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3639,10 +3656,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3653,10 +3670,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3667,10 +3684,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3681,10 +3698,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3695,10 +3712,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3709,10 +3726,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3723,10 +3740,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3737,10 +3754,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>272</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3751,10 +3768,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3765,10 +3782,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3779,10 +3796,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3793,10 +3810,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3807,10 +3824,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3821,10 +3838,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>296</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3835,10 +3852,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3849,10 +3866,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3863,10 +3880,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>308</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3877,10 +3894,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>312</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3891,10 +3908,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>316</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3905,10 +3922,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>320</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3919,10 +3936,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3933,10 +3950,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3947,10 +3964,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>332</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3961,10 +3978,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>336</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3975,10 +3992,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -3989,10 +4006,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>344</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4003,10 +4020,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>348</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4017,10 +4034,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4031,10 +4048,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>356</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4045,10 +4062,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>360</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4059,10 +4076,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4073,10 +4090,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>368</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4087,10 +4104,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>372</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4101,10 +4118,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>376</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4115,10 +4132,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>380</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4129,10 +4146,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4143,10 +4160,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4157,10 +4174,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4171,10 +4188,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4185,10 +4202,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4199,10 +4216,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4213,10 +4230,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4227,10 +4244,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>412</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4241,10 +4258,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>416</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4255,10 +4272,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4269,10 +4286,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4283,10 +4300,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4297,10 +4314,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4311,10 +4328,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>436</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4325,10 +4342,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>440</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4339,10 +4356,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4353,10 +4370,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>448</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4367,10 +4384,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4381,10 +4398,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4395,10 +4412,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>460</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4409,10 +4426,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4423,10 +4440,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>468</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4437,10 +4454,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>472</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4451,10 +4468,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>476</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4465,10 +4482,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>480</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4479,10 +4496,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>484</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4493,10 +4510,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>488</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4507,10 +4524,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>492</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4521,10 +4538,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>496</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4535,10 +4552,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>500</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4549,10 +4566,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>504</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4563,10 +4580,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>508</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4577,10 +4594,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>512</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4591,10 +4608,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>516</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4605,10 +4622,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>520</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4619,10 +4636,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>524</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4633,10 +4650,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>528</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4647,10 +4664,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>532</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4661,10 +4678,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>536</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4675,10 +4692,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>540</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4689,10 +4706,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>544</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4703,10 +4720,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>548</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4717,10 +4734,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>552</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4731,10 +4748,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4745,10 +4762,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>560</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4759,10 +4776,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>564</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4773,10 +4790,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>568</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4787,10 +4804,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>572</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4801,10 +4818,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>576</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4815,10 +4832,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>580</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4829,10 +4846,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>584</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4843,10 +4860,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>588</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4857,10 +4874,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>592</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4871,10 +4888,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>596</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4885,10 +4902,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>600</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4899,10 +4916,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>604</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4913,10 +4930,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>608</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4927,10 +4944,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>612</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4941,10 +4958,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>616</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4955,10 +4972,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>620</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4969,10 +4986,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>624</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4983,10 +5000,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>628</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -4997,10 +5014,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>632</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5011,10 +5028,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>636</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5025,10 +5042,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>640</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5039,10 +5056,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>644</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5053,10 +5070,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>648</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5067,10 +5084,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>652</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5081,10 +5098,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>656</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5095,10 +5112,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>660</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5109,10 +5126,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>664</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5123,10 +5140,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>668</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5137,10 +5154,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>672</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5151,10 +5168,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>676</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5165,10 +5182,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>680</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5179,10 +5196,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>684</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5193,10 +5210,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>688</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5207,10 +5224,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>692</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5221,10 +5238,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>696</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5235,7 +5252,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5246,7 +5263,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5257,7 +5274,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5268,7 +5285,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5279,7 +5296,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5290,7 +5307,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -1,27 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\workspace\testing\animalBiome_Automation\src\test\resources\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3090" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3090"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
     <sheet name="PET_NAME" sheetId="2" r:id="rId2"/>
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:G8"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="791">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2342,18 +2338,65 @@
     <t>Nexra</t>
   </si>
   <si>
-    <t>Rabbit36</t>
-  </si>
-  <si>
-    <t>Sheep32</t>
+    <t>VHKTDY</t>
+  </si>
+  <si>
+    <t>NXMGXU</t>
+  </si>
+  <si>
+    <t>FHPENF</t>
+  </si>
+  <si>
+    <t>KMVFMV</t>
+  </si>
+  <si>
+    <t>FMMDPH</t>
+  </si>
+  <si>
+    <t>VTPC7K</t>
+  </si>
+  <si>
+    <t>RXY4RX</t>
+  </si>
+  <si>
+    <t>U9ANVP</t>
+  </si>
+  <si>
+    <t>NMVMC7</t>
+  </si>
+  <si>
+    <t>YTJTEP</t>
+  </si>
+  <si>
+    <t>ADKXJK</t>
+  </si>
+  <si>
+    <t>7KMMDF</t>
+  </si>
+  <si>
+    <t>7PEXET</t>
+  </si>
+  <si>
+    <t>CAYMTM</t>
+  </si>
+  <si>
+    <t>4YJTMR</t>
+  </si>
+  <si>
+    <t>RKRYJR</t>
+  </si>
+  <si>
+    <t>NJ4YMD</t>
+  </si>
+  <si>
+    <t>NR7KMT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2365,6 +2408,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2387,12 +2437,18 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2402,18 +2458,26 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2"/>
     <cellStyle name="Normal 3" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2422,10 +2486,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2557,7 +2621,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2581,11 +2644,10 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2594,13 +2656,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2676,7 +2738,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2696,34 +2757,35 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K81"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
-    <col min="12" max="16384" style="1" width="8.726563"/>
+    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2755,7 +2817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2772,7 +2834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -2789,7 +2851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -2806,7 +2868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -2823,7 +2885,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -2840,7 +2902,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
@@ -2857,7 +2919,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2874,7 +2936,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
@@ -2891,7 +2953,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
@@ -2908,7 +2970,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
@@ -2925,7 +2987,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
@@ -2942,7 +3004,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>65</v>
       </c>
@@ -2953,7 +3015,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>68</v>
       </c>
@@ -2964,184 +3026,260 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>778</v>
+      </c>
+      <c r="D15" t="s">
+        <v>773</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>779</v>
+      </c>
+      <c r="D16" t="s">
+        <v>774</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>780</v>
+      </c>
+      <c r="D17" t="s">
+        <v>775</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>776</v>
+      </c>
       <c r="E18" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>777</v>
+      </c>
       <c r="E19" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E20" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E21" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E22" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="78">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E23" s="1" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E24" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E25" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E26" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E27" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E28" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E29" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E30" s="1" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E31" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E32" s="1" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="78" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F78" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F81" s="3"/>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.45313"/>
-    <col min="3" max="3" customWidth="true" width="35.63281"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.72656"/>
-    <col min="6" max="6" customWidth="true" width="32.17969"/>
-    <col min="7" max="7" customWidth="true" width="33.63281"/>
-    <col min="8" max="8" customWidth="true" width="31.26953"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.7265625" customWidth="1"/>
+    <col min="6" max="6" width="32.1796875" customWidth="1"/>
+    <col min="7" max="7" width="33.6328125" customWidth="1"/>
+    <col min="8" max="8" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>79</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>80</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>81</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>82</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>84</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>85</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>87</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>87</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>87</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>87</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>87</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>87</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>87</v>
       </c>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984"/>
-    <col min="2" max="2" customWidth="true" width="17.54297"/>
-    <col min="3" max="3" customWidth="true" width="17.36328"/>
-    <col min="4" max="5" customWidth="true" width="17.26953"/>
-    <col min="6" max="6" customWidth="true" width="17.17969"/>
-    <col min="7" max="7" customWidth="true" width="15.36328"/>
-    <col min="8" max="8" customWidth="true" width="17.17969"/>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" customWidth="1"/>
+    <col min="4" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>90</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>92</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>93</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>94</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>96</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3151,11 +3289,11 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>100</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3165,11 +3303,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3179,11 +3317,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>108</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3193,11 +3331,11 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>112</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3207,11 +3345,11 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3221,11 +3359,11 @@
         <v>119</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>120</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3235,11 +3373,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>124</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3249,11 +3387,11 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>128</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3263,11 +3401,11 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>132</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3277,11 +3415,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>136</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3291,11 +3429,11 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>140</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3305,11 +3443,11 @@
         <v>143</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>144</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3319,11 +3457,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>148</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3333,11 +3471,11 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>152</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3347,11 +3485,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>156</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3361,11 +3499,11 @@
         <v>159</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>160</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3375,11 +3513,11 @@
         <v>163</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>164</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3389,11 +3527,11 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>168</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3403,11 +3541,11 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>172</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B21" t="s">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3417,11 +3555,11 @@
         <v>175</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>176</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="B22" t="s">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3431,11 +3569,11 @@
         <v>179</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>180</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3445,11 +3583,11 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>184</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3459,11 +3597,11 @@
         <v>187</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>188</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B25" t="s">
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3473,11 +3611,11 @@
         <v>191</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>192</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>193</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3487,11 +3625,11 @@
         <v>195</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>196</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3501,11 +3639,11 @@
         <v>199</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>200</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3515,11 +3653,11 @@
         <v>203</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>204</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="B29" t="s">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3529,11 +3667,11 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="s" s="0">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>208</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="B30" t="s">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3543,11 +3681,11 @@
         <v>211</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="s" s="0">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>212</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3557,11 +3695,11 @@
         <v>215</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="s" s="0">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>216</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3571,11 +3709,11 @@
         <v>219</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="s" s="0">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>220</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3585,11 +3723,11 @@
         <v>223</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="s" s="0">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>224</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3599,11 +3737,11 @@
         <v>227</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="s" s="0">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>228</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B35" t="s">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3613,11 +3751,11 @@
         <v>231</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="s" s="0">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>232</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="B36" t="s">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3627,11 +3765,11 @@
         <v>235</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="s" s="0">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>236</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B37" t="s">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3641,11 +3779,11 @@
         <v>239</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="s" s="0">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>240</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B38" t="s">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3655,11 +3793,11 @@
         <v>243</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="s" s="0">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>244</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="B39" t="s">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3669,11 +3807,11 @@
         <v>247</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="s" s="0">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>248</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="B40" t="s">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3683,11 +3821,11 @@
         <v>251</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="s" s="0">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>252</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="B41" t="s">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3697,11 +3835,11 @@
         <v>255</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="s" s="0">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>256</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="B42" t="s">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3711,11 +3849,11 @@
         <v>259</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="s" s="0">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>260</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="B43" t="s">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3725,11 +3863,11 @@
         <v>263</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="s" s="0">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>264</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B44" t="s">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3739,11 +3877,11 @@
         <v>267</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>268</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="B45" t="s">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3753,11 +3891,11 @@
         <v>271</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="s" s="0">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>272</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="B46" t="s">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3767,11 +3905,11 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="s" s="0">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>276</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B47" t="s">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3781,11 +3919,11 @@
         <v>279</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="s" s="0">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>280</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="B48" t="s">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3795,11 +3933,11 @@
         <v>283</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="s" s="0">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>284</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="B49" t="s">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3809,11 +3947,11 @@
         <v>287</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="s" s="0">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>288</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="B50" t="s">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3823,11 +3961,11 @@
         <v>291</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="s" s="0">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>292</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="B51" t="s">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3837,11 +3975,11 @@
         <v>295</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="s" s="0">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>296</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="B52" t="s">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3851,11 +3989,11 @@
         <v>299</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="s" s="0">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>300</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="B53" t="s">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3865,11 +4003,11 @@
         <v>303</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="s" s="0">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>304</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="B54" t="s">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3879,11 +4017,11 @@
         <v>307</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="s" s="0">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>308</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -3893,11 +4031,11 @@
         <v>311</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="s" s="0">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>312</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="B56" t="s">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3907,11 +4045,11 @@
         <v>315</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="s" s="0">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>316</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B57" t="s">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -3921,11 +4059,11 @@
         <v>319</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="s" s="0">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>320</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="B58" t="s">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -3935,11 +4073,11 @@
         <v>323</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="s" s="0">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>324</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="B59" t="s">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -3949,11 +4087,11 @@
         <v>327</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="s" s="0">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>328</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="B60" t="s">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -3963,11 +4101,11 @@
         <v>331</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="s" s="0">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>332</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="B61" t="s">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -3977,11 +4115,11 @@
         <v>335</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="s" s="0">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>336</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="B62" t="s">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -3991,11 +4129,11 @@
         <v>339</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="s" s="0">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>340</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="B63" t="s">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4005,11 +4143,11 @@
         <v>343</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="s" s="0">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>344</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="B64" t="s">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4019,11 +4157,11 @@
         <v>347</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="s" s="0">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>348</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="B65" t="s">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4033,11 +4171,11 @@
         <v>351</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="s" s="0">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>352</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="B66" t="s">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4047,11 +4185,11 @@
         <v>355</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="s" s="0">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>356</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="B67" t="s">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4061,11 +4199,11 @@
         <v>359</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="s" s="0">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>360</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B68" t="s">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4075,11 +4213,11 @@
         <v>363</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="s" s="0">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>364</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B69" t="s">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4089,11 +4227,11 @@
         <v>367</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="s" s="0">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>368</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="B70" t="s">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4103,11 +4241,11 @@
         <v>371</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="s" s="0">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>372</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="B71" t="s">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4117,11 +4255,11 @@
         <v>375</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="s" s="0">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>376</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="B72" t="s">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4131,11 +4269,11 @@
         <v>379</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="s" s="0">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>380</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="B73" t="s">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4145,11 +4283,11 @@
         <v>383</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="s" s="0">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>384</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="B74" t="s">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4159,11 +4297,11 @@
         <v>387</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="s" s="0">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>388</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="B75" t="s">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4173,11 +4311,11 @@
         <v>391</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="s" s="0">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>392</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B76" t="s">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4187,11 +4325,11 @@
         <v>395</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="s" s="0">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>396</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="B77" t="s">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4201,11 +4339,11 @@
         <v>399</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="s" s="0">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>400</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B78" t="s">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4215,11 +4353,11 @@
         <v>403</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="s" s="0">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>404</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="B79" t="s">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4229,11 +4367,11 @@
         <v>407</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="s" s="0">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>408</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="B80" t="s">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4243,11 +4381,11 @@
         <v>411</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="s" s="0">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>412</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B81" t="s">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4257,11 +4395,11 @@
         <v>415</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="s" s="0">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>416</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="B82" t="s">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4271,11 +4409,11 @@
         <v>419</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>420</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B83" t="s">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4285,11 +4423,11 @@
         <v>423</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>424</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B84" t="s">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4299,11 +4437,11 @@
         <v>427</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>428</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="B85" t="s">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4313,11 +4451,11 @@
         <v>431</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>432</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="B86" t="s">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4327,11 +4465,11 @@
         <v>435</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>436</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="B87" t="s">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4341,11 +4479,11 @@
         <v>439</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>440</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="B88" t="s">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4355,11 +4493,11 @@
         <v>443</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>444</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="B89" t="s">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4369,11 +4507,11 @@
         <v>447</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>448</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="B90" t="s">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4383,11 +4521,11 @@
         <v>451</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>452</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="B91" t="s">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4397,11 +4535,11 @@
         <v>455</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>456</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="B92" t="s">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4411,11 +4549,11 @@
         <v>459</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="s" s="0">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>460</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B93" t="s">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4425,11 +4563,11 @@
         <v>463</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="s" s="0">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>464</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="B94" t="s">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4439,11 +4577,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="s" s="0">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>468</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="B95" t="s">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4453,11 +4591,11 @@
         <v>471</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="s" s="0">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>472</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="B96" t="s">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4467,11 +4605,11 @@
         <v>475</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="s" s="0">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
         <v>476</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="B97" t="s">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4481,11 +4619,11 @@
         <v>479</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="s" s="0">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
         <v>480</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="B98" t="s">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4495,11 +4633,11 @@
         <v>483</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="s" s="0">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>484</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="B99" t="s">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4509,11 +4647,11 @@
         <v>487</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="s" s="0">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>488</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="B100" t="s">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4523,11 +4661,11 @@
         <v>491</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="s" s="0">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>492</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="B101" t="s">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4537,11 +4675,11 @@
         <v>495</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="s" s="0">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>496</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="B102" t="s">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4551,11 +4689,11 @@
         <v>499</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="s" s="0">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>500</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="B103" t="s">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4565,11 +4703,11 @@
         <v>503</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="s" s="0">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
         <v>504</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="B104" t="s">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4579,11 +4717,11 @@
         <v>507</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="s" s="0">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>508</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="B105" t="s">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4593,11 +4731,11 @@
         <v>511</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="s" s="0">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
         <v>512</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="B106" t="s">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4607,11 +4745,11 @@
         <v>515</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="s" s="0">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
         <v>516</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="B107" t="s">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4621,11 +4759,11 @@
         <v>519</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="s" s="0">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
         <v>520</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="B108" t="s">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4635,11 +4773,11 @@
         <v>523</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="s" s="0">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>524</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="B109" t="s">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4649,11 +4787,11 @@
         <v>527</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="s" s="0">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>528</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="B110" t="s">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4663,11 +4801,11 @@
         <v>531</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="s" s="0">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>532</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="B111" t="s">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4677,11 +4815,11 @@
         <v>535</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="s" s="0">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>536</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="B112" t="s">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4691,11 +4829,11 @@
         <v>539</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="s" s="0">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
         <v>540</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="B113" t="s">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4705,11 +4843,11 @@
         <v>543</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="s" s="0">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
         <v>544</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="B114" t="s">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4719,11 +4857,11 @@
         <v>547</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="s" s="0">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>548</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="B115" t="s">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4733,11 +4871,11 @@
         <v>551</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="s" s="0">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>552</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="B116" t="s">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4747,11 +4885,11 @@
         <v>555</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="s" s="0">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>556</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="B117" t="s">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4761,11 +4899,11 @@
         <v>559</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="s" s="0">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
         <v>560</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="B118" t="s">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4775,11 +4913,11 @@
         <v>563</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="s" s="0">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>564</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="B119" t="s">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4789,11 +4927,11 @@
         <v>567</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="s" s="0">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
         <v>568</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="B120" t="s">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4803,11 +4941,11 @@
         <v>571</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="s" s="0">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
         <v>572</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="B121" t="s">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4817,11 +4955,11 @@
         <v>575</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="s" s="0">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>576</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="B122" t="s">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4831,11 +4969,11 @@
         <v>579</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="s" s="0">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
         <v>580</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="B123" t="s">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4845,11 +4983,11 @@
         <v>583</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="s" s="0">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
         <v>584</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="B124" t="s">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4859,11 +4997,11 @@
         <v>587</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="s" s="0">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
         <v>588</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="B125" t="s">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4873,11 +5011,11 @@
         <v>591</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="s" s="0">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>592</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="B126" t="s">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4887,11 +5025,11 @@
         <v>595</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="s" s="0">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
         <v>596</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="B127" t="s">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -4901,11 +5039,11 @@
         <v>599</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="s" s="0">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>600</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="B128" t="s">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -4915,11 +5053,11 @@
         <v>603</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="s" s="0">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>604</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="B129" t="s">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -4929,11 +5067,11 @@
         <v>607</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="s" s="0">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>608</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="B130" t="s">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -4943,11 +5081,11 @@
         <v>611</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="s" s="0">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
         <v>612</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="B131" t="s">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -4957,11 +5095,11 @@
         <v>615</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="s" s="0">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
         <v>616</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="B132" t="s">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -4971,11 +5109,11 @@
         <v>619</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="s" s="0">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
         <v>620</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="B133" t="s">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -4985,11 +5123,11 @@
         <v>623</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="s" s="0">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
         <v>624</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="B134" t="s">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -4999,11 +5137,11 @@
         <v>627</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="s" s="0">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
         <v>628</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="B135" t="s">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5013,11 +5151,11 @@
         <v>631</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="s" s="0">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
         <v>632</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="B136" t="s">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5027,11 +5165,11 @@
         <v>635</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="s" s="0">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
         <v>636</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="B137" t="s">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5041,11 +5179,11 @@
         <v>639</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="s" s="0">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
         <v>640</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="B138" t="s">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5055,11 +5193,11 @@
         <v>643</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="s" s="0">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
         <v>644</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="B139" t="s">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5069,11 +5207,11 @@
         <v>647</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="s" s="0">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
         <v>648</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="B140" t="s">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5083,11 +5221,11 @@
         <v>651</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="s" s="0">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
         <v>652</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="B141" t="s">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5097,11 +5235,11 @@
         <v>655</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="s" s="0">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
         <v>656</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="B142" t="s">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5111,11 +5249,11 @@
         <v>659</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="s" s="0">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
         <v>660</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="B143" t="s">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5125,11 +5263,11 @@
         <v>663</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="s" s="0">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
         <v>664</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="B144" t="s">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5139,11 +5277,11 @@
         <v>667</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="s" s="0">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
         <v>668</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="B145" t="s">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5153,11 +5291,11 @@
         <v>671</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="s" s="0">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
         <v>672</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="B146" t="s">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5167,11 +5305,11 @@
         <v>675</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="s" s="0">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>676</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="B147" t="s">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5181,11 +5319,11 @@
         <v>679</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="s" s="0">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
         <v>680</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="B148" t="s">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5195,11 +5333,11 @@
         <v>683</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="s" s="0">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>684</v>
       </c>
-      <c r="B149" t="s" s="0">
+      <c r="B149" t="s">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5209,11 +5347,11 @@
         <v>687</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="s" s="0">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
         <v>688</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="B150" t="s">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5223,11 +5361,11 @@
         <v>691</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="s" s="0">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
         <v>692</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="B151" t="s">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5237,11 +5375,11 @@
         <v>695</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="s" s="0">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
         <v>696</v>
       </c>
-      <c r="B152" t="s" s="0">
+      <c r="B152" t="s">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5251,8 +5389,8 @@
         <v>699</v>
       </c>
     </row>
-    <row r="153">
-      <c r="B153" t="s" s="0">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5262,8 +5400,8 @@
         <v>702</v>
       </c>
     </row>
-    <row r="154">
-      <c r="B154" t="s" s="0">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B154" t="s">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5273,8 +5411,8 @@
         <v>705</v>
       </c>
     </row>
-    <row r="155">
-      <c r="B155" t="s" s="0">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5284,8 +5422,8 @@
         <v>708</v>
       </c>
     </row>
-    <row r="156">
-      <c r="B156" t="s" s="0">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5295,8 +5433,8 @@
         <v>711</v>
       </c>
     </row>
-    <row r="157">
-      <c r="B157" t="s" s="0">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B157" t="s">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5306,8 +5444,8 @@
         <v>714</v>
       </c>
     </row>
-    <row r="158">
-      <c r="B158" t="s" s="0">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">
@@ -5317,7 +5455,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C159" s="6" t="s">
         <v>718</v>
       </c>
@@ -5325,7 +5463,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C160" s="6" t="s">
         <v>720</v>
       </c>
@@ -5333,7 +5471,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C161" s="6" t="s">
         <v>722</v>
       </c>
@@ -5341,7 +5479,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C162" s="6" t="s">
         <v>724</v>
       </c>
@@ -5349,7 +5487,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C163" s="6" t="s">
         <v>726</v>
       </c>
@@ -5357,7 +5495,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C164" s="6" t="s">
         <v>728</v>
       </c>
@@ -5365,7 +5503,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C165" s="6" t="s">
         <v>730</v>
       </c>
@@ -5373,7 +5511,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C166" s="6" t="s">
         <v>732</v>
       </c>
@@ -5381,7 +5519,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C167" s="6" t="s">
         <v>734</v>
       </c>
@@ -5389,7 +5527,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C168" s="6" t="s">
         <v>736</v>
       </c>
@@ -5397,7 +5535,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C169" s="6" t="s">
         <v>738</v>
       </c>
@@ -5405,7 +5543,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C170" s="6" t="s">
         <v>740</v>
       </c>
@@ -5413,162 +5551,163 @@
         <v>741</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D171" s="5" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D172" s="5" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D173" s="5" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D174" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D175" s="5" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D176" s="5" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D177" s="5" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D178" s="5" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D179" s="5" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D180" s="5" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D181" s="5" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D182" s="5" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D183" s="5" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D184" s="5" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D185" s="5" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D186" s="5" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D187" s="5" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D188" s="5" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D189" s="5" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D190" s="5" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D191" s="5" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D192" s="5" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D193" s="5" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D194" s="5" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D195" s="5" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D196" s="5" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D197" s="5" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D198" s="5" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D199" s="5" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D200" s="5" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D201" s="5" t="s">
         <v>772</v>
       </c>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="799">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2390,12 +2390,37 @@
   </si>
   <si>
     <t>NR7KMT</t>
+  </si>
+  <si>
+    <t>Charlie93</t>
+  </si>
+  <si>
+    <t>Milo63</t>
+  </si>
+  <si>
+    <t>Taffy61</t>
+  </si>
+  <si>
+    <t>Cutie48</t>
+  </si>
+  <si>
+    <t>Cinder48</t>
+  </si>
+  <si>
+    <t>pony40</t>
+  </si>
+  <si>
+    <t>fury37</t>
+  </si>
+  <si>
+    <t>Rabbit37</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2450,7 +2475,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2462,6 +2487,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2768,21 +2802,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
+    <col min="12" max="16384" style="1" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2889,10 +2923,10 @@
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -2971,7 +3005,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2988,7 +3022,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="11" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -3008,7 +3042,7 @@
       <c r="A13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="13" t="s">
         <v>66</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -3019,7 +3053,7 @@
       <c r="A14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="14" t="s">
         <v>69</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -3027,10 +3061,10 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="1">
         <v>778</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="1">
         <v>773</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -3038,10 +3072,10 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="1">
         <v>779</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="1">
         <v>774</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -3049,10 +3083,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="1">
         <v>780</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="1">
         <v>775</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -3060,7 +3094,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="1">
         <v>776</v>
       </c>
       <c r="E18" s="7" t="s">
@@ -3068,7 +3102,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="1">
         <v>777</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -3076,12 +3110,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="16" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="17" t="s">
         <v>77</v>
       </c>
     </row>
@@ -3157,75 +3191,75 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" customWidth="1"/>
-    <col min="8" max="8" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.453125"/>
+    <col min="3" max="3" customWidth="true" width="35.6328125"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.7265625"/>
+    <col min="6" max="6" customWidth="true" width="32.1796875"/>
+    <col min="7" max="7" customWidth="true" width="33.6328125"/>
+    <col min="8" max="8" customWidth="true" width="31.26953125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s" s="0">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>87</v>
       </c>
     </row>
@@ -3240,46 +3274,46 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984375"/>
+    <col min="2" max="2" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.36328125"/>
+    <col min="4" max="5" customWidth="true" width="17.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.36328125"/>
+    <col min="8" max="8" customWidth="true" width="17.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3290,10 +3324,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3304,10 +3338,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3318,10 +3352,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3332,10 +3366,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3346,10 +3380,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3360,10 +3394,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>121</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3374,10 +3408,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3388,10 +3422,10 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3402,10 +3436,10 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3416,10 +3450,10 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3430,10 +3464,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3444,10 +3478,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3458,10 +3492,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3472,10 +3506,10 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3486,10 +3520,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3500,10 +3534,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3514,10 +3548,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3528,10 +3562,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3542,10 +3576,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3556,10 +3590,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3570,10 +3604,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3584,10 +3618,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>184</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3598,10 +3632,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3612,13 +3646,13 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>193</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="15" t="s">
         <v>194</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -3626,10 +3660,10 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>197</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -3640,10 +3674,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>201</v>
       </c>
       <c r="C28" s="6" t="s">
@@ -3654,10 +3688,10 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>204</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>205</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3668,10 +3702,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>209</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3682,10 +3716,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>213</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3696,10 +3730,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>216</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>217</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3710,10 +3744,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>221</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3724,10 +3758,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>225</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3738,10 +3772,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>228</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>229</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3752,10 +3786,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>232</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>233</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3766,10 +3800,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>236</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>237</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3780,10 +3814,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>240</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>241</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3794,10 +3828,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3808,10 +3842,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3822,10 +3856,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>253</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3836,10 +3870,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>257</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3850,10 +3884,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3864,10 +3898,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>265</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3878,10 +3912,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>269</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3892,10 +3926,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>272</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3906,10 +3940,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3920,10 +3954,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>281</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3934,10 +3968,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3948,10 +3982,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3962,10 +3996,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3976,10 +4010,10 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>296</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3990,10 +4024,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>301</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -4004,10 +4038,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>305</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -4018,10 +4052,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>308</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>309</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -4032,10 +4066,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>312</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>313</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -4046,10 +4080,10 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>316</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>317</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -4060,10 +4094,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>320</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>321</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -4074,10 +4108,10 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>325</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -4088,10 +4122,10 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -4102,10 +4136,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>332</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>333</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -4116,10 +4150,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>336</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>337</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -4130,10 +4164,10 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>341</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4144,10 +4178,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>344</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4158,10 +4192,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>348</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>349</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4172,10 +4206,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>353</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4186,10 +4220,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>356</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>357</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4200,10 +4234,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>360</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>361</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4214,10 +4248,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>365</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4228,10 +4262,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>368</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>369</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4242,10 +4276,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>372</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>373</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4256,10 +4290,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>376</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>377</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4270,10 +4304,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>380</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>381</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4284,10 +4318,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>385</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4298,10 +4332,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>389</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4312,10 +4346,10 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>393</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4326,10 +4360,10 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>397</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4340,10 +4374,10 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>401</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4354,10 +4388,10 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4368,10 +4402,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>409</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4382,10 +4416,10 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>412</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>413</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4396,10 +4430,10 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>416</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>417</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4410,10 +4444,10 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>421</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4424,10 +4458,10 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>425</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4438,10 +4472,10 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>429</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4452,10 +4486,10 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>433</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4466,10 +4500,10 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>436</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>437</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4480,10 +4514,10 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>440</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>441</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4494,10 +4528,10 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>445</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4508,10 +4542,10 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>448</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>449</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4522,10 +4556,10 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4536,10 +4570,10 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4550,10 +4584,10 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>460</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>461</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4564,10 +4598,10 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>465</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4578,10 +4612,10 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>468</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>469</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4592,10 +4626,10 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>472</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>473</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4606,10 +4640,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>476</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>477</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4620,10 +4654,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>480</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4634,10 +4668,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>484</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>485</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4648,10 +4682,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>488</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4662,10 +4696,10 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>492</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4676,10 +4710,10 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>496</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4690,10 +4724,10 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>500</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4704,10 +4738,10 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>504</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>505</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4718,10 +4752,10 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>508</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4732,10 +4766,10 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>512</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4746,10 +4780,10 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>516</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>517</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4760,10 +4794,10 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>520</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>521</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4774,10 +4808,10 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>524</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>525</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4788,10 +4822,10 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>528</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>529</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4802,10 +4836,10 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>532</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>533</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4816,10 +4850,10 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>536</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4830,10 +4864,10 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>540</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4844,10 +4878,10 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>544</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4858,10 +4892,10 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>548</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4872,10 +4906,10 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>552</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4886,10 +4920,10 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4900,10 +4934,10 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>560</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>561</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4914,10 +4948,10 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>564</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>565</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4928,10 +4962,10 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>568</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>569</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4942,10 +4976,10 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>572</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>573</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4956,10 +4990,10 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>576</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>577</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4970,10 +5004,10 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>580</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>581</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4984,10 +5018,10 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>584</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>585</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4998,10 +5032,10 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>588</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>589</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -5012,10 +5046,10 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>592</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>593</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -5026,10 +5060,10 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>596</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>597</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -5040,10 +5074,10 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>600</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>601</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -5054,10 +5088,10 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>604</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>605</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -5068,10 +5102,10 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>608</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>609</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -5082,10 +5116,10 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>612</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>613</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -5096,10 +5130,10 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>616</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>617</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -5110,10 +5144,10 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>620</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>621</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -5124,10 +5158,10 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>624</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>625</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -5138,10 +5172,10 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>628</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>629</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5152,10 +5186,10 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>632</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>633</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5166,10 +5200,10 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>636</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>637</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5180,10 +5214,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>640</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>641</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5194,10 +5228,10 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>644</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>645</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5208,10 +5242,10 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>648</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>649</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5222,10 +5256,10 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>652</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>653</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5236,10 +5270,10 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>656</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>657</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5250,10 +5284,10 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>660</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>661</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5264,10 +5298,10 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>664</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>665</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5278,10 +5312,10 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>668</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>669</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5292,10 +5326,10 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>672</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>673</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5306,10 +5340,10 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>676</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>677</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5320,10 +5354,10 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>680</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>681</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5334,10 +5368,10 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>684</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>685</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5348,10 +5382,10 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>688</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>689</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5362,10 +5396,10 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>692</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>693</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5376,10 +5410,10 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>696</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>697</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5390,7 +5424,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>700</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5401,7 +5435,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5412,7 +5446,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>706</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5423,7 +5457,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>709</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5434,7 +5468,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>712</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5445,7 +5479,7 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="808">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2414,6 +2414,33 @@
   </si>
   <si>
     <t>Rabbit37</t>
+  </si>
+  <si>
+    <t>Charlie94</t>
+  </si>
+  <si>
+    <t>Milo64</t>
+  </si>
+  <si>
+    <t>Taffy62</t>
+  </si>
+  <si>
+    <t>Cutie49</t>
+  </si>
+  <si>
+    <t>Cinder49</t>
+  </si>
+  <si>
+    <t>pony41</t>
+  </si>
+  <si>
+    <t>fury38</t>
+  </si>
+  <si>
+    <t>Rabbit38</t>
+  </si>
+  <si>
+    <t>Sheep33</t>
   </si>
 </sst>
 </file>
@@ -2475,7 +2502,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2487,6 +2514,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -2943,7 +2977,7 @@
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="19" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -3039,7 +3073,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="18" t="s">
         <v>65</v>
       </c>
       <c r="D13" s="13" t="s">
@@ -3064,7 +3098,7 @@
       <c r="A15" t="s" s="1">
         <v>778</v>
       </c>
-      <c r="D15" t="s" s="1">
+      <c r="D15" t="s" s="20">
         <v>773</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -3075,7 +3109,7 @@
       <c r="A16" t="s" s="1">
         <v>779</v>
       </c>
-      <c r="D16" t="s" s="1">
+      <c r="D16" t="s" s="21">
         <v>774</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -3120,12 +3154,12 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="23" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="24" t="s">
         <v>781</v>
       </c>
     </row>
@@ -3235,21 +3269,21 @@
         <v>87</v>
       </c>
       <c r="C2" t="s" s="0">
+        <v>805</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>87</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>798</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>87</v>
+        <v>800</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>87</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>87</v>
+        <v>198</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>87</v>
@@ -3257,10 +3291,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>87</v>
+        <v>801</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>87</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>807</v>
       </c>
     </row>
   </sheetData>
@@ -3666,7 +3703,7 @@
       <c r="B27" t="s" s="0">
         <v>197</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="22" t="s">
         <v>198</v>
       </c>
       <c r="D27" s="5" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\workspace\testing\animalBiome_Automation\src\test\resources\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3090"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3090" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
     <sheet name="PET_NAME" sheetId="2" r:id="rId2"/>
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1:G8"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -232,18 +236,42 @@
     <t>MT3YXX</t>
   </si>
   <si>
+    <t>VTPC7K</t>
+  </si>
+  <si>
+    <t>VHKTDY</t>
+  </si>
+  <si>
     <t>XHFYNX</t>
   </si>
   <si>
+    <t>RXY4RX</t>
+  </si>
+  <si>
+    <t>NXMGXU</t>
+  </si>
+  <si>
     <t>ENJTEH</t>
   </si>
   <si>
+    <t>U9ANVP</t>
+  </si>
+  <si>
+    <t>FHPENF</t>
+  </si>
+  <si>
     <t>VJFKAH</t>
   </si>
   <si>
+    <t>KMVFMV</t>
+  </si>
+  <si>
     <t>RVYMTD</t>
   </si>
   <si>
+    <t>FMMDPH</t>
+  </si>
+  <si>
     <t>HTD7FV</t>
   </si>
   <si>
@@ -256,6 +284,36 @@
     <t>EVAYHN</t>
   </si>
   <si>
+    <t>NMVMC7</t>
+  </si>
+  <si>
+    <t>YTJTEP</t>
+  </si>
+  <si>
+    <t>ADKXJK</t>
+  </si>
+  <si>
+    <t>7KMMDF</t>
+  </si>
+  <si>
+    <t>7PEXET</t>
+  </si>
+  <si>
+    <t>CAYMTM</t>
+  </si>
+  <si>
+    <t>4YJTMR</t>
+  </si>
+  <si>
+    <t>RKRYJR</t>
+  </si>
+  <si>
+    <t>NJ4YMD</t>
+  </si>
+  <si>
+    <t>NR7KMT</t>
+  </si>
+  <si>
     <t>User_Dog</t>
   </si>
   <si>
@@ -2336,119 +2394,13 @@
   </si>
   <si>
     <t>Nexra</t>
-  </si>
-  <si>
-    <t>VHKTDY</t>
-  </si>
-  <si>
-    <t>NXMGXU</t>
-  </si>
-  <si>
-    <t>FHPENF</t>
-  </si>
-  <si>
-    <t>KMVFMV</t>
-  </si>
-  <si>
-    <t>FMMDPH</t>
-  </si>
-  <si>
-    <t>VTPC7K</t>
-  </si>
-  <si>
-    <t>RXY4RX</t>
-  </si>
-  <si>
-    <t>U9ANVP</t>
-  </si>
-  <si>
-    <t>NMVMC7</t>
-  </si>
-  <si>
-    <t>YTJTEP</t>
-  </si>
-  <si>
-    <t>ADKXJK</t>
-  </si>
-  <si>
-    <t>7KMMDF</t>
-  </si>
-  <si>
-    <t>7PEXET</t>
-  </si>
-  <si>
-    <t>CAYMTM</t>
-  </si>
-  <si>
-    <t>4YJTMR</t>
-  </si>
-  <si>
-    <t>RKRYJR</t>
-  </si>
-  <si>
-    <t>NJ4YMD</t>
-  </si>
-  <si>
-    <t>NR7KMT</t>
-  </si>
-  <si>
-    <t>Charlie93</t>
-  </si>
-  <si>
-    <t>Milo63</t>
-  </si>
-  <si>
-    <t>Taffy61</t>
-  </si>
-  <si>
-    <t>Cutie48</t>
-  </si>
-  <si>
-    <t>Cinder48</t>
-  </si>
-  <si>
-    <t>pony40</t>
-  </si>
-  <si>
-    <t>fury37</t>
-  </si>
-  <si>
-    <t>Rabbit37</t>
-  </si>
-  <si>
-    <t>Charlie94</t>
-  </si>
-  <si>
-    <t>Milo64</t>
-  </si>
-  <si>
-    <t>Taffy62</t>
-  </si>
-  <si>
-    <t>Cutie49</t>
-  </si>
-  <si>
-    <t>Cinder49</t>
-  </si>
-  <si>
-    <t>pony41</t>
-  </si>
-  <si>
-    <t>fury38</t>
-  </si>
-  <si>
-    <t>Rabbit38</t>
-  </si>
-  <si>
-    <t>Sheep33</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2460,13 +2412,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2489,20 +2434,14 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2510,42 +2449,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1"/>
     <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -2554,10 +2467,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2689,6 +2602,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2712,10 +2626,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2724,13 +2639,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2806,6 +2721,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2825,35 +2741,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
-    <col min="12" max="16384" style="1" width="8.7265625"/>
+    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.726563" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2885,7 +2799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2902,7 +2816,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -2919,7 +2833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -2936,7 +2850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -2953,14 +2867,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -2970,14 +2884,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -2987,7 +2901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -3004,7 +2918,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
@@ -3021,7 +2935,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
@@ -3038,8 +2952,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+    <row r="11">
+      <c r="A11" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -3055,8 +2969,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
+    <row r="12">
+      <c r="A12" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -3072,2713 +2986,2698 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
+    <row r="13">
+      <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" t="s" s="1">
-        <v>778</v>
-      </c>
-      <c r="D15" t="s" s="20">
-        <v>773</v>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s" s="1">
-        <v>779</v>
-      </c>
-      <c r="D16" t="s" s="21">
-        <v>774</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s" s="1">
-        <v>780</v>
-      </c>
-      <c r="D17" t="s" s="1">
-        <v>775</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D18" t="s" s="1">
-        <v>776</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D19" t="s" s="1">
-        <v>777</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E20" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E21" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E22" s="23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E23" s="24" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="E24" s="1" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="E25" s="1" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="E26" s="1" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="E27" s="1" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="E28" s="1" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="E29" s="1" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="E30" s="1" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="E31" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="E32" s="1" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78">
       <c r="F78" s="3"/>
     </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="F81" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.453125"/>
-    <col min="3" max="3" customWidth="true" width="35.6328125"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.7265625"/>
-    <col min="6" max="6" customWidth="true" width="32.1796875"/>
-    <col min="7" max="7" customWidth="true" width="33.6328125"/>
-    <col min="8" max="8" customWidth="true" width="31.26953125"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.45313" customWidth="1"/>
+    <col min="3" max="3" width="35.63281" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.72656" customWidth="1"/>
+    <col min="6" max="6" width="32.17969" customWidth="1"/>
+    <col min="7" max="7" width="33.63281" customWidth="1"/>
+    <col min="8" max="8" width="31.26953" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>79</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>805</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>800</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>801</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>807</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984375"/>
-    <col min="2" max="2" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" width="17.36328125"/>
-    <col min="4" max="5" customWidth="true" width="17.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.36328125"/>
-    <col min="8" max="8" customWidth="true" width="17.1796875"/>
+    <col min="1" max="1" width="20.08984" customWidth="1"/>
+    <col min="2" max="2" width="17.54297" customWidth="1"/>
+    <col min="3" max="3" width="17.36328" customWidth="1"/>
+    <col min="4" max="5" width="17.26953" customWidth="1"/>
+    <col min="6" max="6" width="17.17969" customWidth="1"/>
+    <col min="7" max="7" width="15.36328" customWidth="1"/>
+    <col min="8" max="8" width="17.17969" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" ht="14.5">
       <c r="A1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>106</v>
+      </c>
+      <c r="B1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" ht="14.5">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" t="s">
+        <v>115</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>101</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5">
+      <c r="A3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s">
+        <v>119</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>105</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" ht="14.5">
+      <c r="A4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>109</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5">
+      <c r="A5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>127</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>113</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
-        <v>116</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>117</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" t="s">
+        <v>135</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="0">
-        <v>120</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>121</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5">
+      <c r="A8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" t="s">
+        <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>125</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s" s="0">
-        <v>128</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>129</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5">
+      <c r="A10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" t="s">
+        <v>147</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s" s="0">
-        <v>132</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>133</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5">
+      <c r="A11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" t="s">
+        <v>151</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s" s="0">
-        <v>136</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>137</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5">
+      <c r="A12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" t="s">
+        <v>155</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s" s="0">
-        <v>140</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>141</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5">
+      <c r="A13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" t="s">
+        <v>159</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s" s="0">
-        <v>144</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>145</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5">
+      <c r="A14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" t="s">
+        <v>163</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s" s="0">
-        <v>148</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>149</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5">
+      <c r="A15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" t="s">
+        <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s" s="0">
-        <v>152</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>153</v>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" ht="14.5">
+      <c r="A16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" t="s">
+        <v>171</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>157</v>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" ht="14.5">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" t="s">
+        <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s" s="0">
-        <v>160</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>161</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" ht="14.5">
+      <c r="A18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" t="s">
+        <v>179</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>165</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" ht="14.5">
+      <c r="A19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" t="s">
+        <v>183</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s" s="0">
-        <v>168</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>169</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" ht="14.5">
+      <c r="A20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" t="s">
+        <v>187</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s" s="0">
-        <v>172</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>173</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" ht="14.5">
+      <c r="A21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" t="s">
+        <v>191</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s" s="0">
-        <v>176</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>177</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" ht="14.5">
+      <c r="A22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" t="s">
+        <v>195</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s" s="0">
-        <v>180</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>181</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" ht="14.5">
+      <c r="A23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" t="s">
+        <v>199</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s" s="0">
-        <v>184</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>185</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" ht="14.5">
+      <c r="A24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" t="s">
+        <v>203</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s" s="0">
-        <v>188</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>189</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" ht="14.5">
+      <c r="A25" t="s">
+        <v>206</v>
+      </c>
+      <c r="B25" t="s">
+        <v>207</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s" s="0">
-        <v>192</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>193</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>194</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" ht="14.5">
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B26" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s" s="0">
-        <v>196</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>198</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="27" ht="14.5">
+      <c r="A27" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s" s="0">
-        <v>200</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>201</v>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" ht="14.5">
+      <c r="A28" t="s">
+        <v>218</v>
+      </c>
+      <c r="B28" t="s">
+        <v>219</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s" s="0">
-        <v>204</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>205</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" ht="14.5">
+      <c r="A29" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" t="s">
+        <v>223</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s" s="0">
-        <v>208</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>209</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" ht="14.5">
+      <c r="A30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" t="s">
+        <v>227</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s" s="0">
-        <v>212</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>213</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" ht="14.5">
+      <c r="A31" t="s">
+        <v>230</v>
+      </c>
+      <c r="B31" t="s">
+        <v>231</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s" s="0">
-        <v>216</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>217</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" ht="14.5">
+      <c r="A32" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" t="s">
+        <v>235</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s" s="0">
-        <v>220</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>221</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" ht="14.5">
+      <c r="A33" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" t="s">
+        <v>239</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>225</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" ht="14.5">
+      <c r="A34" t="s">
+        <v>242</v>
+      </c>
+      <c r="B34" t="s">
+        <v>243</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>229</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" ht="14.5">
+      <c r="A35" t="s">
+        <v>246</v>
+      </c>
+      <c r="B35" t="s">
+        <v>247</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s" s="0">
-        <v>232</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>233</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="36" ht="14.5">
+      <c r="A36" t="s">
+        <v>250</v>
+      </c>
+      <c r="B36" t="s">
+        <v>251</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s" s="0">
-        <v>236</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>237</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="37" ht="14.5">
+      <c r="A37" t="s">
+        <v>254</v>
+      </c>
+      <c r="B37" t="s">
+        <v>255</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s" s="0">
-        <v>240</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>241</v>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="38" ht="14.5">
+      <c r="A38" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" t="s">
+        <v>259</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>245</v>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="39" ht="14.5">
+      <c r="A39" t="s">
+        <v>262</v>
+      </c>
+      <c r="B39" t="s">
+        <v>263</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s" s="0">
-        <v>248</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>249</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="40" ht="14.5">
+      <c r="A40" t="s">
+        <v>266</v>
+      </c>
+      <c r="B40" t="s">
+        <v>267</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s" s="0">
-        <v>252</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>253</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" ht="14.5">
+      <c r="A41" t="s">
+        <v>270</v>
+      </c>
+      <c r="B41" t="s">
+        <v>271</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s" s="0">
-        <v>256</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>257</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" ht="14.5">
+      <c r="A42" t="s">
+        <v>274</v>
+      </c>
+      <c r="B42" t="s">
+        <v>275</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>261</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="43" ht="14.5">
+      <c r="A43" t="s">
+        <v>278</v>
+      </c>
+      <c r="B43" t="s">
+        <v>279</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>265</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="44" ht="14.5">
+      <c r="A44" t="s">
+        <v>282</v>
+      </c>
+      <c r="B44" t="s">
+        <v>283</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s" s="0">
-        <v>268</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>269</v>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="45" ht="14.5">
+      <c r="A45" t="s">
+        <v>286</v>
+      </c>
+      <c r="B45" t="s">
+        <v>287</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s" s="0">
-        <v>272</v>
-      </c>
-      <c r="B46" t="s" s="0">
-        <v>273</v>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="46" ht="14.5">
+      <c r="A46" t="s">
+        <v>290</v>
+      </c>
+      <c r="B46" t="s">
+        <v>291</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s" s="0">
-        <v>276</v>
-      </c>
-      <c r="B47" t="s" s="0">
-        <v>277</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" ht="14.5">
+      <c r="A47" t="s">
+        <v>294</v>
+      </c>
+      <c r="B47" t="s">
+        <v>295</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s" s="0">
-        <v>280</v>
-      </c>
-      <c r="B48" t="s" s="0">
-        <v>281</v>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" ht="14.5">
+      <c r="A48" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" t="s">
+        <v>299</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s" s="0">
-        <v>284</v>
-      </c>
-      <c r="B49" t="s" s="0">
-        <v>285</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="49" ht="14.5">
+      <c r="A49" t="s">
+        <v>302</v>
+      </c>
+      <c r="B49" t="s">
+        <v>303</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s" s="0">
-        <v>288</v>
-      </c>
-      <c r="B50" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="50" ht="14.5">
+      <c r="A50" t="s">
+        <v>306</v>
+      </c>
+      <c r="B50" t="s">
+        <v>307</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s" s="0">
-        <v>292</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>293</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" ht="14.5">
+      <c r="A51" t="s">
+        <v>310</v>
+      </c>
+      <c r="B51" t="s">
+        <v>311</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s" s="0">
-        <v>296</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>297</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="52" ht="14.5">
+      <c r="A52" t="s">
+        <v>314</v>
+      </c>
+      <c r="B52" t="s">
+        <v>315</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s" s="0">
-        <v>300</v>
-      </c>
-      <c r="B53" t="s" s="0">
-        <v>301</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="53" ht="14.5">
+      <c r="A53" t="s">
+        <v>318</v>
+      </c>
+      <c r="B53" t="s">
+        <v>319</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s" s="0">
-        <v>304</v>
-      </c>
-      <c r="B54" t="s" s="0">
-        <v>305</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="54" ht="14.5">
+      <c r="A54" t="s">
+        <v>322</v>
+      </c>
+      <c r="B54" t="s">
+        <v>323</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s" s="0">
-        <v>308</v>
-      </c>
-      <c r="B55" t="s" s="0">
-        <v>309</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="55" ht="14.5">
+      <c r="A55" t="s">
+        <v>326</v>
+      </c>
+      <c r="B55" t="s">
+        <v>327</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s" s="0">
-        <v>312</v>
-      </c>
-      <c r="B56" t="s" s="0">
-        <v>313</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="56" ht="14.5">
+      <c r="A56" t="s">
+        <v>330</v>
+      </c>
+      <c r="B56" t="s">
+        <v>331</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s" s="0">
-        <v>316</v>
-      </c>
-      <c r="B57" t="s" s="0">
-        <v>317</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="57" ht="14.5">
+      <c r="A57" t="s">
+        <v>334</v>
+      </c>
+      <c r="B57" t="s">
+        <v>335</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s" s="0">
-        <v>320</v>
-      </c>
-      <c r="B58" t="s" s="0">
-        <v>321</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="58" ht="14.5">
+      <c r="A58" t="s">
+        <v>338</v>
+      </c>
+      <c r="B58" t="s">
+        <v>339</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s" s="0">
-        <v>324</v>
-      </c>
-      <c r="B59" t="s" s="0">
-        <v>325</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="59" ht="14.5">
+      <c r="A59" t="s">
+        <v>342</v>
+      </c>
+      <c r="B59" t="s">
+        <v>343</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s" s="0">
-        <v>328</v>
-      </c>
-      <c r="B60" t="s" s="0">
-        <v>329</v>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" ht="14.5">
+      <c r="A60" t="s">
+        <v>346</v>
+      </c>
+      <c r="B60" t="s">
+        <v>347</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s" s="0">
-        <v>332</v>
-      </c>
-      <c r="B61" t="s" s="0">
-        <v>333</v>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="61" ht="14.5">
+      <c r="A61" t="s">
+        <v>350</v>
+      </c>
+      <c r="B61" t="s">
+        <v>351</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s" s="0">
-        <v>336</v>
-      </c>
-      <c r="B62" t="s" s="0">
-        <v>337</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="62" ht="14.5">
+      <c r="A62" t="s">
+        <v>354</v>
+      </c>
+      <c r="B62" t="s">
+        <v>355</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s" s="0">
-        <v>340</v>
-      </c>
-      <c r="B63" t="s" s="0">
-        <v>341</v>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" ht="14.5">
+      <c r="A63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B63" t="s">
+        <v>359</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s" s="0">
-        <v>344</v>
-      </c>
-      <c r="B64" t="s" s="0">
-        <v>345</v>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="64" ht="14.5">
+      <c r="A64" t="s">
+        <v>362</v>
+      </c>
+      <c r="B64" t="s">
+        <v>363</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s" s="0">
-        <v>348</v>
-      </c>
-      <c r="B65" t="s" s="0">
-        <v>349</v>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="65" ht="14.5">
+      <c r="A65" t="s">
+        <v>366</v>
+      </c>
+      <c r="B65" t="s">
+        <v>367</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s" s="0">
-        <v>352</v>
-      </c>
-      <c r="B66" t="s" s="0">
-        <v>353</v>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="66" ht="14.5">
+      <c r="A66" t="s">
+        <v>370</v>
+      </c>
+      <c r="B66" t="s">
+        <v>371</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="B67" t="s" s="0">
-        <v>357</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="67" ht="14.5">
+      <c r="A67" t="s">
+        <v>374</v>
+      </c>
+      <c r="B67" t="s">
+        <v>375</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s" s="0">
-        <v>360</v>
-      </c>
-      <c r="B68" t="s" s="0">
-        <v>361</v>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="68" ht="14.5">
+      <c r="A68" t="s">
+        <v>378</v>
+      </c>
+      <c r="B68" t="s">
+        <v>379</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="B69" t="s" s="0">
-        <v>365</v>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="69" ht="14.5">
+      <c r="A69" t="s">
+        <v>382</v>
+      </c>
+      <c r="B69" t="s">
+        <v>383</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s" s="0">
-        <v>368</v>
-      </c>
-      <c r="B70" t="s" s="0">
-        <v>369</v>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="70" ht="14.5">
+      <c r="A70" t="s">
+        <v>386</v>
+      </c>
+      <c r="B70" t="s">
+        <v>387</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s" s="0">
-        <v>372</v>
-      </c>
-      <c r="B71" t="s" s="0">
-        <v>373</v>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="71" ht="14.5">
+      <c r="A71" t="s">
+        <v>390</v>
+      </c>
+      <c r="B71" t="s">
+        <v>391</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s" s="0">
-        <v>376</v>
-      </c>
-      <c r="B72" t="s" s="0">
-        <v>377</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="72" ht="14.5">
+      <c r="A72" t="s">
+        <v>394</v>
+      </c>
+      <c r="B72" t="s">
+        <v>395</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s" s="0">
-        <v>380</v>
-      </c>
-      <c r="B73" t="s" s="0">
-        <v>381</v>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="73" ht="14.5">
+      <c r="A73" t="s">
+        <v>398</v>
+      </c>
+      <c r="B73" t="s">
+        <v>399</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s" s="0">
-        <v>384</v>
-      </c>
-      <c r="B74" t="s" s="0">
-        <v>385</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="74" ht="14.5">
+      <c r="A74" t="s">
+        <v>402</v>
+      </c>
+      <c r="B74" t="s">
+        <v>403</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s" s="0">
-        <v>388</v>
-      </c>
-      <c r="B75" t="s" s="0">
-        <v>389</v>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="75" ht="14.5">
+      <c r="A75" t="s">
+        <v>406</v>
+      </c>
+      <c r="B75" t="s">
+        <v>407</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s" s="0">
-        <v>392</v>
-      </c>
-      <c r="B76" t="s" s="0">
-        <v>393</v>
+        <v>409</v>
+      </c>
+    </row>
+    <row r="76" ht="14.5">
+      <c r="A76" t="s">
+        <v>410</v>
+      </c>
+      <c r="B76" t="s">
+        <v>411</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s" s="0">
-        <v>396</v>
-      </c>
-      <c r="B77" t="s" s="0">
-        <v>397</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="77" ht="14.5">
+      <c r="A77" t="s">
+        <v>414</v>
+      </c>
+      <c r="B77" t="s">
+        <v>415</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s" s="0">
-        <v>400</v>
-      </c>
-      <c r="B78" t="s" s="0">
-        <v>401</v>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="78" ht="14.5">
+      <c r="A78" t="s">
+        <v>418</v>
+      </c>
+      <c r="B78" t="s">
+        <v>419</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="B79" t="s" s="0">
-        <v>405</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="79" ht="14.5">
+      <c r="A79" t="s">
+        <v>422</v>
+      </c>
+      <c r="B79" t="s">
+        <v>423</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="B80" t="s" s="0">
-        <v>409</v>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="80" ht="14.5">
+      <c r="A80" t="s">
+        <v>426</v>
+      </c>
+      <c r="B80" t="s">
+        <v>427</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s" s="0">
-        <v>412</v>
-      </c>
-      <c r="B81" t="s" s="0">
-        <v>413</v>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="81" ht="14.5">
+      <c r="A81" t="s">
+        <v>430</v>
+      </c>
+      <c r="B81" t="s">
+        <v>431</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s" s="0">
-        <v>416</v>
-      </c>
-      <c r="B82" t="s" s="0">
-        <v>417</v>
+        <v>433</v>
+      </c>
+    </row>
+    <row r="82" ht="14.5">
+      <c r="A82" t="s">
+        <v>434</v>
+      </c>
+      <c r="B82" t="s">
+        <v>435</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s" s="0">
-        <v>420</v>
-      </c>
-      <c r="B83" t="s" s="0">
-        <v>421</v>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="83" ht="14.5">
+      <c r="A83" t="s">
+        <v>438</v>
+      </c>
+      <c r="B83" t="s">
+        <v>439</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="B84" t="s" s="0">
-        <v>425</v>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="84" ht="14.5">
+      <c r="A84" t="s">
+        <v>442</v>
+      </c>
+      <c r="B84" t="s">
+        <v>443</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s" s="0">
-        <v>428</v>
-      </c>
-      <c r="B85" t="s" s="0">
-        <v>429</v>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="85" ht="14.5">
+      <c r="A85" t="s">
+        <v>446</v>
+      </c>
+      <c r="B85" t="s">
+        <v>447</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s" s="0">
-        <v>432</v>
-      </c>
-      <c r="B86" t="s" s="0">
-        <v>433</v>
+        <v>449</v>
+      </c>
+    </row>
+    <row r="86" ht="14.5">
+      <c r="A86" t="s">
+        <v>450</v>
+      </c>
+      <c r="B86" t="s">
+        <v>451</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="B87" t="s" s="0">
-        <v>437</v>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="87" ht="14.5">
+      <c r="A87" t="s">
+        <v>454</v>
+      </c>
+      <c r="B87" t="s">
+        <v>455</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="B88" t="s" s="0">
-        <v>441</v>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="88" ht="14.5">
+      <c r="A88" t="s">
+        <v>458</v>
+      </c>
+      <c r="B88" t="s">
+        <v>459</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s" s="0">
-        <v>444</v>
-      </c>
-      <c r="B89" t="s" s="0">
-        <v>445</v>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="89" ht="14.5">
+      <c r="A89" t="s">
+        <v>462</v>
+      </c>
+      <c r="B89" t="s">
+        <v>463</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s" s="0">
-        <v>448</v>
-      </c>
-      <c r="B90" t="s" s="0">
-        <v>449</v>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="90" ht="14.5">
+      <c r="A90" t="s">
+        <v>466</v>
+      </c>
+      <c r="B90" t="s">
+        <v>467</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s" s="0">
-        <v>452</v>
-      </c>
-      <c r="B91" t="s" s="0">
-        <v>453</v>
+        <v>469</v>
+      </c>
+    </row>
+    <row r="91" ht="14.5">
+      <c r="A91" t="s">
+        <v>470</v>
+      </c>
+      <c r="B91" t="s">
+        <v>471</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s" s="0">
-        <v>456</v>
-      </c>
-      <c r="B92" t="s" s="0">
-        <v>457</v>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="92" ht="14.5">
+      <c r="A92" t="s">
+        <v>474</v>
+      </c>
+      <c r="B92" t="s">
+        <v>475</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s" s="0">
-        <v>460</v>
-      </c>
-      <c r="B93" t="s" s="0">
-        <v>461</v>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="93" ht="14.5">
+      <c r="A93" t="s">
+        <v>478</v>
+      </c>
+      <c r="B93" t="s">
+        <v>479</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s" s="0">
-        <v>464</v>
-      </c>
-      <c r="B94" t="s" s="0">
-        <v>465</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="94" ht="14.5">
+      <c r="A94" t="s">
+        <v>482</v>
+      </c>
+      <c r="B94" t="s">
+        <v>483</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s" s="0">
-        <v>468</v>
-      </c>
-      <c r="B95" t="s" s="0">
-        <v>469</v>
+        <v>485</v>
+      </c>
+    </row>
+    <row r="95" ht="14.5">
+      <c r="A95" t="s">
+        <v>486</v>
+      </c>
+      <c r="B95" t="s">
+        <v>487</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s" s="0">
-        <v>472</v>
-      </c>
-      <c r="B96" t="s" s="0">
-        <v>473</v>
+        <v>489</v>
+      </c>
+    </row>
+    <row r="96" ht="14.5">
+      <c r="A96" t="s">
+        <v>490</v>
+      </c>
+      <c r="B96" t="s">
+        <v>491</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s" s="0">
-        <v>476</v>
-      </c>
-      <c r="B97" t="s" s="0">
-        <v>477</v>
+        <v>493</v>
+      </c>
+    </row>
+    <row r="97" ht="14.5">
+      <c r="A97" t="s">
+        <v>494</v>
+      </c>
+      <c r="B97" t="s">
+        <v>495</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s" s="0">
-        <v>480</v>
-      </c>
-      <c r="B98" t="s" s="0">
-        <v>481</v>
+        <v>497</v>
+      </c>
+    </row>
+    <row r="98" ht="14.5">
+      <c r="A98" t="s">
+        <v>498</v>
+      </c>
+      <c r="B98" t="s">
+        <v>499</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s" s="0">
-        <v>484</v>
-      </c>
-      <c r="B99" t="s" s="0">
-        <v>485</v>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="99" ht="14.5">
+      <c r="A99" t="s">
+        <v>502</v>
+      </c>
+      <c r="B99" t="s">
+        <v>503</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s" s="0">
-        <v>488</v>
-      </c>
-      <c r="B100" t="s" s="0">
-        <v>489</v>
+        <v>505</v>
+      </c>
+    </row>
+    <row r="100" ht="14.5">
+      <c r="A100" t="s">
+        <v>506</v>
+      </c>
+      <c r="B100" t="s">
+        <v>507</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s" s="0">
-        <v>492</v>
-      </c>
-      <c r="B101" t="s" s="0">
-        <v>493</v>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="101" ht="14.5">
+      <c r="A101" t="s">
+        <v>510</v>
+      </c>
+      <c r="B101" t="s">
+        <v>511</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s" s="0">
-        <v>496</v>
-      </c>
-      <c r="B102" t="s" s="0">
-        <v>497</v>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="102" ht="14.5">
+      <c r="A102" t="s">
+        <v>514</v>
+      </c>
+      <c r="B102" t="s">
+        <v>515</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s" s="0">
-        <v>500</v>
-      </c>
-      <c r="B103" t="s" s="0">
-        <v>501</v>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="103" ht="14.5">
+      <c r="A103" t="s">
+        <v>518</v>
+      </c>
+      <c r="B103" t="s">
+        <v>519</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s" s="0">
-        <v>504</v>
-      </c>
-      <c r="B104" t="s" s="0">
-        <v>505</v>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="104" ht="14.5">
+      <c r="A104" t="s">
+        <v>522</v>
+      </c>
+      <c r="B104" t="s">
+        <v>523</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s" s="0">
-        <v>508</v>
-      </c>
-      <c r="B105" t="s" s="0">
-        <v>509</v>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="105" ht="14.5">
+      <c r="A105" t="s">
+        <v>526</v>
+      </c>
+      <c r="B105" t="s">
+        <v>527</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s" s="0">
-        <v>512</v>
-      </c>
-      <c r="B106" t="s" s="0">
-        <v>513</v>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="106" ht="14.5">
+      <c r="A106" t="s">
+        <v>530</v>
+      </c>
+      <c r="B106" t="s">
+        <v>531</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s" s="0">
-        <v>516</v>
-      </c>
-      <c r="B107" t="s" s="0">
-        <v>517</v>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="107" ht="14.5">
+      <c r="A107" t="s">
+        <v>534</v>
+      </c>
+      <c r="B107" t="s">
+        <v>535</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s" s="0">
-        <v>520</v>
-      </c>
-      <c r="B108" t="s" s="0">
-        <v>521</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="108" ht="14.5">
+      <c r="A108" t="s">
+        <v>538</v>
+      </c>
+      <c r="B108" t="s">
+        <v>539</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s" s="0">
-        <v>524</v>
-      </c>
-      <c r="B109" t="s" s="0">
-        <v>525</v>
+        <v>541</v>
+      </c>
+    </row>
+    <row r="109" ht="14.5">
+      <c r="A109" t="s">
+        <v>542</v>
+      </c>
+      <c r="B109" t="s">
+        <v>543</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s" s="0">
-        <v>528</v>
-      </c>
-      <c r="B110" t="s" s="0">
-        <v>529</v>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="110" ht="14.5">
+      <c r="A110" t="s">
+        <v>546</v>
+      </c>
+      <c r="B110" t="s">
+        <v>547</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s" s="0">
-        <v>532</v>
-      </c>
-      <c r="B111" t="s" s="0">
-        <v>533</v>
+        <v>549</v>
+      </c>
+    </row>
+    <row r="111" ht="14.5">
+      <c r="A111" t="s">
+        <v>550</v>
+      </c>
+      <c r="B111" t="s">
+        <v>551</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s" s="0">
-        <v>536</v>
-      </c>
-      <c r="B112" t="s" s="0">
-        <v>537</v>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="112" ht="14.5">
+      <c r="A112" t="s">
+        <v>554</v>
+      </c>
+      <c r="B112" t="s">
+        <v>555</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s" s="0">
-        <v>540</v>
-      </c>
-      <c r="B113" t="s" s="0">
-        <v>541</v>
+        <v>557</v>
+      </c>
+    </row>
+    <row r="113" ht="14.5">
+      <c r="A113" t="s">
+        <v>558</v>
+      </c>
+      <c r="B113" t="s">
+        <v>559</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="B114" t="s" s="0">
-        <v>545</v>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="114" ht="14.5">
+      <c r="A114" t="s">
+        <v>562</v>
+      </c>
+      <c r="B114" t="s">
+        <v>563</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s" s="0">
-        <v>548</v>
-      </c>
-      <c r="B115" t="s" s="0">
-        <v>549</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="115" ht="14.5">
+      <c r="A115" t="s">
+        <v>566</v>
+      </c>
+      <c r="B115" t="s">
+        <v>567</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s" s="0">
-        <v>552</v>
-      </c>
-      <c r="B116" t="s" s="0">
-        <v>553</v>
+        <v>569</v>
+      </c>
+    </row>
+    <row r="116" ht="14.5">
+      <c r="A116" t="s">
+        <v>570</v>
+      </c>
+      <c r="B116" t="s">
+        <v>571</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s" s="0">
-        <v>556</v>
-      </c>
-      <c r="B117" t="s" s="0">
-        <v>557</v>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="117" ht="14.5">
+      <c r="A117" t="s">
+        <v>574</v>
+      </c>
+      <c r="B117" t="s">
+        <v>575</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s" s="0">
-        <v>560</v>
-      </c>
-      <c r="B118" t="s" s="0">
-        <v>561</v>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="118" ht="14.5">
+      <c r="A118" t="s">
+        <v>578</v>
+      </c>
+      <c r="B118" t="s">
+        <v>579</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s" s="0">
-        <v>564</v>
-      </c>
-      <c r="B119" t="s" s="0">
-        <v>565</v>
+        <v>581</v>
+      </c>
+    </row>
+    <row r="119" ht="14.5">
+      <c r="A119" t="s">
+        <v>582</v>
+      </c>
+      <c r="B119" t="s">
+        <v>583</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s" s="0">
-        <v>568</v>
-      </c>
-      <c r="B120" t="s" s="0">
-        <v>569</v>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="120" ht="14.5">
+      <c r="A120" t="s">
+        <v>586</v>
+      </c>
+      <c r="B120" t="s">
+        <v>587</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s" s="0">
-        <v>572</v>
-      </c>
-      <c r="B121" t="s" s="0">
-        <v>573</v>
+        <v>589</v>
+      </c>
+    </row>
+    <row r="121" ht="14.5">
+      <c r="A121" t="s">
+        <v>590</v>
+      </c>
+      <c r="B121" t="s">
+        <v>591</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s" s="0">
-        <v>576</v>
-      </c>
-      <c r="B122" t="s" s="0">
-        <v>577</v>
+        <v>593</v>
+      </c>
+    </row>
+    <row r="122" ht="14.5">
+      <c r="A122" t="s">
+        <v>594</v>
+      </c>
+      <c r="B122" t="s">
+        <v>595</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s" s="0">
-        <v>580</v>
-      </c>
-      <c r="B123" t="s" s="0">
-        <v>581</v>
+        <v>597</v>
+      </c>
+    </row>
+    <row r="123" ht="14.5">
+      <c r="A123" t="s">
+        <v>598</v>
+      </c>
+      <c r="B123" t="s">
+        <v>599</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s" s="0">
-        <v>584</v>
-      </c>
-      <c r="B124" t="s" s="0">
-        <v>585</v>
+        <v>601</v>
+      </c>
+    </row>
+    <row r="124" ht="14.5">
+      <c r="A124" t="s">
+        <v>602</v>
+      </c>
+      <c r="B124" t="s">
+        <v>603</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s" s="0">
-        <v>588</v>
-      </c>
-      <c r="B125" t="s" s="0">
-        <v>589</v>
+        <v>605</v>
+      </c>
+    </row>
+    <row r="125" ht="14.5">
+      <c r="A125" t="s">
+        <v>606</v>
+      </c>
+      <c r="B125" t="s">
+        <v>607</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s" s="0">
-        <v>592</v>
-      </c>
-      <c r="B126" t="s" s="0">
-        <v>593</v>
+        <v>609</v>
+      </c>
+    </row>
+    <row r="126" ht="14.5">
+      <c r="A126" t="s">
+        <v>610</v>
+      </c>
+      <c r="B126" t="s">
+        <v>611</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s" s="0">
-        <v>596</v>
-      </c>
-      <c r="B127" t="s" s="0">
-        <v>597</v>
+        <v>613</v>
+      </c>
+    </row>
+    <row r="127" ht="14.5">
+      <c r="A127" t="s">
+        <v>614</v>
+      </c>
+      <c r="B127" t="s">
+        <v>615</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s" s="0">
-        <v>600</v>
-      </c>
-      <c r="B128" t="s" s="0">
-        <v>601</v>
+        <v>617</v>
+      </c>
+    </row>
+    <row r="128" ht="14.5">
+      <c r="A128" t="s">
+        <v>618</v>
+      </c>
+      <c r="B128" t="s">
+        <v>619</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s" s="0">
-        <v>604</v>
-      </c>
-      <c r="B129" t="s" s="0">
-        <v>605</v>
+        <v>621</v>
+      </c>
+    </row>
+    <row r="129" ht="14.5">
+      <c r="A129" t="s">
+        <v>622</v>
+      </c>
+      <c r="B129" t="s">
+        <v>623</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s" s="0">
-        <v>608</v>
-      </c>
-      <c r="B130" t="s" s="0">
-        <v>609</v>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="130" ht="14.5">
+      <c r="A130" t="s">
+        <v>626</v>
+      </c>
+      <c r="B130" t="s">
+        <v>627</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s" s="0">
-        <v>612</v>
-      </c>
-      <c r="B131" t="s" s="0">
-        <v>613</v>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="131" ht="14.5">
+      <c r="A131" t="s">
+        <v>630</v>
+      </c>
+      <c r="B131" t="s">
+        <v>631</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>614</v>
+        <v>632</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s" s="0">
-        <v>616</v>
-      </c>
-      <c r="B132" t="s" s="0">
-        <v>617</v>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="132" ht="14.5">
+      <c r="A132" t="s">
+        <v>634</v>
+      </c>
+      <c r="B132" t="s">
+        <v>635</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s" s="0">
-        <v>620</v>
-      </c>
-      <c r="B133" t="s" s="0">
-        <v>621</v>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="133" ht="14.5">
+      <c r="A133" t="s">
+        <v>638</v>
+      </c>
+      <c r="B133" t="s">
+        <v>639</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s" s="0">
-        <v>624</v>
-      </c>
-      <c r="B134" t="s" s="0">
-        <v>625</v>
+        <v>641</v>
+      </c>
+    </row>
+    <row r="134" ht="14.5">
+      <c r="A134" t="s">
+        <v>642</v>
+      </c>
+      <c r="B134" t="s">
+        <v>643</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s" s="0">
-        <v>628</v>
-      </c>
-      <c r="B135" t="s" s="0">
-        <v>629</v>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="135" ht="14.5">
+      <c r="A135" t="s">
+        <v>646</v>
+      </c>
+      <c r="B135" t="s">
+        <v>647</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s" s="0">
-        <v>632</v>
-      </c>
-      <c r="B136" t="s" s="0">
-        <v>633</v>
+        <v>649</v>
+      </c>
+    </row>
+    <row r="136" ht="14.5">
+      <c r="A136" t="s">
+        <v>650</v>
+      </c>
+      <c r="B136" t="s">
+        <v>651</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s" s="0">
-        <v>636</v>
-      </c>
-      <c r="B137" t="s" s="0">
-        <v>637</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="137" ht="14.5">
+      <c r="A137" t="s">
+        <v>654</v>
+      </c>
+      <c r="B137" t="s">
+        <v>655</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s" s="0">
-        <v>640</v>
-      </c>
-      <c r="B138" t="s" s="0">
-        <v>641</v>
+        <v>657</v>
+      </c>
+    </row>
+    <row r="138" ht="14.5">
+      <c r="A138" t="s">
+        <v>658</v>
+      </c>
+      <c r="B138" t="s">
+        <v>659</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>642</v>
+        <v>660</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s" s="0">
-        <v>644</v>
-      </c>
-      <c r="B139" t="s" s="0">
-        <v>645</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="139" ht="14.5">
+      <c r="A139" t="s">
+        <v>662</v>
+      </c>
+      <c r="B139" t="s">
+        <v>663</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>646</v>
+        <v>664</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s" s="0">
-        <v>648</v>
-      </c>
-      <c r="B140" t="s" s="0">
-        <v>649</v>
+        <v>665</v>
+      </c>
+    </row>
+    <row r="140" ht="14.5">
+      <c r="A140" t="s">
+        <v>666</v>
+      </c>
+      <c r="B140" t="s">
+        <v>667</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>650</v>
+        <v>668</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s" s="0">
-        <v>652</v>
-      </c>
-      <c r="B141" t="s" s="0">
-        <v>653</v>
+        <v>669</v>
+      </c>
+    </row>
+    <row r="141" ht="14.5">
+      <c r="A141" t="s">
+        <v>670</v>
+      </c>
+      <c r="B141" t="s">
+        <v>671</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s" s="0">
-        <v>656</v>
-      </c>
-      <c r="B142" t="s" s="0">
-        <v>657</v>
+        <v>673</v>
+      </c>
+    </row>
+    <row r="142" ht="14.5">
+      <c r="A142" t="s">
+        <v>674</v>
+      </c>
+      <c r="B142" t="s">
+        <v>675</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s" s="0">
-        <v>660</v>
-      </c>
-      <c r="B143" t="s" s="0">
-        <v>661</v>
+        <v>677</v>
+      </c>
+    </row>
+    <row r="143" ht="14.5">
+      <c r="A143" t="s">
+        <v>678</v>
+      </c>
+      <c r="B143" t="s">
+        <v>679</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s" s="0">
-        <v>664</v>
-      </c>
-      <c r="B144" t="s" s="0">
-        <v>665</v>
+        <v>681</v>
+      </c>
+    </row>
+    <row r="144" ht="14.5">
+      <c r="A144" t="s">
+        <v>682</v>
+      </c>
+      <c r="B144" t="s">
+        <v>683</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s" s="0">
-        <v>668</v>
-      </c>
-      <c r="B145" t="s" s="0">
-        <v>669</v>
+        <v>685</v>
+      </c>
+    </row>
+    <row r="145" ht="14.5">
+      <c r="A145" t="s">
+        <v>686</v>
+      </c>
+      <c r="B145" t="s">
+        <v>687</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s" s="0">
-        <v>672</v>
-      </c>
-      <c r="B146" t="s" s="0">
-        <v>673</v>
+        <v>689</v>
+      </c>
+    </row>
+    <row r="146" ht="14.5">
+      <c r="A146" t="s">
+        <v>690</v>
+      </c>
+      <c r="B146" t="s">
+        <v>691</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s" s="0">
-        <v>676</v>
-      </c>
-      <c r="B147" t="s" s="0">
-        <v>677</v>
+        <v>693</v>
+      </c>
+    </row>
+    <row r="147" ht="14.5">
+      <c r="A147" t="s">
+        <v>694</v>
+      </c>
+      <c r="B147" t="s">
+        <v>695</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s" s="0">
-        <v>680</v>
-      </c>
-      <c r="B148" t="s" s="0">
-        <v>681</v>
+        <v>697</v>
+      </c>
+    </row>
+    <row r="148" ht="14.5">
+      <c r="A148" t="s">
+        <v>698</v>
+      </c>
+      <c r="B148" t="s">
+        <v>699</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s" s="0">
-        <v>684</v>
-      </c>
-      <c r="B149" t="s" s="0">
-        <v>685</v>
+        <v>701</v>
+      </c>
+    </row>
+    <row r="149" ht="14.5">
+      <c r="A149" t="s">
+        <v>702</v>
+      </c>
+      <c r="B149" t="s">
+        <v>703</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s" s="0">
-        <v>688</v>
-      </c>
-      <c r="B150" t="s" s="0">
-        <v>689</v>
+        <v>705</v>
+      </c>
+    </row>
+    <row r="150" ht="14.5">
+      <c r="A150" t="s">
+        <v>706</v>
+      </c>
+      <c r="B150" t="s">
+        <v>707</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s" s="0">
-        <v>692</v>
-      </c>
-      <c r="B151" t="s" s="0">
-        <v>693</v>
+        <v>709</v>
+      </c>
+    </row>
+    <row r="151" ht="14.5">
+      <c r="A151" t="s">
+        <v>710</v>
+      </c>
+      <c r="B151" t="s">
+        <v>711</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s" s="0">
-        <v>696</v>
-      </c>
-      <c r="B152" t="s" s="0">
-        <v>697</v>
+        <v>713</v>
+      </c>
+    </row>
+    <row r="152" ht="14.5">
+      <c r="A152" t="s">
+        <v>714</v>
+      </c>
+      <c r="B152" t="s">
+        <v>715</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>698</v>
+        <v>716</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s" s="0">
-        <v>700</v>
+        <v>717</v>
+      </c>
+    </row>
+    <row r="153" ht="14.5">
+      <c r="B153" t="s">
+        <v>718</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>701</v>
+        <v>719</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s" s="0">
-        <v>703</v>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="154" ht="14.5">
+      <c r="B154" t="s">
+        <v>721</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>704</v>
+        <v>722</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s" s="0">
-        <v>706</v>
+        <v>723</v>
+      </c>
+    </row>
+    <row r="155" ht="14.5">
+      <c r="B155" t="s">
+        <v>724</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>707</v>
+        <v>725</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s" s="0">
-        <v>709</v>
+        <v>726</v>
+      </c>
+    </row>
+    <row r="156" ht="14.5">
+      <c r="B156" t="s">
+        <v>727</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s" s="0">
-        <v>712</v>
+        <v>729</v>
+      </c>
+    </row>
+    <row r="157" ht="14.5">
+      <c r="B157" t="s">
+        <v>730</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s" s="0">
-        <v>715</v>
+        <v>732</v>
+      </c>
+    </row>
+    <row r="158" ht="14.5">
+      <c r="B158" t="s">
+        <v>733</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="159" ht="14.5">
       <c r="C159" s="6" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="160" ht="14.5">
       <c r="C160" s="6" t="s">
-        <v>720</v>
+        <v>738</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="161" ht="14.5">
       <c r="C161" s="6" t="s">
-        <v>722</v>
+        <v>740</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="162" ht="14.5">
       <c r="C162" s="6" t="s">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="163" ht="14.5">
       <c r="C163" s="6" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="164" ht="14.5">
       <c r="C164" s="6" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="165" ht="14.5">
       <c r="C165" s="6" t="s">
-        <v>730</v>
+        <v>748</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="166" ht="14.5">
       <c r="C166" s="6" t="s">
-        <v>732</v>
+        <v>750</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="167" ht="14.5">
       <c r="C167" s="6" t="s">
-        <v>734</v>
+        <v>752</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="168" ht="14.5">
       <c r="C168" s="6" t="s">
-        <v>736</v>
+        <v>754</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="169" ht="14.5">
       <c r="C169" s="6" t="s">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="170" spans="3:4" x14ac:dyDescent="0.35">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="170" ht="14.5">
       <c r="C170" s="6" t="s">
-        <v>740</v>
+        <v>758</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="171" spans="3:4" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="171" ht="14.5">
       <c r="D171" s="5" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="172" spans="3:4" x14ac:dyDescent="0.35">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="172" ht="14.5">
       <c r="D172" s="5" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="173" spans="3:4" x14ac:dyDescent="0.35">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="173" ht="14.5">
       <c r="D173" s="5" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="174" spans="3:4" x14ac:dyDescent="0.35">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="174" ht="14.5">
       <c r="D174" s="5" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="175" spans="3:4" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="175" ht="14.5">
       <c r="D175" s="5" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="176" spans="3:4" x14ac:dyDescent="0.35">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="176" ht="14.5">
       <c r="D176" s="5" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.35">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="177" ht="14.5">
       <c r="D177" s="5" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.35">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="178" ht="14.5">
       <c r="D178" s="5" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="179" ht="14.5">
       <c r="D179" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.35">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="180" ht="14.5">
       <c r="D180" s="5" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.35">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="181" ht="14.5">
       <c r="D181" s="5" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.35">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="182" ht="14.5">
       <c r="D182" s="5" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.35">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="183" ht="14.5">
       <c r="D183" s="5" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.35">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="184" ht="14.5">
       <c r="D184" s="5" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.35">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="185" ht="14.5">
       <c r="D185" s="5" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.35">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="186" ht="14.5">
       <c r="D186" s="5" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.35">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="187" ht="14.5">
       <c r="D187" s="5" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.35">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="188" ht="14.5">
       <c r="D188" s="5" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.35">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="189" ht="14.5">
       <c r="D189" s="5" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.35">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="190" ht="14.5">
       <c r="D190" s="5" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.35">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="191" ht="14.5">
       <c r="D191" s="5" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.35">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="192" ht="14.5">
       <c r="D192" s="5" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.35">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="193" ht="14.5">
       <c r="D193" s="5" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.35">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="194" ht="14.5">
       <c r="D194" s="5" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.35">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="195" ht="14.5">
       <c r="D195" s="5" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.35">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="196" ht="14.5">
       <c r="D196" s="5" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="197" ht="14.5">
       <c r="D197" s="5" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.35">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="198" ht="14.5">
       <c r="D198" s="5" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.35">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="199" ht="14.5">
       <c r="D199" s="5" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.35">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="200" ht="14.5">
       <c r="D200" s="5" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.35">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="201" ht="14.5">
       <c r="D201" s="5" t="s">
-        <v>772</v>
+        <v>790</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2394,12 +2394,40 @@
   </si>
   <si>
     <t>Nexra</t>
+  </si>
+  <si>
+    <t>Charlie96</t>
+  </si>
+  <si>
+    <t>Milo66</t>
+  </si>
+  <si>
+    <t>Taffy64</t>
+  </si>
+  <si>
+    <t>Cutie51</t>
+  </si>
+  <si>
+    <t>Cinder51</t>
+  </si>
+  <si>
+    <t>pony43</t>
+  </si>
+  <si>
+    <t>fury40</t>
+  </si>
+  <si>
+    <t>Rabbit40</t>
+  </si>
+  <si>
+    <t>Sheep35</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -2441,7 +2469,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2451,6 +2479,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2751,20 +2790,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.726563" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
+    <col min="12" max="16384" style="1" width="8.726563"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2888,7 +2928,7 @@
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -2908,7 +2948,7 @@
       <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -2998,7 +3038,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="7" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -3009,7 +3049,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -3034,7 +3074,7 @@
       <c r="A17" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="11" t="s">
         <v>78</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -3042,7 +3082,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="12" t="s">
         <v>80</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -3078,22 +3118,22 @@
       </c>
     </row>
     <row r="24">
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="14" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="25">
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="27">
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="17" t="s">
         <v>91</v>
       </c>
     </row>
@@ -3135,72 +3175,81 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.45313" customWidth="1"/>
-    <col min="3" max="3" width="35.63281" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.72656" customWidth="1"/>
-    <col min="6" max="6" width="32.17969" customWidth="1"/>
-    <col min="7" max="7" width="33.63281" customWidth="1"/>
-    <col min="8" max="8" width="31.26953" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.45313"/>
+    <col min="3" max="3" customWidth="true" width="35.63281"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.72656"/>
+    <col min="6" max="6" customWidth="true" width="32.17969"/>
+    <col min="7" max="7" customWidth="true" width="33.63281"/>
+    <col min="8" max="8" customWidth="true" width="31.26953"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>104</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="C2"/>
-      <c r="D2" t="s">
+      <c r="C2" t="s" s="0">
         <v>105</v>
       </c>
+      <c r="D2" t="s" s="0">
+        <v>105</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="C3"/>
-      <c r="D3" t="s">
+      <c r="B3" t="s" s="0">
         <v>105</v>
       </c>
+      <c r="C3" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>105</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4"/>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="D4"/>
+      <c r="B4" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="D4" s="0"/>
     </row>
   </sheetData>
   <pageSetup r:id="rId1" orientation="portrait"/>
@@ -3209,48 +3258,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984" customWidth="1"/>
-    <col min="2" max="2" width="17.54297" customWidth="1"/>
-    <col min="3" max="3" width="17.36328" customWidth="1"/>
-    <col min="4" max="5" width="17.26953" customWidth="1"/>
-    <col min="6" max="6" width="17.17969" customWidth="1"/>
-    <col min="7" max="7" width="15.36328" customWidth="1"/>
-    <col min="8" max="8" width="17.17969" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984"/>
+    <col min="2" max="2" customWidth="true" width="17.54297"/>
+    <col min="3" max="3" customWidth="true" width="17.36328"/>
+    <col min="4" max="5" customWidth="true" width="17.26953"/>
+    <col min="6" max="6" customWidth="true" width="17.17969"/>
+    <col min="7" max="7" customWidth="true" width="15.36328"/>
+    <col min="8" max="8" customWidth="true" width="17.17969"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.5">
       <c r="A1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>109</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>113</v>
       </c>
     </row>
     <row r="2" ht="14.5">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>115</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3261,10 +3311,10 @@
       </c>
     </row>
     <row r="3" ht="14.5">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>119</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3275,10 +3325,10 @@
       </c>
     </row>
     <row r="4" ht="14.5">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>123</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3289,10 +3339,10 @@
       </c>
     </row>
     <row r="5" ht="14.5">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>127</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3303,10 +3353,10 @@
       </c>
     </row>
     <row r="6" ht="14.5">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3317,10 +3367,10 @@
       </c>
     </row>
     <row r="7" ht="14.5">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>135</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3331,10 +3381,10 @@
       </c>
     </row>
     <row r="8" ht="14.5">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>138</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3345,10 +3395,10 @@
       </c>
     </row>
     <row r="9" ht="14.5">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>143</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3359,10 +3409,10 @@
       </c>
     </row>
     <row r="10" ht="14.5">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>147</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3373,10 +3423,10 @@
       </c>
     </row>
     <row r="11" ht="14.5">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>151</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3387,10 +3437,10 @@
       </c>
     </row>
     <row r="12" ht="14.5">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>154</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>155</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3401,10 +3451,10 @@
       </c>
     </row>
     <row r="13" ht="14.5">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>159</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3415,10 +3465,10 @@
       </c>
     </row>
     <row r="14" ht="14.5">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>163</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3429,10 +3479,10 @@
       </c>
     </row>
     <row r="15" ht="14.5">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>166</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3443,10 +3493,10 @@
       </c>
     </row>
     <row r="16" ht="14.5">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>171</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3457,10 +3507,10 @@
       </c>
     </row>
     <row r="17" ht="14.5">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3471,10 +3521,10 @@
       </c>
     </row>
     <row r="18" ht="14.5">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3485,10 +3535,10 @@
       </c>
     </row>
     <row r="19" ht="14.5">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>182</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>183</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3499,10 +3549,10 @@
       </c>
     </row>
     <row r="20" ht="14.5">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>186</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>187</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3513,10 +3563,10 @@
       </c>
     </row>
     <row r="21" ht="14.5">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>190</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>191</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3527,10 +3577,10 @@
       </c>
     </row>
     <row r="22" ht="14.5">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>195</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3541,10 +3591,10 @@
       </c>
     </row>
     <row r="23" ht="14.5">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>198</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>199</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3555,10 +3605,10 @@
       </c>
     </row>
     <row r="24" ht="14.5">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>202</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>203</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3569,10 +3619,10 @@
       </c>
     </row>
     <row r="25" ht="14.5">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>207</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3583,10 +3633,10 @@
       </c>
     </row>
     <row r="26" ht="14.5">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>211</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3597,10 +3647,10 @@
       </c>
     </row>
     <row r="27" ht="14.5">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>215</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -3611,13 +3661,13 @@
       </c>
     </row>
     <row r="28" ht="14.5">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>218</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>219</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="13" t="s">
         <v>220</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -3625,10 +3675,10 @@
       </c>
     </row>
     <row r="29" ht="14.5">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>222</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>223</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3639,10 +3689,10 @@
       </c>
     </row>
     <row r="30" ht="14.5">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>227</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3653,10 +3703,10 @@
       </c>
     </row>
     <row r="31" ht="14.5">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>230</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>231</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3667,10 +3717,10 @@
       </c>
     </row>
     <row r="32" ht="14.5">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>234</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>235</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3681,10 +3731,10 @@
       </c>
     </row>
     <row r="33" ht="14.5">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>238</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>239</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3695,10 +3745,10 @@
       </c>
     </row>
     <row r="34" ht="14.5">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>242</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>243</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3709,10 +3759,10 @@
       </c>
     </row>
     <row r="35" ht="14.5">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>247</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3723,10 +3773,10 @@
       </c>
     </row>
     <row r="36" ht="14.5">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>250</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>251</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3737,10 +3787,10 @@
       </c>
     </row>
     <row r="37" ht="14.5">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>254</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>255</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3751,10 +3801,10 @@
       </c>
     </row>
     <row r="38" ht="14.5">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>259</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3765,10 +3815,10 @@
       </c>
     </row>
     <row r="39" ht="14.5">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>262</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>263</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3779,10 +3829,10 @@
       </c>
     </row>
     <row r="40" ht="14.5">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>266</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>267</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3793,10 +3843,10 @@
       </c>
     </row>
     <row r="41" ht="14.5">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>270</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3807,10 +3857,10 @@
       </c>
     </row>
     <row r="42" ht="14.5">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>275</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3821,10 +3871,10 @@
       </c>
     </row>
     <row r="43" ht="14.5">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>279</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3835,10 +3885,10 @@
       </c>
     </row>
     <row r="44" ht="14.5">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>282</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>283</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3849,10 +3899,10 @@
       </c>
     </row>
     <row r="45" ht="14.5">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>286</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>287</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3863,10 +3913,10 @@
       </c>
     </row>
     <row r="46" ht="14.5">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>290</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>291</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3877,10 +3927,10 @@
       </c>
     </row>
     <row r="47" ht="14.5">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>294</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>295</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3891,10 +3941,10 @@
       </c>
     </row>
     <row r="48" ht="14.5">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>298</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>299</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3905,10 +3955,10 @@
       </c>
     </row>
     <row r="49" ht="14.5">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>302</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>303</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3919,10 +3969,10 @@
       </c>
     </row>
     <row r="50" ht="14.5">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>306</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>307</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3933,10 +3983,10 @@
       </c>
     </row>
     <row r="51" ht="14.5">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>311</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3947,10 +3997,10 @@
       </c>
     </row>
     <row r="52" ht="14.5">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>314</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>315</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -3961,10 +4011,10 @@
       </c>
     </row>
     <row r="53" ht="14.5">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>318</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>319</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -3975,10 +4025,10 @@
       </c>
     </row>
     <row r="54" ht="14.5">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>322</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>323</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -3989,10 +4039,10 @@
       </c>
     </row>
     <row r="55" ht="14.5">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>326</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>327</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -4003,10 +4053,10 @@
       </c>
     </row>
     <row r="56" ht="14.5">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>330</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>331</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -4017,10 +4067,10 @@
       </c>
     </row>
     <row r="57" ht="14.5">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>334</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>335</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -4031,10 +4081,10 @@
       </c>
     </row>
     <row r="58" ht="14.5">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>338</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>339</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -4045,10 +4095,10 @@
       </c>
     </row>
     <row r="59" ht="14.5">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>342</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>343</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -4059,10 +4109,10 @@
       </c>
     </row>
     <row r="60" ht="14.5">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>346</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>347</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -4073,10 +4123,10 @@
       </c>
     </row>
     <row r="61" ht="14.5">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>350</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>351</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -4087,10 +4137,10 @@
       </c>
     </row>
     <row r="62" ht="14.5">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>354</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>355</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -4101,10 +4151,10 @@
       </c>
     </row>
     <row r="63" ht="14.5">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>358</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>359</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4115,10 +4165,10 @@
       </c>
     </row>
     <row r="64" ht="14.5">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>362</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>363</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4129,10 +4179,10 @@
       </c>
     </row>
     <row r="65" ht="14.5">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>366</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>367</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4143,10 +4193,10 @@
       </c>
     </row>
     <row r="66" ht="14.5">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>370</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>371</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4157,10 +4207,10 @@
       </c>
     </row>
     <row r="67" ht="14.5">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>374</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>375</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4171,10 +4221,10 @@
       </c>
     </row>
     <row r="68" ht="14.5">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>378</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>379</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4185,10 +4235,10 @@
       </c>
     </row>
     <row r="69" ht="14.5">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>383</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4199,10 +4249,10 @@
       </c>
     </row>
     <row r="70" ht="14.5">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>387</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4213,10 +4263,10 @@
       </c>
     </row>
     <row r="71" ht="14.5">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>390</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>391</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4227,10 +4277,10 @@
       </c>
     </row>
     <row r="72" ht="14.5">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>395</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4241,10 +4291,10 @@
       </c>
     </row>
     <row r="73" ht="14.5">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>399</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4255,10 +4305,10 @@
       </c>
     </row>
     <row r="74" ht="14.5">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>403</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4269,10 +4319,10 @@
       </c>
     </row>
     <row r="75" ht="14.5">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>406</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>407</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4283,10 +4333,10 @@
       </c>
     </row>
     <row r="76" ht="14.5">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>410</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>411</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4297,10 +4347,10 @@
       </c>
     </row>
     <row r="77" ht="14.5">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>414</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>415</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4311,10 +4361,10 @@
       </c>
     </row>
     <row r="78" ht="14.5">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>418</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>419</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4325,10 +4375,10 @@
       </c>
     </row>
     <row r="79" ht="14.5">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>423</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4339,10 +4389,10 @@
       </c>
     </row>
     <row r="80" ht="14.5">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>427</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4353,10 +4403,10 @@
       </c>
     </row>
     <row r="81" ht="14.5">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>430</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>431</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4367,10 +4417,10 @@
       </c>
     </row>
     <row r="82" ht="14.5">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>435</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4381,10 +4431,10 @@
       </c>
     </row>
     <row r="83" ht="14.5">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>438</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>439</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4395,10 +4445,10 @@
       </c>
     </row>
     <row r="84" ht="14.5">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>443</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4409,10 +4459,10 @@
       </c>
     </row>
     <row r="85" ht="14.5">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>447</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4423,10 +4473,10 @@
       </c>
     </row>
     <row r="86" ht="14.5">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>450</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>451</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4437,10 +4487,10 @@
       </c>
     </row>
     <row r="87" ht="14.5">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>454</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>455</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4451,10 +4501,10 @@
       </c>
     </row>
     <row r="88" ht="14.5">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>458</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>459</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4465,10 +4515,10 @@
       </c>
     </row>
     <row r="89" ht="14.5">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>463</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4479,10 +4529,10 @@
       </c>
     </row>
     <row r="90" ht="14.5">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>466</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>467</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4493,10 +4543,10 @@
       </c>
     </row>
     <row r="91" ht="14.5">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>470</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>471</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4507,10 +4557,10 @@
       </c>
     </row>
     <row r="92" ht="14.5">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>474</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>475</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4521,10 +4571,10 @@
       </c>
     </row>
     <row r="93" ht="14.5">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>478</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>479</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4535,10 +4585,10 @@
       </c>
     </row>
     <row r="94" ht="14.5">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>483</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4549,10 +4599,10 @@
       </c>
     </row>
     <row r="95" ht="14.5">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>486</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>487</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4563,10 +4613,10 @@
       </c>
     </row>
     <row r="96" ht="14.5">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>491</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4577,10 +4627,10 @@
       </c>
     </row>
     <row r="97" ht="14.5">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>494</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>495</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4591,10 +4641,10 @@
       </c>
     </row>
     <row r="98" ht="14.5">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>498</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>499</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4605,10 +4655,10 @@
       </c>
     </row>
     <row r="99" ht="14.5">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>502</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>503</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4619,10 +4669,10 @@
       </c>
     </row>
     <row r="100" ht="14.5">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>506</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>507</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4633,10 +4683,10 @@
       </c>
     </row>
     <row r="101" ht="14.5">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>510</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>511</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4647,10 +4697,10 @@
       </c>
     </row>
     <row r="102" ht="14.5">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>514</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>515</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4661,10 +4711,10 @@
       </c>
     </row>
     <row r="103" ht="14.5">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>518</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>519</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4675,10 +4725,10 @@
       </c>
     </row>
     <row r="104" ht="14.5">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>522</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>523</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4689,10 +4739,10 @@
       </c>
     </row>
     <row r="105" ht="14.5">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>526</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>527</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4703,10 +4753,10 @@
       </c>
     </row>
     <row r="106" ht="14.5">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>530</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>531</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4717,10 +4767,10 @@
       </c>
     </row>
     <row r="107" ht="14.5">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>534</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>535</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4731,10 +4781,10 @@
       </c>
     </row>
     <row r="108" ht="14.5">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>538</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>539</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4745,10 +4795,10 @@
       </c>
     </row>
     <row r="109" ht="14.5">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>542</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>543</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4759,10 +4809,10 @@
       </c>
     </row>
     <row r="110" ht="14.5">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>546</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>547</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4773,10 +4823,10 @@
       </c>
     </row>
     <row r="111" ht="14.5">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>550</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>551</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4787,10 +4837,10 @@
       </c>
     </row>
     <row r="112" ht="14.5">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>555</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4801,10 +4851,10 @@
       </c>
     </row>
     <row r="113" ht="14.5">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>558</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>559</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4815,10 +4865,10 @@
       </c>
     </row>
     <row r="114" ht="14.5">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>562</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>563</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4829,10 +4879,10 @@
       </c>
     </row>
     <row r="115" ht="14.5">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>566</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>567</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4843,10 +4893,10 @@
       </c>
     </row>
     <row r="116" ht="14.5">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>570</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>571</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4857,10 +4907,10 @@
       </c>
     </row>
     <row r="117" ht="14.5">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>574</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>575</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4871,10 +4921,10 @@
       </c>
     </row>
     <row r="118" ht="14.5">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>578</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>579</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4885,10 +4935,10 @@
       </c>
     </row>
     <row r="119" ht="14.5">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>582</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>583</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4899,10 +4949,10 @@
       </c>
     </row>
     <row r="120" ht="14.5">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>586</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>587</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4913,10 +4963,10 @@
       </c>
     </row>
     <row r="121" ht="14.5">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>590</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>591</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4927,10 +4977,10 @@
       </c>
     </row>
     <row r="122" ht="14.5">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>594</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>595</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4941,10 +4991,10 @@
       </c>
     </row>
     <row r="123" ht="14.5">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>598</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>599</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -4955,10 +5005,10 @@
       </c>
     </row>
     <row r="124" ht="14.5">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>602</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>603</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -4969,10 +5019,10 @@
       </c>
     </row>
     <row r="125" ht="14.5">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>606</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>607</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -4983,10 +5033,10 @@
       </c>
     </row>
     <row r="126" ht="14.5">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>610</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>611</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -4997,10 +5047,10 @@
       </c>
     </row>
     <row r="127" ht="14.5">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>614</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>615</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -5011,10 +5061,10 @@
       </c>
     </row>
     <row r="128" ht="14.5">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>618</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>619</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -5025,10 +5075,10 @@
       </c>
     </row>
     <row r="129" ht="14.5">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>622</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>623</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -5039,10 +5089,10 @@
       </c>
     </row>
     <row r="130" ht="14.5">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>626</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>627</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -5053,10 +5103,10 @@
       </c>
     </row>
     <row r="131" ht="14.5">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>630</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>631</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -5067,10 +5117,10 @@
       </c>
     </row>
     <row r="132" ht="14.5">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>634</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>635</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -5081,10 +5131,10 @@
       </c>
     </row>
     <row r="133" ht="14.5">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>638</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>639</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -5095,10 +5145,10 @@
       </c>
     </row>
     <row r="134" ht="14.5">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>642</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>643</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -5109,10 +5159,10 @@
       </c>
     </row>
     <row r="135" ht="14.5">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>646</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>647</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5123,10 +5173,10 @@
       </c>
     </row>
     <row r="136" ht="14.5">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>650</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>651</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5137,10 +5187,10 @@
       </c>
     </row>
     <row r="137" ht="14.5">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>654</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>655</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5151,10 +5201,10 @@
       </c>
     </row>
     <row r="138" ht="14.5">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>658</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>659</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5165,10 +5215,10 @@
       </c>
     </row>
     <row r="139" ht="14.5">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>662</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>663</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5179,10 +5229,10 @@
       </c>
     </row>
     <row r="140" ht="14.5">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>666</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>667</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5193,10 +5243,10 @@
       </c>
     </row>
     <row r="141" ht="14.5">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>670</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>671</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5207,10 +5257,10 @@
       </c>
     </row>
     <row r="142" ht="14.5">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>674</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>675</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5221,10 +5271,10 @@
       </c>
     </row>
     <row r="143" ht="14.5">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>678</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>679</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5235,10 +5285,10 @@
       </c>
     </row>
     <row r="144" ht="14.5">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>682</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>683</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5249,10 +5299,10 @@
       </c>
     </row>
     <row r="145" ht="14.5">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>686</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>687</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5263,10 +5313,10 @@
       </c>
     </row>
     <row r="146" ht="14.5">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>690</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>691</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5277,10 +5327,10 @@
       </c>
     </row>
     <row r="147" ht="14.5">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>694</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>695</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5291,10 +5341,10 @@
       </c>
     </row>
     <row r="148" ht="14.5">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>698</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>699</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5305,10 +5355,10 @@
       </c>
     </row>
     <row r="149" ht="14.5">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>702</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5319,10 +5369,10 @@
       </c>
     </row>
     <row r="150" ht="14.5">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>706</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>707</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5333,10 +5383,10 @@
       </c>
     </row>
     <row r="151" ht="14.5">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>710</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>711</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5347,10 +5397,10 @@
       </c>
     </row>
     <row r="152" ht="14.5">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>714</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5361,7 +5411,7 @@
       </c>
     </row>
     <row r="153" ht="14.5">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>718</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5372,7 +5422,7 @@
       </c>
     </row>
     <row r="154" ht="14.5">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>721</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5383,7 +5433,7 @@
       </c>
     </row>
     <row r="155" ht="14.5">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>724</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5394,7 +5444,7 @@
       </c>
     </row>
     <row r="156" ht="14.5">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>727</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5405,7 +5455,7 @@
       </c>
     </row>
     <row r="157" ht="14.5">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>730</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5416,7 +5466,7 @@
       </c>
     </row>
     <row r="158" ht="14.5">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>733</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -1,27 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\workspace\testing\animalBiome_Automation\src\test\resources\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3090" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3690"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
     <sheet name="PET_NAME" sheetId="2" r:id="rId2"/>
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A7:G12"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="830">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2396,39 +2392,128 @@
     <t>Nexra</t>
   </si>
   <si>
-    <t>Charlie96</t>
-  </si>
-  <si>
-    <t>Milo66</t>
-  </si>
-  <si>
-    <t>Taffy64</t>
-  </si>
-  <si>
-    <t>Cutie51</t>
-  </si>
-  <si>
-    <t>Cinder51</t>
-  </si>
-  <si>
-    <t>pony43</t>
-  </si>
-  <si>
-    <t>fury40</t>
-  </si>
-  <si>
-    <t>Rabbit40</t>
-  </si>
-  <si>
-    <t>Sheep35</t>
+    <t>DY6HJV</t>
+  </si>
+  <si>
+    <t>EXXEFV</t>
+  </si>
+  <si>
+    <t>G7KNYD</t>
+  </si>
+  <si>
+    <t>EAYFTE</t>
+  </si>
+  <si>
+    <t>ECXR37</t>
+  </si>
+  <si>
+    <t>4NUXJE</t>
+  </si>
+  <si>
+    <t>PCKRDP</t>
+  </si>
+  <si>
+    <t>MMAYCA</t>
+  </si>
+  <si>
+    <t>HCXJMR</t>
+  </si>
+  <si>
+    <t>JFGPXE</t>
+  </si>
+  <si>
+    <t>VDJUJA</t>
+  </si>
+  <si>
+    <t>RPECGA</t>
+  </si>
+  <si>
+    <t>CNAEUM</t>
+  </si>
+  <si>
+    <t>MVJDMF</t>
+  </si>
+  <si>
+    <t>EFE7VM</t>
+  </si>
+  <si>
+    <t>CAC6PG</t>
+  </si>
+  <si>
+    <t>7MFKA4</t>
+  </si>
+  <si>
+    <t>CXVHFJ</t>
+  </si>
+  <si>
+    <t>HHXGKR</t>
+  </si>
+  <si>
+    <t>KGE36H</t>
+  </si>
+  <si>
+    <t>9CYHKC</t>
+  </si>
+  <si>
+    <t>7KDJJH</t>
+  </si>
+  <si>
+    <t>7CFRFV</t>
+  </si>
+  <si>
+    <t>ARP4NF</t>
+  </si>
+  <si>
+    <t>9HCNXK</t>
+  </si>
+  <si>
+    <t>YRDARC</t>
+  </si>
+  <si>
+    <t>RJURVR</t>
+  </si>
+  <si>
+    <t>9NDXHD</t>
+  </si>
+  <si>
+    <t>K9CFFU</t>
+  </si>
+  <si>
+    <t>T3DVGH</t>
+  </si>
+  <si>
+    <t>DRGYYX</t>
+  </si>
+  <si>
+    <t>FHUUPV</t>
+  </si>
+  <si>
+    <t>J7A3FD</t>
+  </si>
+  <si>
+    <t>EGJN4C</t>
+  </si>
+  <si>
+    <t>EUHY7H</t>
+  </si>
+  <si>
+    <t>FRXMAG</t>
+  </si>
+  <si>
+    <t>TFV9UN</t>
+  </si>
+  <si>
+    <t>DARTH9</t>
+  </si>
+  <si>
+    <t>MYDFNX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2440,6 +2525,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2462,12 +2554,18 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2477,27 +2575,35 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2"/>
     <cellStyle name="Normal 3" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2506,10 +2612,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2641,7 +2747,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2665,11 +2770,10 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2678,13 +2782,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2760,7 +2864,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2780,34 +2883,35 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K81"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81641"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.45313"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.63281"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.17969"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.45313"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328"/>
-    <col min="12" max="16384" style="1" width="8.726563"/>
+    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2839,7 +2943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2856,7 +2960,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -2873,7 +2977,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -2890,7 +2994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -2907,7 +3011,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -2924,7 +3028,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
@@ -2941,7 +3045,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2958,7 +3062,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
@@ -2975,7 +3079,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
@@ -2992,7 +3096,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>55</v>
       </c>
@@ -3009,7 +3113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>60</v>
       </c>
@@ -3026,10 +3130,16 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
+      <c r="B13" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="C13" t="s">
+        <v>806</v>
+      </c>
       <c r="D13" s="2" t="s">
         <v>66</v>
       </c>
@@ -3037,10 +3147,16 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>68</v>
       </c>
+      <c r="B14" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C14" t="s">
+        <v>807</v>
+      </c>
       <c r="D14" s="2" t="s">
         <v>69</v>
       </c>
@@ -3048,10 +3164,16 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>71</v>
       </c>
+      <c r="B15" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="C15" t="s">
+        <v>808</v>
+      </c>
       <c r="D15" s="2" t="s">
         <v>72</v>
       </c>
@@ -3059,10 +3181,16 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="B16" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="C16" t="s">
+        <v>809</v>
+      </c>
       <c r="D16" s="2" t="s">
         <v>75</v>
       </c>
@@ -3070,10 +3198,16 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="B17" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C17" t="s">
+        <v>810</v>
+      </c>
       <c r="D17" s="11" t="s">
         <v>78</v>
       </c>
@@ -3081,7 +3215,13 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>791</v>
+      </c>
+      <c r="C18" t="s">
+        <v>811</v>
+      </c>
       <c r="D18" s="12" t="s">
         <v>80</v>
       </c>
@@ -3089,7 +3229,10 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>792</v>
+      </c>
       <c r="D19" s="1" t="s">
         <v>82</v>
       </c>
@@ -3097,210 +3240,309 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>793</v>
+      </c>
+      <c r="D20" t="s">
+        <v>812</v>
+      </c>
       <c r="E20" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>794</v>
+      </c>
+      <c r="D21" t="s">
+        <v>813</v>
+      </c>
       <c r="E21" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>795</v>
+      </c>
+      <c r="D22" t="s">
+        <v>814</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>796</v>
+      </c>
+      <c r="D23" t="s">
+        <v>815</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>797</v>
+      </c>
+      <c r="D24" t="s">
+        <v>816</v>
+      </c>
       <c r="E24" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>798</v>
+      </c>
+      <c r="D25" t="s">
+        <v>817</v>
+      </c>
       <c r="E25" s="15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>799</v>
+      </c>
+      <c r="D26" t="s">
+        <v>818</v>
+      </c>
       <c r="E26" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>800</v>
+      </c>
+      <c r="D27" t="s">
+        <v>819</v>
+      </c>
       <c r="E27" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E28" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E29" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E30" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E31" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E32" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="78">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E33" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E34" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E35" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E36" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E37" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E38" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E39" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E40" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E41" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E42" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="78" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F78" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F81" s="3"/>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.45313"/>
-    <col min="3" max="3" customWidth="true" width="35.63281"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.72656"/>
-    <col min="6" max="6" customWidth="true" width="32.17969"/>
-    <col min="7" max="7" customWidth="true" width="33.63281"/>
-    <col min="8" max="8" customWidth="true" width="31.26953"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="35.6328125" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.7265625" customWidth="1"/>
+    <col min="6" max="6" width="32.1796875" customWidth="1"/>
+    <col min="7" max="7" width="33.6328125" customWidth="1"/>
+    <col min="8" max="8" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>97</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>98</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>99</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>100</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>101</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>103</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>105</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>105</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>105</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>105</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>105</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>105</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>105</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="0"/>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984"/>
-    <col min="2" max="2" customWidth="true" width="17.54297"/>
-    <col min="3" max="3" customWidth="true" width="17.36328"/>
-    <col min="4" max="5" customWidth="true" width="17.26953"/>
-    <col min="6" max="6" customWidth="true" width="17.17969"/>
-    <col min="7" max="7" customWidth="true" width="15.36328"/>
-    <col min="8" max="8" customWidth="true" width="17.17969"/>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" customWidth="1"/>
+    <col min="4" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>107</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>108</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>109</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>110</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>111</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>112</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="2" ht="14.5">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>115</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3310,11 +3552,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" ht="14.5">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>118</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>119</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3324,11 +3566,11 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" ht="14.5">
-      <c r="A4" t="s" s="0">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>122</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>123</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3338,11 +3580,11 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" ht="14.5">
-      <c r="A5" t="s" s="0">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>126</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>127</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3352,11 +3594,11 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" ht="14.5">
-      <c r="A6" t="s" s="0">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>130</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3366,11 +3608,11 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" ht="14.5">
-      <c r="A7" t="s" s="0">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>134</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>135</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3380,11 +3622,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" ht="14.5">
-      <c r="A8" t="s" s="0">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>138</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3394,11 +3636,11 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" ht="14.5">
-      <c r="A9" t="s" s="0">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>142</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>143</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3408,11 +3650,11 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" ht="14.5">
-      <c r="A10" t="s" s="0">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>146</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>147</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3422,11 +3664,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" ht="14.5">
-      <c r="A11" t="s" s="0">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>150</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>151</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3436,11 +3678,11 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" ht="14.5">
-      <c r="A12" t="s" s="0">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>154</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>155</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3450,11 +3692,11 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" ht="14.5">
-      <c r="A13" t="s" s="0">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>158</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>159</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3464,11 +3706,11 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" ht="14.5">
-      <c r="A14" t="s" s="0">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>162</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>163</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3478,11 +3720,11 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" ht="14.5">
-      <c r="A15" t="s" s="0">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>166</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3492,11 +3734,11 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" ht="14.5">
-      <c r="A16" t="s" s="0">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>170</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>171</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3506,11 +3748,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" ht="14.5">
-      <c r="A17" t="s" s="0">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>174</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3520,11 +3762,11 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" ht="14.5">
-      <c r="A18" t="s" s="0">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>178</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>179</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3534,11 +3776,11 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" ht="14.5">
-      <c r="A19" t="s" s="0">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>182</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>183</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3548,11 +3790,11 @@
         <v>185</v>
       </c>
     </row>
-    <row r="20" ht="14.5">
-      <c r="A20" t="s" s="0">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>186</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>187</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3562,11 +3804,11 @@
         <v>189</v>
       </c>
     </row>
-    <row r="21" ht="14.5">
-      <c r="A21" t="s" s="0">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>190</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B21" t="s">
         <v>191</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3576,11 +3818,11 @@
         <v>193</v>
       </c>
     </row>
-    <row r="22" ht="14.5">
-      <c r="A22" t="s" s="0">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>194</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="B22" t="s">
         <v>195</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3590,11 +3832,11 @@
         <v>197</v>
       </c>
     </row>
-    <row r="23" ht="14.5">
-      <c r="A23" t="s" s="0">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>198</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>199</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3604,11 +3846,11 @@
         <v>201</v>
       </c>
     </row>
-    <row r="24" ht="14.5">
-      <c r="A24" t="s" s="0">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>202</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>203</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3618,11 +3860,11 @@
         <v>205</v>
       </c>
     </row>
-    <row r="25" ht="14.5">
-      <c r="A25" t="s" s="0">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>206</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B25" t="s">
         <v>207</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3632,11 +3874,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="26" ht="14.5">
-      <c r="A26" t="s" s="0">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>210</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>211</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3646,11 +3888,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="27" ht="14.5">
-      <c r="A27" t="s" s="0">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>214</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>215</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -3660,11 +3902,11 @@
         <v>217</v>
       </c>
     </row>
-    <row r="28" ht="14.5">
-      <c r="A28" t="s" s="0">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>218</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>219</v>
       </c>
       <c r="C28" s="13" t="s">
@@ -3674,11 +3916,11 @@
         <v>221</v>
       </c>
     </row>
-    <row r="29" ht="14.5">
-      <c r="A29" t="s" s="0">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>222</v>
       </c>
-      <c r="B29" t="s" s="0">
+      <c r="B29" t="s">
         <v>223</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -3688,11 +3930,11 @@
         <v>225</v>
       </c>
     </row>
-    <row r="30" ht="14.5">
-      <c r="A30" t="s" s="0">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>226</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="B30" t="s">
         <v>227</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3702,11 +3944,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="31" ht="14.5">
-      <c r="A31" t="s" s="0">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>230</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>231</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3716,11 +3958,11 @@
         <v>233</v>
       </c>
     </row>
-    <row r="32" ht="14.5">
-      <c r="A32" t="s" s="0">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>234</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>235</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3730,11 +3972,11 @@
         <v>237</v>
       </c>
     </row>
-    <row r="33" ht="14.5">
-      <c r="A33" t="s" s="0">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>238</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>239</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3744,11 +3986,11 @@
         <v>241</v>
       </c>
     </row>
-    <row r="34" ht="14.5">
-      <c r="A34" t="s" s="0">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>242</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>243</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -3758,11 +4000,11 @@
         <v>245</v>
       </c>
     </row>
-    <row r="35" ht="14.5">
-      <c r="A35" t="s" s="0">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>246</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B35" t="s">
         <v>247</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3772,11 +4014,11 @@
         <v>249</v>
       </c>
     </row>
-    <row r="36" ht="14.5">
-      <c r="A36" t="s" s="0">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>250</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="B36" t="s">
         <v>251</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -3786,11 +4028,11 @@
         <v>253</v>
       </c>
     </row>
-    <row r="37" ht="14.5">
-      <c r="A37" t="s" s="0">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>254</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="B37" t="s">
         <v>255</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -3800,11 +4042,11 @@
         <v>257</v>
       </c>
     </row>
-    <row r="38" ht="14.5">
-      <c r="A38" t="s" s="0">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>258</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B38" t="s">
         <v>259</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3814,11 +4056,11 @@
         <v>261</v>
       </c>
     </row>
-    <row r="39" ht="14.5">
-      <c r="A39" t="s" s="0">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>262</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="B39" t="s">
         <v>263</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -3828,11 +4070,11 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" ht="14.5">
-      <c r="A40" t="s" s="0">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>266</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="B40" t="s">
         <v>267</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -3842,11 +4084,11 @@
         <v>269</v>
       </c>
     </row>
-    <row r="41" ht="14.5">
-      <c r="A41" t="s" s="0">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>270</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="B41" t="s">
         <v>271</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3856,11 +4098,11 @@
         <v>273</v>
       </c>
     </row>
-    <row r="42" ht="14.5">
-      <c r="A42" t="s" s="0">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>274</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="B42" t="s">
         <v>275</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -3870,11 +4112,11 @@
         <v>277</v>
       </c>
     </row>
-    <row r="43" ht="14.5">
-      <c r="A43" t="s" s="0">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>278</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="B43" t="s">
         <v>279</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -3884,11 +4126,11 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" ht="14.5">
-      <c r="A44" t="s" s="0">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>282</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B44" t="s">
         <v>283</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -3898,11 +4140,11 @@
         <v>285</v>
       </c>
     </row>
-    <row r="45" ht="14.5">
-      <c r="A45" t="s" s="0">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>286</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="B45" t="s">
         <v>287</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3912,11 +4154,11 @@
         <v>289</v>
       </c>
     </row>
-    <row r="46" ht="14.5">
-      <c r="A46" t="s" s="0">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>290</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="B46" t="s">
         <v>291</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3926,11 +4168,11 @@
         <v>293</v>
       </c>
     </row>
-    <row r="47" ht="14.5">
-      <c r="A47" t="s" s="0">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>294</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B47" t="s">
         <v>295</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -3940,11 +4182,11 @@
         <v>297</v>
       </c>
     </row>
-    <row r="48" ht="14.5">
-      <c r="A48" t="s" s="0">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>298</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="B48" t="s">
         <v>299</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -3954,11 +4196,11 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" ht="14.5">
-      <c r="A49" t="s" s="0">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>302</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="B49" t="s">
         <v>303</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -3968,11 +4210,11 @@
         <v>305</v>
       </c>
     </row>
-    <row r="50" ht="14.5">
-      <c r="A50" t="s" s="0">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>306</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="B50" t="s">
         <v>307</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -3982,11 +4224,11 @@
         <v>309</v>
       </c>
     </row>
-    <row r="51" ht="14.5">
-      <c r="A51" t="s" s="0">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>310</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="B51" t="s">
         <v>311</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -3996,11 +4238,11 @@
         <v>313</v>
       </c>
     </row>
-    <row r="52" ht="14.5">
-      <c r="A52" t="s" s="0">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>314</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="B52" t="s">
         <v>315</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -4010,11 +4252,11 @@
         <v>317</v>
       </c>
     </row>
-    <row r="53" ht="14.5">
-      <c r="A53" t="s" s="0">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>318</v>
       </c>
-      <c r="B53" t="s" s="0">
+      <c r="B53" t="s">
         <v>319</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -4024,11 +4266,11 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" ht="14.5">
-      <c r="A54" t="s" s="0">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>322</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="B54" t="s">
         <v>323</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -4038,11 +4280,11 @@
         <v>325</v>
       </c>
     </row>
-    <row r="55" ht="14.5">
-      <c r="A55" t="s" s="0">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>326</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s">
         <v>327</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -4052,11 +4294,11 @@
         <v>329</v>
       </c>
     </row>
-    <row r="56" ht="14.5">
-      <c r="A56" t="s" s="0">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>330</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="B56" t="s">
         <v>331</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -4066,11 +4308,11 @@
         <v>333</v>
       </c>
     </row>
-    <row r="57" ht="14.5">
-      <c r="A57" t="s" s="0">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>334</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B57" t="s">
         <v>335</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -4080,11 +4322,11 @@
         <v>337</v>
       </c>
     </row>
-    <row r="58" ht="14.5">
-      <c r="A58" t="s" s="0">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>338</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="B58" t="s">
         <v>339</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -4094,11 +4336,11 @@
         <v>341</v>
       </c>
     </row>
-    <row r="59" ht="14.5">
-      <c r="A59" t="s" s="0">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>342</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="B59" t="s">
         <v>343</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -4108,11 +4350,11 @@
         <v>345</v>
       </c>
     </row>
-    <row r="60" ht="14.5">
-      <c r="A60" t="s" s="0">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>346</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="B60" t="s">
         <v>347</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -4122,11 +4364,11 @@
         <v>349</v>
       </c>
     </row>
-    <row r="61" ht="14.5">
-      <c r="A61" t="s" s="0">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>350</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="B61" t="s">
         <v>351</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -4136,11 +4378,11 @@
         <v>353</v>
       </c>
     </row>
-    <row r="62" ht="14.5">
-      <c r="A62" t="s" s="0">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>354</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="B62" t="s">
         <v>355</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -4150,11 +4392,11 @@
         <v>357</v>
       </c>
     </row>
-    <row r="63" ht="14.5">
-      <c r="A63" t="s" s="0">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>358</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="B63" t="s">
         <v>359</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4164,11 +4406,11 @@
         <v>361</v>
       </c>
     </row>
-    <row r="64" ht="14.5">
-      <c r="A64" t="s" s="0">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>362</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="B64" t="s">
         <v>363</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4178,11 +4420,11 @@
         <v>365</v>
       </c>
     </row>
-    <row r="65" ht="14.5">
-      <c r="A65" t="s" s="0">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>366</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="B65" t="s">
         <v>367</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4192,11 +4434,11 @@
         <v>369</v>
       </c>
     </row>
-    <row r="66" ht="14.5">
-      <c r="A66" t="s" s="0">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>370</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="B66" t="s">
         <v>371</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4206,11 +4448,11 @@
         <v>373</v>
       </c>
     </row>
-    <row r="67" ht="14.5">
-      <c r="A67" t="s" s="0">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>374</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="B67" t="s">
         <v>375</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4220,11 +4462,11 @@
         <v>377</v>
       </c>
     </row>
-    <row r="68" ht="14.5">
-      <c r="A68" t="s" s="0">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>378</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B68" t="s">
         <v>379</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4234,11 +4476,11 @@
         <v>381</v>
       </c>
     </row>
-    <row r="69" ht="14.5">
-      <c r="A69" t="s" s="0">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>382</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B69" t="s">
         <v>383</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4248,11 +4490,11 @@
         <v>385</v>
       </c>
     </row>
-    <row r="70" ht="14.5">
-      <c r="A70" t="s" s="0">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>386</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="B70" t="s">
         <v>387</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4262,11 +4504,11 @@
         <v>389</v>
       </c>
     </row>
-    <row r="71" ht="14.5">
-      <c r="A71" t="s" s="0">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>390</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="B71" t="s">
         <v>391</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4276,11 +4518,11 @@
         <v>393</v>
       </c>
     </row>
-    <row r="72" ht="14.5">
-      <c r="A72" t="s" s="0">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>394</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="B72" t="s">
         <v>395</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4290,11 +4532,11 @@
         <v>397</v>
       </c>
     </row>
-    <row r="73" ht="14.5">
-      <c r="A73" t="s" s="0">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>398</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="B73" t="s">
         <v>399</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4304,11 +4546,11 @@
         <v>401</v>
       </c>
     </row>
-    <row r="74" ht="14.5">
-      <c r="A74" t="s" s="0">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>402</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="B74" t="s">
         <v>403</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4318,11 +4560,11 @@
         <v>405</v>
       </c>
     </row>
-    <row r="75" ht="14.5">
-      <c r="A75" t="s" s="0">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>406</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="B75" t="s">
         <v>407</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4332,11 +4574,11 @@
         <v>409</v>
       </c>
     </row>
-    <row r="76" ht="14.5">
-      <c r="A76" t="s" s="0">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>410</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B76" t="s">
         <v>411</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4346,11 +4588,11 @@
         <v>413</v>
       </c>
     </row>
-    <row r="77" ht="14.5">
-      <c r="A77" t="s" s="0">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>414</v>
       </c>
-      <c r="B77" t="s" s="0">
+      <c r="B77" t="s">
         <v>415</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4360,11 +4602,11 @@
         <v>417</v>
       </c>
     </row>
-    <row r="78" ht="14.5">
-      <c r="A78" t="s" s="0">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>418</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B78" t="s">
         <v>419</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4374,11 +4616,11 @@
         <v>421</v>
       </c>
     </row>
-    <row r="79" ht="14.5">
-      <c r="A79" t="s" s="0">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>422</v>
       </c>
-      <c r="B79" t="s" s="0">
+      <c r="B79" t="s">
         <v>423</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4388,11 +4630,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="80" ht="14.5">
-      <c r="A80" t="s" s="0">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>426</v>
       </c>
-      <c r="B80" t="s" s="0">
+      <c r="B80" t="s">
         <v>427</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4402,11 +4644,11 @@
         <v>429</v>
       </c>
     </row>
-    <row r="81" ht="14.5">
-      <c r="A81" t="s" s="0">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>430</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B81" t="s">
         <v>431</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4416,11 +4658,11 @@
         <v>433</v>
       </c>
     </row>
-    <row r="82" ht="14.5">
-      <c r="A82" t="s" s="0">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>434</v>
       </c>
-      <c r="B82" t="s" s="0">
+      <c r="B82" t="s">
         <v>435</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4430,11 +4672,11 @@
         <v>437</v>
       </c>
     </row>
-    <row r="83" ht="14.5">
-      <c r="A83" t="s" s="0">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>438</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B83" t="s">
         <v>439</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4444,11 +4686,11 @@
         <v>441</v>
       </c>
     </row>
-    <row r="84" ht="14.5">
-      <c r="A84" t="s" s="0">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>442</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B84" t="s">
         <v>443</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4458,11 +4700,11 @@
         <v>445</v>
       </c>
     </row>
-    <row r="85" ht="14.5">
-      <c r="A85" t="s" s="0">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>446</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="B85" t="s">
         <v>447</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4472,11 +4714,11 @@
         <v>449</v>
       </c>
     </row>
-    <row r="86" ht="14.5">
-      <c r="A86" t="s" s="0">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>450</v>
       </c>
-      <c r="B86" t="s" s="0">
+      <c r="B86" t="s">
         <v>451</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4486,11 +4728,11 @@
         <v>453</v>
       </c>
     </row>
-    <row r="87" ht="14.5">
-      <c r="A87" t="s" s="0">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>454</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="B87" t="s">
         <v>455</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4500,11 +4742,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="88" ht="14.5">
-      <c r="A88" t="s" s="0">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>458</v>
       </c>
-      <c r="B88" t="s" s="0">
+      <c r="B88" t="s">
         <v>459</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4514,11 +4756,11 @@
         <v>461</v>
       </c>
     </row>
-    <row r="89" ht="14.5">
-      <c r="A89" t="s" s="0">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>462</v>
       </c>
-      <c r="B89" t="s" s="0">
+      <c r="B89" t="s">
         <v>463</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4528,11 +4770,11 @@
         <v>465</v>
       </c>
     </row>
-    <row r="90" ht="14.5">
-      <c r="A90" t="s" s="0">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>466</v>
       </c>
-      <c r="B90" t="s" s="0">
+      <c r="B90" t="s">
         <v>467</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4542,11 +4784,11 @@
         <v>469</v>
       </c>
     </row>
-    <row r="91" ht="14.5">
-      <c r="A91" t="s" s="0">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>470</v>
       </c>
-      <c r="B91" t="s" s="0">
+      <c r="B91" t="s">
         <v>471</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4556,11 +4798,11 @@
         <v>473</v>
       </c>
     </row>
-    <row r="92" ht="14.5">
-      <c r="A92" t="s" s="0">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>474</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="B92" t="s">
         <v>475</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4570,11 +4812,11 @@
         <v>477</v>
       </c>
     </row>
-    <row r="93" ht="14.5">
-      <c r="A93" t="s" s="0">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>478</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B93" t="s">
         <v>479</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4584,11 +4826,11 @@
         <v>481</v>
       </c>
     </row>
-    <row r="94" ht="14.5">
-      <c r="A94" t="s" s="0">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>482</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="B94" t="s">
         <v>483</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4598,11 +4840,11 @@
         <v>485</v>
       </c>
     </row>
-    <row r="95" ht="14.5">
-      <c r="A95" t="s" s="0">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>486</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="B95" t="s">
         <v>487</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4612,11 +4854,11 @@
         <v>489</v>
       </c>
     </row>
-    <row r="96" ht="14.5">
-      <c r="A96" t="s" s="0">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>490</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="B96" t="s">
         <v>491</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4626,11 +4868,11 @@
         <v>493</v>
       </c>
     </row>
-    <row r="97" ht="14.5">
-      <c r="A97" t="s" s="0">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
         <v>494</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="B97" t="s">
         <v>495</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4640,11 +4882,11 @@
         <v>497</v>
       </c>
     </row>
-    <row r="98" ht="14.5">
-      <c r="A98" t="s" s="0">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
         <v>498</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="B98" t="s">
         <v>499</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4654,11 +4896,11 @@
         <v>501</v>
       </c>
     </row>
-    <row r="99" ht="14.5">
-      <c r="A99" t="s" s="0">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>502</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="B99" t="s">
         <v>503</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4668,11 +4910,11 @@
         <v>505</v>
       </c>
     </row>
-    <row r="100" ht="14.5">
-      <c r="A100" t="s" s="0">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>506</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="B100" t="s">
         <v>507</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4682,11 +4924,11 @@
         <v>509</v>
       </c>
     </row>
-    <row r="101" ht="14.5">
-      <c r="A101" t="s" s="0">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>510</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="B101" t="s">
         <v>511</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4696,11 +4938,11 @@
         <v>513</v>
       </c>
     </row>
-    <row r="102" ht="14.5">
-      <c r="A102" t="s" s="0">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>514</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="B102" t="s">
         <v>515</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4710,11 +4952,11 @@
         <v>517</v>
       </c>
     </row>
-    <row r="103" ht="14.5">
-      <c r="A103" t="s" s="0">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>518</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="B103" t="s">
         <v>519</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4724,11 +4966,11 @@
         <v>521</v>
       </c>
     </row>
-    <row r="104" ht="14.5">
-      <c r="A104" t="s" s="0">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
         <v>522</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="B104" t="s">
         <v>523</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4738,11 +4980,11 @@
         <v>525</v>
       </c>
     </row>
-    <row r="105" ht="14.5">
-      <c r="A105" t="s" s="0">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>526</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="B105" t="s">
         <v>527</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4752,11 +4994,11 @@
         <v>529</v>
       </c>
     </row>
-    <row r="106" ht="14.5">
-      <c r="A106" t="s" s="0">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
         <v>530</v>
       </c>
-      <c r="B106" t="s" s="0">
+      <c r="B106" t="s">
         <v>531</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -4766,11 +5008,11 @@
         <v>533</v>
       </c>
     </row>
-    <row r="107" ht="14.5">
-      <c r="A107" t="s" s="0">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
         <v>534</v>
       </c>
-      <c r="B107" t="s" s="0">
+      <c r="B107" t="s">
         <v>535</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -4780,11 +5022,11 @@
         <v>537</v>
       </c>
     </row>
-    <row r="108" ht="14.5">
-      <c r="A108" t="s" s="0">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
         <v>538</v>
       </c>
-      <c r="B108" t="s" s="0">
+      <c r="B108" t="s">
         <v>539</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4794,11 +5036,11 @@
         <v>541</v>
       </c>
     </row>
-    <row r="109" ht="14.5">
-      <c r="A109" t="s" s="0">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>542</v>
       </c>
-      <c r="B109" t="s" s="0">
+      <c r="B109" t="s">
         <v>543</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -4808,11 +5050,11 @@
         <v>545</v>
       </c>
     </row>
-    <row r="110" ht="14.5">
-      <c r="A110" t="s" s="0">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>546</v>
       </c>
-      <c r="B110" t="s" s="0">
+      <c r="B110" t="s">
         <v>547</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -4822,11 +5064,11 @@
         <v>549</v>
       </c>
     </row>
-    <row r="111" ht="14.5">
-      <c r="A111" t="s" s="0">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>550</v>
       </c>
-      <c r="B111" t="s" s="0">
+      <c r="B111" t="s">
         <v>551</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -4836,11 +5078,11 @@
         <v>553</v>
       </c>
     </row>
-    <row r="112" ht="14.5">
-      <c r="A112" t="s" s="0">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>554</v>
       </c>
-      <c r="B112" t="s" s="0">
+      <c r="B112" t="s">
         <v>555</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -4850,11 +5092,11 @@
         <v>557</v>
       </c>
     </row>
-    <row r="113" ht="14.5">
-      <c r="A113" t="s" s="0">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
         <v>558</v>
       </c>
-      <c r="B113" t="s" s="0">
+      <c r="B113" t="s">
         <v>559</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -4864,11 +5106,11 @@
         <v>561</v>
       </c>
     </row>
-    <row r="114" ht="14.5">
-      <c r="A114" t="s" s="0">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
         <v>562</v>
       </c>
-      <c r="B114" t="s" s="0">
+      <c r="B114" t="s">
         <v>563</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -4878,11 +5120,11 @@
         <v>565</v>
       </c>
     </row>
-    <row r="115" ht="14.5">
-      <c r="A115" t="s" s="0">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>566</v>
       </c>
-      <c r="B115" t="s" s="0">
+      <c r="B115" t="s">
         <v>567</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4892,11 +5134,11 @@
         <v>569</v>
       </c>
     </row>
-    <row r="116" ht="14.5">
-      <c r="A116" t="s" s="0">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>570</v>
       </c>
-      <c r="B116" t="s" s="0">
+      <c r="B116" t="s">
         <v>571</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -4906,11 +5148,11 @@
         <v>573</v>
       </c>
     </row>
-    <row r="117" ht="14.5">
-      <c r="A117" t="s" s="0">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>574</v>
       </c>
-      <c r="B117" t="s" s="0">
+      <c r="B117" t="s">
         <v>575</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -4920,11 +5162,11 @@
         <v>577</v>
       </c>
     </row>
-    <row r="118" ht="14.5">
-      <c r="A118" t="s" s="0">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
         <v>578</v>
       </c>
-      <c r="B118" t="s" s="0">
+      <c r="B118" t="s">
         <v>579</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4934,11 +5176,11 @@
         <v>581</v>
       </c>
     </row>
-    <row r="119" ht="14.5">
-      <c r="A119" t="s" s="0">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>582</v>
       </c>
-      <c r="B119" t="s" s="0">
+      <c r="B119" t="s">
         <v>583</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -4948,11 +5190,11 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" ht="14.5">
-      <c r="A120" t="s" s="0">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
         <v>586</v>
       </c>
-      <c r="B120" t="s" s="0">
+      <c r="B120" t="s">
         <v>587</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -4962,11 +5204,11 @@
         <v>589</v>
       </c>
     </row>
-    <row r="121" ht="14.5">
-      <c r="A121" t="s" s="0">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
         <v>590</v>
       </c>
-      <c r="B121" t="s" s="0">
+      <c r="B121" t="s">
         <v>591</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4976,11 +5218,11 @@
         <v>593</v>
       </c>
     </row>
-    <row r="122" ht="14.5">
-      <c r="A122" t="s" s="0">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>594</v>
       </c>
-      <c r="B122" t="s" s="0">
+      <c r="B122" t="s">
         <v>595</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -4990,11 +5232,11 @@
         <v>597</v>
       </c>
     </row>
-    <row r="123" ht="14.5">
-      <c r="A123" t="s" s="0">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
         <v>598</v>
       </c>
-      <c r="B123" t="s" s="0">
+      <c r="B123" t="s">
         <v>599</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -5004,11 +5246,11 @@
         <v>601</v>
       </c>
     </row>
-    <row r="124" ht="14.5">
-      <c r="A124" t="s" s="0">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
         <v>602</v>
       </c>
-      <c r="B124" t="s" s="0">
+      <c r="B124" t="s">
         <v>603</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -5018,11 +5260,11 @@
         <v>605</v>
       </c>
     </row>
-    <row r="125" ht="14.5">
-      <c r="A125" t="s" s="0">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
         <v>606</v>
       </c>
-      <c r="B125" t="s" s="0">
+      <c r="B125" t="s">
         <v>607</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -5032,11 +5274,11 @@
         <v>609</v>
       </c>
     </row>
-    <row r="126" ht="14.5">
-      <c r="A126" t="s" s="0">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>610</v>
       </c>
-      <c r="B126" t="s" s="0">
+      <c r="B126" t="s">
         <v>611</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -5046,11 +5288,11 @@
         <v>613</v>
       </c>
     </row>
-    <row r="127" ht="14.5">
-      <c r="A127" t="s" s="0">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
         <v>614</v>
       </c>
-      <c r="B127" t="s" s="0">
+      <c r="B127" t="s">
         <v>615</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -5060,11 +5302,11 @@
         <v>617</v>
       </c>
     </row>
-    <row r="128" ht="14.5">
-      <c r="A128" t="s" s="0">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>618</v>
       </c>
-      <c r="B128" t="s" s="0">
+      <c r="B128" t="s">
         <v>619</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -5074,11 +5316,11 @@
         <v>621</v>
       </c>
     </row>
-    <row r="129" ht="14.5">
-      <c r="A129" t="s" s="0">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>622</v>
       </c>
-      <c r="B129" t="s" s="0">
+      <c r="B129" t="s">
         <v>623</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -5088,11 +5330,11 @@
         <v>625</v>
       </c>
     </row>
-    <row r="130" ht="14.5">
-      <c r="A130" t="s" s="0">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>626</v>
       </c>
-      <c r="B130" t="s" s="0">
+      <c r="B130" t="s">
         <v>627</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -5102,11 +5344,11 @@
         <v>629</v>
       </c>
     </row>
-    <row r="131" ht="14.5">
-      <c r="A131" t="s" s="0">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
         <v>630</v>
       </c>
-      <c r="B131" t="s" s="0">
+      <c r="B131" t="s">
         <v>631</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -5116,11 +5358,11 @@
         <v>633</v>
       </c>
     </row>
-    <row r="132" ht="14.5">
-      <c r="A132" t="s" s="0">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
         <v>634</v>
       </c>
-      <c r="B132" t="s" s="0">
+      <c r="B132" t="s">
         <v>635</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -5130,11 +5372,11 @@
         <v>637</v>
       </c>
     </row>
-    <row r="133" ht="14.5">
-      <c r="A133" t="s" s="0">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
         <v>638</v>
       </c>
-      <c r="B133" t="s" s="0">
+      <c r="B133" t="s">
         <v>639</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -5144,11 +5386,11 @@
         <v>641</v>
       </c>
     </row>
-    <row r="134" ht="14.5">
-      <c r="A134" t="s" s="0">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
         <v>642</v>
       </c>
-      <c r="B134" t="s" s="0">
+      <c r="B134" t="s">
         <v>643</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -5158,11 +5400,11 @@
         <v>645</v>
       </c>
     </row>
-    <row r="135" ht="14.5">
-      <c r="A135" t="s" s="0">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
         <v>646</v>
       </c>
-      <c r="B135" t="s" s="0">
+      <c r="B135" t="s">
         <v>647</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5172,11 +5414,11 @@
         <v>649</v>
       </c>
     </row>
-    <row r="136" ht="14.5">
-      <c r="A136" t="s" s="0">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
         <v>650</v>
       </c>
-      <c r="B136" t="s" s="0">
+      <c r="B136" t="s">
         <v>651</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5186,11 +5428,11 @@
         <v>653</v>
       </c>
     </row>
-    <row r="137" ht="14.5">
-      <c r="A137" t="s" s="0">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
         <v>654</v>
       </c>
-      <c r="B137" t="s" s="0">
+      <c r="B137" t="s">
         <v>655</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5200,11 +5442,11 @@
         <v>657</v>
       </c>
     </row>
-    <row r="138" ht="14.5">
-      <c r="A138" t="s" s="0">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
         <v>658</v>
       </c>
-      <c r="B138" t="s" s="0">
+      <c r="B138" t="s">
         <v>659</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5214,11 +5456,11 @@
         <v>661</v>
       </c>
     </row>
-    <row r="139" ht="14.5">
-      <c r="A139" t="s" s="0">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
         <v>662</v>
       </c>
-      <c r="B139" t="s" s="0">
+      <c r="B139" t="s">
         <v>663</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5228,11 +5470,11 @@
         <v>665</v>
       </c>
     </row>
-    <row r="140" ht="14.5">
-      <c r="A140" t="s" s="0">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
         <v>666</v>
       </c>
-      <c r="B140" t="s" s="0">
+      <c r="B140" t="s">
         <v>667</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5242,11 +5484,11 @@
         <v>669</v>
       </c>
     </row>
-    <row r="141" ht="14.5">
-      <c r="A141" t="s" s="0">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
         <v>670</v>
       </c>
-      <c r="B141" t="s" s="0">
+      <c r="B141" t="s">
         <v>671</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5256,11 +5498,11 @@
         <v>673</v>
       </c>
     </row>
-    <row r="142" ht="14.5">
-      <c r="A142" t="s" s="0">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
         <v>674</v>
       </c>
-      <c r="B142" t="s" s="0">
+      <c r="B142" t="s">
         <v>675</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5270,11 +5512,11 @@
         <v>677</v>
       </c>
     </row>
-    <row r="143" ht="14.5">
-      <c r="A143" t="s" s="0">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
         <v>678</v>
       </c>
-      <c r="B143" t="s" s="0">
+      <c r="B143" t="s">
         <v>679</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5284,11 +5526,11 @@
         <v>681</v>
       </c>
     </row>
-    <row r="144" ht="14.5">
-      <c r="A144" t="s" s="0">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
         <v>682</v>
       </c>
-      <c r="B144" t="s" s="0">
+      <c r="B144" t="s">
         <v>683</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5298,11 +5540,11 @@
         <v>685</v>
       </c>
     </row>
-    <row r="145" ht="14.5">
-      <c r="A145" t="s" s="0">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
         <v>686</v>
       </c>
-      <c r="B145" t="s" s="0">
+      <c r="B145" t="s">
         <v>687</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5312,11 +5554,11 @@
         <v>689</v>
       </c>
     </row>
-    <row r="146" ht="14.5">
-      <c r="A146" t="s" s="0">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
         <v>690</v>
       </c>
-      <c r="B146" t="s" s="0">
+      <c r="B146" t="s">
         <v>691</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5326,11 +5568,11 @@
         <v>693</v>
       </c>
     </row>
-    <row r="147" ht="14.5">
-      <c r="A147" t="s" s="0">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>694</v>
       </c>
-      <c r="B147" t="s" s="0">
+      <c r="B147" t="s">
         <v>695</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5340,11 +5582,11 @@
         <v>697</v>
       </c>
     </row>
-    <row r="148" ht="14.5">
-      <c r="A148" t="s" s="0">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
         <v>698</v>
       </c>
-      <c r="B148" t="s" s="0">
+      <c r="B148" t="s">
         <v>699</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5354,11 +5596,11 @@
         <v>701</v>
       </c>
     </row>
-    <row r="149" ht="14.5">
-      <c r="A149" t="s" s="0">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>702</v>
       </c>
-      <c r="B149" t="s" s="0">
+      <c r="B149" t="s">
         <v>703</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5368,11 +5610,11 @@
         <v>705</v>
       </c>
     </row>
-    <row r="150" ht="14.5">
-      <c r="A150" t="s" s="0">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
         <v>706</v>
       </c>
-      <c r="B150" t="s" s="0">
+      <c r="B150" t="s">
         <v>707</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5382,11 +5624,11 @@
         <v>709</v>
       </c>
     </row>
-    <row r="151" ht="14.5">
-      <c r="A151" t="s" s="0">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
         <v>710</v>
       </c>
-      <c r="B151" t="s" s="0">
+      <c r="B151" t="s">
         <v>711</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5396,11 +5638,11 @@
         <v>713</v>
       </c>
     </row>
-    <row r="152" ht="14.5">
-      <c r="A152" t="s" s="0">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
         <v>714</v>
       </c>
-      <c r="B152" t="s" s="0">
+      <c r="B152" t="s">
         <v>715</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5410,8 +5652,8 @@
         <v>717</v>
       </c>
     </row>
-    <row r="153" ht="14.5">
-      <c r="B153" t="s" s="0">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
         <v>718</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5421,8 +5663,8 @@
         <v>720</v>
       </c>
     </row>
-    <row r="154" ht="14.5">
-      <c r="B154" t="s" s="0">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B154" t="s">
         <v>721</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5432,8 +5674,8 @@
         <v>723</v>
       </c>
     </row>
-    <row r="155" ht="14.5">
-      <c r="B155" t="s" s="0">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
         <v>724</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5443,8 +5685,8 @@
         <v>726</v>
       </c>
     </row>
-    <row r="156" ht="14.5">
-      <c r="B156" t="s" s="0">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
         <v>727</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5454,8 +5696,8 @@
         <v>729</v>
       </c>
     </row>
-    <row r="157" ht="14.5">
-      <c r="B157" t="s" s="0">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B157" t="s">
         <v>730</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5465,8 +5707,8 @@
         <v>732</v>
       </c>
     </row>
-    <row r="158" ht="14.5">
-      <c r="B158" t="s" s="0">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
         <v>733</v>
       </c>
       <c r="C158" s="6" t="s">
@@ -5476,7 +5718,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="159" ht="14.5">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C159" s="6" t="s">
         <v>736</v>
       </c>
@@ -5484,7 +5726,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="160" ht="14.5">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C160" s="6" t="s">
         <v>738</v>
       </c>
@@ -5492,7 +5734,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="161" ht="14.5">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C161" s="6" t="s">
         <v>740</v>
       </c>
@@ -5500,7 +5742,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="162" ht="14.5">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C162" s="6" t="s">
         <v>742</v>
       </c>
@@ -5508,7 +5750,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="163" ht="14.5">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C163" s="6" t="s">
         <v>744</v>
       </c>
@@ -5516,7 +5758,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="164" ht="14.5">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C164" s="6" t="s">
         <v>746</v>
       </c>
@@ -5524,7 +5766,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="165" ht="14.5">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C165" s="6" t="s">
         <v>748</v>
       </c>
@@ -5532,7 +5774,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="166" ht="14.5">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C166" s="6" t="s">
         <v>750</v>
       </c>
@@ -5540,7 +5782,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="167" ht="14.5">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C167" s="6" t="s">
         <v>752</v>
       </c>
@@ -5548,7 +5790,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="168" ht="14.5">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C168" s="6" t="s">
         <v>754</v>
       </c>
@@ -5556,7 +5798,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="169" ht="14.5">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C169" s="6" t="s">
         <v>756</v>
       </c>
@@ -5564,7 +5806,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="170" ht="14.5">
+    <row r="170" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C170" s="6" t="s">
         <v>758</v>
       </c>
@@ -5572,162 +5814,163 @@
         <v>759</v>
       </c>
     </row>
-    <row r="171" ht="14.5">
+    <row r="171" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D171" s="5" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="172" ht="14.5">
+    <row r="172" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D172" s="5" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="173" ht="14.5">
+    <row r="173" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D173" s="5" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="174" ht="14.5">
+    <row r="174" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D174" s="5" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="175" ht="14.5">
+    <row r="175" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D175" s="5" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="176" ht="14.5">
+    <row r="176" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D176" s="5" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="177" ht="14.5">
+    <row r="177" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D177" s="5" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="178" ht="14.5">
+    <row r="178" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D178" s="5" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="179" ht="14.5">
+    <row r="179" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D179" s="5" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="180" ht="14.5">
+    <row r="180" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D180" s="5" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="181" ht="14.5">
+    <row r="181" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D181" s="5" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="182" ht="14.5">
+    <row r="182" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D182" s="5" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="183" ht="14.5">
+    <row r="183" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D183" s="5" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="184" ht="14.5">
+    <row r="184" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D184" s="5" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="185" ht="14.5">
+    <row r="185" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D185" s="5" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="186" ht="14.5">
+    <row r="186" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D186" s="5" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="187" ht="14.5">
+    <row r="187" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D187" s="5" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="188" ht="14.5">
+    <row r="188" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D188" s="5" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="189" ht="14.5">
+    <row r="189" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D189" s="5" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="190" ht="14.5">
+    <row r="190" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D190" s="5" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="191" ht="14.5">
+    <row r="191" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D191" s="5" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="192" ht="14.5">
+    <row r="192" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D192" s="5" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="193" ht="14.5">
+    <row r="193" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D193" s="5" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="194" ht="14.5">
+    <row r="194" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D194" s="5" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="195" ht="14.5">
+    <row r="195" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D195" s="5" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="196" ht="14.5">
+    <row r="196" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D196" s="5" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="197" ht="14.5">
+    <row r="197" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D197" s="5" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="198" ht="14.5">
+    <row r="198" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D198" s="5" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="199" ht="14.5">
+    <row r="199" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D199" s="5" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="200" ht="14.5">
+    <row r="200" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D200" s="5" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="201" ht="14.5">
+    <row r="201" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D201" s="5" t="s">
         <v>790</v>
       </c>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="839">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -2507,12 +2507,40 @@
   </si>
   <si>
     <t>MYDFNX</t>
+  </si>
+  <si>
+    <t>Charlie97</t>
+  </si>
+  <si>
+    <t>Milo67</t>
+  </si>
+  <si>
+    <t>Taffy65</t>
+  </si>
+  <si>
+    <t>Cutie52</t>
+  </si>
+  <si>
+    <t>Cinder52</t>
+  </si>
+  <si>
+    <t>pony44</t>
+  </si>
+  <si>
+    <t>fury41</t>
+  </si>
+  <si>
+    <t>Rabbit41</t>
+  </si>
+  <si>
+    <t>Sheep36</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2567,7 +2595,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2588,6 +2616,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2894,21 +2933,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
+    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
+    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
+    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
+    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
+    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
+    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
+    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
+    <col min="12" max="16384" style="1" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -3049,7 +3088,7 @@
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="19" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="10" t="s">
@@ -3069,7 +3108,7 @@
       <c r="B9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -3137,7 +3176,7 @@
       <c r="B13" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="1">
         <v>806</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -3154,7 +3193,7 @@
       <c r="B14" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="1">
         <v>807</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -3171,7 +3210,7 @@
       <c r="B15" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="1">
         <v>808</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -3182,13 +3221,13 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="18" t="s">
         <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="1">
         <v>809</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -3199,13 +3238,13 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="20" t="s">
         <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="1">
         <v>810</v>
       </c>
       <c r="D17" s="11" t="s">
@@ -3216,10 +3255,10 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="1">
         <v>791</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="1">
         <v>811</v>
       </c>
       <c r="D18" s="12" t="s">
@@ -3230,10 +3269,10 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="1">
         <v>792</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="22" t="s">
         <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -3241,10 +3280,10 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="1">
         <v>793</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="23">
         <v>812</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -3252,10 +3291,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="1">
         <v>794</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="1">
         <v>813</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -3263,10 +3302,10 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="1">
         <v>795</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="1">
         <v>814</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -3274,10 +3313,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="1">
         <v>796</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="1">
         <v>815</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -3285,10 +3324,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="1">
         <v>797</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="1">
         <v>816</v>
       </c>
       <c r="E24" s="14" t="s">
@@ -3296,10 +3335,10 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="1">
         <v>798</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="s" s="1">
         <v>817</v>
       </c>
       <c r="E25" s="15" t="s">
@@ -3307,10 +3346,10 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="1">
         <v>799</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" t="s" s="1">
         <v>818</v>
       </c>
       <c r="E26" s="16" t="s">
@@ -3318,10 +3357,10 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="1">
         <v>800</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" t="s" s="1">
         <v>819</v>
       </c>
       <c r="E27" s="17" t="s">
@@ -3329,22 +3368,22 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="25" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="26" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="27" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="28" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3354,52 +3393,52 @@
       </c>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E33" t="s">
+      <c r="E33" t="s" s="1">
         <v>820</v>
       </c>
     </row>
     <row r="34" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E34" t="s">
+      <c r="E34" t="s" s="1">
         <v>821</v>
       </c>
     </row>
     <row r="35" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E35" t="s">
+      <c r="E35" t="s" s="1">
         <v>822</v>
       </c>
     </row>
     <row r="36" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E36" t="s">
+      <c r="E36" t="s" s="1">
         <v>823</v>
       </c>
     </row>
     <row r="37" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E37" t="s">
+      <c r="E37" t="s" s="1">
         <v>824</v>
       </c>
     </row>
     <row r="38" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E38" t="s">
+      <c r="E38" t="s" s="1">
         <v>825</v>
       </c>
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E39" t="s">
+      <c r="E39" t="s" s="1">
         <v>826</v>
       </c>
     </row>
     <row r="40" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E40" t="s">
+      <c r="E40" t="s" s="1">
         <v>827</v>
       </c>
     </row>
     <row r="41" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E41" t="s">
+      <c r="E41" t="s" s="1">
         <v>828</v>
       </c>
     </row>
     <row r="42" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E42" t="s">
+      <c r="E42" t="s" s="1">
         <v>829</v>
       </c>
     </row>
@@ -3420,75 +3459,75 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" customWidth="1"/>
-    <col min="7" max="7" width="33.6328125" customWidth="1"/>
-    <col min="8" max="8" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.90625"/>
+    <col min="2" max="2" customWidth="true" width="29.453125"/>
+    <col min="3" max="3" customWidth="true" width="35.6328125"/>
+    <col min="4" max="4" customWidth="true" width="30.90625"/>
+    <col min="5" max="5" customWidth="true" width="32.7265625"/>
+    <col min="6" max="6" customWidth="true" width="32.1796875"/>
+    <col min="7" max="7" customWidth="true" width="33.6328125"/>
+    <col min="8" max="8" customWidth="true" width="31.26953125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>105</v>
       </c>
     </row>
@@ -3503,46 +3542,46 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="20.08984375"/>
+    <col min="2" max="2" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" width="17.36328125"/>
+    <col min="4" max="5" customWidth="true" width="17.26953125"/>
+    <col min="6" max="6" customWidth="true" width="17.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.36328125"/>
+    <col min="8" max="8" customWidth="true" width="17.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>109</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>115</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3553,10 +3592,10 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>119</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3567,10 +3606,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>123</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3581,10 +3620,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>127</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3595,10 +3634,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3609,10 +3648,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>135</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3623,10 +3662,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>138</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3637,10 +3676,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>143</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3651,10 +3690,10 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>147</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3665,10 +3704,10 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>151</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3679,10 +3718,10 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>154</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>155</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3693,10 +3732,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>159</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3707,10 +3746,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>163</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3721,10 +3760,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>166</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3735,10 +3774,10 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>171</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3749,10 +3788,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>175</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3763,10 +3802,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3777,10 +3816,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>182</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>183</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3791,10 +3830,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>186</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>187</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3805,10 +3844,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>190</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>191</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3819,10 +3858,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>195</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3833,10 +3872,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>198</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>199</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3847,10 +3886,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>202</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>203</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3861,10 +3900,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>207</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3875,10 +3914,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>211</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3889,10 +3928,10 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>215</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -3903,10 +3942,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>218</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>219</v>
       </c>
       <c r="C28" s="13" t="s">
@@ -3917,13 +3956,13 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>222</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>223</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="24" t="s">
         <v>224</v>
       </c>
       <c r="D29" s="5" t="s">
@@ -3931,10 +3970,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>227</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -3945,10 +3984,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>230</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>231</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -3959,10 +3998,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>234</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>235</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -3973,10 +4012,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>238</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>239</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3987,10 +4026,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>242</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>243</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -4001,10 +4040,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>247</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -4015,10 +4054,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>250</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>251</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -4029,10 +4068,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>254</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>255</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -4043,10 +4082,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>259</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -4057,10 +4096,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>262</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>263</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -4071,10 +4110,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>266</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>267</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -4085,10 +4124,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>270</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -4099,10 +4138,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>275</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -4113,10 +4152,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>279</v>
       </c>
       <c r="C43" s="6" t="s">
@@ -4127,10 +4166,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>282</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>283</v>
       </c>
       <c r="C44" s="6" t="s">
@@ -4141,10 +4180,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>286</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>287</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -4155,10 +4194,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>290</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>291</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -4169,10 +4208,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>294</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>295</v>
       </c>
       <c r="C47" s="6" t="s">
@@ -4183,10 +4222,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>298</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>299</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -4197,10 +4236,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>302</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>303</v>
       </c>
       <c r="C49" s="6" t="s">
@@ -4211,10 +4250,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>306</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>307</v>
       </c>
       <c r="C50" s="6" t="s">
@@ -4225,10 +4264,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>311</v>
       </c>
       <c r="C51" s="6" t="s">
@@ -4239,10 +4278,10 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>314</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>315</v>
       </c>
       <c r="C52" s="6" t="s">
@@ -4253,10 +4292,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>318</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>319</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -4267,10 +4306,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>322</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>323</v>
       </c>
       <c r="C54" s="6" t="s">
@@ -4281,10 +4320,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="A55" t="s" s="0">
         <v>326</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>327</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -4295,10 +4334,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="A56" t="s" s="0">
         <v>330</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>331</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -4309,10 +4348,10 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="A57" t="s" s="0">
         <v>334</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>335</v>
       </c>
       <c r="C57" s="6" t="s">
@@ -4323,10 +4362,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="A58" t="s" s="0">
         <v>338</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>339</v>
       </c>
       <c r="C58" s="6" t="s">
@@ -4337,10 +4376,10 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="A59" t="s" s="0">
         <v>342</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>343</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -4351,10 +4390,10 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="A60" t="s" s="0">
         <v>346</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>347</v>
       </c>
       <c r="C60" s="6" t="s">
@@ -4365,10 +4404,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="A61" t="s" s="0">
         <v>350</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>351</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -4379,10 +4418,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="A62" t="s" s="0">
         <v>354</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>355</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -4393,10 +4432,10 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="A63" t="s" s="0">
         <v>358</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>359</v>
       </c>
       <c r="C63" s="6" t="s">
@@ -4407,10 +4446,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+      <c r="A64" t="s" s="0">
         <v>362</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>363</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -4421,10 +4460,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="A65" t="s" s="0">
         <v>366</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>367</v>
       </c>
       <c r="C65" s="6" t="s">
@@ -4435,10 +4474,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="A66" t="s" s="0">
         <v>370</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>371</v>
       </c>
       <c r="C66" s="6" t="s">
@@ -4449,10 +4488,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+      <c r="A67" t="s" s="0">
         <v>374</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>375</v>
       </c>
       <c r="C67" s="6" t="s">
@@ -4463,10 +4502,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" t="s" s="0">
         <v>378</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>379</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -4477,10 +4516,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+      <c r="A69" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>383</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -4491,10 +4530,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+      <c r="A70" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>387</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -4505,10 +4544,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+      <c r="A71" t="s" s="0">
         <v>390</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>391</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -4519,10 +4558,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+      <c r="A72" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>395</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -4533,10 +4572,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+      <c r="A73" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>399</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -4547,10 +4586,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>403</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -4561,10 +4600,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="A75" t="s" s="0">
         <v>406</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>407</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -4575,10 +4614,10 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+      <c r="A76" t="s" s="0">
         <v>410</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>411</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -4589,10 +4628,10 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+      <c r="A77" t="s" s="0">
         <v>414</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>415</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -4603,10 +4642,10 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="A78" t="s" s="0">
         <v>418</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>419</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4617,10 +4656,10 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="A79" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>423</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -4631,10 +4670,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="A80" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>427</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -4645,10 +4684,10 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="A81" t="s" s="0">
         <v>430</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>431</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -4659,10 +4698,10 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="A82" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>435</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -4673,10 +4712,10 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="A83" t="s" s="0">
         <v>438</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>439</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -4687,10 +4726,10 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="A84" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>443</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -4701,10 +4740,10 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="A85" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>447</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -4715,10 +4754,10 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="A86" t="s" s="0">
         <v>450</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>451</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -4729,10 +4768,10 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="A87" t="s" s="0">
         <v>454</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>455</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -4743,10 +4782,10 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="A88" t="s" s="0">
         <v>458</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>459</v>
       </c>
       <c r="C88" s="6" t="s">
@@ -4757,10 +4796,10 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+      <c r="A89" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>463</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -4771,10 +4810,10 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="A90" t="s" s="0">
         <v>466</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>467</v>
       </c>
       <c r="C90" s="6" t="s">
@@ -4785,10 +4824,10 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="A91" t="s" s="0">
         <v>470</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>471</v>
       </c>
       <c r="C91" s="6" t="s">
@@ -4799,10 +4838,10 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" t="s" s="0">
         <v>474</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>475</v>
       </c>
       <c r="C92" s="6" t="s">
@@ -4813,10 +4852,10 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+      <c r="A93" t="s" s="0">
         <v>478</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>479</v>
       </c>
       <c r="C93" s="6" t="s">
@@ -4827,10 +4866,10 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="A94" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>483</v>
       </c>
       <c r="C94" s="6" t="s">
@@ -4841,10 +4880,10 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="A95" t="s" s="0">
         <v>486</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>487</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -4855,10 +4894,10 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>491</v>
       </c>
       <c r="C96" s="6" t="s">
@@ -4869,10 +4908,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+      <c r="A97" t="s" s="0">
         <v>494</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>495</v>
       </c>
       <c r="C97" s="6" t="s">
@@ -4883,10 +4922,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+      <c r="A98" t="s" s="0">
         <v>498</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>499</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -4897,10 +4936,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+      <c r="A99" t="s" s="0">
         <v>502</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>503</v>
       </c>
       <c r="C99" s="6" t="s">
@@ -4911,10 +4950,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+      <c r="A100" t="s" s="0">
         <v>506</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>507</v>
       </c>
       <c r="C100" s="6" t="s">
@@ -4925,10 +4964,10 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+      <c r="A101" t="s" s="0">
         <v>510</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>511</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -4939,10 +4978,10 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="A102" t="s" s="0">
         <v>514</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>515</v>
       </c>
       <c r="C102" s="6" t="s">
@@ -4953,10 +4992,10 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+      <c r="A103" t="s" s="0">
         <v>518</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>519</v>
       </c>
       <c r="C103" s="6" t="s">
@@ -4967,10 +5006,10 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+      <c r="A104" t="s" s="0">
         <v>522</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>523</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4981,10 +5020,10 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="A105" t="s" s="0">
         <v>526</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>527</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -4995,10 +5034,10 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+      <c r="A106" t="s" s="0">
         <v>530</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>531</v>
       </c>
       <c r="C106" s="6" t="s">
@@ -5009,10 +5048,10 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+      <c r="A107" t="s" s="0">
         <v>534</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>535</v>
       </c>
       <c r="C107" s="6" t="s">
@@ -5023,10 +5062,10 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+      <c r="A108" t="s" s="0">
         <v>538</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>539</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -5037,10 +5076,10 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+      <c r="A109" t="s" s="0">
         <v>542</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>543</v>
       </c>
       <c r="C109" s="6" t="s">
@@ -5051,10 +5090,10 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="A110" t="s" s="0">
         <v>546</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>547</v>
       </c>
       <c r="C110" s="6" t="s">
@@ -5065,10 +5104,10 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" t="s" s="0">
         <v>550</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>551</v>
       </c>
       <c r="C111" s="6" t="s">
@@ -5079,10 +5118,10 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>555</v>
       </c>
       <c r="C112" s="6" t="s">
@@ -5093,10 +5132,10 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="A113" t="s" s="0">
         <v>558</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>559</v>
       </c>
       <c r="C113" s="6" t="s">
@@ -5107,10 +5146,10 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" t="s" s="0">
         <v>562</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>563</v>
       </c>
       <c r="C114" s="6" t="s">
@@ -5121,10 +5160,10 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="A115" t="s" s="0">
         <v>566</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>567</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -5135,10 +5174,10 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+      <c r="A116" t="s" s="0">
         <v>570</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>571</v>
       </c>
       <c r="C116" s="6" t="s">
@@ -5149,10 +5188,10 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="A117" t="s" s="0">
         <v>574</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>575</v>
       </c>
       <c r="C117" s="6" t="s">
@@ -5163,10 +5202,10 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="A118" t="s" s="0">
         <v>578</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>579</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -5177,10 +5216,10 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+      <c r="A119" t="s" s="0">
         <v>582</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>583</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -5191,10 +5230,10 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+      <c r="A120" t="s" s="0">
         <v>586</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>587</v>
       </c>
       <c r="C120" s="6" t="s">
@@ -5205,10 +5244,10 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+      <c r="A121" t="s" s="0">
         <v>590</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>591</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -5219,10 +5258,10 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="A122" t="s" s="0">
         <v>594</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>595</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -5233,10 +5272,10 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="A123" t="s" s="0">
         <v>598</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>599</v>
       </c>
       <c r="C123" s="6" t="s">
@@ -5247,10 +5286,10 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="A124" t="s" s="0">
         <v>602</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>603</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -5261,10 +5300,10 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="A125" t="s" s="0">
         <v>606</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>607</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -5275,10 +5314,10 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="A126" t="s" s="0">
         <v>610</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>611</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -5289,10 +5328,10 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+      <c r="A127" t="s" s="0">
         <v>614</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>615</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -5303,10 +5342,10 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+      <c r="A128" t="s" s="0">
         <v>618</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>619</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -5317,10 +5356,10 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+      <c r="A129" t="s" s="0">
         <v>622</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>623</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -5331,10 +5370,10 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+      <c r="A130" t="s" s="0">
         <v>626</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>627</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -5345,10 +5384,10 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+      <c r="A131" t="s" s="0">
         <v>630</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>631</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -5359,10 +5398,10 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+      <c r="A132" t="s" s="0">
         <v>634</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>635</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -5373,10 +5412,10 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+      <c r="A133" t="s" s="0">
         <v>638</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>639</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -5387,10 +5426,10 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+      <c r="A134" t="s" s="0">
         <v>642</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>643</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -5401,10 +5440,10 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+      <c r="A135" t="s" s="0">
         <v>646</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>647</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -5415,10 +5454,10 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+      <c r="A136" t="s" s="0">
         <v>650</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>651</v>
       </c>
       <c r="C136" s="6" t="s">
@@ -5429,10 +5468,10 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+      <c r="A137" t="s" s="0">
         <v>654</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>655</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -5443,10 +5482,10 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+      <c r="A138" t="s" s="0">
         <v>658</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>659</v>
       </c>
       <c r="C138" s="6" t="s">
@@ -5457,10 +5496,10 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="A139" t="s" s="0">
         <v>662</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>663</v>
       </c>
       <c r="C139" s="6" t="s">
@@ -5471,10 +5510,10 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+      <c r="A140" t="s" s="0">
         <v>666</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>667</v>
       </c>
       <c r="C140" s="6" t="s">
@@ -5485,10 +5524,10 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+      <c r="A141" t="s" s="0">
         <v>670</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>671</v>
       </c>
       <c r="C141" s="6" t="s">
@@ -5499,10 +5538,10 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+      <c r="A142" t="s" s="0">
         <v>674</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>675</v>
       </c>
       <c r="C142" s="6" t="s">
@@ -5513,10 +5552,10 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+      <c r="A143" t="s" s="0">
         <v>678</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>679</v>
       </c>
       <c r="C143" s="6" t="s">
@@ -5527,10 +5566,10 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+      <c r="A144" t="s" s="0">
         <v>682</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>683</v>
       </c>
       <c r="C144" s="6" t="s">
@@ -5541,10 +5580,10 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+      <c r="A145" t="s" s="0">
         <v>686</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>687</v>
       </c>
       <c r="C145" s="6" t="s">
@@ -5555,10 +5594,10 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+      <c r="A146" t="s" s="0">
         <v>690</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>691</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -5569,10 +5608,10 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+      <c r="A147" t="s" s="0">
         <v>694</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>695</v>
       </c>
       <c r="C147" s="6" t="s">
@@ -5583,10 +5622,10 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+      <c r="A148" t="s" s="0">
         <v>698</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>699</v>
       </c>
       <c r="C148" s="6" t="s">
@@ -5597,10 +5636,10 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+      <c r="A149" t="s" s="0">
         <v>702</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>703</v>
       </c>
       <c r="C149" s="6" t="s">
@@ -5611,10 +5650,10 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+      <c r="A150" t="s" s="0">
         <v>706</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>707</v>
       </c>
       <c r="C150" s="6" t="s">
@@ -5625,10 +5664,10 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+      <c r="A151" t="s" s="0">
         <v>710</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>711</v>
       </c>
       <c r="C151" s="6" t="s">
@@ -5639,10 +5678,10 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+      <c r="A152" t="s" s="0">
         <v>714</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>715</v>
       </c>
       <c r="C152" s="6" t="s">
@@ -5653,7 +5692,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>718</v>
       </c>
       <c r="C153" s="6" t="s">
@@ -5664,7 +5703,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>721</v>
       </c>
       <c r="C154" s="6" t="s">
@@ -5675,7 +5714,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>724</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -5686,7 +5725,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>727</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -5697,7 +5736,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>730</v>
       </c>
       <c r="C157" s="6" t="s">
@@ -5708,7 +5747,7 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>733</v>
       </c>
       <c r="C158" s="6" t="s">

--- a/animalBiome_Automation/src/test/resources/data/samples.xlsx
+++ b/animalBiome_Automation/src/test/resources/data/samples.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\workspace\testing\animalBiome_Automation\src\test\resources\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3690"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="3690" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE_ID" sheetId="1" r:id="rId1"/>
     <sheet name="PET_NAME" sheetId="2" r:id="rId2"/>
     <sheet name="ADD_PET" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A7:G12"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>User_Dog_Gut</t>
   </si>
@@ -217,6 +221,12 @@
     <t>4F66HY</t>
   </si>
   <si>
+    <t>VDJUJA</t>
+  </si>
+  <si>
+    <t>CAC6PG</t>
+  </si>
+  <si>
     <t>E4FR3M</t>
   </si>
   <si>
@@ -226,6 +236,12 @@
     <t>HHUXJN</t>
   </si>
   <si>
+    <t>RPECGA</t>
+  </si>
+  <si>
+    <t>7MFKA4</t>
+  </si>
+  <si>
     <t>EMDDGE</t>
   </si>
   <si>
@@ -235,6 +251,12 @@
     <t>VTPC7K</t>
   </si>
   <si>
+    <t>CNAEUM</t>
+  </si>
+  <si>
+    <t>CXVHFJ</t>
+  </si>
+  <si>
     <t>VHKTDY</t>
   </si>
   <si>
@@ -244,6 +266,12 @@
     <t>RXY4RX</t>
   </si>
   <si>
+    <t>MVJDMF</t>
+  </si>
+  <si>
+    <t>HHXGKR</t>
+  </si>
+  <si>
     <t>NXMGXU</t>
   </si>
   <si>
@@ -253,45 +281,108 @@
     <t>U9ANVP</t>
   </si>
   <si>
+    <t>EFE7VM</t>
+  </si>
+  <si>
+    <t>KGE36H</t>
+  </si>
+  <si>
     <t>FHPENF</t>
   </si>
   <si>
     <t>VJFKAH</t>
   </si>
   <si>
+    <t>DY6HJV</t>
+  </si>
+  <si>
+    <t>9CYHKC</t>
+  </si>
+  <si>
     <t>KMVFMV</t>
   </si>
   <si>
     <t>RVYMTD</t>
   </si>
   <si>
+    <t>EXXEFV</t>
+  </si>
+  <si>
     <t>FMMDPH</t>
   </si>
   <si>
     <t>HTD7FV</t>
   </si>
   <si>
+    <t>G7KNYD</t>
+  </si>
+  <si>
+    <t>7KDJJH</t>
+  </si>
+  <si>
     <t>D7RM3G</t>
   </si>
   <si>
+    <t>EAYFTE</t>
+  </si>
+  <si>
+    <t>7CFRFV</t>
+  </si>
+  <si>
     <t>DPXN44</t>
   </si>
   <si>
+    <t>ECXR37</t>
+  </si>
+  <si>
+    <t>ARP4NF</t>
+  </si>
+  <si>
     <t>EVAYHN</t>
   </si>
   <si>
+    <t>4NUXJE</t>
+  </si>
+  <si>
+    <t>9HCNXK</t>
+  </si>
+  <si>
     <t>NMVMC7</t>
   </si>
   <si>
+    <t>PCKRDP</t>
+  </si>
+  <si>
+    <t>YRDARC</t>
+  </si>
+  <si>
     <t>YTJTEP</t>
   </si>
   <si>
+    <t>MMAYCA</t>
+  </si>
+  <si>
+    <t>RJURVR</t>
+  </si>
+  <si>
     <t>ADKXJK</t>
   </si>
   <si>
+    <t>HCXJMR</t>
+  </si>
+  <si>
+    <t>9NDXHD</t>
+  </si>
+  <si>
     <t>7KMMDF</t>
   </si>
   <si>
+    <t>JFGPXE</t>
+  </si>
+  <si>
+    <t>K9CFFU</t>
+  </si>
+  <si>
     <t>7PEXET</t>
   </si>
   <si>
@@ -310,6 +401,36 @@
     <t>NR7KMT</t>
   </si>
   <si>
+    <t>T3DVGH</t>
+  </si>
+  <si>
+    <t>DRGYYX</t>
+  </si>
+  <si>
+    <t>FHUUPV</t>
+  </si>
+  <si>
+    <t>J7A3FD</t>
+  </si>
+  <si>
+    <t>EGJN4C</t>
+  </si>
+  <si>
+    <t>EUHY7H</t>
+  </si>
+  <si>
+    <t>FRXMAG</t>
+  </si>
+  <si>
+    <t>TFV9UN</t>
+  </si>
+  <si>
+    <t>DARTH9</t>
+  </si>
+  <si>
+    <t>MYDFNX</t>
+  </si>
+  <si>
     <t>User_Dog</t>
   </si>
   <si>
@@ -2390,158 +2511,13 @@
   </si>
   <si>
     <t>Nexra</t>
-  </si>
-  <si>
-    <t>DY6HJV</t>
-  </si>
-  <si>
-    <t>EXXEFV</t>
-  </si>
-  <si>
-    <t>G7KNYD</t>
-  </si>
-  <si>
-    <t>EAYFTE</t>
-  </si>
-  <si>
-    <t>ECXR37</t>
-  </si>
-  <si>
-    <t>4NUXJE</t>
-  </si>
-  <si>
-    <t>PCKRDP</t>
-  </si>
-  <si>
-    <t>MMAYCA</t>
-  </si>
-  <si>
-    <t>HCXJMR</t>
-  </si>
-  <si>
-    <t>JFGPXE</t>
-  </si>
-  <si>
-    <t>VDJUJA</t>
-  </si>
-  <si>
-    <t>RPECGA</t>
-  </si>
-  <si>
-    <t>CNAEUM</t>
-  </si>
-  <si>
-    <t>MVJDMF</t>
-  </si>
-  <si>
-    <t>EFE7VM</t>
-  </si>
-  <si>
-    <t>CAC6PG</t>
-  </si>
-  <si>
-    <t>7MFKA4</t>
-  </si>
-  <si>
-    <t>CXVHFJ</t>
-  </si>
-  <si>
-    <t>HHXGKR</t>
-  </si>
-  <si>
-    <t>KGE36H</t>
-  </si>
-  <si>
-    <t>9CYHKC</t>
-  </si>
-  <si>
-    <t>7KDJJH</t>
-  </si>
-  <si>
-    <t>7CFRFV</t>
-  </si>
-  <si>
-    <t>ARP4NF</t>
-  </si>
-  <si>
-    <t>9HCNXK</t>
-  </si>
-  <si>
-    <t>YRDARC</t>
-  </si>
-  <si>
-    <t>RJURVR</t>
-  </si>
-  <si>
-    <t>9NDXHD</t>
-  </si>
-  <si>
-    <t>K9CFFU</t>
-  </si>
-  <si>
-    <t>T3DVGH</t>
-  </si>
-  <si>
-    <t>DRGYYX</t>
-  </si>
-  <si>
-    <t>FHUUPV</t>
-  </si>
-  <si>
-    <t>J7A3FD</t>
-  </si>
-  <si>
-    <t>EGJN4C</t>
-  </si>
-  <si>
-    <t>EUHY7H</t>
-  </si>
-  <si>
-    <t>FRXMAG</t>
-  </si>
-  <si>
-    <t>TFV9UN</t>
-  </si>
-  <si>
-    <t>DARTH9</t>
-  </si>
-  <si>
-    <t>MYDFNX</t>
-  </si>
-  <si>
-    <t>Charlie97</t>
-  </si>
-  <si>
-    <t>Milo67</t>
-  </si>
-  <si>
-    <t>Taffy65</t>
-  </si>
-  <si>
-    <t>Cutie52</t>
-  </si>
-  <si>
-    <t>Cinder52</t>
-  </si>
-  <si>
-    <t>pony44</t>
-  </si>
-  <si>
-    <t>fury41</t>
-  </si>
-  <si>
-    <t>Rabbit41</t>
-  </si>
-  <si>
-    <t>Sheep36</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2553,13 +2529,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2582,20 +2551,14 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2603,46 +2566,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1"/>
     <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -2651,10 +2584,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2786,6 +2719,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2809,10 +2743,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2821,13 +2756,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2903,6 +2838,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2922,35 +2858,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="17.81640625"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.36328125"/>
-    <col min="4" max="4" customWidth="true" style="1" width="17.453125"/>
-    <col min="5" max="5" customWidth="true" style="1" width="16.6328125"/>
-    <col min="6" max="6" customWidth="true" style="1" width="18.0"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125"/>
-    <col min="8" max="8" customWidth="true" style="1" width="18.1796875"/>
-    <col min="9" max="9" customWidth="true" style="1" width="18.36328125"/>
-    <col min="10" max="10" customWidth="true" style="1" width="17.453125"/>
-    <col min="11" max="11" customWidth="true" style="1" width="17.36328125"/>
-    <col min="12" max="16384" style="1" width="8.7265625"/>
+    <col min="1" max="1" width="17.81641" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.63281" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.26953" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.17969" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.45313" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.726563" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2982,7 +2916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2999,7 +2933,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -3016,7 +2950,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -3033,7 +2967,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -3050,7 +2984,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -3067,11 +3001,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3084,14 +3018,14 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -3101,14 +3035,14 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -3118,7 +3052,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
@@ -3135,7 +3069,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="2" t="s">
         <v>55</v>
       </c>
@@ -3152,7 +3086,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="2" t="s">
         <v>60</v>
       </c>
@@ -3169,2847 +3103,2840 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C13" t="s" s="1">
-        <v>806</v>
+        <v>66</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="C14" t="s" s="1">
-        <v>807</v>
+        <v>71</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="C15" t="s" s="1">
-        <v>808</v>
+        <v>76</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>74</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="C16" t="s" s="1">
-        <v>809</v>
+        <v>81</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="20" t="s">
-        <v>77</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="C17" t="s" s="1">
-        <v>810</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>78</v>
+        <v>86</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s" s="1">
-        <v>791</v>
-      </c>
-      <c r="C18" t="s" s="1">
-        <v>811</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>80</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s" s="1">
-        <v>792</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>82</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s" s="1">
-        <v>793</v>
-      </c>
-      <c r="D20" t="s" s="23">
-        <v>812</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s" s="1">
-        <v>794</v>
-      </c>
-      <c r="D21" t="s" s="1">
-        <v>813</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s" s="1">
-        <v>795</v>
-      </c>
-      <c r="D22" t="s" s="1">
-        <v>814</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s" s="1">
-        <v>796</v>
-      </c>
-      <c r="D23" t="s" s="1">
-        <v>815</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s" s="1">
-        <v>797</v>
-      </c>
-      <c r="D24" t="s" s="1">
-        <v>816</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s" s="1">
-        <v>798</v>
-      </c>
-      <c r="D25" t="s" s="1">
-        <v>817</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s" s="1">
-        <v>799</v>
-      </c>
-      <c r="D26" t="s" s="1">
-        <v>818</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s" s="1">
-        <v>800</v>
-      </c>
-      <c r="D27" t="s" s="1">
-        <v>819</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E28" s="25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E29" s="26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E30" s="27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E31" s="28" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="E32" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E33" t="s" s="1">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E34" t="s" s="1">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E35" t="s" s="1">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E36" t="s" s="1">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E37" t="s" s="1">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E38" t="s" s="1">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E39" t="s" s="1">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E40" t="s" s="1">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E41" t="s" s="1">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E42" t="s" s="1">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78">
       <c r="F78" s="3"/>
     </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="F81" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="26.90625"/>
-    <col min="2" max="2" customWidth="true" width="29.453125"/>
-    <col min="3" max="3" customWidth="true" width="35.6328125"/>
-    <col min="4" max="4" customWidth="true" width="30.90625"/>
-    <col min="5" max="5" customWidth="true" width="32.7265625"/>
-    <col min="6" max="6" customWidth="true" width="32.1796875"/>
-    <col min="7" max="7" customWidth="true" width="33.6328125"/>
-    <col min="8" max="8" customWidth="true" width="31.26953125"/>
+    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.45313" customWidth="1"/>
+    <col min="3" max="3" width="35.63281" customWidth="1"/>
+    <col min="4" max="4" width="30.90625" customWidth="1"/>
+    <col min="5" max="5" width="32.72656" customWidth="1"/>
+    <col min="6" max="6" width="32.17969" customWidth="1"/>
+    <col min="7" max="7" width="33.63281" customWidth="1"/>
+    <col min="8" max="8" width="31.26953" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>101</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>102</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>105</v>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="20.08984375"/>
-    <col min="2" max="2" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" width="17.36328125"/>
-    <col min="4" max="5" customWidth="true" width="17.26953125"/>
-    <col min="6" max="6" customWidth="true" width="17.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.36328125"/>
-    <col min="8" max="8" customWidth="true" width="17.1796875"/>
+    <col min="1" max="1" width="20.08984" customWidth="1"/>
+    <col min="2" max="2" width="17.54297" customWidth="1"/>
+    <col min="3" max="3" width="17.36328" customWidth="1"/>
+    <col min="4" max="5" width="17.26953" customWidth="1"/>
+    <col min="6" max="6" width="17.17969" customWidth="1"/>
+    <col min="7" max="7" width="15.36328" customWidth="1"/>
+    <col min="8" max="8" width="17.17969" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" ht="14.5">
       <c r="A1" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>107</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>111</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>114</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>115</v>
+        <v>145</v>
+      </c>
+      <c r="B1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" ht="14.5">
+      <c r="A2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" t="s">
+        <v>154</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>119</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5">
+      <c r="A3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" t="s">
+        <v>158</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>123</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" ht="14.5">
+      <c r="A4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>127</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5">
+      <c r="A5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" t="s">
+        <v>166</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
-        <v>130</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>131</v>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5">
+      <c r="A6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" t="s">
+        <v>170</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
-        <v>134</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>135</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5">
+      <c r="A7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" t="s">
+        <v>174</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="0">
-        <v>138</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>139</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5">
+      <c r="A8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s">
+        <v>178</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>143</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5">
+      <c r="A9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" t="s">
+        <v>182</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>147</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5">
+      <c r="A10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" t="s">
+        <v>186</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s" s="0">
-        <v>150</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>151</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5">
+      <c r="A11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" t="s">
+        <v>190</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>155</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5">
+      <c r="A12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" t="s">
+        <v>194</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s" s="0">
-        <v>158</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>159</v>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5">
+      <c r="A13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" t="s">
+        <v>198</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s" s="0">
-        <v>162</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>163</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5">
+      <c r="A14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" t="s">
+        <v>202</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>167</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5">
+      <c r="A15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" t="s">
+        <v>206</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s" s="0">
-        <v>170</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>171</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" ht="14.5">
+      <c r="A16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" t="s">
+        <v>210</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s" s="0">
-        <v>174</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>175</v>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" ht="14.5">
+      <c r="A17" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" t="s">
+        <v>214</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s" s="0">
-        <v>178</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>179</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" ht="14.5">
+      <c r="A18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" t="s">
+        <v>218</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s" s="0">
-        <v>182</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>183</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" ht="1